--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA667A-55D7-214D-8908-D54ADC20854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C23D507-5956-8542-B88A-23B4BE44A379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="-39780" windowWidth="46820" windowHeight="33400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19800" yWindow="-35140" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
   <si>
     <t>Entry Date</t>
   </si>
@@ -2187,7 +2187,7 @@
         <v>21</v>
       </c>
       <c r="U19" s="4">
-        <v>709</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
@@ -2832,7 +2832,7 @@
         <v>21</v>
       </c>
       <c r="U29" s="4">
-        <v>-562</v>
+        <v>-394</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
@@ -2900,7 +2900,7 @@
         <v>21</v>
       </c>
       <c r="U30" s="4">
-        <v>-1361</v>
+        <v>-1930</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
@@ -2919,56 +2919,54 @@
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="33" t="s">
+      <c r="H31" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="32" t="s">
+      <c r="J31" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="4">
         <v>400</v>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="4">
         <v>331.50700000000001</v>
       </c>
-      <c r="M31" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="34">
+      <c r="M31" s="4">
+        <v>334.31</v>
+      </c>
+      <c r="N31" s="4">
+        <v>334.31</v>
+      </c>
+      <c r="O31" s="16">
         <v>132602</v>
       </c>
-      <c r="P31" s="32">
-        <v>1.18</v>
-      </c>
-      <c r="Q31" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="S31" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T31" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="U31" s="4">
-        <v>-624</v>
+      <c r="P31" s="4">
+        <v>6.69</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>1</v>
+      </c>
+      <c r="R31" s="5">
+        <f>IF(Q31=1, ABS(M31-L31)/L31, 0)</f>
+        <v>8.455326735182055E-3</v>
+      </c>
+      <c r="S31" s="4">
+        <v>1121</v>
+      </c>
+      <c r="T31" s="13">
+        <v>1121</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
@@ -3036,7 +3034,7 @@
         <v>21</v>
       </c>
       <c r="U32" s="4">
-        <v>549</v>
+        <v>749</v>
       </c>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.2">
@@ -3072,12 +3070,12 @@
       <c r="F36" s="11"/>
       <c r="H36" s="11"/>
       <c r="T36" s="16">
-        <f>SUM(T2:T28)</f>
-        <v>61441.47</v>
+        <f>SUM(T2:T31)</f>
+        <v>62562.47</v>
       </c>
       <c r="U36" s="16">
         <f>SUM(U2:U32)</f>
-        <v>-1289</v>
+        <v>-1078</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.2">
@@ -3106,7 +3104,7 @@
       <c r="F39" s="11"/>
       <c r="T39" s="16">
         <f>T36+U36</f>
-        <v>60152.47</v>
+        <v>61484.47</v>
       </c>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.2">
@@ -3132,7 +3130,7 @@
     <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="T45" s="23">
         <f>T39/T42</f>
-        <v>0.18063804804804806</v>
+        <v>0.18463804804804806</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C23D507-5956-8542-B88A-23B4BE44A379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439B6E20-71AB-724B-99F7-C04DA7C7FDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19800" yWindow="-35140" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20180" yWindow="-35140" windowWidth="51480" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -1684,11 +1684,11 @@
       </c>
       <c r="C12" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>20</v>
@@ -2132,11 +2132,11 @@
       </c>
       <c r="C19" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>37</v>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="C20" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>80</v>
@@ -2583,11 +2583,11 @@
       </c>
       <c r="C26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" ref="D26:D32" ca="1" si="4">C26-B26</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>102</v>
@@ -2711,11 +2711,11 @@
       </c>
       <c r="C28" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>108</v>
@@ -2773,11 +2773,11 @@
       </c>
       <c r="B29" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C29" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" ca="1" si="4"/>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="B30" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C30" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" ca="1" si="4"/>
@@ -2909,11 +2909,11 @@
       </c>
       <c r="B31" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C31" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" ca="1" si="4"/>
@@ -2975,11 +2975,11 @@
       </c>
       <c r="B32" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C32" s="1">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" ca="1" si="4"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E36" s="7">
         <f ca="1">AVERAGE(D2:D24)</f>
-        <v>11.217391304347826</v>
+        <v>11.347826086956522</v>
       </c>
       <c r="F36" s="11"/>
       <c r="H36" s="11"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E37" s="7">
         <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
-        <v>6.5</v>
+        <v>6.5909090909090908</v>
       </c>
       <c r="F37" s="11"/>
       <c r="T37" s="4" t="s">
@@ -3143,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -3186,8 +3186,8 @@
         <v>85</v>
       </c>
       <c r="H2" s="19">
-        <f>AVERAGE(C3:C60)</f>
-        <v>1161.7429310344821</v>
+        <f>AVERAGE(C3:C61)</f>
+        <v>1163.848983050847</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -3209,8 +3209,8 @@
         <v>87</v>
       </c>
       <c r="H3" s="19">
-        <f>_xlfn.STDEV.S(C3:C60)</f>
-        <v>4573.412333447518</v>
+        <f>_xlfn.STDEV.S(C3:C61)</f>
+        <v>4533.8438044752129</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -3221,11 +3221,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="20">
-        <f t="shared" ref="C4:C60" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C61" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="26">
-        <f t="shared" ref="D4:D60" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D61" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
       <c r="G4" s="36" t="s">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H4" s="22">
         <f>(H2/H3)*SQRT(252)</f>
-        <v>4.0324589065698859</v>
+        <v>4.0750256589102625</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -3255,8 +3255,8 @@
         <v>107</v>
       </c>
       <c r="H5" s="27">
-        <f>_xlfn.STDEV.S(D2:D60)*SQRT(252)</f>
-        <v>0.19926468183180066</v>
+        <f>_xlfn.STDEV.S(D2:D61)*SQRT(252)</f>
+        <v>0.19756878191419452</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -3278,8 +3278,8 @@
         <v>111</v>
       </c>
       <c r="H6" s="27" cm="1">
-        <f t="array" ref="H6">PRODUCT(1+D2:D60)-1</f>
-        <v>0.20206913285584815</v>
+        <f t="array" ref="H6">PRODUCT(1+D2:D61)-1</f>
+        <v>0.20592571791335645</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -3301,8 +3301,8 @@
         <v>110</v>
       </c>
       <c r="H7" s="27" cm="1">
-        <f t="array" ref="H7">PRODUCT(1+D2:D60)^(252/COUNT(D2:D60))-1</f>
-        <v>1.1947929833927429</v>
+        <f t="array" ref="H7">PRODUCT(1+D2:D61)^(252/COUNT(D2:D61))-1</f>
+        <v>1.195565207449981</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4188,6 +4188,23 @@
       <c r="D60" s="26">
         <f t="shared" si="1"/>
         <v>3.9246652613676792E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="18">
+        <v>46267</v>
+      </c>
+      <c r="B61" s="20">
+        <f>B60-274+71-569+1738+320</f>
+        <v>402122.72</v>
+      </c>
+      <c r="C61" s="20">
+        <f t="shared" si="0"/>
+        <v>1286</v>
+      </c>
+      <c r="D61" s="26">
+        <f t="shared" si="1"/>
+        <v>3.2082889012763106E-3</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439B6E20-71AB-724B-99F7-C04DA7C7FDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EA4102-5AB0-254F-AC47-0CB273C475FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20180" yWindow="-35140" windowWidth="51480" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20180" yWindow="-35140" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
     <sheet name="Daily PnL" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,7 +62,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="120">
+  <si>
+    <t>Trade ID</t>
+  </si>
   <si>
     <t>Entry Date</t>
   </si>
@@ -76,6 +79,21 @@
     <t>Symbol</t>
   </si>
   <si>
+    <t>Instrument Name</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
+  </si>
+  <si>
+    <t>RV Theme</t>
+  </si>
+  <si>
+    <t>Asset Class</t>
+  </si>
+  <si>
+    <t>IB_TICKER</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -85,6 +103,9 @@
     <t>Exit Price</t>
   </si>
   <si>
+    <t>Last Price</t>
+  </si>
+  <si>
     <t>Notional</t>
   </si>
   <si>
@@ -100,217 +121,277 @@
     <t>Leg PnL</t>
   </si>
   <si>
-    <t>Trade ID</t>
-  </si>
-  <si>
-    <t>Trade Type</t>
-  </si>
-  <si>
     <t>Trade PnL</t>
   </si>
   <si>
+    <t>Unrealized</t>
+  </si>
+  <si>
     <t>MU</t>
   </si>
   <si>
+    <t>Micron Technologies</t>
+  </si>
+  <si>
     <t>Directional</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Equities</t>
+  </si>
+  <si>
     <t>JPM</t>
   </si>
   <si>
+    <t>JP Morgan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI </t>
+  </si>
+  <si>
+    <t>Silver Futures</t>
+  </si>
+  <si>
+    <t>RV</t>
+  </si>
+  <si>
+    <t>Long Silver / Short Gold</t>
+  </si>
+  <si>
+    <t>Futures</t>
+  </si>
+  <si>
+    <t>SIQ6</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Euro Futures</t>
+  </si>
+  <si>
+    <t>QI</t>
+  </si>
+  <si>
+    <t>Silver Futures Mini</t>
+  </si>
+  <si>
+    <t>QIQ6</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Cocoa Futures</t>
+  </si>
+  <si>
+    <t>CCU6</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>Swiss Franc Futures</t>
+  </si>
+  <si>
+    <t>SFU6</t>
+  </si>
+  <si>
     <t>IWD</t>
   </si>
   <si>
+    <t>iShares Russell 1000 Value ETF</t>
+  </si>
+  <si>
+    <t>Long Value / Short Growth Stocks</t>
+  </si>
+  <si>
+    <t>ETFs</t>
+  </si>
+  <si>
     <t>IWF</t>
   </si>
   <si>
+    <t>iShares Russell 1000 Growth ETF</t>
+  </si>
+  <si>
+    <t>QO</t>
+  </si>
+  <si>
+    <t>Gold Futures</t>
+  </si>
+  <si>
+    <t>QOQ6</t>
+  </si>
+  <si>
     <t>KRE</t>
   </si>
   <si>
+    <t>State Street S&amp;P Regional Banking ETF</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>VXM</t>
+  </si>
+  <si>
+    <t>Vix Futures Mini</t>
+  </si>
+  <si>
+    <t>VXMU6</t>
+  </si>
+  <si>
+    <t>KC</t>
+  </si>
+  <si>
+    <t>Coffee Futures</t>
+  </si>
+  <si>
+    <t>KCU6</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Eli Lilly &amp; Co</t>
+  </si>
+  <si>
+    <t>SPCX</t>
+  </si>
+  <si>
+    <t>SpaceX</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>EFA</t>
+  </si>
+  <si>
+    <t>iShares MSCI Mid-Cap Developed Mkt Equities ETF</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>SPCX</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>RV</t>
-  </si>
-  <si>
-    <t>IB_TICKER</t>
-  </si>
-  <si>
-    <t>SIQ6</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>QIQ6</t>
-  </si>
-  <si>
-    <t>CCU6</t>
-  </si>
-  <si>
-    <t>SFU6</t>
-  </si>
-  <si>
-    <t>QOQ6</t>
-  </si>
-  <si>
-    <t>VXMU6</t>
-  </si>
-  <si>
-    <t>KCU6</t>
-  </si>
-  <si>
-    <t>Last Price</t>
-  </si>
-  <si>
-    <t>EFA</t>
-  </si>
-  <si>
-    <t>Instrument Name</t>
-  </si>
-  <si>
-    <t>Micron Technologies</t>
-  </si>
-  <si>
-    <t>JP Morgan</t>
-  </si>
-  <si>
-    <t>Silver Futures</t>
-  </si>
-  <si>
-    <t>Euro Futures</t>
-  </si>
-  <si>
-    <t>Silver Futures Mini</t>
-  </si>
-  <si>
-    <t>Cocoa Futures</t>
-  </si>
-  <si>
-    <t>Swiss Franc Futures</t>
-  </si>
-  <si>
-    <t>iShares Russell 1000 Value ETF</t>
-  </si>
-  <si>
-    <t>iShares Russell 1000 Growth ETF</t>
-  </si>
-  <si>
-    <t>Gold Futures</t>
-  </si>
-  <si>
-    <t>State Street S&amp;P Regional Banking ETF</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Vix Futures Mini</t>
-  </si>
-  <si>
-    <t>SpaceX</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>iShares MSCI Mid-Cap Developed Mkt Equities ETF</t>
+    <t>XAI</t>
+  </si>
+  <si>
+    <t>S&amp;P Industrials Sector Futures</t>
+  </si>
+  <si>
+    <t>XAIU6</t>
   </si>
   <si>
     <t>TLT</t>
   </si>
   <si>
-    <t>RV Theme</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>iShares 20+ Year Treasury Bond ETF</t>
   </si>
   <si>
+    <t>Long Bonds(Long End) / Short Equities</t>
+  </si>
+  <si>
     <t>MES</t>
   </si>
   <si>
     <t>Micro S&amp;P Futures</t>
   </si>
   <si>
+    <t>SB</t>
+  </si>
+  <si>
     <t>Sugar Futures</t>
   </si>
   <si>
-    <t>Coffee Futures</t>
-  </si>
-  <si>
     <t>SBV6</t>
   </si>
   <si>
-    <t>S&amp;P Industrials Sector Futures</t>
-  </si>
-  <si>
-    <t>XAIU6</t>
-  </si>
-  <si>
-    <t>Long Silver / Short Gold</t>
-  </si>
-  <si>
-    <t>Long Value / Short Growth Stocks</t>
-  </si>
-  <si>
-    <t>Long Bonds(Long End) / Short Equities</t>
-  </si>
-  <si>
-    <t>Asset Class</t>
-  </si>
-  <si>
-    <t>Equities</t>
-  </si>
-  <si>
-    <t>Futures</t>
-  </si>
-  <si>
-    <t>ETFs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI </t>
-  </si>
-  <si>
-    <t>QI</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>QO</t>
-  </si>
-  <si>
-    <t>VXM</t>
-  </si>
-  <si>
-    <t>KC</t>
-  </si>
-  <si>
-    <t>XAI</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t>Eli Lilly &amp; Co</t>
+    <t>6EU6</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>Canadian Dollar Futures</t>
+  </si>
+  <si>
+    <t>6CU6</t>
+  </si>
+  <si>
+    <t>MGC</t>
+  </si>
+  <si>
+    <t>Gold Micro</t>
+  </si>
+  <si>
+    <t>MGCZ6</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>SLB Limited</t>
+  </si>
+  <si>
+    <t>ITW</t>
+  </si>
+  <si>
+    <t>Illnois Tool Works</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>Parker-Hannifin Corporation</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
+    <t>Sherwin-Williams Company</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>Verizon</t>
+  </si>
+  <si>
+    <t>Avg Holding Period for Daily/Weekly/Monthly Signals:</t>
+  </si>
+  <si>
+    <t>Avg Holding Period for Daily + Weekly Signals:</t>
+  </si>
+  <si>
+    <t>Total Realized</t>
+  </si>
+  <si>
+    <t>Total Unrealized</t>
+  </si>
+  <si>
+    <t>Net PnL</t>
+  </si>
+  <si>
+    <t>Starting Account Balance</t>
+  </si>
+  <si>
+    <t>RoC</t>
   </si>
   <si>
     <t>Date</t>
@@ -319,109 +400,28 @@
     <t>Account Balance</t>
   </si>
   <si>
+    <t>PnL</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
     <t>Mean daily PnL</t>
   </si>
   <si>
-    <t>PnL</t>
-  </si>
-  <si>
     <t>Daily PnL std</t>
   </si>
   <si>
     <t>Ann. Sharpe</t>
   </si>
   <si>
-    <t>6EU6</t>
-  </si>
-  <si>
-    <t>Unrealized</t>
-  </si>
-  <si>
-    <t>Total Unrealized</t>
-  </si>
-  <si>
-    <t>Total Realized</t>
-  </si>
-  <si>
-    <t>Starting Account Balance</t>
-  </si>
-  <si>
-    <t>RoC</t>
-  </si>
-  <si>
-    <t>Net PnL</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>Canadian Dollar Futures</t>
-  </si>
-  <si>
-    <t>6CU6</t>
-  </si>
-  <si>
-    <t>Avg Holding Period for Daily + Weekly Signals:</t>
-  </si>
-  <si>
-    <t>Avg Holding Period for Daily/Weekly/Monthly Signals:</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>MGC</t>
-  </si>
-  <si>
-    <t>Gold Micro</t>
-  </si>
-  <si>
-    <t>MGCZ6</t>
-  </si>
-  <si>
-    <t>Newmont Corporation</t>
-  </si>
-  <si>
-    <t>Return</t>
-  </si>
-  <si>
     <t>Ann. Volatility</t>
   </si>
   <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>SLB Limited</t>
+    <t>Cumulative Return</t>
   </si>
   <si>
     <t>Ann. Return</t>
-  </si>
-  <si>
-    <t>Cumulative Return</t>
-  </si>
-  <si>
-    <t>ITW</t>
-  </si>
-  <si>
-    <t>Illnois Tool Works</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>Parker-Hannifin Corporation</t>
-  </si>
-  <si>
-    <t>SHW</t>
-  </si>
-  <si>
-    <t>Sherwin-Williams Company</t>
-  </si>
-  <si>
-    <t>VZ</t>
-  </si>
-  <si>
-    <t>Verizon</t>
   </si>
 </sst>
 </file>
@@ -472,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,12 +500,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,18 +591,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -623,6 +605,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -966,67 +960,67 @@
   <sheetData>
     <row r="1" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="O1" s="10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
@@ -1044,22 +1038,22 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4">
         <v>-100</v>
@@ -1109,22 +1103,22 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K3" s="3">
         <v>-450</v>
@@ -1173,22 +1167,22 @@
         <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K4" s="4">
         <v>2</v>
@@ -1238,22 +1232,22 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K5" s="4">
         <v>10</v>
@@ -1302,22 +1296,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K6" s="4">
         <v>3</v>
@@ -1367,22 +1361,22 @@
         <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K7" s="4">
         <v>-3</v>
@@ -1432,22 +1426,22 @@
         <v>11</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K8" s="4">
         <v>20</v>
@@ -1497,22 +1491,22 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K9" s="3">
         <v>400</v>
@@ -1561,22 +1555,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>67</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K10" s="3">
         <v>800</v>
@@ -1625,22 +1619,22 @@
         <v>0</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K11" s="4">
         <v>-1</v>
@@ -1691,22 +1685,22 @@
         <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="K12" s="3">
         <v>-3000</v>
@@ -1755,22 +1749,22 @@
         <v>2</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="K13" s="3">
         <v>100</v>
@@ -1795,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" ref="R13:R18" si="3">IF(Q13=1, ABS(M13-L13)/L13, 0)</f>
+        <f t="shared" ref="R13:R19" si="3">IF(Q13=1, ABS(M13-L13)/L13, 0)</f>
         <v>8.5709094212773618E-2</v>
       </c>
       <c r="S13" s="3">
@@ -1820,22 +1814,22 @@
         <v>52</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K14" s="4">
         <v>60</v>
@@ -1884,22 +1878,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="K15" s="4">
         <v>-1</v>
@@ -1949,22 +1943,22 @@
         <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H16" s="12" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="K16" s="3">
         <v>-75</v>
@@ -2014,22 +2008,22 @@
         <v>2</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="K17" s="4">
         <v>2000</v>
@@ -2076,22 +2070,22 @@
         <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="J18" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="K18" s="4">
         <v>-300</v>
@@ -2138,56 +2132,54 @@
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="K19" s="28">
+      <c r="E19" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="33">
         <v>-500</v>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="33">
         <v>108.102</v>
       </c>
-      <c r="M19" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="28">
-        <v>107.26</v>
-      </c>
-      <c r="O19" s="30">
+      <c r="M19" s="33">
+        <v>107.749</v>
+      </c>
+      <c r="N19" s="33">
+        <v>107.749</v>
+      </c>
+      <c r="O19" s="35">
         <v>54051</v>
       </c>
-      <c r="P19" s="28">
+      <c r="P19" s="33">
         <v>4.5599999999999996</v>
       </c>
-      <c r="Q19" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="S19" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="U19" s="4">
-        <v>497</v>
+      <c r="Q19" s="33">
+        <v>1</v>
+      </c>
+      <c r="R19" s="36">
+        <f t="shared" si="3"/>
+        <v>3.2654344970491629E-3</v>
+      </c>
+      <c r="S19" s="33">
+        <v>177</v>
+      </c>
+      <c r="T19" s="13">
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
@@ -2206,22 +2198,22 @@
         <v>24</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K20" s="4">
         <v>-1</v>
@@ -2270,22 +2262,22 @@
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="K21" s="4">
         <v>2000</v>
@@ -2334,22 +2326,22 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="K22" s="4">
         <v>-4</v>
@@ -2401,19 +2393,19 @@
         <v>81</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K23" s="4">
         <v>-10</v>
@@ -2462,22 +2454,22 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K24" s="4">
         <v>-10</v>
@@ -2525,22 +2517,22 @@
         <v>2</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K25" s="4">
         <v>-6</v>
@@ -2590,22 +2582,22 @@
         <v>10</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="K26" s="4">
         <v>-3</v>
@@ -2653,22 +2645,22 @@
         <v>0</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K27" s="4">
         <v>-1000</v>
@@ -2718,22 +2710,22 @@
         <v>3</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K28" s="4">
         <v>-1000</v>
@@ -2783,56 +2775,54 @@
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="E29" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="K29" s="32">
-        <v>500</v>
-      </c>
-      <c r="L29" s="32">
-        <v>271.25880000000001</v>
-      </c>
-      <c r="M29" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="34">
-        <v>135629</v>
-      </c>
-      <c r="P29" s="32">
-        <v>1.85</v>
-      </c>
-      <c r="Q29" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="S29" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T29" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="U29" s="4">
-        <v>-394</v>
+      <c r="E29" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="33">
+        <v>900</v>
+      </c>
+      <c r="L29" s="33">
+        <v>269.69299999999998</v>
+      </c>
+      <c r="M29" s="33">
+        <v>270.42500000000001</v>
+      </c>
+      <c r="N29" s="33">
+        <v>270.42500000000001</v>
+      </c>
+      <c r="O29" s="35">
+        <v>242723</v>
+      </c>
+      <c r="P29" s="33">
+        <v>12.28</v>
+      </c>
+      <c r="Q29" s="33">
+        <v>1</v>
+      </c>
+      <c r="R29" s="36">
+        <f>IF(Q29=1, ABS(M29-L29)/L29, 0)</f>
+        <v>2.7141972539147393E-3</v>
+      </c>
+      <c r="S29" s="33">
+        <v>2891</v>
+      </c>
+      <c r="T29" s="13">
+        <v>2891</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
@@ -2851,56 +2841,54 @@
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="E30" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J30" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="K30" s="32">
-        <v>210</v>
-      </c>
-      <c r="L30" s="32">
-        <v>958.57</v>
-      </c>
-      <c r="M30" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="34">
-        <v>201299</v>
-      </c>
-      <c r="P30" s="32">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="Q30" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="S30" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T30" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="U30" s="4">
-        <v>-1930</v>
+      <c r="E30" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" s="33">
+        <v>310</v>
+      </c>
+      <c r="L30" s="33">
+        <v>951.66</v>
+      </c>
+      <c r="M30" s="33">
+        <v>949.6</v>
+      </c>
+      <c r="N30" s="33">
+        <v>949.6</v>
+      </c>
+      <c r="O30" s="35">
+        <v>295017</v>
+      </c>
+      <c r="P30" s="33">
+        <v>9.18</v>
+      </c>
+      <c r="Q30" s="33">
+        <v>0</v>
+      </c>
+      <c r="R30" s="36">
+        <f>IF(Q30=1, ABS(M30-L30)/L30, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="33">
+        <v>-642</v>
+      </c>
+      <c r="T30" s="25">
+        <v>-642</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
@@ -2920,22 +2908,22 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="K31" s="4">
         <v>400</v>
@@ -2963,10 +2951,10 @@
         <v>8.455326735182055E-3</v>
       </c>
       <c r="S31" s="4">
-        <v>1121</v>
+        <v>4108</v>
       </c>
       <c r="T31" s="13">
-        <v>1121</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
@@ -2985,53 +2973,53 @@
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="E32" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="G32" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="K32" s="32">
+      <c r="E32" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="K32" s="28">
         <v>-4000</v>
       </c>
-      <c r="L32" s="32">
+      <c r="L32" s="28">
         <v>50.406999999999996</v>
       </c>
-      <c r="M32" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="34">
+      <c r="M32" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="N32" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" s="30">
         <v>201080</v>
       </c>
-      <c r="P32" s="32">
+      <c r="P32" s="28">
         <v>1.21</v>
       </c>
-      <c r="Q32" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R32" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="S32" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T32" s="34" t="s">
-        <v>21</v>
+      <c r="Q32" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="R32" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="S32" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="T32" s="30" t="s">
+        <v>72</v>
       </c>
       <c r="U32" s="4">
         <v>749</v>
@@ -3061,7 +3049,7 @@
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D36" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E36" s="7">
         <f ca="1">AVERAGE(D2:D24)</f>
@@ -3071,16 +3059,16 @@
       <c r="H36" s="11"/>
       <c r="T36" s="16">
         <f>SUM(T2:T31)</f>
-        <v>62562.47</v>
+        <v>67975.47</v>
       </c>
       <c r="U36" s="16">
         <f>SUM(U2:U32)</f>
-        <v>-1078</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D37" s="24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E37" s="7">
         <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
@@ -3088,23 +3076,23 @@
       </c>
       <c r="F37" s="11"/>
       <c r="T37" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F38" s="11"/>
       <c r="T38" s="4" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F39" s="11"/>
       <c r="T39" s="16">
         <f>T36+U36</f>
-        <v>61484.47</v>
+        <v>68724.47</v>
       </c>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.2">
@@ -3113,7 +3101,7 @@
     <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F41" s="11"/>
       <c r="T41" s="11" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.2">
@@ -3124,13 +3112,13 @@
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="T44" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="T45" s="23">
         <f>T39/T42</f>
-        <v>0.18463804804804806</v>
+        <v>0.2063797897897898</v>
       </c>
     </row>
   </sheetData>
@@ -3144,7 +3132,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
   <dimension ref="A1:H61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="20" customWidth="1"/>
@@ -3156,18 +3144,18 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="36"/>
+        <v>113</v>
+      </c>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="18">
@@ -3182,8 +3170,8 @@
       <c r="D2" s="26">
         <v>0</v>
       </c>
-      <c r="G2" s="36" t="s">
-        <v>85</v>
+      <c r="G2" s="32" t="s">
+        <v>114</v>
       </c>
       <c r="H2" s="19">
         <f>AVERAGE(C3:C61)</f>
@@ -3205,8 +3193,8 @@
         <f>C3/B2</f>
         <v>5.0265608051062075E-2</v>
       </c>
-      <c r="G3" s="36" t="s">
-        <v>87</v>
+      <c r="G3" s="32" t="s">
+        <v>115</v>
       </c>
       <c r="H3" s="19">
         <f>_xlfn.STDEV.S(C3:C61)</f>
@@ -3228,8 +3216,8 @@
         <f t="shared" ref="D4:D61" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>88</v>
+      <c r="G4" s="32" t="s">
+        <v>116</v>
       </c>
       <c r="H4" s="22">
         <f>(H2/H3)*SQRT(252)</f>
@@ -3251,8 +3239,8 @@
         <f t="shared" si="1"/>
         <v>-1.4330935556555255E-2</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>107</v>
+      <c r="G5" s="32" t="s">
+        <v>117</v>
       </c>
       <c r="H5" s="27">
         <f>_xlfn.STDEV.S(D2:D61)*SQRT(252)</f>
@@ -3274,8 +3262,8 @@
         <f t="shared" si="1"/>
         <v>1.8960279435109632E-2</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>111</v>
+      <c r="G6" s="32" t="s">
+        <v>118</v>
       </c>
       <c r="H6" s="27" cm="1">
         <f t="array" ref="H6">PRODUCT(1+D2:D61)-1</f>
@@ -3297,8 +3285,8 @@
         <f t="shared" si="1"/>
         <v>6.3379600224845786E-3</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>110</v>
+      <c r="G7" s="32" t="s">
+        <v>119</v>
       </c>
       <c r="H7" s="27" cm="1">
         <f t="array" ref="H7">PRODUCT(1+D2:D61)^(252/COUNT(D2:D61))-1</f>
@@ -3336,7 +3324,7 @@
         <f t="shared" si="1"/>
         <v>-2.4696164445931968E-2</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="18">
@@ -3353,7 +3341,7 @@
         <f t="shared" si="1"/>
         <v>2.4974757131671892E-3</v>
       </c>
-      <c r="G10" s="36"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="18">
@@ -3370,7 +3358,7 @@
         <f t="shared" si="1"/>
         <v>-1.219430553672287E-2</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="18">
@@ -3387,7 +3375,7 @@
         <f t="shared" si="1"/>
         <v>3.8753584027505917E-3</v>
       </c>
-      <c r="G12" s="36"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="18">
@@ -3404,7 +3392,7 @@
         <f t="shared" si="1"/>
         <v>6.5896035776255831E-3</v>
       </c>
-      <c r="G13" s="36"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="18">
@@ -3421,7 +3409,7 @@
         <f t="shared" si="1"/>
         <v>2.2987887845197601E-2</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="18">
@@ -3438,7 +3426,7 @@
         <f t="shared" si="1"/>
         <v>4.9669811404690978E-3</v>
       </c>
-      <c r="G15" s="36"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="18">
@@ -3455,7 +3443,7 @@
         <f t="shared" si="1"/>
         <v>5.3408025590434456E-3</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="18">
@@ -3472,7 +3460,7 @@
         <f t="shared" si="1"/>
         <v>3.1022876813363312E-2</v>
       </c>
-      <c r="G17" s="36"/>
+      <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="18">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EA4102-5AB0-254F-AC47-0CB273C475FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DB0DDE-CD4D-7B47-897E-8A9073A6385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20180" yWindow="-35140" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,7 +430,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -516,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -587,7 +587,7 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -605,18 +605,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2132,50 +2120,50 @@
         <f t="shared" ca="1" si="0"/>
         <v>24</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="34" t="s">
+      <c r="H19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="33">
+      <c r="K19" s="4">
         <v>-500</v>
       </c>
-      <c r="L19" s="33">
+      <c r="L19" s="4">
         <v>108.102</v>
       </c>
-      <c r="M19" s="33">
+      <c r="M19" s="4">
         <v>107.749</v>
       </c>
-      <c r="N19" s="33">
+      <c r="N19" s="4">
         <v>107.749</v>
       </c>
-      <c r="O19" s="35">
+      <c r="O19" s="16">
         <v>54051</v>
       </c>
-      <c r="P19" s="33">
+      <c r="P19" s="4">
         <v>4.5599999999999996</v>
       </c>
-      <c r="Q19" s="33">
+      <c r="Q19" s="4">
         <v>1</v>
       </c>
-      <c r="R19" s="36">
+      <c r="R19" s="5">
         <f t="shared" si="3"/>
         <v>3.2654344970491629E-3</v>
       </c>
-      <c r="S19" s="33">
+      <c r="S19" s="4">
         <v>177</v>
       </c>
       <c r="T19" s="13">
@@ -2556,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="5">
-        <f>IF(Q25=1, ABS(M25-L25)/L25, 0)</f>
+        <f t="shared" ref="R25:R31" si="4">IF(Q25=1, ABS(M25-L25)/L25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="S25" s="4">
@@ -2578,7 +2566,7 @@
         <v>46268</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" ref="D26:D32" ca="1" si="4">C26-B26</f>
+        <f t="shared" ref="D26:D32" ca="1" si="5">C26-B26</f>
         <v>10</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -2621,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="R26" s="5">
-        <f>IF(Q26=1, ABS(M26-L26)/L26, 0)</f>
+        <f t="shared" si="4"/>
         <v>8.4025752021974973E-3</v>
       </c>
       <c r="S26" s="4">
@@ -2684,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="R27" s="5">
-        <f>IF(Q27=1, ABS(M27-L27)/L27, 0)</f>
+        <f t="shared" si="4"/>
         <v>2.623408180713668E-2</v>
       </c>
       <c r="S27" s="4">
@@ -2702,12 +2690,11 @@
         <v>46265</v>
       </c>
       <c r="C28" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>93</v>
@@ -2749,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="5">
-        <f>IF(Q28=1, ABS(M28-L28)/L28, 0)</f>
+        <f t="shared" si="4"/>
         <v>3.0251341995685504E-2</v>
       </c>
       <c r="S28" s="4">
@@ -2764,61 +2751,59 @@
         <v>24</v>
       </c>
       <c r="B29" s="1">
-        <f ca="1">TODAY()</f>
+        <v>46266</v>
+      </c>
+      <c r="C29" s="1">
         <v>46268</v>
       </c>
-      <c r="C29" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
-      </c>
       <c r="D29" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="33" t="s">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="34" t="s">
+      <c r="H29" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="33" t="s">
+      <c r="I29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J29" s="33" t="s">
+      <c r="J29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="4">
         <v>900</v>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="4">
         <v>269.69299999999998</v>
       </c>
-      <c r="M29" s="33">
+      <c r="M29" s="4">
         <v>270.42500000000001</v>
       </c>
-      <c r="N29" s="33">
+      <c r="N29" s="4">
         <v>270.42500000000001</v>
       </c>
-      <c r="O29" s="35">
+      <c r="O29" s="16">
         <v>242723</v>
       </c>
-      <c r="P29" s="33">
+      <c r="P29" s="4">
         <v>12.28</v>
       </c>
-      <c r="Q29" s="33">
+      <c r="Q29" s="4">
         <v>1</v>
       </c>
-      <c r="R29" s="36">
-        <f>IF(Q29=1, ABS(M29-L29)/L29, 0)</f>
+      <c r="R29" s="5">
+        <f t="shared" si="4"/>
         <v>2.7141972539147393E-3</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="4">
         <v>2891</v>
       </c>
       <c r="T29" s="13">
@@ -2830,61 +2815,59 @@
         <v>25</v>
       </c>
       <c r="B30" s="1">
-        <f ca="1">TODAY()</f>
+        <v>46266</v>
+      </c>
+      <c r="C30" s="1">
         <v>46268</v>
       </c>
-      <c r="C30" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
-      </c>
       <c r="D30" s="2">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" s="4">
+        <v>310</v>
+      </c>
+      <c r="L30" s="4">
+        <v>951.66</v>
+      </c>
+      <c r="M30" s="4">
+        <v>949.6</v>
+      </c>
+      <c r="N30" s="4">
+        <v>949.6</v>
+      </c>
+      <c r="O30" s="16">
+        <v>295017</v>
+      </c>
+      <c r="P30" s="4">
+        <v>9.18</v>
+      </c>
+      <c r="Q30" s="4">
         <v>0</v>
       </c>
-      <c r="E30" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="G30" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="K30" s="33">
-        <v>310</v>
-      </c>
-      <c r="L30" s="33">
-        <v>951.66</v>
-      </c>
-      <c r="M30" s="33">
-        <v>949.6</v>
-      </c>
-      <c r="N30" s="33">
-        <v>949.6</v>
-      </c>
-      <c r="O30" s="35">
-        <v>295017</v>
-      </c>
-      <c r="P30" s="33">
-        <v>9.18</v>
-      </c>
-      <c r="Q30" s="33">
+      <c r="R30" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R30" s="36">
-        <f>IF(Q30=1, ABS(M30-L30)/L30, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="33">
+      <c r="S30" s="4">
         <v>-642</v>
       </c>
       <c r="T30" s="25">
@@ -2896,16 +2879,14 @@
         <v>26</v>
       </c>
       <c r="B31" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="C31" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>99</v>
@@ -2947,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="R31" s="5">
-        <f>IF(Q31=1, ABS(M31-L31)/L31, 0)</f>
+        <f t="shared" si="4"/>
         <v>8.455326735182055E-3</v>
       </c>
       <c r="S31" s="4">
@@ -2962,16 +2943,14 @@
         <v>27</v>
       </c>
       <c r="B32" s="1">
-        <f ca="1">TODAY()</f>
+        <v>46266</v>
+      </c>
+      <c r="C32" s="1">
         <v>46268</v>
       </c>
-      <c r="C32" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46268</v>
-      </c>
       <c r="D32" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="E32" s="28" t="s">
         <v>101</v>
@@ -3052,8 +3031,8 @@
         <v>103</v>
       </c>
       <c r="E36" s="7">
-        <f ca="1">AVERAGE(D2:D24)</f>
-        <v>11.347826086956522</v>
+        <f ca="1">AVERAGE(D2:D32)</f>
+        <v>9.064516129032258</v>
       </c>
       <c r="F36" s="11"/>
       <c r="H36" s="11"/>
@@ -3071,8 +3050,8 @@
         <v>104</v>
       </c>
       <c r="E37" s="7">
-        <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
-        <v>6.5909090909090908</v>
+        <f ca="1">AVERAGE(D2:D11,D13,D15:D32)</f>
+        <v>5.6206896551724137</v>
       </c>
       <c r="F37" s="11"/>
       <c r="T37" s="4" t="s">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/bookmonitor_serve/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DB0DDE-CD4D-7B47-897E-8A9073A6385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3923FAC1-FA40-6749-8962-F03D7D6758A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20180" yWindow="-35140" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="-38360" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="120">
   <si>
     <t>Trade ID</t>
   </si>
@@ -430,7 +430,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -587,7 +587,7 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2979,8 +2979,8 @@
       <c r="M32" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="N32" s="28" t="s">
-        <v>72</v>
+      <c r="N32" s="28">
+        <v>50.59</v>
       </c>
       <c r="O32" s="30">
         <v>201080</v>
@@ -3001,7 +3001,7 @@
         <v>72</v>
       </c>
       <c r="U32" s="4">
-        <v>749</v>
+        <v>-366</v>
       </c>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.2">
@@ -3031,8 +3031,8 @@
         <v>103</v>
       </c>
       <c r="E36" s="7">
-        <f ca="1">AVERAGE(D2:D32)</f>
-        <v>9.064516129032258</v>
+        <f ca="1">AVERAGE(D2:D24)</f>
+        <v>11.347826086956522</v>
       </c>
       <c r="F36" s="11"/>
       <c r="H36" s="11"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="U36" s="16">
         <f>SUM(U2:U32)</f>
-        <v>749</v>
+        <v>-366</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.2">
@@ -3050,8 +3050,8 @@
         <v>104</v>
       </c>
       <c r="E37" s="7">
-        <f ca="1">AVERAGE(D2:D11,D13,D15:D32)</f>
-        <v>5.6206896551724137</v>
+        <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
+        <v>6.5909090909090908</v>
       </c>
       <c r="F37" s="11"/>
       <c r="T37" s="4" t="s">
@@ -3071,7 +3071,7 @@
       <c r="F39" s="11"/>
       <c r="T39" s="16">
         <f>T36+U36</f>
-        <v>68724.47</v>
+        <v>67609.47</v>
       </c>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.2">
@@ -3097,7 +3097,7 @@
     <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="T45" s="23">
         <f>T39/T42</f>
-        <v>0.2063797897897898</v>
+        <v>0.20303144144144145</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3923FAC1-FA40-6749-8962-F03D7D6758A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE0BED5-5DF6-6A45-9BB0-BC4AFAA85A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="-38360" windowWidth="51480" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11760" yWindow="-42240" windowWidth="37340" windowHeight="41180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
     <sheet name="Daily PnL" sheetId="3" r:id="rId2"/>
+    <sheet name="exposure" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
   <si>
     <t>Trade ID</t>
   </si>
@@ -422,6 +423,30 @@
   </si>
   <si>
     <t>Ann. Return</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Total Exposure</t>
+  </si>
+  <si>
+    <t>Equity_Exposure</t>
+  </si>
+  <si>
+    <t>Cash_Exposure</t>
+  </si>
+  <si>
+    <t>Futures_Exposure</t>
+  </si>
+  <si>
+    <t>ETF_Exposure</t>
   </si>
 </sst>
 </file>
@@ -430,7 +455,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -472,7 +497,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,6 +528,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -516,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -569,15 +600,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -587,10 +609,6 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -603,9 +621,44 @@
     <xf numFmtId="10" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1847,7 +1900,7 @@
       <c r="S14" s="4">
         <v>-16354</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T14" s="20">
         <v>-16354</v>
       </c>
     </row>
@@ -2870,7 +2923,7 @@
       <c r="S30" s="4">
         <v>-642</v>
       </c>
-      <c r="T30" s="25">
+      <c r="T30" s="20">
         <v>-642</v>
       </c>
     </row>
@@ -2952,52 +3005,52 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="28" t="s">
+      <c r="J32" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="21">
         <v>-4000</v>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="21">
         <v>50.406999999999996</v>
       </c>
-      <c r="M32" s="28" t="s">
+      <c r="M32" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="N32" s="28">
+      <c r="N32" s="21">
         <v>50.59</v>
       </c>
-      <c r="O32" s="30">
+      <c r="O32" s="23">
         <v>201080</v>
       </c>
-      <c r="P32" s="28">
+      <c r="P32" s="21">
         <v>1.21</v>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="Q32" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="R32" s="31" t="s">
+      <c r="R32" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="S32" s="28" t="s">
+      <c r="S32" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="T32" s="30" t="s">
+      <c r="T32" s="23" t="s">
         <v>72</v>
       </c>
       <c r="U32" s="4">
@@ -3027,7 +3080,7 @@
       <c r="H35" s="11"/>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="19" t="s">
         <v>103</v>
       </c>
       <c r="E36" s="7">
@@ -3046,7 +3099,7 @@
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="19" t="s">
         <v>104</v>
       </c>
       <c r="E37" s="7">
@@ -3095,7 +3148,7 @@
       </c>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="T45" s="23">
+      <c r="T45" s="18">
         <f>T39/T42</f>
         <v>0.20303144144144145</v>
       </c>
@@ -3113,1063 +3166,1065 @@
   <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.5" style="35"/>
+    <col min="7" max="7" width="15.33203125" style="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="35" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="32"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="18">
+      <c r="A2" s="37">
         <v>46184</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="29">
         <v>333455.63</v>
       </c>
-      <c r="C2" s="21">
-        <v>0</v>
-      </c>
-      <c r="D2" s="26">
-        <v>0</v>
-      </c>
-      <c r="G2" s="32" t="s">
+      <c r="C2" s="33">
+        <v>0</v>
+      </c>
+      <c r="D2" s="34">
+        <v>0</v>
+      </c>
+      <c r="G2" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="38">
         <f>AVERAGE(C3:C61)</f>
         <v>1163.848983050847</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
+      <c r="A3" s="37">
         <v>46185</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="29">
         <v>350216.98</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="29">
         <f>B3-B2</f>
         <v>16761.349999999977</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="34">
         <f>C3/B2</f>
         <v>5.0265608051062075E-2</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="38">
         <f>_xlfn.STDEV.S(C3:C61)</f>
         <v>4533.8438044752129</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="37">
         <v>46188</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="29">
         <v>356930.64</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="29">
         <f t="shared" ref="C4:C61" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="34">
         <f t="shared" ref="D4:D61" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="39">
         <f>(H2/H3)*SQRT(252)</f>
         <v>4.0750256589102625</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+      <c r="A5" s="37">
         <v>46189</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="29">
         <v>351815.49</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="29">
         <f t="shared" si="0"/>
         <v>-5115.1500000000233</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="34">
         <f t="shared" si="1"/>
         <v>-1.4330935556555255E-2</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="40">
         <f>_xlfn.STDEV.S(D2:D61)*SQRT(252)</f>
         <v>0.19756878191419452</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="37">
         <v>46190</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="29">
         <v>358486.01</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="29">
         <f t="shared" si="0"/>
         <v>6670.5200000000186</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="34">
         <f t="shared" si="1"/>
         <v>1.8960279435109632E-2</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="27" cm="1">
+      <c r="H6" s="40" cm="1">
         <f t="array" ref="H6">PRODUCT(1+D2:D61)-1</f>
         <v>0.20592571791335645</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="37">
         <v>46191</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="29">
         <v>360758.08</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>2272.070000000007</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="34">
         <f t="shared" si="1"/>
         <v>6.3379600224845786E-3</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="27" cm="1">
+      <c r="H7" s="40" cm="1">
         <f t="array" ref="H7">PRODUCT(1+D2:D61)^(252/COUNT(D2:D61))-1</f>
         <v>1.195565207449981</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="37">
         <v>46192</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="29">
         <v>360243.39</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>-514.69000000000233</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="34">
         <f t="shared" si="1"/>
         <v>-1.4266901520265389E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+      <c r="A9" s="37">
         <v>46195</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="29">
         <v>351346.76</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>-8896.6300000000047</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="34">
         <f t="shared" si="1"/>
         <v>-2.4696164445931968E-2</v>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="36"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="37">
         <v>46196</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="29">
         <v>352224.24</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>877.47999999998137</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="34">
         <f t="shared" si="1"/>
         <v>2.4974757131671892E-3</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="36"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="18">
+      <c r="A11" s="37">
         <v>46197</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="29">
         <v>347929.11</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>-4295.1300000000047</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="34">
         <f t="shared" si="1"/>
         <v>-1.219430553672287E-2</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="36"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="37">
         <v>46198</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="29">
         <v>349277.46</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>1348.3500000000349</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="34">
         <f t="shared" si="1"/>
         <v>3.8753584027505917E-3</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="36"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+      <c r="A13" s="37">
         <v>46199</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="29">
         <v>351579.06</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>2301.5999999999767</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="34">
         <f t="shared" si="1"/>
         <v>6.5896035776255831E-3</v>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="37">
         <v>46202</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="29">
         <v>359661.12</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>8082.0599999999977</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="34">
         <f t="shared" si="1"/>
         <v>2.2987887845197601E-2</v>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="18">
+      <c r="A15" s="37">
         <v>46203</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="29">
         <v>361447.55</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>1786.429999999993</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="34">
         <f t="shared" si="1"/>
         <v>4.9669811404690978E-3</v>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="37">
         <v>46204</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="29">
         <v>363377.97</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>1930.4199999999837</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="34">
         <f t="shared" si="1"/>
         <v>5.3408025590434456E-3</v>
       </c>
-      <c r="G16" s="32"/>
+      <c r="G16" s="36"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="18">
+      <c r="A17" s="37">
         <v>46205</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="29">
         <v>374651</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>11273.030000000028</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="34">
         <f t="shared" si="1"/>
         <v>3.1022876813363312E-2</v>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="37">
         <v>46206</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="29">
         <v>374479.39</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>-171.60999999998603</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="34">
         <f t="shared" si="1"/>
         <v>-4.5805296128926929E-4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="18">
+      <c r="A19" s="37">
         <v>46209</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="29">
         <v>372801.92</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="29">
         <f t="shared" si="0"/>
         <v>-1677.4700000000303</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="34">
         <f t="shared" si="1"/>
         <v>-4.4794721546625839E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+      <c r="A20" s="37">
         <v>46210</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="29">
         <v>375246.11</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="29">
         <f t="shared" si="0"/>
         <v>2444.1900000000023</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="34">
         <f t="shared" si="1"/>
         <v>6.5562698818718594E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="18">
+      <c r="A21" s="37">
         <v>46211</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="29">
         <v>377280.97</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="29">
         <f t="shared" si="0"/>
         <v>2034.859999999986</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="34">
         <f t="shared" si="1"/>
         <v>5.4227344288791859E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="37">
         <v>46212</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="29">
         <v>374471.51</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="29">
         <f t="shared" si="0"/>
         <v>-2809.4599999999627</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="34">
         <f t="shared" si="1"/>
         <v>-7.4465987510580322E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="18">
+      <c r="A23" s="37">
         <v>46213</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="29">
         <v>376468.72</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="29">
         <f t="shared" si="0"/>
         <v>1997.2099999999627</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="34">
         <f t="shared" si="1"/>
         <v>5.3334097432404474E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="37">
         <v>46216</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="29">
         <v>379175.63</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="29">
         <f t="shared" si="0"/>
         <v>2706.9100000000326</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="34">
         <f t="shared" si="1"/>
         <v>7.190265369191982E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="18">
+      <c r="A25" s="37">
         <v>46217</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="29">
         <v>378852.03</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="29">
         <f t="shared" si="0"/>
         <v>-323.59999999997672</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="34">
         <f t="shared" si="1"/>
         <v>-8.5343037473156356E-4</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="18">
+      <c r="A26" s="37">
         <v>46218</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="29">
         <v>374437.1</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="29">
         <f t="shared" si="0"/>
         <v>-4414.9300000000512</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="34">
         <f t="shared" si="1"/>
         <v>-1.1653441582456483E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+      <c r="A27" s="37">
         <v>46219</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="29">
         <v>372248.26</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="29">
         <f t="shared" si="0"/>
         <v>-2188.8399999999674</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="34">
         <f t="shared" si="1"/>
         <v>-5.8456814241963934E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
+      <c r="A28" s="37">
         <v>46220</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="29">
         <v>376025.4</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="29">
         <f t="shared" si="0"/>
         <v>3777.140000000014</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="34">
         <f t="shared" si="1"/>
         <v>1.0146830504996891E-2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="18">
+      <c r="A29" s="37">
         <v>46223</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="29">
         <v>375009.72</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="29">
         <f t="shared" si="0"/>
         <v>-1015.6800000000512</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="34">
         <f t="shared" si="1"/>
         <v>-2.7010941282159429E-3</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+      <c r="A30" s="37">
         <v>46224</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="29">
         <v>375731.28</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="29">
         <f t="shared" si="0"/>
         <v>721.56000000005588</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="34">
         <f t="shared" si="1"/>
         <v>1.9241101270656557E-3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="18">
+      <c r="A31" s="37">
         <v>46225</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="29">
         <v>378174.99</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="29">
         <f t="shared" si="0"/>
         <v>2443.7099999999627</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="34">
         <f t="shared" si="1"/>
         <v>6.5038769196963386E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="18">
+      <c r="A32" s="37">
         <v>46226</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="29">
         <v>380362.45</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="29">
         <f t="shared" si="0"/>
         <v>2187.460000000021</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="34">
         <f t="shared" si="1"/>
         <v>5.7842534748266169E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="18">
+      <c r="A33" s="37">
         <v>46227</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="29">
         <f>B32-1740-1437</f>
         <v>377185.45</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="29">
         <f t="shared" si="0"/>
         <v>-3177</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="34">
         <f t="shared" si="1"/>
         <v>-8.3525595126437945E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="A34" s="37">
         <v>46230</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="29">
         <f>B33+322+630+1019-936</f>
         <v>378220.45</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="29">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="34">
         <f t="shared" si="1"/>
         <v>2.7440082855794143E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="18">
+      <c r="A35" s="37">
         <v>46231</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="29">
         <f>B34-951+8872.25-771</f>
         <v>385370.7</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="29">
         <f t="shared" si="0"/>
         <v>7150.25</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="34">
         <f t="shared" si="1"/>
         <v>1.8904979886730081E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="18">
+      <c r="A36" s="37">
         <v>46232</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="29">
         <f>B35+567+1830-7720+5262</f>
         <v>385309.7</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="29">
         <f t="shared" si="0"/>
         <v>-61</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="34">
         <f t="shared" si="1"/>
         <v>-1.5828914860418811E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="18">
+      <c r="A37" s="37">
         <v>46233</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="29">
         <f>B36+2088+840+8949-5393</f>
         <v>391793.7</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="29">
         <f t="shared" si="0"/>
         <v>6484</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="34">
         <f t="shared" si="1"/>
         <v>1.6828021718633089E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="18">
+      <c r="A38" s="37">
         <v>46234</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="29">
         <f>B37-480-2572</f>
         <v>388741.7</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="29">
         <f t="shared" si="0"/>
         <v>-3052</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="34">
         <f t="shared" si="1"/>
         <v>-7.7898138739852119E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="18">
+      <c r="A39" s="37">
         <v>46237</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="29">
         <f>B38-3000-427</f>
         <v>385314.7</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="29">
         <f t="shared" si="0"/>
         <v>-3427</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="34">
         <f t="shared" si="1"/>
         <v>-8.8156223013893288E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="18">
+      <c r="A40" s="37">
         <v>46238</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="29">
         <f>B39-2340+453</f>
         <v>383427.7</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="29">
         <f t="shared" si="0"/>
         <v>-1887</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="34">
         <f t="shared" si="1"/>
         <v>-4.8972956391230334E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="18">
+      <c r="A41" s="37">
         <v>46239</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="29">
         <f>B40+1500-3275</f>
         <v>381652.7</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="29">
         <f t="shared" si="0"/>
         <v>-1775</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="34">
         <f t="shared" si="1"/>
         <v>-4.6292951709018416E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="18">
+      <c r="A42" s="37">
         <v>46240</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="29">
         <f>B41+2550-1004</f>
         <v>383198.7</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="29">
         <f t="shared" si="0"/>
         <v>1546</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="34">
         <f t="shared" si="1"/>
         <v>4.0508032564685117E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="18">
+      <c r="A43" s="37">
         <v>46241</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="29">
         <f>B42+840+738</f>
         <v>384776.7</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="29">
         <f t="shared" si="0"/>
         <v>1578</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="34">
         <f t="shared" si="1"/>
         <v>4.1179680411233127E-3</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="18">
+      <c r="A44" s="37">
         <v>46244</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="29">
         <f>B43+41+540-398-50</f>
         <v>384909.7</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="29">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="34">
         <f t="shared" si="1"/>
         <v>3.4565502536925964E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="18">
+      <c r="A45" s="37">
         <v>46245</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="29">
         <f>B44-40-2340-824-1009-1010</f>
         <v>379686.7</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="29">
         <f t="shared" si="0"/>
         <v>-5223</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="34">
         <f t="shared" si="1"/>
         <v>-1.3569416411173841E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="18">
+      <c r="A46" s="37">
         <v>46246</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="29">
         <f>B45-205-1710-410+2950-212+6683-2764-240</f>
         <v>383778.7</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="29">
         <f t="shared" si="0"/>
         <v>4092</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="34">
         <f t="shared" si="1"/>
         <v>1.0777306658358061E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="18">
+      <c r="A47" s="37">
         <v>46247</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="29">
         <f>B46-95-1110+960-1500-1040+875+120</f>
         <v>381988.7</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="29">
         <f t="shared" si="0"/>
         <v>-1790</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="34">
         <f t="shared" si="1"/>
         <v>-4.6641462905575529E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="18">
+      <c r="A48" s="37">
         <v>46248</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="29">
         <f>B47+25-540-1100-7593+350-1166-690</f>
         <v>371274.7</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="29">
         <f t="shared" si="0"/>
         <v>-10714</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="34">
         <f t="shared" si="1"/>
         <v>-2.8047950109518945E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="18">
+      <c r="A49" s="37">
         <v>46251</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="29">
         <f>B48+95+1620-1380+725+796+220</f>
         <v>373350.7</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="29">
         <f t="shared" si="0"/>
         <v>2076</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="34">
         <f t="shared" si="1"/>
         <v>5.5915471751778398E-3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="18">
+      <c r="A50" s="37">
         <v>46252</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="29">
         <f>B49+590+1620+620+1095+826+2690</f>
         <v>380791.7</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="29">
         <f t="shared" si="0"/>
         <v>7441</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="34">
         <f t="shared" si="1"/>
         <v>1.9930322884087266E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="18">
+      <c r="A51" s="37">
         <v>46253</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="29">
         <f>B50-195+5550+2720-300-3504+1730</f>
         <v>386792.7</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="29">
         <f t="shared" si="0"/>
         <v>6001</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="34">
         <f t="shared" si="1"/>
         <v>1.5759272063965678E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="18">
+      <c r="A52" s="37">
         <v>46254</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="29">
         <f>B51+155+870-1360+1107.05+1330+1165.8+1267.76</f>
         <v>391328.31</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="29">
         <f t="shared" si="0"/>
         <v>4535.609999999986</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="34">
         <f t="shared" si="1"/>
         <v>1.1726203726181973E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="18">
+      <c r="A53" s="37">
         <v>46255</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="29">
         <f>B52-445-450-580+585-575-2123</f>
         <v>387740.31</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="29">
         <f t="shared" si="0"/>
         <v>-3588</v>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="34">
         <f t="shared" si="1"/>
         <v>-9.1687718683066913E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="18">
+      <c r="A54" s="37">
         <v>46258</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="29">
         <f>B53+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="29">
         <f t="shared" si="0"/>
         <v>6121</v>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="34">
         <f t="shared" si="1"/>
         <v>1.5786339057705916E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="18">
+      <c r="A55" s="37">
         <v>46259</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="29">
         <f>B54-390+1290+906-402+1017</f>
         <v>396282.31</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="29">
         <f t="shared" si="0"/>
         <v>2421</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="34">
         <f t="shared" si="1"/>
         <v>6.1468337674497652E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="18">
+      <c r="A56" s="37">
         <v>46260</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="29">
         <f>B55+270-750</f>
         <v>395802.31</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="29">
         <f t="shared" si="0"/>
         <v>-480</v>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="34">
         <f t="shared" si="1"/>
         <v>-1.2112577016117625E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="18">
+      <c r="A57" s="37">
         <v>46261</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="29">
         <f>B56+125+690</f>
         <v>396617.31</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="29">
         <f t="shared" si="0"/>
         <v>815</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="34">
         <f t="shared" si="1"/>
         <v>2.0591087505275043E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="18">
+      <c r="A58" s="37">
         <v>46262</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="29">
         <f>B57+300</f>
         <v>396917.31</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="29">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="D58" s="26">
+      <c r="D58" s="34">
         <f t="shared" si="1"/>
         <v>7.5639663836154808E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="18">
+      <c r="A59" s="37">
         <v>46265</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="29">
         <f>B58+135+2220-2.59</f>
         <v>399269.72</v>
       </c>
-      <c r="C59" s="20">
+      <c r="C59" s="29">
         <f t="shared" si="0"/>
         <v>2352.4099999999744</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="34">
         <f t="shared" si="1"/>
         <v>5.9267004505295434E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="18">
+      <c r="A60" s="37">
         <v>46266</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="29">
         <f>B59+480-562+1405-1361-623+1800+428</f>
         <v>400836.72</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C60" s="29">
         <f t="shared" si="0"/>
         <v>1567</v>
       </c>
-      <c r="D60" s="26">
+      <c r="D60" s="34">
         <f t="shared" si="1"/>
         <v>3.9246652613676792E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="18">
+      <c r="A61" s="37">
         <v>46267</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="29">
         <f>B60-274+71-569+1738+320</f>
         <v>402122.72</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="29">
         <f t="shared" si="0"/>
         <v>1286</v>
       </c>
-      <c r="D61" s="26">
+      <c r="D61" s="34">
         <f t="shared" si="1"/>
         <v>3.2082889012763106E-3</v>
       </c>
@@ -4178,4 +4233,2867 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F1EF3D-9B19-B84A-BFA9-71A8CF817AA5}">
+  <dimension ref="A1:L1048543"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="31"/>
+    <col min="13" max="16384" width="9.1640625" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="L1" s="27"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="28">
+        <v>46175</v>
+      </c>
+      <c r="B2" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C2" s="29">
+        <v>105712</v>
+      </c>
+      <c r="D2" s="30">
+        <v>194288</v>
+      </c>
+      <c r="E2" s="30">
+        <v>0</v>
+      </c>
+      <c r="F2" s="30">
+        <v>0</v>
+      </c>
+      <c r="G2" s="30">
+        <v>300000</v>
+      </c>
+      <c r="H2" s="32">
+        <f>C2/G2</f>
+        <v>0.35237333333333332</v>
+      </c>
+      <c r="I2" s="32">
+        <f>D2/G2</f>
+        <v>0.64762666666666668</v>
+      </c>
+      <c r="J2" s="32">
+        <f>E2/G2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="32">
+        <f>F2/G2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="28">
+        <v>46176</v>
+      </c>
+      <c r="B3" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C3" s="29">
+        <v>105712</v>
+      </c>
+      <c r="D3" s="30">
+        <v>194288</v>
+      </c>
+      <c r="E3" s="30">
+        <v>0</v>
+      </c>
+      <c r="F3" s="30">
+        <v>0</v>
+      </c>
+      <c r="G3" s="30">
+        <v>300000</v>
+      </c>
+      <c r="H3" s="32">
+        <f t="shared" ref="H3:H66" si="0">C3/G3</f>
+        <v>0.35237333333333332</v>
+      </c>
+      <c r="I3" s="32">
+        <f t="shared" ref="I3:I66" si="1">D3/G3</f>
+        <v>0.64762666666666668</v>
+      </c>
+      <c r="J3" s="32">
+        <f t="shared" ref="J3:J66" si="2">E3/G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="32">
+        <f t="shared" ref="K3:K66" si="3">F3/G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="28">
+        <v>46177</v>
+      </c>
+      <c r="B4" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C4" s="30">
+        <v>244380</v>
+      </c>
+      <c r="D4" s="30">
+        <v>55620</v>
+      </c>
+      <c r="E4" s="30">
+        <v>0</v>
+      </c>
+      <c r="F4" s="30">
+        <v>0</v>
+      </c>
+      <c r="G4" s="30">
+        <v>300000</v>
+      </c>
+      <c r="H4" s="32">
+        <f t="shared" si="0"/>
+        <v>0.81459999999999999</v>
+      </c>
+      <c r="I4" s="32">
+        <f t="shared" si="1"/>
+        <v>0.18540000000000001</v>
+      </c>
+      <c r="J4" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="28">
+        <v>46178</v>
+      </c>
+      <c r="B5" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C5" s="30">
+        <v>244380</v>
+      </c>
+      <c r="D5" s="30">
+        <v>0</v>
+      </c>
+      <c r="E5" s="30">
+        <v>663350</v>
+      </c>
+      <c r="F5" s="30">
+        <v>0</v>
+      </c>
+      <c r="G5" s="30">
+        <v>907730</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" si="0"/>
+        <v>0.2692210238727375</v>
+      </c>
+      <c r="I5" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="32">
+        <f t="shared" si="2"/>
+        <v>0.7307789761272625</v>
+      </c>
+      <c r="K5" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="28">
+        <v>46181</v>
+      </c>
+      <c r="B6" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C6" s="30">
+        <v>138668</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0</v>
+      </c>
+      <c r="E6" s="30">
+        <v>3558250</v>
+      </c>
+      <c r="F6" s="30">
+        <v>0</v>
+      </c>
+      <c r="G6" s="30">
+        <v>3696918</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="0"/>
+        <v>3.7509081889292646E-2</v>
+      </c>
+      <c r="I6" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="32">
+        <f t="shared" si="2"/>
+        <v>0.96249091811070731</v>
+      </c>
+      <c r="K6" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="28">
+        <v>46182</v>
+      </c>
+      <c r="B7" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="30">
+        <v>138668</v>
+      </c>
+      <c r="D7" s="30">
+        <v>0</v>
+      </c>
+      <c r="E7" s="30">
+        <v>663350</v>
+      </c>
+      <c r="F7" s="30">
+        <v>0</v>
+      </c>
+      <c r="G7" s="30">
+        <v>802018</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
+        <v>0.17289886261904347</v>
+      </c>
+      <c r="I7" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="32">
+        <f t="shared" si="2"/>
+        <v>0.82710113738095659</v>
+      </c>
+      <c r="K7" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="28">
+        <v>46183</v>
+      </c>
+      <c r="B8" s="29">
+        <v>300000</v>
+      </c>
+      <c r="C8" s="30">
+        <v>138668</v>
+      </c>
+      <c r="D8" s="30">
+        <v>0</v>
+      </c>
+      <c r="E8" s="30">
+        <v>461469</v>
+      </c>
+      <c r="F8" s="30">
+        <v>0</v>
+      </c>
+      <c r="G8" s="30">
+        <v>600137</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" si="0"/>
+        <v>0.23106057450215534</v>
+      </c>
+      <c r="I8" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="32">
+        <f t="shared" si="2"/>
+        <v>0.76893942549784466</v>
+      </c>
+      <c r="K8" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="28">
+        <v>46184</v>
+      </c>
+      <c r="B9" s="29">
+        <v>333455.63</v>
+      </c>
+      <c r="C9" s="30">
+        <v>138668</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>461469</v>
+      </c>
+      <c r="F9" s="30">
+        <v>0</v>
+      </c>
+      <c r="G9" s="30">
+        <v>600137</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" si="0"/>
+        <v>0.23106057450215534</v>
+      </c>
+      <c r="I9" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="32">
+        <f t="shared" si="2"/>
+        <v>0.76893942549784466</v>
+      </c>
+      <c r="K9" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="28">
+        <v>46185</v>
+      </c>
+      <c r="B10" s="29">
+        <v>350216.98</v>
+      </c>
+      <c r="C10" s="30">
+        <v>0</v>
+      </c>
+      <c r="D10" s="30">
+        <v>0</v>
+      </c>
+      <c r="E10" s="30">
+        <v>461469</v>
+      </c>
+      <c r="F10" s="30">
+        <v>0</v>
+      </c>
+      <c r="G10" s="30">
+        <v>461469</v>
+      </c>
+      <c r="H10" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="28">
+        <v>46188</v>
+      </c>
+      <c r="B11" s="29">
+        <v>356930.64</v>
+      </c>
+      <c r="C11" s="30">
+        <v>0</v>
+      </c>
+      <c r="D11" s="30">
+        <v>0</v>
+      </c>
+      <c r="E11" s="30">
+        <v>461469</v>
+      </c>
+      <c r="F11" s="30">
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>461469</v>
+      </c>
+      <c r="H11" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="28">
+        <v>46189</v>
+      </c>
+      <c r="B12" s="29">
+        <v>351815.49</v>
+      </c>
+      <c r="C12" s="30">
+        <v>0</v>
+      </c>
+      <c r="D12" s="30">
+        <v>0</v>
+      </c>
+      <c r="E12" s="30">
+        <v>461469</v>
+      </c>
+      <c r="F12" s="30">
+        <v>0</v>
+      </c>
+      <c r="G12" s="30">
+        <v>461469</v>
+      </c>
+      <c r="H12" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="28">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="29">
+        <v>358486.01</v>
+      </c>
+      <c r="C13" s="30">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30">
+        <f>B13-E13</f>
+        <v>227246.01</v>
+      </c>
+      <c r="E13" s="30">
+        <v>131240</v>
+      </c>
+      <c r="F13" s="30">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(C13:F13)</f>
+        <v>358486.01</v>
+      </c>
+      <c r="H13" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="32">
+        <f t="shared" si="1"/>
+        <v>0.63390482099984879</v>
+      </c>
+      <c r="J13" s="32">
+        <f t="shared" si="2"/>
+        <v>0.36609517900015121</v>
+      </c>
+      <c r="K13" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="28">
+        <v>46191</v>
+      </c>
+      <c r="B14" s="29">
+        <v>360758.08</v>
+      </c>
+      <c r="C14" s="30">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30">
+        <f>B14-E14</f>
+        <v>229518.08000000002</v>
+      </c>
+      <c r="E14" s="30">
+        <v>131240</v>
+      </c>
+      <c r="F14" s="30">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30">
+        <f>SUM(C14:F14)</f>
+        <v>360758.08</v>
+      </c>
+      <c r="H14" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="32">
+        <f t="shared" si="1"/>
+        <v>0.63621050428032</v>
+      </c>
+      <c r="J14" s="32">
+        <f t="shared" si="2"/>
+        <v>0.36378949571968006</v>
+      </c>
+      <c r="K14" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="28">
+        <v>46192</v>
+      </c>
+      <c r="B15" s="29">
+        <v>360243.39</v>
+      </c>
+      <c r="C15" s="30">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30">
+        <f>B15-E15</f>
+        <v>229003.39</v>
+      </c>
+      <c r="E15" s="30">
+        <v>131240</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30">
+        <f>SUM(C15:F15)</f>
+        <v>360243.39</v>
+      </c>
+      <c r="H15" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="32">
+        <f t="shared" si="1"/>
+        <v>0.63569074785799684</v>
+      </c>
+      <c r="J15" s="32">
+        <f t="shared" si="2"/>
+        <v>0.36430925214200321</v>
+      </c>
+      <c r="K15" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="28">
+        <v>46195</v>
+      </c>
+      <c r="B16" s="29">
+        <v>351346.76</v>
+      </c>
+      <c r="C16" s="30">
+        <v>0</v>
+      </c>
+      <c r="D16" s="30">
+        <v>0</v>
+      </c>
+      <c r="E16" s="30">
+        <v>3124781</v>
+      </c>
+      <c r="F16" s="30">
+        <v>0</v>
+      </c>
+      <c r="G16" s="30">
+        <f>SUM(C16:F16)</f>
+        <v>3124781</v>
+      </c>
+      <c r="H16" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="28">
+        <v>46196</v>
+      </c>
+      <c r="B17" s="29">
+        <v>352224.24</v>
+      </c>
+      <c r="C17" s="30">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30">
+        <v>3124781</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30">
+        <f>SUM(C17:F17)</f>
+        <v>3124781</v>
+      </c>
+      <c r="H17" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="28">
+        <v>46197</v>
+      </c>
+      <c r="B18" s="29">
+        <v>347929.11</v>
+      </c>
+      <c r="C18" s="30">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30">
+        <v>3124781</v>
+      </c>
+      <c r="F18" s="30">
+        <v>193096</v>
+      </c>
+      <c r="G18" s="30">
+        <f>SUM(C18:F18)</f>
+        <v>3317877</v>
+      </c>
+      <c r="H18" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="32">
+        <f t="shared" si="2"/>
+        <v>0.94180133862707993</v>
+      </c>
+      <c r="K18" s="32">
+        <f t="shared" si="3"/>
+        <v>5.8198661372920096E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="28">
+        <v>46198</v>
+      </c>
+      <c r="B19" s="29">
+        <v>349277.46</v>
+      </c>
+      <c r="C19" s="30">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30">
+        <f>3124781+202125</f>
+        <v>3326906</v>
+      </c>
+      <c r="F19" s="30">
+        <v>193096</v>
+      </c>
+      <c r="G19" s="30">
+        <f>SUM(C19:F19)</f>
+        <v>3520002</v>
+      </c>
+      <c r="H19" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="32">
+        <f t="shared" si="2"/>
+        <v>0.94514321298681081</v>
+      </c>
+      <c r="K19" s="32">
+        <f t="shared" si="3"/>
+        <v>5.4856787013189197E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="28">
+        <v>46199</v>
+      </c>
+      <c r="B20" s="29">
+        <v>351579.06</v>
+      </c>
+      <c r="C20" s="30">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30">
+        <v>3326906</v>
+      </c>
+      <c r="F20" s="30">
+        <v>193096</v>
+      </c>
+      <c r="G20" s="30">
+        <f>SUM(C20:F20)</f>
+        <v>3520002</v>
+      </c>
+      <c r="H20" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="32">
+        <f t="shared" si="2"/>
+        <v>0.94514321298681081</v>
+      </c>
+      <c r="K20" s="32">
+        <f t="shared" si="3"/>
+        <v>5.4856787013189197E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="28">
+        <v>46202</v>
+      </c>
+      <c r="B21" s="29">
+        <v>359661.12</v>
+      </c>
+      <c r="C21" s="30">
+        <v>55035</v>
+      </c>
+      <c r="D21" s="30">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30">
+        <v>3326906</v>
+      </c>
+      <c r="F21" s="30">
+        <f>193096+223843</f>
+        <v>416939</v>
+      </c>
+      <c r="G21" s="30">
+        <f>SUM(C21:F21)</f>
+        <v>3798880</v>
+      </c>
+      <c r="H21" s="32">
+        <f t="shared" si="0"/>
+        <v>1.4487164637998567E-2</v>
+      </c>
+      <c r="I21" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="32">
+        <f t="shared" si="2"/>
+        <v>0.87575969759508066</v>
+      </c>
+      <c r="K21" s="32">
+        <f t="shared" si="3"/>
+        <v>0.10975313776692078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="28">
+        <v>46203</v>
+      </c>
+      <c r="B22" s="29">
+        <v>361447.55</v>
+      </c>
+      <c r="C22" s="30">
+        <v>55035</v>
+      </c>
+      <c r="D22" s="30">
+        <v>0</v>
+      </c>
+      <c r="E22" s="30">
+        <f>E21-E12-202125+121064</f>
+        <v>2784376</v>
+      </c>
+      <c r="F22" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G22" s="30">
+        <f>SUM(C22:F22)</f>
+        <v>3063254</v>
+      </c>
+      <c r="H22" s="32">
+        <f t="shared" si="0"/>
+        <v>1.7966188895860415E-2</v>
+      </c>
+      <c r="I22" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="32">
+        <f t="shared" si="2"/>
+        <v>0.9089602102861859</v>
+      </c>
+      <c r="K22" s="32">
+        <f t="shared" si="3"/>
+        <v>7.3073600817953721E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="28">
+        <v>46204</v>
+      </c>
+      <c r="B23" s="29">
+        <v>363377.97</v>
+      </c>
+      <c r="C23" s="30">
+        <v>0</v>
+      </c>
+      <c r="D23" s="30">
+        <v>0</v>
+      </c>
+      <c r="E23" s="30">
+        <v>2784376</v>
+      </c>
+      <c r="F23" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G23" s="30">
+        <f>SUM(C23:F23)</f>
+        <v>3008219</v>
+      </c>
+      <c r="H23" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="32">
+        <f t="shared" si="2"/>
+        <v>0.92558952656040006</v>
+      </c>
+      <c r="K23" s="32">
+        <f t="shared" si="3"/>
+        <v>7.4410473439599972E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="28">
+        <v>46205</v>
+      </c>
+      <c r="B24" s="29">
+        <v>374651</v>
+      </c>
+      <c r="C24" s="30">
+        <v>0</v>
+      </c>
+      <c r="D24" s="30">
+        <f>B24-E24-F24</f>
+        <v>29744</v>
+      </c>
+      <c r="E24" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F24" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G24" s="30">
+        <f>SUM(C24:F24)</f>
+        <v>374651</v>
+      </c>
+      <c r="H24" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="32">
+        <f t="shared" si="1"/>
+        <v>7.9391220095502216E-2</v>
+      </c>
+      <c r="J24" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32313806716117133</v>
+      </c>
+      <c r="K24" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59747071274332642</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="28">
+        <v>46206</v>
+      </c>
+      <c r="B25" s="29">
+        <v>374479.39</v>
+      </c>
+      <c r="C25" s="30">
+        <v>0</v>
+      </c>
+      <c r="D25" s="30">
+        <f>B25-E25-F25</f>
+        <v>29572.390000000014</v>
+      </c>
+      <c r="E25" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F25" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G25" s="30">
+        <f>SUM(C25:F25)</f>
+        <v>374479.39</v>
+      </c>
+      <c r="H25" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="32">
+        <f t="shared" si="1"/>
+        <v>7.8969339273918415E-2</v>
+      </c>
+      <c r="J25" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32328614933921995</v>
+      </c>
+      <c r="K25" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59774451138686158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="28">
+        <v>46209</v>
+      </c>
+      <c r="B26" s="29">
+        <v>372801.92</v>
+      </c>
+      <c r="C26" s="30">
+        <v>0</v>
+      </c>
+      <c r="D26" s="30">
+        <f>B26-E26-F26</f>
+        <v>27894.919999999984</v>
+      </c>
+      <c r="E26" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F26" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G26" s="30">
+        <f>SUM(C26:F26)</f>
+        <v>372801.92</v>
+      </c>
+      <c r="H26" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="32">
+        <f t="shared" si="1"/>
+        <v>7.4825043819516768E-2</v>
+      </c>
+      <c r="J26" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32474081678549299</v>
+      </c>
+      <c r="K26" s="32">
+        <f t="shared" si="3"/>
+        <v>0.60043413939499024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="28">
+        <v>46210</v>
+      </c>
+      <c r="B27" s="29">
+        <v>375246.11</v>
+      </c>
+      <c r="C27" s="30">
+        <v>0</v>
+      </c>
+      <c r="D27" s="30">
+        <f>B27-E27-F27</f>
+        <v>30339.109999999986</v>
+      </c>
+      <c r="E27" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F27" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G27" s="30">
+        <f>SUM(C27:F27)</f>
+        <v>375246.11</v>
+      </c>
+      <c r="H27" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="32">
+        <f t="shared" si="1"/>
+        <v>8.0851231209298838E-2</v>
+      </c>
+      <c r="J27" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32262559630531545</v>
+      </c>
+      <c r="K27" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59652317248538567</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="28">
+        <v>46211</v>
+      </c>
+      <c r="B28" s="29">
+        <v>377280.97</v>
+      </c>
+      <c r="C28" s="30">
+        <v>90811</v>
+      </c>
+      <c r="D28" s="30">
+        <v>0</v>
+      </c>
+      <c r="E28" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F28" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G28" s="30">
+        <f>SUM(C28:F28)</f>
+        <v>435718</v>
+      </c>
+      <c r="H28" s="32">
+        <f t="shared" si="0"/>
+        <v>0.20841691185583336</v>
+      </c>
+      <c r="I28" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="32">
+        <f t="shared" si="2"/>
+        <v>0.27784943472613022</v>
+      </c>
+      <c r="K28" s="32">
+        <f t="shared" si="3"/>
+        <v>0.51373365341803645</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="28">
+        <v>46212</v>
+      </c>
+      <c r="B29" s="29">
+        <v>374471.51</v>
+      </c>
+      <c r="C29" s="30">
+        <v>90811</v>
+      </c>
+      <c r="D29" s="30">
+        <v>0</v>
+      </c>
+      <c r="E29" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F29" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G29" s="30">
+        <f>SUM(C29:F29)</f>
+        <v>435718</v>
+      </c>
+      <c r="H29" s="32">
+        <f t="shared" si="0"/>
+        <v>0.20841691185583336</v>
+      </c>
+      <c r="I29" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="32">
+        <f t="shared" si="2"/>
+        <v>0.27784943472613022</v>
+      </c>
+      <c r="K29" s="32">
+        <f t="shared" si="3"/>
+        <v>0.51373365341803645</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="28">
+        <v>46213</v>
+      </c>
+      <c r="B30" s="29">
+        <v>376468.72</v>
+      </c>
+      <c r="C30" s="30">
+        <v>90811</v>
+      </c>
+      <c r="D30" s="30">
+        <v>0</v>
+      </c>
+      <c r="E30" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F30" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G30" s="30">
+        <f>SUM(C30:F30)</f>
+        <v>435718</v>
+      </c>
+      <c r="H30" s="32">
+        <f t="shared" si="0"/>
+        <v>0.20841691185583336</v>
+      </c>
+      <c r="I30" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="32">
+        <f t="shared" si="2"/>
+        <v>0.27784943472613022</v>
+      </c>
+      <c r="K30" s="32">
+        <f t="shared" si="3"/>
+        <v>0.51373365341803645</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="28">
+        <v>46216</v>
+      </c>
+      <c r="B31" s="29">
+        <v>379175.63</v>
+      </c>
+      <c r="C31" s="30">
+        <v>90811</v>
+      </c>
+      <c r="D31" s="30">
+        <v>0</v>
+      </c>
+      <c r="E31" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F31" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G31" s="30">
+        <f>SUM(C31:F31)</f>
+        <v>435718</v>
+      </c>
+      <c r="H31" s="32">
+        <f t="shared" si="0"/>
+        <v>0.20841691185583336</v>
+      </c>
+      <c r="I31" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="32">
+        <f t="shared" si="2"/>
+        <v>0.27784943472613022</v>
+      </c>
+      <c r="K31" s="32">
+        <f t="shared" si="3"/>
+        <v>0.51373365341803645</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="28">
+        <v>46217</v>
+      </c>
+      <c r="B32" s="29">
+        <v>378852.03</v>
+      </c>
+      <c r="C32" s="30">
+        <v>0</v>
+      </c>
+      <c r="D32" s="30">
+        <f>B32-E32-F32</f>
+        <v>33945.030000000028</v>
+      </c>
+      <c r="E32" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F32" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G32" s="30">
+        <f>SUM(C32:F32)</f>
+        <v>378852.03</v>
+      </c>
+      <c r="H32" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="32">
+        <f t="shared" si="1"/>
+        <v>8.9599704665697652E-2</v>
+      </c>
+      <c r="J32" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31955484044786558</v>
+      </c>
+      <c r="K32" s="32">
+        <f t="shared" si="3"/>
+        <v>0.5908454548864368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="28">
+        <v>46218</v>
+      </c>
+      <c r="B33" s="29">
+        <v>374437.1</v>
+      </c>
+      <c r="C33" s="30">
+        <v>0</v>
+      </c>
+      <c r="D33" s="30">
+        <f t="shared" ref="D33:D41" si="4">B33-E33-F33</f>
+        <v>29530.099999999977</v>
+      </c>
+      <c r="E33" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F33" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G33" s="30">
+        <f t="shared" ref="G33:G69" si="5">SUM(C33:F33)</f>
+        <v>374437.1</v>
+      </c>
+      <c r="H33" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="32">
+        <f t="shared" si="1"/>
+        <v>7.8865315429480623E-2</v>
+      </c>
+      <c r="J33" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32332266220414591</v>
+      </c>
+      <c r="K33" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59781202236637343</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="28">
+        <v>46219</v>
+      </c>
+      <c r="B34" s="29">
+        <v>372248.26</v>
+      </c>
+      <c r="C34" s="30">
+        <v>0</v>
+      </c>
+      <c r="D34" s="30">
+        <f t="shared" si="4"/>
+        <v>27341.260000000009</v>
+      </c>
+      <c r="E34" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F34" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G34" s="30">
+        <f t="shared" si="5"/>
+        <v>372248.26</v>
+      </c>
+      <c r="H34" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="32">
+        <f t="shared" si="1"/>
+        <v>7.3448993421755704E-2</v>
+      </c>
+      <c r="J34" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32522381703006481</v>
+      </c>
+      <c r="K34" s="32">
+        <f t="shared" si="3"/>
+        <v>0.60132718954817943</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="28">
+        <v>46220</v>
+      </c>
+      <c r="B35" s="29">
+        <v>376025.4</v>
+      </c>
+      <c r="C35" s="30">
+        <v>0</v>
+      </c>
+      <c r="D35" s="30">
+        <f t="shared" si="4"/>
+        <v>31118.400000000023</v>
+      </c>
+      <c r="E35" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F35" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G35" s="30">
+        <f t="shared" si="5"/>
+        <v>376025.4</v>
+      </c>
+      <c r="H35" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="32">
+        <f t="shared" si="1"/>
+        <v>8.2756111688199838E-2</v>
+      </c>
+      <c r="J35" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32195697418312696</v>
+      </c>
+      <c r="K35" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59528691412867318</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="28">
+        <v>46223</v>
+      </c>
+      <c r="B36" s="29">
+        <v>375009.72</v>
+      </c>
+      <c r="C36" s="30">
+        <v>0</v>
+      </c>
+      <c r="D36" s="30">
+        <f t="shared" si="4"/>
+        <v>30102.719999999972</v>
+      </c>
+      <c r="E36" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F36" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G36" s="30">
+        <f t="shared" si="5"/>
+        <v>375009.72</v>
+      </c>
+      <c r="H36" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="32">
+        <f t="shared" si="1"/>
+        <v>8.0271839353923874E-2</v>
+      </c>
+      <c r="J36" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32282896560654484</v>
+      </c>
+      <c r="K36" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59689919503953126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="28">
+        <v>46224</v>
+      </c>
+      <c r="B37" s="29">
+        <v>375731.28</v>
+      </c>
+      <c r="C37" s="30">
+        <v>0</v>
+      </c>
+      <c r="D37" s="30">
+        <f t="shared" si="4"/>
+        <v>30824.280000000028</v>
+      </c>
+      <c r="E37" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F37" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G37" s="30">
+        <f t="shared" si="5"/>
+        <v>375731.28</v>
+      </c>
+      <c r="H37" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="32">
+        <f t="shared" si="1"/>
+        <v>8.2038099143622076E-2</v>
+      </c>
+      <c r="J37" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32220900000660047</v>
+      </c>
+      <c r="K37" s="32">
+        <f t="shared" si="3"/>
+        <v>0.5957529008497775</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="28">
+        <v>46225</v>
+      </c>
+      <c r="B38" s="29">
+        <v>378174.99</v>
+      </c>
+      <c r="C38" s="30">
+        <v>0</v>
+      </c>
+      <c r="D38" s="30">
+        <f t="shared" si="4"/>
+        <v>33267.989999999991</v>
+      </c>
+      <c r="E38" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F38" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G38" s="30">
+        <f t="shared" si="5"/>
+        <v>378174.99</v>
+      </c>
+      <c r="H38" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="32">
+        <f t="shared" si="1"/>
+        <v>8.79698311091381E-2</v>
+      </c>
+      <c r="J38" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32012693383028845</v>
+      </c>
+      <c r="K38" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59190323506057341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="28">
+        <v>46226</v>
+      </c>
+      <c r="B39" s="29">
+        <v>380362.45</v>
+      </c>
+      <c r="C39" s="30">
+        <v>0</v>
+      </c>
+      <c r="D39" s="30">
+        <f t="shared" si="4"/>
+        <v>35455.450000000012</v>
+      </c>
+      <c r="E39" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F39" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G39" s="30">
+        <f t="shared" si="5"/>
+        <v>380362.45</v>
+      </c>
+      <c r="H39" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="32">
+        <f t="shared" si="1"/>
+        <v>9.3214905940373474E-2</v>
+      </c>
+      <c r="J39" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31828588757907095</v>
+      </c>
+      <c r="K39" s="32">
+        <f t="shared" si="3"/>
+        <v>0.58849920648055554</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="28">
+        <v>46227</v>
+      </c>
+      <c r="B40" s="29">
+        <f>B39-1740-1437</f>
+        <v>377185.45</v>
+      </c>
+      <c r="C40" s="30">
+        <v>0</v>
+      </c>
+      <c r="D40" s="30">
+        <f t="shared" si="4"/>
+        <v>32278.450000000012</v>
+      </c>
+      <c r="E40" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F40" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G40" s="30">
+        <f t="shared" si="5"/>
+        <v>377185.45</v>
+      </c>
+      <c r="H40" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="32">
+        <f t="shared" si="1"/>
+        <v>8.5577134536870422E-2</v>
+      </c>
+      <c r="J40" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32096678172501086</v>
+      </c>
+      <c r="K40" s="32">
+        <f t="shared" si="3"/>
+        <v>0.59345608373811876</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="28">
+        <v>46230</v>
+      </c>
+      <c r="B41" s="29">
+        <f>B40+322+630+1019-936</f>
+        <v>378220.45</v>
+      </c>
+      <c r="C41" s="30">
+        <v>0</v>
+      </c>
+      <c r="D41" s="30">
+        <f t="shared" si="4"/>
+        <v>33313.450000000012</v>
+      </c>
+      <c r="E41" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F41" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G41" s="30">
+        <f t="shared" si="5"/>
+        <v>378220.45</v>
+      </c>
+      <c r="H41" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="32">
+        <f t="shared" si="1"/>
+        <v>8.807945207616355E-2</v>
+      </c>
+      <c r="J41" s="32">
+        <f t="shared" si="2"/>
+        <v>0.32008845634867178</v>
+      </c>
+      <c r="K41" s="32">
+        <f t="shared" si="3"/>
+        <v>0.5918320915751647</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="28">
+        <v>46231</v>
+      </c>
+      <c r="B42" s="29">
+        <f>B41-951+8872.25-771</f>
+        <v>385370.7</v>
+      </c>
+      <c r="C42" s="26">
+        <v>334624</v>
+      </c>
+      <c r="D42" s="27">
+        <v>0</v>
+      </c>
+      <c r="E42" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F42" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G42" s="30">
+        <f t="shared" si="5"/>
+        <v>679531</v>
+      </c>
+      <c r="H42" s="32">
+        <f t="shared" si="0"/>
+        <v>0.49243375210255308</v>
+      </c>
+      <c r="I42" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="32">
+        <f t="shared" si="2"/>
+        <v>0.17815817085607574</v>
+      </c>
+      <c r="K42" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32940807704137121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="28">
+        <v>46232</v>
+      </c>
+      <c r="B43" s="29">
+        <f>B42+567+1830-7720+5262</f>
+        <v>385309.7</v>
+      </c>
+      <c r="C43" s="26">
+        <v>334624</v>
+      </c>
+      <c r="D43" s="27">
+        <v>0</v>
+      </c>
+      <c r="E43" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F43" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G43" s="30">
+        <f t="shared" si="5"/>
+        <v>679531</v>
+      </c>
+      <c r="H43" s="32">
+        <f t="shared" si="0"/>
+        <v>0.49243375210255308</v>
+      </c>
+      <c r="I43" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="32">
+        <f t="shared" si="2"/>
+        <v>0.17815817085607574</v>
+      </c>
+      <c r="K43" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32940807704137121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="28">
+        <v>46233</v>
+      </c>
+      <c r="B44" s="29">
+        <f>B43+2088+840+8949-5393</f>
+        <v>391793.7</v>
+      </c>
+      <c r="C44" s="26">
+        <v>0</v>
+      </c>
+      <c r="D44" s="30">
+        <f t="shared" ref="D44:D52" si="6">B44-E44-F44</f>
+        <v>46886.700000000012</v>
+      </c>
+      <c r="E44" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F44" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G44" s="30">
+        <f t="shared" si="5"/>
+        <v>391793.7</v>
+      </c>
+      <c r="H44" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="32">
+        <f t="shared" si="1"/>
+        <v>0.11967190896637697</v>
+      </c>
+      <c r="J44" s="32">
+        <f t="shared" si="2"/>
+        <v>0.30899935348628627</v>
+      </c>
+      <c r="K44" s="32">
+        <f t="shared" si="3"/>
+        <v>0.57132873754733671</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="28">
+        <v>46234</v>
+      </c>
+      <c r="B45" s="29">
+        <f>B44-480-2572</f>
+        <v>388741.7</v>
+      </c>
+      <c r="C45" s="26">
+        <v>0</v>
+      </c>
+      <c r="D45" s="30">
+        <f t="shared" si="6"/>
+        <v>43834.700000000012</v>
+      </c>
+      <c r="E45" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F45" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G45" s="30">
+        <f t="shared" si="5"/>
+        <v>388741.7</v>
+      </c>
+      <c r="H45" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="32">
+        <f t="shared" si="1"/>
+        <v>0.11276047823014616</v>
+      </c>
+      <c r="J45" s="32">
+        <f t="shared" si="2"/>
+        <v>0.3114252985980151</v>
+      </c>
+      <c r="K45" s="32">
+        <f t="shared" si="3"/>
+        <v>0.57581422317183872</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="28">
+        <v>46237</v>
+      </c>
+      <c r="B46" s="29">
+        <f>B45-3000-427</f>
+        <v>385314.7</v>
+      </c>
+      <c r="C46" s="26">
+        <v>0</v>
+      </c>
+      <c r="D46" s="30">
+        <f t="shared" si="6"/>
+        <v>40407.700000000012</v>
+      </c>
+      <c r="E46" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F46" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G46" s="30">
+        <f t="shared" si="5"/>
+        <v>385314.7</v>
+      </c>
+      <c r="H46" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="32">
+        <f t="shared" si="1"/>
+        <v>0.10486934446051503</v>
+      </c>
+      <c r="J46" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31419512414138362</v>
+      </c>
+      <c r="K46" s="32">
+        <f t="shared" si="3"/>
+        <v>0.58093553139810128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="28">
+        <v>46238</v>
+      </c>
+      <c r="B47" s="29">
+        <f>B46-2340+453</f>
+        <v>383427.7</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="30">
+        <f t="shared" si="6"/>
+        <v>38520.700000000012</v>
+      </c>
+      <c r="E47" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F47" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G47" s="30">
+        <f t="shared" si="5"/>
+        <v>383427.7</v>
+      </c>
+      <c r="H47" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="32">
+        <f t="shared" si="1"/>
+        <v>0.1004640509801457</v>
+      </c>
+      <c r="J47" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31574140313806226</v>
+      </c>
+      <c r="K47" s="32">
+        <f t="shared" si="3"/>
+        <v>0.58379454588179203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="28">
+        <v>46239</v>
+      </c>
+      <c r="B48" s="29">
+        <f>B47+1500-3275</f>
+        <v>381652.7</v>
+      </c>
+      <c r="C48" s="26">
+        <v>0</v>
+      </c>
+      <c r="D48" s="30">
+        <f t="shared" si="6"/>
+        <v>36745.700000000012</v>
+      </c>
+      <c r="E48" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F48" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G48" s="30">
+        <f t="shared" si="5"/>
+        <v>381652.7</v>
+      </c>
+      <c r="H48" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="32">
+        <f t="shared" si="1"/>
+        <v>9.6280466507901064E-2</v>
+      </c>
+      <c r="J48" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31720986121675543</v>
+      </c>
+      <c r="K48" s="32">
+        <f t="shared" si="3"/>
+        <v>0.58650967227534356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="28">
+        <v>46240</v>
+      </c>
+      <c r="B49" s="29">
+        <f>B48+2550-1004</f>
+        <v>383198.7</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="30">
+        <f t="shared" si="6"/>
+        <v>38291.700000000012</v>
+      </c>
+      <c r="E49" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F49" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G49" s="30">
+        <f t="shared" si="5"/>
+        <v>383198.7</v>
+      </c>
+      <c r="H49" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="32">
+        <f t="shared" si="1"/>
+        <v>9.9926487224513055E-2</v>
+      </c>
+      <c r="J49" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31593009057702959</v>
+      </c>
+      <c r="K49" s="32">
+        <f t="shared" si="3"/>
+        <v>0.58414342219845738</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="28">
+        <v>46241</v>
+      </c>
+      <c r="B50" s="29">
+        <f>B49+840+738</f>
+        <v>384776.7</v>
+      </c>
+      <c r="C50" s="26">
+        <v>0</v>
+      </c>
+      <c r="D50" s="30">
+        <f t="shared" si="6"/>
+        <v>39869.700000000012</v>
+      </c>
+      <c r="E50" s="30">
+        <v>121064</v>
+      </c>
+      <c r="F50" s="30">
+        <v>223843</v>
+      </c>
+      <c r="G50" s="30">
+        <f t="shared" si="5"/>
+        <v>384776.7</v>
+      </c>
+      <c r="H50" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="32">
+        <f t="shared" si="1"/>
+        <v>0.10361776063883289</v>
+      </c>
+      <c r="J50" s="32">
+        <f t="shared" si="2"/>
+        <v>0.31463443602484248</v>
+      </c>
+      <c r="K50" s="32">
+        <f t="shared" si="3"/>
+        <v>0.5817478033363247</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="28">
+        <v>46244</v>
+      </c>
+      <c r="B51" s="29">
+        <f>B50+41+540-398-50</f>
+        <v>384909.7</v>
+      </c>
+      <c r="C51" s="26">
+        <v>0</v>
+      </c>
+      <c r="D51" s="30">
+        <f t="shared" si="6"/>
+        <v>24412.700000000012</v>
+      </c>
+      <c r="E51" s="27">
+        <f>185382+121064</f>
+        <v>306446</v>
+      </c>
+      <c r="F51" s="27">
+        <v>54051</v>
+      </c>
+      <c r="G51" s="30">
+        <f t="shared" si="5"/>
+        <v>384909.7</v>
+      </c>
+      <c r="H51" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="32">
+        <f t="shared" si="1"/>
+        <v>6.342448631458239E-2</v>
+      </c>
+      <c r="J51" s="32">
+        <f t="shared" si="2"/>
+        <v>0.79615036981401088</v>
+      </c>
+      <c r="K51" s="32">
+        <f t="shared" si="3"/>
+        <v>0.14042514387140673</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="28">
+        <v>46245</v>
+      </c>
+      <c r="B52" s="29">
+        <f>B51-40-2340-824-1009-1010</f>
+        <v>379686.7</v>
+      </c>
+      <c r="C52" s="26">
+        <v>0</v>
+      </c>
+      <c r="D52" s="30">
+        <f t="shared" si="6"/>
+        <v>19189.700000000012</v>
+      </c>
+      <c r="E52" s="27">
+        <f>185382+121064</f>
+        <v>306446</v>
+      </c>
+      <c r="F52" s="27">
+        <v>54051</v>
+      </c>
+      <c r="G52" s="30">
+        <f t="shared" si="5"/>
+        <v>379686.7</v>
+      </c>
+      <c r="H52" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="32">
+        <f t="shared" si="1"/>
+        <v>5.0540880151977961E-2</v>
+      </c>
+      <c r="J52" s="32">
+        <f t="shared" si="2"/>
+        <v>0.80710227669286283</v>
+      </c>
+      <c r="K52" s="32">
+        <f t="shared" si="3"/>
+        <v>0.14235684315515923</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="28">
+        <v>46246</v>
+      </c>
+      <c r="B53" s="29">
+        <f>B52-205-1710-410+2950-212+6683-2764-240</f>
+        <v>383778.7</v>
+      </c>
+      <c r="C53" s="26">
+        <v>0</v>
+      </c>
+      <c r="D53" s="27">
+        <v>0</v>
+      </c>
+      <c r="E53" s="27">
+        <f>E52+154290</f>
+        <v>460736</v>
+      </c>
+      <c r="F53" s="27">
+        <f>F52+164620</f>
+        <v>218671</v>
+      </c>
+      <c r="G53" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H53" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K53" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="28">
+        <v>46247</v>
+      </c>
+      <c r="B54" s="29">
+        <f>B53-95-1110+960-1500-1040+875+120</f>
+        <v>381988.7</v>
+      </c>
+      <c r="C54" s="26">
+        <v>0</v>
+      </c>
+      <c r="D54" s="27">
+        <v>0</v>
+      </c>
+      <c r="E54" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F54" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G54" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H54" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K54" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="28">
+        <v>46248</v>
+      </c>
+      <c r="B55" s="29">
+        <f>B54+25-540-1100-7593+350-1166-690</f>
+        <v>371274.7</v>
+      </c>
+      <c r="C55" s="26">
+        <v>0</v>
+      </c>
+      <c r="D55" s="27">
+        <v>0</v>
+      </c>
+      <c r="E55" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F55" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G55" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H55" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K55" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="28">
+        <v>46251</v>
+      </c>
+      <c r="B56" s="29">
+        <f>B55+95+1620-1380+725+796+220</f>
+        <v>373350.7</v>
+      </c>
+      <c r="C56" s="26">
+        <v>0</v>
+      </c>
+      <c r="D56" s="27">
+        <v>0</v>
+      </c>
+      <c r="E56" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F56" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G56" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H56" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K56" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="28">
+        <v>46252</v>
+      </c>
+      <c r="B57" s="29">
+        <f>B56+590+1620+620+1095+826+2690</f>
+        <v>380791.7</v>
+      </c>
+      <c r="C57" s="26">
+        <v>0</v>
+      </c>
+      <c r="D57" s="27">
+        <v>0</v>
+      </c>
+      <c r="E57" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F57" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G57" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H57" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K57" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="28">
+        <v>46253</v>
+      </c>
+      <c r="B58" s="29">
+        <f>B57-195+5550+2720-300-3504+1730</f>
+        <v>386792.7</v>
+      </c>
+      <c r="C58" s="26">
+        <v>0</v>
+      </c>
+      <c r="D58" s="27">
+        <v>0</v>
+      </c>
+      <c r="E58" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F58" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G58" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H58" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K58" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="28">
+        <v>46254</v>
+      </c>
+      <c r="B59" s="29">
+        <f>B58+155+870-1360+1107.05+1330+1165.8+1267.76</f>
+        <v>391328.31</v>
+      </c>
+      <c r="C59" s="26">
+        <v>0</v>
+      </c>
+      <c r="D59" s="27">
+        <v>0</v>
+      </c>
+      <c r="E59" s="27">
+        <v>460736</v>
+      </c>
+      <c r="F59" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G59" s="30">
+        <f t="shared" si="5"/>
+        <v>679407</v>
+      </c>
+      <c r="H59" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="32">
+        <f t="shared" si="2"/>
+        <v>0.67814432291689664</v>
+      </c>
+      <c r="K59" s="32">
+        <f t="shared" si="3"/>
+        <v>0.32185567708310336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="28">
+        <v>46255</v>
+      </c>
+      <c r="B60" s="29">
+        <f>B59-445-450-580+585-575-2123</f>
+        <v>387740.31</v>
+      </c>
+      <c r="C60" s="26">
+        <v>0</v>
+      </c>
+      <c r="D60" s="27">
+        <v>0</v>
+      </c>
+      <c r="E60" s="27">
+        <v>775877</v>
+      </c>
+      <c r="F60" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G60" s="30">
+        <f t="shared" si="5"/>
+        <v>994548</v>
+      </c>
+      <c r="H60" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="32">
+        <f t="shared" si="2"/>
+        <v>0.78013027023331205</v>
+      </c>
+      <c r="K60" s="32">
+        <f t="shared" si="3"/>
+        <v>0.21986972976668798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="28">
+        <v>46258</v>
+      </c>
+      <c r="B61" s="29">
+        <f>B60+105+300+3482+1020+1095+430-311</f>
+        <v>393861.31</v>
+      </c>
+      <c r="C61" s="26">
+        <v>0</v>
+      </c>
+      <c r="D61" s="27">
+        <v>0</v>
+      </c>
+      <c r="E61" s="27">
+        <v>480842</v>
+      </c>
+      <c r="F61" s="27">
+        <v>218671</v>
+      </c>
+      <c r="G61" s="30">
+        <f t="shared" si="5"/>
+        <v>699513</v>
+      </c>
+      <c r="H61" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="32">
+        <f t="shared" si="2"/>
+        <v>0.6873953736385171</v>
+      </c>
+      <c r="K61" s="32">
+        <f t="shared" si="3"/>
+        <v>0.3126046263614829</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="28">
+        <v>46259</v>
+      </c>
+      <c r="B62" s="29">
+        <f>B61-390+1290+906-402+1017</f>
+        <v>396282.31</v>
+      </c>
+      <c r="C62" s="26">
+        <v>0</v>
+      </c>
+      <c r="D62" s="30">
+        <f t="shared" ref="D62:D65" si="7">B62-E62-F62</f>
+        <v>341611.31</v>
+      </c>
+      <c r="E62" s="27">
+        <v>0</v>
+      </c>
+      <c r="F62" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G62" s="30">
+        <f t="shared" si="5"/>
+        <v>396282.31</v>
+      </c>
+      <c r="H62" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="32">
+        <f t="shared" si="1"/>
+        <v>0.86204027123996529</v>
+      </c>
+      <c r="J62" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="32">
+        <f t="shared" si="3"/>
+        <v>0.13795972876003473</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="28">
+        <v>46260</v>
+      </c>
+      <c r="B63" s="29">
+        <f>B62+270-750</f>
+        <v>395802.31</v>
+      </c>
+      <c r="C63" s="26">
+        <v>0</v>
+      </c>
+      <c r="D63" s="30">
+        <f t="shared" si="7"/>
+        <v>341131.31</v>
+      </c>
+      <c r="E63" s="27">
+        <v>0</v>
+      </c>
+      <c r="F63" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G63" s="30">
+        <f t="shared" si="5"/>
+        <v>395802.31</v>
+      </c>
+      <c r="H63" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="32">
+        <f t="shared" si="1"/>
+        <v>0.86187296380357159</v>
+      </c>
+      <c r="J63" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="32">
+        <f t="shared" si="3"/>
+        <v>0.13812703619642847</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="28">
+        <v>46261</v>
+      </c>
+      <c r="B64" s="29">
+        <f>B63+125+690</f>
+        <v>396617.31</v>
+      </c>
+      <c r="C64" s="26">
+        <v>0</v>
+      </c>
+      <c r="D64" s="30">
+        <f t="shared" si="7"/>
+        <v>341946.31</v>
+      </c>
+      <c r="E64" s="27">
+        <v>0</v>
+      </c>
+      <c r="F64" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G64" s="30">
+        <f t="shared" si="5"/>
+        <v>396617.31</v>
+      </c>
+      <c r="H64" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="32">
+        <f t="shared" si="1"/>
+        <v>0.8621567979471193</v>
+      </c>
+      <c r="J64" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="32">
+        <f t="shared" si="3"/>
+        <v>0.13784320205288064</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="28">
+        <v>46262</v>
+      </c>
+      <c r="B65" s="29">
+        <f>B64+300</f>
+        <v>396917.31</v>
+      </c>
+      <c r="C65" s="26">
+        <v>0</v>
+      </c>
+      <c r="D65" s="30">
+        <f t="shared" si="7"/>
+        <v>342246.31</v>
+      </c>
+      <c r="E65" s="27">
+        <v>0</v>
+      </c>
+      <c r="F65" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G65" s="30">
+        <f t="shared" si="5"/>
+        <v>396917.31</v>
+      </c>
+      <c r="H65" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="32">
+        <f t="shared" si="1"/>
+        <v>0.86226098327634038</v>
+      </c>
+      <c r="J65" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="32">
+        <f t="shared" si="3"/>
+        <v>0.13773901672365965</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="28">
+        <v>46265</v>
+      </c>
+      <c r="B66" s="29">
+        <f>B65+135+2220-2.59</f>
+        <v>399269.72</v>
+      </c>
+      <c r="C66" s="26">
+        <v>59799</v>
+      </c>
+      <c r="D66" s="30">
+        <v>0</v>
+      </c>
+      <c r="E66" s="27">
+        <v>0</v>
+      </c>
+      <c r="F66" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G66" s="30">
+        <f t="shared" si="5"/>
+        <v>114470</v>
+      </c>
+      <c r="H66" s="32">
+        <f t="shared" si="0"/>
+        <v>0.52239888180309246</v>
+      </c>
+      <c r="I66" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K66" s="32">
+        <f t="shared" si="3"/>
+        <v>0.47760111819690748</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="28">
+        <v>46266</v>
+      </c>
+      <c r="B67" s="29">
+        <f>B66+480-562+1405-1361-623+1800+428</f>
+        <v>400836.72</v>
+      </c>
+      <c r="C67" s="26">
+        <v>871422</v>
+      </c>
+      <c r="D67" s="27">
+        <v>0</v>
+      </c>
+      <c r="E67" s="27">
+        <v>0</v>
+      </c>
+      <c r="F67" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G67" s="30">
+        <f t="shared" si="5"/>
+        <v>926093</v>
+      </c>
+      <c r="H67" s="32">
+        <f t="shared" ref="H67:H70" si="8">C67/G67</f>
+        <v>0.94096597209999433</v>
+      </c>
+      <c r="I67" s="32">
+        <f t="shared" ref="I67:I70" si="9">D67/G67</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="32">
+        <f t="shared" ref="J67:J70" si="10">E67/G67</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="32">
+        <f t="shared" ref="K67:K70" si="11">F67/G67</f>
+        <v>5.9034027900005726E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="28">
+        <v>46267</v>
+      </c>
+      <c r="B68" s="29">
+        <f>B67-274+71-569+1738+320</f>
+        <v>402122.72</v>
+      </c>
+      <c r="C68" s="26">
+        <f>C67-132000</f>
+        <v>739422</v>
+      </c>
+      <c r="D68" s="27">
+        <v>0</v>
+      </c>
+      <c r="E68" s="27">
+        <v>0</v>
+      </c>
+      <c r="F68" s="27">
+        <v>54671</v>
+      </c>
+      <c r="G68" s="30">
+        <f t="shared" si="5"/>
+        <v>794093</v>
+      </c>
+      <c r="H68" s="32">
+        <f t="shared" si="8"/>
+        <v>0.93115290022705144</v>
+      </c>
+      <c r="I68" s="32">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="32">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="32">
+        <f t="shared" si="11"/>
+        <v>6.8847099772948506E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="28">
+        <v>46268</v>
+      </c>
+      <c r="B69" s="29">
+        <f>B68-274+71-569+1738+320</f>
+        <v>403408.72</v>
+      </c>
+      <c r="C69" s="26">
+        <v>101060</v>
+      </c>
+      <c r="D69" s="30">
+        <f>B69-C69</f>
+        <v>302348.71999999997</v>
+      </c>
+      <c r="E69" s="27">
+        <v>0</v>
+      </c>
+      <c r="F69" s="27">
+        <v>0</v>
+      </c>
+      <c r="G69" s="30">
+        <f t="shared" si="5"/>
+        <v>403408.72</v>
+      </c>
+      <c r="H69" s="32">
+        <f t="shared" si="8"/>
+        <v>0.25051515991027662</v>
+      </c>
+      <c r="I69" s="32">
+        <f t="shared" si="9"/>
+        <v>0.74948484008972338</v>
+      </c>
+      <c r="J69" s="32">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="32">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="28">
+        <v>46269</v>
+      </c>
+      <c r="H70" s="32" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I70" s="32" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J70" s="32" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K70" s="32" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1048543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1048543" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE0BED5-5DF6-6A45-9BB0-BC4AFAA85A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A8418E-C92C-7E42-BDA1-775D05FEF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="-42240" windowWidth="37340" windowHeight="41180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6860" yWindow="-38360" windowWidth="45300" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
     <sheet name="Daily PnL" sheetId="3" r:id="rId2"/>
-    <sheet name="exposure" sheetId="4" r:id="rId3"/>
+    <sheet name="exposure" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -455,7 +455,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -600,6 +600,15 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -609,6 +618,10 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -620,6 +633,9 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -639,26 +655,12 @@
     <xf numFmtId="3" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1719,11 +1721,11 @@
       </c>
       <c r="C12" s="1">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>54</v>
@@ -1900,7 +1902,7 @@
       <c r="S14" s="4">
         <v>-16354</v>
       </c>
-      <c r="T14" s="20">
+      <c r="T14" s="25">
         <v>-16354</v>
       </c>
     </row>
@@ -2167,11 +2169,11 @@
       </c>
       <c r="C19" s="1">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>70</v>
@@ -2232,11 +2234,11 @@
       </c>
       <c r="C20" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>73</v>
@@ -2616,11 +2618,11 @@
       </c>
       <c r="C26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" ref="D26:D32" ca="1" si="5">C26-B26</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>88</v>
@@ -2923,7 +2925,7 @@
       <c r="S30" s="4">
         <v>-642</v>
       </c>
-      <c r="T30" s="20">
+      <c r="T30" s="25">
         <v>-642</v>
       </c>
     </row>
@@ -3005,56 +3007,56 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="21" t="s">
+      <c r="I32" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="K32" s="21">
-        <v>-4000</v>
-      </c>
-      <c r="L32" s="21">
+      <c r="K32" s="28">
+        <v>-2000</v>
+      </c>
+      <c r="L32" s="28">
         <v>50.406999999999996</v>
       </c>
-      <c r="M32" s="21" t="s">
+      <c r="M32" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="N32" s="21">
+      <c r="N32" s="28">
         <v>50.59</v>
       </c>
-      <c r="O32" s="23">
-        <v>201080</v>
-      </c>
-      <c r="P32" s="21">
+      <c r="O32" s="30">
+        <v>100080</v>
+      </c>
+      <c r="P32" s="28">
         <v>1.21</v>
       </c>
-      <c r="Q32" s="21" t="s">
+      <c r="Q32" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="R32" s="24" t="s">
+      <c r="R32" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="S32" s="21" t="s">
+      <c r="S32" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="T32" s="23" t="s">
+      <c r="T32" s="30" t="s">
         <v>72</v>
       </c>
       <c r="U32" s="4">
-        <v>-366</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.2">
@@ -3080,12 +3082,12 @@
       <c r="H35" s="11"/>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="24" t="s">
         <v>103</v>
       </c>
       <c r="E36" s="7">
         <f ca="1">AVERAGE(D2:D24)</f>
-        <v>11.347826086956522</v>
+        <v>11.478260869565217</v>
       </c>
       <c r="F36" s="11"/>
       <c r="H36" s="11"/>
@@ -3095,16 +3097,16 @@
       </c>
       <c r="U36" s="16">
         <f>SUM(U2:U32)</f>
-        <v>-366</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="E37" s="7">
         <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
-        <v>6.5909090909090908</v>
+        <v>6.6818181818181817</v>
       </c>
       <c r="F37" s="11"/>
       <c r="T37" s="4" t="s">
@@ -3124,7 +3126,7 @@
       <c r="F39" s="11"/>
       <c r="T39" s="16">
         <f>T36+U36</f>
-        <v>67609.47</v>
+        <v>67879.47</v>
       </c>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.2">
@@ -3148,9 +3150,9 @@
       </c>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="T45" s="18">
+      <c r="T45" s="23">
         <f>T39/T42</f>
-        <v>0.20303144144144145</v>
+        <v>0.20384225225225225</v>
       </c>
     </row>
   </sheetData>
@@ -3163,1070 +3165,1085 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.5" style="35"/>
-    <col min="7" max="7" width="15.33203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="35" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.5" style="35"/>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="36"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="37">
+      <c r="A2" s="18">
         <v>46184</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="20">
         <v>333455.63</v>
       </c>
-      <c r="C2" s="33">
-        <v>0</v>
-      </c>
-      <c r="D2" s="34">
-        <v>0</v>
-      </c>
-      <c r="G2" s="36" t="s">
+      <c r="C2" s="21">
+        <v>0</v>
+      </c>
+      <c r="D2" s="26">
+        <v>0</v>
+      </c>
+      <c r="G2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="38">
-        <f>AVERAGE(C3:C61)</f>
-        <v>1163.848983050847</v>
+      <c r="H2" s="19">
+        <f>AVERAGE(C3:C62)</f>
+        <v>1236.5848333333329</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="37">
+      <c r="A3" s="18">
         <v>46185</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="20">
         <v>350216.98</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="20">
         <f>B3-B2</f>
         <v>16761.349999999977</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="26">
         <f>C3/B2</f>
         <v>5.0265608051062075E-2</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="38">
-        <f>_xlfn.STDEV.S(C3:C61)</f>
-        <v>4533.8438044752129</v>
+      <c r="H3" s="19">
+        <f>_xlfn.STDEV.S(C3:C62)</f>
+        <v>4530.4268575400629</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="37">
+      <c r="A4" s="18">
         <v>46188</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="20">
         <v>356930.64</v>
       </c>
-      <c r="C4" s="29">
-        <f t="shared" ref="C4:C61" si="0">B4-B3</f>
+      <c r="C4" s="20">
+        <f t="shared" ref="C4:C62" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
-      <c r="D4" s="34">
-        <f t="shared" ref="D4:D61" si="1">C4/B3</f>
+      <c r="D4" s="26">
+        <f t="shared" ref="D4:D62" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="39">
+      <c r="H4" s="22">
         <f>(H2/H3)*SQRT(252)</f>
-        <v>4.0750256589102625</v>
+        <v>4.33296382029316</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="37">
+      <c r="A5" s="18">
         <v>46189</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="20">
         <v>351815.49</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="20">
         <f t="shared" si="0"/>
         <v>-5115.1500000000233</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="26">
         <f t="shared" si="1"/>
         <v>-1.4330935556555255E-2</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="40">
-        <f>_xlfn.STDEV.S(D2:D61)*SQRT(252)</f>
-        <v>0.19756878191419452</v>
+      <c r="H5" s="27">
+        <f>_xlfn.STDEV.S(D2:D62)*SQRT(252)</f>
+        <v>0.1970845339269621</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="18">
         <v>46190</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="20">
         <v>358486.01</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="20">
         <f t="shared" si="0"/>
         <v>6670.5200000000186</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="26">
         <f t="shared" si="1"/>
         <v>1.8960279435109632E-2</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="40" cm="1">
-        <f t="array" ref="H6">PRODUCT(1+D2:D61)-1</f>
-        <v>0.20592571791335645</v>
+      <c r="H6" s="27" cm="1">
+        <f t="array" ref="H6">PRODUCT(1+D2:D62)-1</f>
+        <v>0.22250363564112119</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="37">
+      <c r="A7" s="18">
         <v>46191</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="20">
         <v>360758.08</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="20">
         <f t="shared" si="0"/>
         <v>2272.070000000007</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="26">
         <f t="shared" si="1"/>
         <v>6.3379600224845786E-3</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="40" cm="1">
-        <f t="array" ref="H7">PRODUCT(1+D2:D61)^(252/COUNT(D2:D61))-1</f>
-        <v>1.195565207449981</v>
+      <c r="H7" s="27" cm="1">
+        <f t="array" ref="H7">PRODUCT(1+D2:D62)^(252/COUNT(D2:D62))-1</f>
+        <v>1.2932071188156953</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="18">
         <v>46192</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="20">
         <v>360243.39</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="20">
         <f t="shared" si="0"/>
         <v>-514.69000000000233</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="26">
         <f t="shared" si="1"/>
         <v>-1.4266901520265389E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="37">
+      <c r="A9" s="18">
         <v>46195</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="20">
         <v>351346.76</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="20">
         <f t="shared" si="0"/>
         <v>-8896.6300000000047</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="26">
         <f t="shared" si="1"/>
         <v>-2.4696164445931968E-2</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="18">
         <v>46196</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="20">
         <v>352224.24</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="20">
         <f t="shared" si="0"/>
         <v>877.47999999998137</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="26">
         <f t="shared" si="1"/>
         <v>2.4974757131671892E-3</v>
       </c>
-      <c r="G10" s="36"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="37">
+      <c r="A11" s="18">
         <v>46197</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="20">
         <v>347929.11</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="20">
         <f t="shared" si="0"/>
         <v>-4295.1300000000047</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="26">
         <f t="shared" si="1"/>
         <v>-1.219430553672287E-2</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
+      <c r="A12" s="18">
         <v>46198</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="20">
         <v>349277.46</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="20">
         <f t="shared" si="0"/>
         <v>1348.3500000000349</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="26">
         <f t="shared" si="1"/>
         <v>3.8753584027505917E-3</v>
       </c>
-      <c r="G12" s="36"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="37">
+      <c r="A13" s="18">
         <v>46199</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="20">
         <v>351579.06</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="20">
         <f t="shared" si="0"/>
         <v>2301.5999999999767</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="26">
         <f t="shared" si="1"/>
         <v>6.5896035776255831E-3</v>
       </c>
-      <c r="G13" s="36"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="18">
         <v>46202</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="20">
         <v>359661.12</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="20">
         <f t="shared" si="0"/>
         <v>8082.0599999999977</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="26">
         <f t="shared" si="1"/>
         <v>2.2987887845197601E-2</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="37">
+      <c r="A15" s="18">
         <v>46203</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="20">
         <v>361447.55</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="20">
         <f t="shared" si="0"/>
         <v>1786.429999999993</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="26">
         <f t="shared" si="1"/>
         <v>4.9669811404690978E-3</v>
       </c>
-      <c r="G15" s="36"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="37">
+      <c r="A16" s="18">
         <v>46204</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="20">
         <v>363377.97</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="20">
         <f t="shared" si="0"/>
         <v>1930.4199999999837</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="26">
         <f t="shared" si="1"/>
         <v>5.3408025590434456E-3</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="37">
+      <c r="A17" s="18">
         <v>46205</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="20">
         <v>374651</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="20">
         <f t="shared" si="0"/>
         <v>11273.030000000028</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="26">
         <f t="shared" si="1"/>
         <v>3.1022876813363312E-2</v>
       </c>
-      <c r="G17" s="36"/>
+      <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="37">
+      <c r="A18" s="18">
         <v>46206</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="20">
         <v>374479.39</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="20">
         <f t="shared" si="0"/>
         <v>-171.60999999998603</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="26">
         <f t="shared" si="1"/>
         <v>-4.5805296128926929E-4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="37">
+      <c r="A19" s="18">
         <v>46209</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="20">
         <v>372801.92</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="20">
         <f t="shared" si="0"/>
         <v>-1677.4700000000303</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="26">
         <f t="shared" si="1"/>
         <v>-4.4794721546625839E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="37">
+      <c r="A20" s="18">
         <v>46210</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="20">
         <v>375246.11</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="20">
         <f t="shared" si="0"/>
         <v>2444.1900000000023</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="26">
         <f t="shared" si="1"/>
         <v>6.5562698818718594E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="37">
+      <c r="A21" s="18">
         <v>46211</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="20">
         <v>377280.97</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="20">
         <f t="shared" si="0"/>
         <v>2034.859999999986</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="26">
         <f t="shared" si="1"/>
         <v>5.4227344288791859E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="37">
+      <c r="A22" s="18">
         <v>46212</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="20">
         <v>374471.51</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="20">
         <f t="shared" si="0"/>
         <v>-2809.4599999999627</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="26">
         <f t="shared" si="1"/>
         <v>-7.4465987510580322E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="37">
+      <c r="A23" s="18">
         <v>46213</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="20">
         <v>376468.72</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="20">
         <f t="shared" si="0"/>
         <v>1997.2099999999627</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="26">
         <f t="shared" si="1"/>
         <v>5.3334097432404474E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="37">
+      <c r="A24" s="18">
         <v>46216</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="20">
         <v>379175.63</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="20">
         <f t="shared" si="0"/>
         <v>2706.9100000000326</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="26">
         <f t="shared" si="1"/>
         <v>7.190265369191982E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="37">
+      <c r="A25" s="18">
         <v>46217</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="20">
         <v>378852.03</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="20">
         <f t="shared" si="0"/>
         <v>-323.59999999997672</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="26">
         <f t="shared" si="1"/>
         <v>-8.5343037473156356E-4</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="37">
+      <c r="A26" s="18">
         <v>46218</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="20">
         <v>374437.1</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="20">
         <f t="shared" si="0"/>
         <v>-4414.9300000000512</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="26">
         <f t="shared" si="1"/>
         <v>-1.1653441582456483E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="37">
+      <c r="A27" s="18">
         <v>46219</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="20">
         <v>372248.26</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="20">
         <f t="shared" si="0"/>
         <v>-2188.8399999999674</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="26">
         <f t="shared" si="1"/>
         <v>-5.8456814241963934E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="37">
+      <c r="A28" s="18">
         <v>46220</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="20">
         <v>376025.4</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="20">
         <f t="shared" si="0"/>
         <v>3777.140000000014</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="26">
         <f t="shared" si="1"/>
         <v>1.0146830504996891E-2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="37">
+      <c r="A29" s="18">
         <v>46223</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="20">
         <v>375009.72</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="20">
         <f t="shared" si="0"/>
         <v>-1015.6800000000512</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="26">
         <f t="shared" si="1"/>
         <v>-2.7010941282159429E-3</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="37">
+      <c r="A30" s="18">
         <v>46224</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="20">
         <v>375731.28</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="20">
         <f t="shared" si="0"/>
         <v>721.56000000005588</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="26">
         <f t="shared" si="1"/>
         <v>1.9241101270656557E-3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="37">
+      <c r="A31" s="18">
         <v>46225</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="20">
         <v>378174.99</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="20">
         <f t="shared" si="0"/>
         <v>2443.7099999999627</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="26">
         <f t="shared" si="1"/>
         <v>6.5038769196963386E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="37">
+      <c r="A32" s="18">
         <v>46226</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="20">
         <v>380362.45</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="20">
         <f t="shared" si="0"/>
         <v>2187.460000000021</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="26">
         <f t="shared" si="1"/>
         <v>5.7842534748266169E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="37">
+      <c r="A33" s="18">
         <v>46227</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="20">
         <f>B32-1740-1437</f>
         <v>377185.45</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="20">
         <f t="shared" si="0"/>
         <v>-3177</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="26">
         <f t="shared" si="1"/>
         <v>-8.3525595126437945E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="37">
+      <c r="A34" s="18">
         <v>46230</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="20">
         <f>B33+322+630+1019-936</f>
         <v>378220.45</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="20">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="26">
         <f t="shared" si="1"/>
         <v>2.7440082855794143E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="37">
+      <c r="A35" s="18">
         <v>46231</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="20">
         <f>B34-951+8872.25-771</f>
         <v>385370.7</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="20">
         <f t="shared" si="0"/>
         <v>7150.25</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="26">
         <f t="shared" si="1"/>
         <v>1.8904979886730081E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="37">
+      <c r="A36" s="18">
         <v>46232</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="20">
         <f>B35+567+1830-7720+5262</f>
         <v>385309.7</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="20">
         <f t="shared" si="0"/>
         <v>-61</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="26">
         <f t="shared" si="1"/>
         <v>-1.5828914860418811E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="37">
+      <c r="A37" s="18">
         <v>46233</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="20">
         <f>B36+2088+840+8949-5393</f>
         <v>391793.7</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="20">
         <f t="shared" si="0"/>
         <v>6484</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="26">
         <f t="shared" si="1"/>
         <v>1.6828021718633089E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="37">
+      <c r="A38" s="18">
         <v>46234</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="20">
         <f>B37-480-2572</f>
         <v>388741.7</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="20">
         <f t="shared" si="0"/>
         <v>-3052</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="26">
         <f t="shared" si="1"/>
         <v>-7.7898138739852119E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="37">
+      <c r="A39" s="18">
         <v>46237</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="20">
         <f>B38-3000-427</f>
         <v>385314.7</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="20">
         <f t="shared" si="0"/>
         <v>-3427</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="26">
         <f t="shared" si="1"/>
         <v>-8.8156223013893288E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="37">
+      <c r="A40" s="18">
         <v>46238</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="20">
         <f>B39-2340+453</f>
         <v>383427.7</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="20">
         <f t="shared" si="0"/>
         <v>-1887</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="26">
         <f t="shared" si="1"/>
         <v>-4.8972956391230334E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="37">
+      <c r="A41" s="18">
         <v>46239</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="20">
         <f>B40+1500-3275</f>
         <v>381652.7</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="20">
         <f t="shared" si="0"/>
         <v>-1775</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="26">
         <f t="shared" si="1"/>
         <v>-4.6292951709018416E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="37">
+      <c r="A42" s="18">
         <v>46240</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="20">
         <f>B41+2550-1004</f>
         <v>383198.7</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="20">
         <f t="shared" si="0"/>
         <v>1546</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="26">
         <f t="shared" si="1"/>
         <v>4.0508032564685117E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="37">
+      <c r="A43" s="18">
         <v>46241</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="20">
         <f>B42+840+738</f>
         <v>384776.7</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="20">
         <f t="shared" si="0"/>
         <v>1578</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="26">
         <f t="shared" si="1"/>
         <v>4.1179680411233127E-3</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="37">
+      <c r="A44" s="18">
         <v>46244</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="20">
         <f>B43+41+540-398-50</f>
         <v>384909.7</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="20">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="26">
         <f t="shared" si="1"/>
         <v>3.4565502536925964E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="37">
+      <c r="A45" s="18">
         <v>46245</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="20">
         <f>B44-40-2340-824-1009-1010</f>
         <v>379686.7</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="20">
         <f t="shared" si="0"/>
         <v>-5223</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="26">
         <f t="shared" si="1"/>
         <v>-1.3569416411173841E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="37">
+      <c r="A46" s="18">
         <v>46246</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="20">
         <f>B45-205-1710-410+2950-212+6683-2764-240</f>
         <v>383778.7</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="20">
         <f t="shared" si="0"/>
         <v>4092</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="26">
         <f t="shared" si="1"/>
         <v>1.0777306658358061E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="37">
+      <c r="A47" s="18">
         <v>46247</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="20">
         <f>B46-95-1110+960-1500-1040+875+120</f>
         <v>381988.7</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="20">
         <f t="shared" si="0"/>
         <v>-1790</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="26">
         <f t="shared" si="1"/>
         <v>-4.6641462905575529E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="37">
+      <c r="A48" s="18">
         <v>46248</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="20">
         <f>B47+25-540-1100-7593+350-1166-690</f>
         <v>371274.7</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="20">
         <f t="shared" si="0"/>
         <v>-10714</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="26">
         <f t="shared" si="1"/>
         <v>-2.8047950109518945E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="37">
+      <c r="A49" s="18">
         <v>46251</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="20">
         <f>B48+95+1620-1380+725+796+220</f>
         <v>373350.7</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="20">
         <f t="shared" si="0"/>
         <v>2076</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="26">
         <f t="shared" si="1"/>
         <v>5.5915471751778398E-3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="37">
+      <c r="A50" s="18">
         <v>46252</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="20">
         <f>B49+590+1620+620+1095+826+2690</f>
         <v>380791.7</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="20">
         <f t="shared" si="0"/>
         <v>7441</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="26">
         <f t="shared" si="1"/>
         <v>1.9930322884087266E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="37">
+      <c r="A51" s="18">
         <v>46253</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="20">
         <f>B50-195+5550+2720-300-3504+1730</f>
         <v>386792.7</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="20">
         <f t="shared" si="0"/>
         <v>6001</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="26">
         <f t="shared" si="1"/>
         <v>1.5759272063965678E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="37">
+      <c r="A52" s="18">
         <v>46254</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="20">
         <f>B51+155+870-1360+1107.05+1330+1165.8+1267.76</f>
         <v>391328.31</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="20">
         <f t="shared" si="0"/>
         <v>4535.609999999986</v>
       </c>
-      <c r="D52" s="34">
+      <c r="D52" s="26">
         <f t="shared" si="1"/>
         <v>1.1726203726181973E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="37">
+      <c r="A53" s="18">
         <v>46255</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="20">
         <f>B52-445-450-580+585-575-2123</f>
         <v>387740.31</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="20">
         <f t="shared" si="0"/>
         <v>-3588</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="26">
         <f t="shared" si="1"/>
         <v>-9.1687718683066913E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="37">
+      <c r="A54" s="18">
         <v>46258</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="20">
         <f>B53+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="20">
         <f t="shared" si="0"/>
         <v>6121</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="26">
         <f t="shared" si="1"/>
         <v>1.5786339057705916E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="37">
+      <c r="A55" s="18">
         <v>46259</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="20">
         <f>B54-390+1290+906-402+1017</f>
         <v>396282.31</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="20">
         <f t="shared" si="0"/>
         <v>2421</v>
       </c>
-      <c r="D55" s="34">
+      <c r="D55" s="26">
         <f t="shared" si="1"/>
         <v>6.1468337674497652E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="37">
+      <c r="A56" s="18">
         <v>46260</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="20">
         <f>B55+270-750</f>
         <v>395802.31</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="20">
         <f t="shared" si="0"/>
         <v>-480</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="26">
         <f t="shared" si="1"/>
         <v>-1.2112577016117625E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="37">
+      <c r="A57" s="18">
         <v>46261</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="20">
         <f>B56+125+690</f>
         <v>396617.31</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="20">
         <f t="shared" si="0"/>
         <v>815</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="26">
         <f t="shared" si="1"/>
         <v>2.0591087505275043E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="37">
+      <c r="A58" s="18">
         <v>46262</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="20">
         <f>B57+300</f>
         <v>396917.31</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="20">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="26">
         <f t="shared" si="1"/>
         <v>7.5639663836154808E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="37">
+      <c r="A59" s="18">
         <v>46265</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="20">
         <f>B58+135+2220-2.59</f>
         <v>399269.72</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="20">
         <f t="shared" si="0"/>
         <v>2352.4099999999744</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="26">
         <f t="shared" si="1"/>
         <v>5.9267004505295434E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="37">
+      <c r="A60" s="18">
         <v>46266</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="20">
         <f>B59+480-562+1405-1361-623+1800+428</f>
         <v>400836.72</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="20">
         <f t="shared" si="0"/>
         <v>1567</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="26">
         <f t="shared" si="1"/>
         <v>3.9246652613676792E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="37">
+      <c r="A61" s="18">
         <v>46267</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="20">
         <f>B60-274+71-569+1738+320</f>
         <v>402122.72</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="20">
         <f t="shared" si="0"/>
         <v>1286</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D61" s="26">
         <f t="shared" si="1"/>
         <v>3.2082889012763106E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="18">
+        <v>46268</v>
+      </c>
+      <c r="B62" s="20">
+        <f>B61-359+2891+4108-1112</f>
+        <v>407650.72</v>
+      </c>
+      <c r="C62" s="20">
+        <f t="shared" si="0"/>
+        <v>5528</v>
+      </c>
+      <c r="D62" s="26">
+        <f t="shared" si="1"/>
+        <v>1.3747047170077832E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4236,2862 +4253,2862 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F1EF3D-9B19-B84A-BFA9-71A8CF817AA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCEC7B0-BA8A-0742-BC28-9DF7B1D541EE}">
   <dimension ref="A1:L1048543"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" style="31"/>
-    <col min="13" max="16384" width="9.1640625" style="27"/>
+    <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="40"/>
+    <col min="13" max="16384" width="9.1640625" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="L1" s="27"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="28">
+      <c r="A2" s="36">
         <v>46175</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="37">
         <v>300000</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="37">
         <v>105712</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="38">
         <v>194288</v>
       </c>
-      <c r="E2" s="30">
-        <v>0</v>
-      </c>
-      <c r="F2" s="30">
-        <v>0</v>
-      </c>
-      <c r="G2" s="30">
+      <c r="E2" s="38">
+        <v>0</v>
+      </c>
+      <c r="F2" s="38">
+        <v>0</v>
+      </c>
+      <c r="G2" s="38">
         <v>300000</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="39">
         <f>C2/G2</f>
         <v>0.35237333333333332</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="39">
         <f>D2/G2</f>
         <v>0.64762666666666668</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="39">
         <f>E2/G2</f>
         <v>0</v>
       </c>
-      <c r="K2" s="32">
+      <c r="K2" s="39">
         <f>F2/G2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="28">
+      <c r="A3" s="36">
         <v>46176</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="37">
         <v>300000</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="37">
         <v>105712</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="38">
         <v>194288</v>
       </c>
-      <c r="E3" s="30">
-        <v>0</v>
-      </c>
-      <c r="F3" s="30">
-        <v>0</v>
-      </c>
-      <c r="G3" s="30">
+      <c r="E3" s="38">
+        <v>0</v>
+      </c>
+      <c r="F3" s="38">
+        <v>0</v>
+      </c>
+      <c r="G3" s="38">
         <v>300000</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="39">
         <f t="shared" ref="H3:H66" si="0">C3/G3</f>
         <v>0.35237333333333332</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="39">
         <f t="shared" ref="I3:I66" si="1">D3/G3</f>
         <v>0.64762666666666668</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="39">
         <f t="shared" ref="J3:J66" si="2">E3/G3</f>
         <v>0</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="39">
         <f t="shared" ref="K3:K66" si="3">F3/G3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="28">
+      <c r="A4" s="36">
         <v>46177</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="37">
         <v>300000</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="38">
         <v>244380</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="38">
         <v>55620</v>
       </c>
-      <c r="E4" s="30">
-        <v>0</v>
-      </c>
-      <c r="F4" s="30">
-        <v>0</v>
-      </c>
-      <c r="G4" s="30">
+      <c r="E4" s="38">
+        <v>0</v>
+      </c>
+      <c r="F4" s="38">
+        <v>0</v>
+      </c>
+      <c r="G4" s="38">
         <v>300000</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="39">
         <f t="shared" si="0"/>
         <v>0.81459999999999999</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="39">
         <f t="shared" si="1"/>
         <v>0.18540000000000001</v>
       </c>
-      <c r="J4" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="32">
+      <c r="J4" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="28">
+      <c r="A5" s="36">
         <v>46178</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="37">
         <v>300000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="38">
         <v>244380</v>
       </c>
-      <c r="D5" s="30">
-        <v>0</v>
-      </c>
-      <c r="E5" s="30">
+      <c r="D5" s="38">
+        <v>0</v>
+      </c>
+      <c r="E5" s="38">
         <v>663350</v>
       </c>
-      <c r="F5" s="30">
-        <v>0</v>
-      </c>
-      <c r="G5" s="30">
+      <c r="F5" s="38">
+        <v>0</v>
+      </c>
+      <c r="G5" s="38">
         <v>907730</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="39">
         <f t="shared" si="0"/>
         <v>0.2692210238727375</v>
       </c>
-      <c r="I5" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="32">
+      <c r="I5" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="39">
         <f t="shared" si="2"/>
         <v>0.7307789761272625</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="28">
+      <c r="A6" s="36">
         <v>46181</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="37">
         <v>300000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="38">
         <v>138668</v>
       </c>
-      <c r="D6" s="30">
-        <v>0</v>
-      </c>
-      <c r="E6" s="30">
+      <c r="D6" s="38">
+        <v>0</v>
+      </c>
+      <c r="E6" s="38">
         <v>3558250</v>
       </c>
-      <c r="F6" s="30">
-        <v>0</v>
-      </c>
-      <c r="G6" s="30">
+      <c r="F6" s="38">
+        <v>0</v>
+      </c>
+      <c r="G6" s="38">
         <v>3696918</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="39">
         <f t="shared" si="0"/>
         <v>3.7509081889292646E-2</v>
       </c>
-      <c r="I6" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="32">
+      <c r="I6" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="39">
         <f t="shared" si="2"/>
         <v>0.96249091811070731</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="28">
+      <c r="A7" s="36">
         <v>46182</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="37">
         <v>300000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="38">
         <v>138668</v>
       </c>
-      <c r="D7" s="30">
-        <v>0</v>
-      </c>
-      <c r="E7" s="30">
+      <c r="D7" s="38">
+        <v>0</v>
+      </c>
+      <c r="E7" s="38">
         <v>663350</v>
       </c>
-      <c r="F7" s="30">
-        <v>0</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="38">
+        <v>0</v>
+      </c>
+      <c r="G7" s="38">
         <v>802018</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="39">
         <f t="shared" si="0"/>
         <v>0.17289886261904347</v>
       </c>
-      <c r="I7" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="32">
+      <c r="I7" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="39">
         <f t="shared" si="2"/>
         <v>0.82710113738095659</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="28">
+      <c r="A8" s="36">
         <v>46183</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="37">
         <v>300000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="38">
         <v>138668</v>
       </c>
-      <c r="D8" s="30">
-        <v>0</v>
-      </c>
-      <c r="E8" s="30">
+      <c r="D8" s="38">
+        <v>0</v>
+      </c>
+      <c r="E8" s="38">
         <v>461469</v>
       </c>
-      <c r="F8" s="30">
-        <v>0</v>
-      </c>
-      <c r="G8" s="30">
+      <c r="F8" s="38">
+        <v>0</v>
+      </c>
+      <c r="G8" s="38">
         <v>600137</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="39">
         <f t="shared" si="0"/>
         <v>0.23106057450215534</v>
       </c>
-      <c r="I8" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="32">
+      <c r="I8" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="39">
         <f t="shared" si="2"/>
         <v>0.76893942549784466</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="28">
+      <c r="A9" s="36">
         <v>46184</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="37">
         <v>333455.63</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="38">
         <v>138668</v>
       </c>
-      <c r="D9" s="30">
-        <v>0</v>
-      </c>
-      <c r="E9" s="30">
+      <c r="D9" s="38">
+        <v>0</v>
+      </c>
+      <c r="E9" s="38">
         <v>461469</v>
       </c>
-      <c r="F9" s="30">
-        <v>0</v>
-      </c>
-      <c r="G9" s="30">
+      <c r="F9" s="38">
+        <v>0</v>
+      </c>
+      <c r="G9" s="38">
         <v>600137</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="39">
         <f t="shared" si="0"/>
         <v>0.23106057450215534</v>
       </c>
-      <c r="I9" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="32">
+      <c r="I9" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="39">
         <f t="shared" si="2"/>
         <v>0.76893942549784466</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="28">
+      <c r="A10" s="36">
         <v>46185</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="37">
         <v>350216.98</v>
       </c>
-      <c r="C10" s="30">
-        <v>0</v>
-      </c>
-      <c r="D10" s="30">
-        <v>0</v>
-      </c>
-      <c r="E10" s="30">
+      <c r="C10" s="38">
+        <v>0</v>
+      </c>
+      <c r="D10" s="38">
+        <v>0</v>
+      </c>
+      <c r="E10" s="38">
         <v>461469</v>
       </c>
-      <c r="F10" s="30">
-        <v>0</v>
-      </c>
-      <c r="G10" s="30">
+      <c r="F10" s="38">
+        <v>0</v>
+      </c>
+      <c r="G10" s="38">
         <v>461469</v>
       </c>
-      <c r="H10" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="32">
+      <c r="H10" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="28">
+      <c r="A11" s="36">
         <v>46188</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="37">
         <v>356930.64</v>
       </c>
-      <c r="C11" s="30">
-        <v>0</v>
-      </c>
-      <c r="D11" s="30">
-        <v>0</v>
-      </c>
-      <c r="E11" s="30">
+      <c r="C11" s="38">
+        <v>0</v>
+      </c>
+      <c r="D11" s="38">
+        <v>0</v>
+      </c>
+      <c r="E11" s="38">
         <v>461469</v>
       </c>
-      <c r="F11" s="30">
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
+      <c r="F11" s="38">
+        <v>0</v>
+      </c>
+      <c r="G11" s="38">
         <v>461469</v>
       </c>
-      <c r="H11" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="32">
+      <c r="H11" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="28">
+      <c r="A12" s="36">
         <v>46189</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="37">
         <v>351815.49</v>
       </c>
-      <c r="C12" s="30">
-        <v>0</v>
-      </c>
-      <c r="D12" s="30">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
+      <c r="C12" s="38">
+        <v>0</v>
+      </c>
+      <c r="D12" s="38">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38">
         <v>461469</v>
       </c>
-      <c r="F12" s="30">
-        <v>0</v>
-      </c>
-      <c r="G12" s="30">
+      <c r="F12" s="38">
+        <v>0</v>
+      </c>
+      <c r="G12" s="38">
         <v>461469</v>
       </c>
-      <c r="H12" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="32">
+      <c r="H12" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="28">
+      <c r="A13" s="36">
         <v>46190</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="37">
         <v>358486.01</v>
       </c>
-      <c r="C13" s="30">
-        <v>0</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="C13" s="38">
+        <v>0</v>
+      </c>
+      <c r="D13" s="38">
         <f>B13-E13</f>
         <v>227246.01</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="38">
         <v>131240</v>
       </c>
-      <c r="F13" s="30">
-        <v>0</v>
-      </c>
-      <c r="G13" s="30">
+      <c r="F13" s="38">
+        <v>0</v>
+      </c>
+      <c r="G13" s="38">
         <f>SUM(C13:F13)</f>
         <v>358486.01</v>
       </c>
-      <c r="H13" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="32">
+      <c r="H13" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="39">
         <f t="shared" si="1"/>
         <v>0.63390482099984879</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="39">
         <f t="shared" si="2"/>
         <v>0.36609517900015121</v>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="28">
+      <c r="A14" s="36">
         <v>46191</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="37">
         <v>360758.08</v>
       </c>
-      <c r="C14" s="30">
-        <v>0</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="C14" s="38">
+        <v>0</v>
+      </c>
+      <c r="D14" s="38">
         <f>B14-E14</f>
         <v>229518.08000000002</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="38">
         <v>131240</v>
       </c>
-      <c r="F14" s="30">
-        <v>0</v>
-      </c>
-      <c r="G14" s="30">
+      <c r="F14" s="38">
+        <v>0</v>
+      </c>
+      <c r="G14" s="38">
         <f>SUM(C14:F14)</f>
         <v>360758.08</v>
       </c>
-      <c r="H14" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="32">
+      <c r="H14" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="39">
         <f t="shared" si="1"/>
         <v>0.63621050428032</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="39">
         <f t="shared" si="2"/>
         <v>0.36378949571968006</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="28">
+      <c r="A15" s="36">
         <v>46192</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="37">
         <v>360243.39</v>
       </c>
-      <c r="C15" s="30">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30">
+      <c r="C15" s="38">
+        <v>0</v>
+      </c>
+      <c r="D15" s="38">
         <f>B15-E15</f>
         <v>229003.39</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="38">
         <v>131240</v>
       </c>
-      <c r="F15" s="30">
-        <v>0</v>
-      </c>
-      <c r="G15" s="30">
+      <c r="F15" s="38">
+        <v>0</v>
+      </c>
+      <c r="G15" s="38">
         <f>SUM(C15:F15)</f>
         <v>360243.39</v>
       </c>
-      <c r="H15" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="32">
+      <c r="H15" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="39">
         <f t="shared" si="1"/>
         <v>0.63569074785799684</v>
       </c>
-      <c r="J15" s="32">
+      <c r="J15" s="39">
         <f t="shared" si="2"/>
         <v>0.36430925214200321</v>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="28">
+      <c r="A16" s="36">
         <v>46195</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="37">
         <v>351346.76</v>
       </c>
-      <c r="C16" s="30">
-        <v>0</v>
-      </c>
-      <c r="D16" s="30">
-        <v>0</v>
-      </c>
-      <c r="E16" s="30">
+      <c r="C16" s="38">
+        <v>0</v>
+      </c>
+      <c r="D16" s="38">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38">
         <v>3124781</v>
       </c>
-      <c r="F16" s="30">
-        <v>0</v>
-      </c>
-      <c r="G16" s="30">
+      <c r="F16" s="38">
+        <v>0</v>
+      </c>
+      <c r="G16" s="38">
         <f>SUM(C16:F16)</f>
         <v>3124781</v>
       </c>
-      <c r="H16" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="32">
+      <c r="H16" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="28">
+      <c r="A17" s="36">
         <v>46196</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="37">
         <v>352224.24</v>
       </c>
-      <c r="C17" s="30">
-        <v>0</v>
-      </c>
-      <c r="D17" s="30">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30">
+      <c r="C17" s="38">
+        <v>0</v>
+      </c>
+      <c r="D17" s="38">
+        <v>0</v>
+      </c>
+      <c r="E17" s="38">
         <v>3124781</v>
       </c>
-      <c r="F17" s="30">
-        <v>0</v>
-      </c>
-      <c r="G17" s="30">
+      <c r="F17" s="38">
+        <v>0</v>
+      </c>
+      <c r="G17" s="38">
         <f>SUM(C17:F17)</f>
         <v>3124781</v>
       </c>
-      <c r="H17" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="32">
+      <c r="H17" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="28">
+      <c r="A18" s="36">
         <v>46197</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="37">
         <v>347929.11</v>
       </c>
-      <c r="C18" s="30">
-        <v>0</v>
-      </c>
-      <c r="D18" s="30">
-        <v>0</v>
-      </c>
-      <c r="E18" s="30">
+      <c r="C18" s="38">
+        <v>0</v>
+      </c>
+      <c r="D18" s="38">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
         <v>3124781</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="38">
         <v>193096</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="38">
         <f>SUM(C18:F18)</f>
         <v>3317877</v>
       </c>
-      <c r="H18" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="32">
+      <c r="H18" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="39">
         <f t="shared" si="2"/>
         <v>0.94180133862707993</v>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="39">
         <f t="shared" si="3"/>
         <v>5.8198661372920096E-2</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="28">
+      <c r="A19" s="36">
         <v>46198</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="37">
         <v>349277.46</v>
       </c>
-      <c r="C19" s="30">
-        <v>0</v>
-      </c>
-      <c r="D19" s="30">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30">
+      <c r="C19" s="38">
+        <v>0</v>
+      </c>
+      <c r="D19" s="38">
+        <v>0</v>
+      </c>
+      <c r="E19" s="38">
         <f>3124781+202125</f>
         <v>3326906</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="38">
         <v>193096</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="38">
         <f>SUM(C19:F19)</f>
         <v>3520002</v>
       </c>
-      <c r="H19" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="32">
+      <c r="H19" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="39">
         <f t="shared" si="2"/>
         <v>0.94514321298681081</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="39">
         <f t="shared" si="3"/>
         <v>5.4856787013189197E-2</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="28">
+      <c r="A20" s="36">
         <v>46199</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="37">
         <v>351579.06</v>
       </c>
-      <c r="C20" s="30">
-        <v>0</v>
-      </c>
-      <c r="D20" s="30">
-        <v>0</v>
-      </c>
-      <c r="E20" s="30">
+      <c r="C20" s="38">
+        <v>0</v>
+      </c>
+      <c r="D20" s="38">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38">
         <v>3326906</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="38">
         <v>193096</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="38">
         <f>SUM(C20:F20)</f>
         <v>3520002</v>
       </c>
-      <c r="H20" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="32">
+      <c r="H20" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="39">
         <f t="shared" si="2"/>
         <v>0.94514321298681081</v>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="39">
         <f t="shared" si="3"/>
         <v>5.4856787013189197E-2</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="28">
+      <c r="A21" s="36">
         <v>46202</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="37">
         <v>359661.12</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="38">
         <v>55035</v>
       </c>
-      <c r="D21" s="30">
-        <v>0</v>
-      </c>
-      <c r="E21" s="30">
+      <c r="D21" s="38">
+        <v>0</v>
+      </c>
+      <c r="E21" s="38">
         <v>3326906</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="38">
         <f>193096+223843</f>
         <v>416939</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="38">
         <f>SUM(C21:F21)</f>
         <v>3798880</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="39">
         <f t="shared" si="0"/>
         <v>1.4487164637998567E-2</v>
       </c>
-      <c r="I21" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="32">
+      <c r="I21" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="39">
         <f t="shared" si="2"/>
         <v>0.87575969759508066</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="39">
         <f t="shared" si="3"/>
         <v>0.10975313776692078</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="28">
+      <c r="A22" s="36">
         <v>46203</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="37">
         <v>361447.55</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="38">
         <v>55035</v>
       </c>
-      <c r="D22" s="30">
-        <v>0</v>
-      </c>
-      <c r="E22" s="30">
+      <c r="D22" s="38">
+        <v>0</v>
+      </c>
+      <c r="E22" s="38">
         <f>E21-E12-202125+121064</f>
         <v>2784376</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="38">
         <v>223843</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="38">
         <f>SUM(C22:F22)</f>
         <v>3063254</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="39">
         <f t="shared" si="0"/>
         <v>1.7966188895860415E-2</v>
       </c>
-      <c r="I22" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="32">
+      <c r="I22" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="39">
         <f t="shared" si="2"/>
         <v>0.9089602102861859</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="39">
         <f t="shared" si="3"/>
         <v>7.3073600817953721E-2</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="28">
+      <c r="A23" s="36">
         <v>46204</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="37">
         <v>363377.97</v>
       </c>
-      <c r="C23" s="30">
-        <v>0</v>
-      </c>
-      <c r="D23" s="30">
-        <v>0</v>
-      </c>
-      <c r="E23" s="30">
+      <c r="C23" s="38">
+        <v>0</v>
+      </c>
+      <c r="D23" s="38">
+        <v>0</v>
+      </c>
+      <c r="E23" s="38">
         <v>2784376</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="38">
         <v>223843</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="38">
         <f>SUM(C23:F23)</f>
         <v>3008219</v>
       </c>
-      <c r="H23" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="32">
+      <c r="H23" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="39">
         <f t="shared" si="2"/>
         <v>0.92558952656040006</v>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="39">
         <f t="shared" si="3"/>
         <v>7.4410473439599972E-2</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="28">
+      <c r="A24" s="36">
         <v>46205</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="37">
         <v>374651</v>
       </c>
-      <c r="C24" s="30">
-        <v>0</v>
-      </c>
-      <c r="D24" s="30">
+      <c r="C24" s="38">
+        <v>0</v>
+      </c>
+      <c r="D24" s="38">
         <f>B24-E24-F24</f>
         <v>29744</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="38">
         <v>121064</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="38">
         <v>223843</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="38">
         <f>SUM(C24:F24)</f>
         <v>374651</v>
       </c>
-      <c r="H24" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="32">
+      <c r="H24" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="39">
         <f t="shared" si="1"/>
         <v>7.9391220095502216E-2</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="39">
         <f t="shared" si="2"/>
         <v>0.32313806716117133</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="39">
         <f t="shared" si="3"/>
         <v>0.59747071274332642</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="28">
+      <c r="A25" s="36">
         <v>46206</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="37">
         <v>374479.39</v>
       </c>
-      <c r="C25" s="30">
-        <v>0</v>
-      </c>
-      <c r="D25" s="30">
+      <c r="C25" s="38">
+        <v>0</v>
+      </c>
+      <c r="D25" s="38">
         <f>B25-E25-F25</f>
         <v>29572.390000000014</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="38">
         <v>121064</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="38">
         <v>223843</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="38">
         <f>SUM(C25:F25)</f>
         <v>374479.39</v>
       </c>
-      <c r="H25" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="32">
+      <c r="H25" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="39">
         <f t="shared" si="1"/>
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="39">
         <f t="shared" si="2"/>
         <v>0.32328614933921995</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="39">
         <f t="shared" si="3"/>
         <v>0.59774451138686158</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="28">
+      <c r="A26" s="36">
         <v>46209</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="37">
         <v>372801.92</v>
       </c>
-      <c r="C26" s="30">
-        <v>0</v>
-      </c>
-      <c r="D26" s="30">
+      <c r="C26" s="38">
+        <v>0</v>
+      </c>
+      <c r="D26" s="38">
         <f>B26-E26-F26</f>
         <v>27894.919999999984</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="38">
         <v>121064</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="38">
         <v>223843</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="38">
         <f>SUM(C26:F26)</f>
         <v>372801.92</v>
       </c>
-      <c r="H26" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="32">
+      <c r="H26" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="39">
         <f t="shared" si="1"/>
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="J26" s="32">
+      <c r="J26" s="39">
         <f t="shared" si="2"/>
         <v>0.32474081678549299</v>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="39">
         <f t="shared" si="3"/>
         <v>0.60043413939499024</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="28">
+      <c r="A27" s="36">
         <v>46210</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="37">
         <v>375246.11</v>
       </c>
-      <c r="C27" s="30">
-        <v>0</v>
-      </c>
-      <c r="D27" s="30">
+      <c r="C27" s="38">
+        <v>0</v>
+      </c>
+      <c r="D27" s="38">
         <f>B27-E27-F27</f>
         <v>30339.109999999986</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="38">
         <v>121064</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="38">
         <v>223843</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="38">
         <f>SUM(C27:F27)</f>
         <v>375246.11</v>
       </c>
-      <c r="H27" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="32">
+      <c r="H27" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="39">
         <f t="shared" si="1"/>
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="39">
         <f t="shared" si="2"/>
         <v>0.32262559630531545</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="39">
         <f t="shared" si="3"/>
         <v>0.59652317248538567</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="28">
+      <c r="A28" s="36">
         <v>46211</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="37">
         <v>377280.97</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="38">
         <v>90811</v>
       </c>
-      <c r="D28" s="30">
-        <v>0</v>
-      </c>
-      <c r="E28" s="30">
+      <c r="D28" s="38">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38">
         <v>121064</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="38">
         <v>223843</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="38">
         <f>SUM(C28:F28)</f>
         <v>435718</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="39">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I28" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="32">
+      <c r="I28" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="39">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="39">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="28">
+      <c r="A29" s="36">
         <v>46212</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="37">
         <v>374471.51</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="38">
         <v>90811</v>
       </c>
-      <c r="D29" s="30">
-        <v>0</v>
-      </c>
-      <c r="E29" s="30">
+      <c r="D29" s="38">
+        <v>0</v>
+      </c>
+      <c r="E29" s="38">
         <v>121064</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="38">
         <v>223843</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="38">
         <f>SUM(C29:F29)</f>
         <v>435718</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="39">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I29" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="32">
+      <c r="I29" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="39">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="39">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="28">
+      <c r="A30" s="36">
         <v>46213</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="37">
         <v>376468.72</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="38">
         <v>90811</v>
       </c>
-      <c r="D30" s="30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="30">
+      <c r="D30" s="38">
+        <v>0</v>
+      </c>
+      <c r="E30" s="38">
         <v>121064</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="38">
         <v>223843</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="38">
         <f>SUM(C30:F30)</f>
         <v>435718</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="39">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I30" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="32">
+      <c r="I30" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="39">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="39">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="28">
+      <c r="A31" s="36">
         <v>46216</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="37">
         <v>379175.63</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="38">
         <v>90811</v>
       </c>
-      <c r="D31" s="30">
-        <v>0</v>
-      </c>
-      <c r="E31" s="30">
+      <c r="D31" s="38">
+        <v>0</v>
+      </c>
+      <c r="E31" s="38">
         <v>121064</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="38">
         <v>223843</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="38">
         <f>SUM(C31:F31)</f>
         <v>435718</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="39">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I31" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="32">
+      <c r="I31" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="39">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="39">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="28">
+      <c r="A32" s="36">
         <v>46217</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="37">
         <v>378852.03</v>
       </c>
-      <c r="C32" s="30">
-        <v>0</v>
-      </c>
-      <c r="D32" s="30">
+      <c r="C32" s="38">
+        <v>0</v>
+      </c>
+      <c r="D32" s="38">
         <f>B32-E32-F32</f>
         <v>33945.030000000028</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="38">
         <v>121064</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="38">
         <v>223843</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="38">
         <f>SUM(C32:F32)</f>
         <v>378852.03</v>
       </c>
-      <c r="H32" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="32">
+      <c r="H32" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="39">
         <f t="shared" si="1"/>
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="J32" s="32">
+      <c r="J32" s="39">
         <f t="shared" si="2"/>
         <v>0.31955484044786558</v>
       </c>
-      <c r="K32" s="32">
+      <c r="K32" s="39">
         <f t="shared" si="3"/>
         <v>0.5908454548864368</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="28">
+      <c r="A33" s="36">
         <v>46218</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="37">
         <v>374437.1</v>
       </c>
-      <c r="C33" s="30">
-        <v>0</v>
-      </c>
-      <c r="D33" s="30">
+      <c r="C33" s="38">
+        <v>0</v>
+      </c>
+      <c r="D33" s="38">
         <f t="shared" ref="D33:D41" si="4">B33-E33-F33</f>
         <v>29530.099999999977</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="38">
         <v>121064</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="38">
         <v>223843</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="38">
         <f t="shared" ref="G33:G69" si="5">SUM(C33:F33)</f>
         <v>374437.1</v>
       </c>
-      <c r="H33" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="32">
+      <c r="H33" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="39">
         <f t="shared" si="1"/>
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="39">
         <f t="shared" si="2"/>
         <v>0.32332266220414591</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="39">
         <f t="shared" si="3"/>
         <v>0.59781202236637343</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="28">
+      <c r="A34" s="36">
         <v>46219</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="37">
         <v>372248.26</v>
       </c>
-      <c r="C34" s="30">
-        <v>0</v>
-      </c>
-      <c r="D34" s="30">
+      <c r="C34" s="38">
+        <v>0</v>
+      </c>
+      <c r="D34" s="38">
         <f t="shared" si="4"/>
         <v>27341.260000000009</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="38">
         <v>121064</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="38">
         <v>223843</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="38">
         <f t="shared" si="5"/>
         <v>372248.26</v>
       </c>
-      <c r="H34" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="32">
+      <c r="H34" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="39">
         <f t="shared" si="1"/>
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="39">
         <f t="shared" si="2"/>
         <v>0.32522381703006481</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="39">
         <f t="shared" si="3"/>
         <v>0.60132718954817943</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="28">
+      <c r="A35" s="36">
         <v>46220</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="37">
         <v>376025.4</v>
       </c>
-      <c r="C35" s="30">
-        <v>0</v>
-      </c>
-      <c r="D35" s="30">
+      <c r="C35" s="38">
+        <v>0</v>
+      </c>
+      <c r="D35" s="38">
         <f t="shared" si="4"/>
         <v>31118.400000000023</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="38">
         <v>121064</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="38">
         <v>223843</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="38">
         <f t="shared" si="5"/>
         <v>376025.4</v>
       </c>
-      <c r="H35" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="32">
+      <c r="H35" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="39">
         <f t="shared" si="1"/>
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="39">
         <f t="shared" si="2"/>
         <v>0.32195697418312696</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="39">
         <f t="shared" si="3"/>
         <v>0.59528691412867318</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="28">
+      <c r="A36" s="36">
         <v>46223</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="37">
         <v>375009.72</v>
       </c>
-      <c r="C36" s="30">
-        <v>0</v>
-      </c>
-      <c r="D36" s="30">
+      <c r="C36" s="38">
+        <v>0</v>
+      </c>
+      <c r="D36" s="38">
         <f t="shared" si="4"/>
         <v>30102.719999999972</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="38">
         <v>121064</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="38">
         <v>223843</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="38">
         <f t="shared" si="5"/>
         <v>375009.72</v>
       </c>
-      <c r="H36" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="32">
+      <c r="H36" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="39">
         <f t="shared" si="1"/>
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="39">
         <f t="shared" si="2"/>
         <v>0.32282896560654484</v>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="39">
         <f t="shared" si="3"/>
         <v>0.59689919503953126</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="28">
+      <c r="A37" s="36">
         <v>46224</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="37">
         <v>375731.28</v>
       </c>
-      <c r="C37" s="30">
-        <v>0</v>
-      </c>
-      <c r="D37" s="30">
+      <c r="C37" s="38">
+        <v>0</v>
+      </c>
+      <c r="D37" s="38">
         <f t="shared" si="4"/>
         <v>30824.280000000028</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="38">
         <v>121064</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="38">
         <v>223843</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="38">
         <f t="shared" si="5"/>
         <v>375731.28</v>
       </c>
-      <c r="H37" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="32">
+      <c r="H37" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="39">
         <f t="shared" si="1"/>
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="J37" s="32">
+      <c r="J37" s="39">
         <f t="shared" si="2"/>
         <v>0.32220900000660047</v>
       </c>
-      <c r="K37" s="32">
+      <c r="K37" s="39">
         <f t="shared" si="3"/>
         <v>0.5957529008497775</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="28">
+      <c r="A38" s="36">
         <v>46225</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="37">
         <v>378174.99</v>
       </c>
-      <c r="C38" s="30">
-        <v>0</v>
-      </c>
-      <c r="D38" s="30">
+      <c r="C38" s="38">
+        <v>0</v>
+      </c>
+      <c r="D38" s="38">
         <f t="shared" si="4"/>
         <v>33267.989999999991</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="38">
         <v>121064</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="38">
         <v>223843</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="38">
         <f t="shared" si="5"/>
         <v>378174.99</v>
       </c>
-      <c r="H38" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="32">
+      <c r="H38" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="39">
         <f t="shared" si="1"/>
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="39">
         <f t="shared" si="2"/>
         <v>0.32012693383028845</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="39">
         <f t="shared" si="3"/>
         <v>0.59190323506057341</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="28">
+      <c r="A39" s="36">
         <v>46226</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="37">
         <v>380362.45</v>
       </c>
-      <c r="C39" s="30">
-        <v>0</v>
-      </c>
-      <c r="D39" s="30">
+      <c r="C39" s="38">
+        <v>0</v>
+      </c>
+      <c r="D39" s="38">
         <f t="shared" si="4"/>
         <v>35455.450000000012</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="38">
         <v>121064</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="38">
         <v>223843</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="38">
         <f t="shared" si="5"/>
         <v>380362.45</v>
       </c>
-      <c r="H39" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="32">
+      <c r="H39" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="39">
         <f t="shared" si="1"/>
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="39">
         <f t="shared" si="2"/>
         <v>0.31828588757907095</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="39">
         <f t="shared" si="3"/>
         <v>0.58849920648055554</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="28">
+      <c r="A40" s="36">
         <v>46227</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="37">
         <f>B39-1740-1437</f>
         <v>377185.45</v>
       </c>
-      <c r="C40" s="30">
-        <v>0</v>
-      </c>
-      <c r="D40" s="30">
+      <c r="C40" s="38">
+        <v>0</v>
+      </c>
+      <c r="D40" s="38">
         <f t="shared" si="4"/>
         <v>32278.450000000012</v>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="38">
         <v>121064</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="38">
         <v>223843</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="38">
         <f t="shared" si="5"/>
         <v>377185.45</v>
       </c>
-      <c r="H40" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="32">
+      <c r="H40" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="39">
         <f t="shared" si="1"/>
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="J40" s="32">
+      <c r="J40" s="39">
         <f t="shared" si="2"/>
         <v>0.32096678172501086</v>
       </c>
-      <c r="K40" s="32">
+      <c r="K40" s="39">
         <f t="shared" si="3"/>
         <v>0.59345608373811876</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="28">
+      <c r="A41" s="36">
         <v>46230</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="37">
         <f>B40+322+630+1019-936</f>
         <v>378220.45</v>
       </c>
-      <c r="C41" s="30">
-        <v>0</v>
-      </c>
-      <c r="D41" s="30">
+      <c r="C41" s="38">
+        <v>0</v>
+      </c>
+      <c r="D41" s="38">
         <f t="shared" si="4"/>
         <v>33313.450000000012</v>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="38">
         <v>121064</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="38">
         <v>223843</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="38">
         <f t="shared" si="5"/>
         <v>378220.45</v>
       </c>
-      <c r="H41" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="32">
+      <c r="H41" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="39">
         <f t="shared" si="1"/>
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="39">
         <f t="shared" si="2"/>
         <v>0.32008845634867178</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="39">
         <f t="shared" si="3"/>
         <v>0.5918320915751647</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="28">
+      <c r="A42" s="36">
         <v>46231</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="37">
         <f>B41-951+8872.25-771</f>
         <v>385370.7</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="34">
         <v>334624</v>
       </c>
-      <c r="D42" s="27">
-        <v>0</v>
-      </c>
-      <c r="E42" s="30">
+      <c r="D42" s="35">
+        <v>0</v>
+      </c>
+      <c r="E42" s="38">
         <v>121064</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="38">
         <v>223843</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="38">
         <f t="shared" si="5"/>
         <v>679531</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="39">
         <f t="shared" si="0"/>
         <v>0.49243375210255308</v>
       </c>
-      <c r="I42" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="32">
+      <c r="I42" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="39">
         <f t="shared" si="2"/>
         <v>0.17815817085607574</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="39">
         <f t="shared" si="3"/>
         <v>0.32940807704137121</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="28">
+      <c r="A43" s="36">
         <v>46232</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="37">
         <f>B42+567+1830-7720+5262</f>
         <v>385309.7</v>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="34">
         <v>334624</v>
       </c>
-      <c r="D43" s="27">
-        <v>0</v>
-      </c>
-      <c r="E43" s="30">
+      <c r="D43" s="35">
+        <v>0</v>
+      </c>
+      <c r="E43" s="38">
         <v>121064</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="38">
         <v>223843</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="38">
         <f t="shared" si="5"/>
         <v>679531</v>
       </c>
-      <c r="H43" s="32">
+      <c r="H43" s="39">
         <f t="shared" si="0"/>
         <v>0.49243375210255308</v>
       </c>
-      <c r="I43" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="32">
+      <c r="I43" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="39">
         <f t="shared" si="2"/>
         <v>0.17815817085607574</v>
       </c>
-      <c r="K43" s="32">
+      <c r="K43" s="39">
         <f t="shared" si="3"/>
         <v>0.32940807704137121</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="28">
+      <c r="A44" s="36">
         <v>46233</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="37">
         <f>B43+2088+840+8949-5393</f>
         <v>391793.7</v>
       </c>
-      <c r="C44" s="26">
-        <v>0</v>
-      </c>
-      <c r="D44" s="30">
+      <c r="C44" s="34">
+        <v>0</v>
+      </c>
+      <c r="D44" s="38">
         <f t="shared" ref="D44:D52" si="6">B44-E44-F44</f>
         <v>46886.700000000012</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="38">
         <v>121064</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="38">
         <v>223843</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="38">
         <f t="shared" si="5"/>
         <v>391793.7</v>
       </c>
-      <c r="H44" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="32">
+      <c r="H44" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="39">
         <f t="shared" si="1"/>
         <v>0.11967190896637697</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="39">
         <f t="shared" si="2"/>
         <v>0.30899935348628627</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="39">
         <f t="shared" si="3"/>
         <v>0.57132873754733671</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="28">
+      <c r="A45" s="36">
         <v>46234</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="37">
         <f>B44-480-2572</f>
         <v>388741.7</v>
       </c>
-      <c r="C45" s="26">
-        <v>0</v>
-      </c>
-      <c r="D45" s="30">
+      <c r="C45" s="34">
+        <v>0</v>
+      </c>
+      <c r="D45" s="38">
         <f t="shared" si="6"/>
         <v>43834.700000000012</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="38">
         <v>121064</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F45" s="38">
         <v>223843</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="38">
         <f t="shared" si="5"/>
         <v>388741.7</v>
       </c>
-      <c r="H45" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="32">
+      <c r="H45" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="39">
         <f t="shared" si="1"/>
         <v>0.11276047823014616</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="39">
         <f t="shared" si="2"/>
         <v>0.3114252985980151</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="39">
         <f t="shared" si="3"/>
         <v>0.57581422317183872</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="28">
+      <c r="A46" s="36">
         <v>46237</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="37">
         <f>B45-3000-427</f>
         <v>385314.7</v>
       </c>
-      <c r="C46" s="26">
-        <v>0</v>
-      </c>
-      <c r="D46" s="30">
+      <c r="C46" s="34">
+        <v>0</v>
+      </c>
+      <c r="D46" s="38">
         <f t="shared" si="6"/>
         <v>40407.700000000012</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="38">
         <v>121064</v>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="38">
         <v>223843</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="38">
         <f t="shared" si="5"/>
         <v>385314.7</v>
       </c>
-      <c r="H46" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="32">
+      <c r="H46" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="39">
         <f t="shared" si="1"/>
         <v>0.10486934446051503</v>
       </c>
-      <c r="J46" s="32">
+      <c r="J46" s="39">
         <f t="shared" si="2"/>
         <v>0.31419512414138362</v>
       </c>
-      <c r="K46" s="32">
+      <c r="K46" s="39">
         <f t="shared" si="3"/>
         <v>0.58093553139810128</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="28">
+      <c r="A47" s="36">
         <v>46238</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="37">
         <f>B46-2340+453</f>
         <v>383427.7</v>
       </c>
-      <c r="C47" s="26">
-        <v>0</v>
-      </c>
-      <c r="D47" s="30">
+      <c r="C47" s="34">
+        <v>0</v>
+      </c>
+      <c r="D47" s="38">
         <f t="shared" si="6"/>
         <v>38520.700000000012</v>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="38">
         <v>121064</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="38">
         <v>223843</v>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="38">
         <f t="shared" si="5"/>
         <v>383427.7</v>
       </c>
-      <c r="H47" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="32">
+      <c r="H47" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="39">
         <f t="shared" si="1"/>
         <v>0.1004640509801457</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="39">
         <f t="shared" si="2"/>
         <v>0.31574140313806226</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="39">
         <f t="shared" si="3"/>
         <v>0.58379454588179203</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="28">
+      <c r="A48" s="36">
         <v>46239</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="37">
         <f>B47+1500-3275</f>
         <v>381652.7</v>
       </c>
-      <c r="C48" s="26">
-        <v>0</v>
-      </c>
-      <c r="D48" s="30">
+      <c r="C48" s="34">
+        <v>0</v>
+      </c>
+      <c r="D48" s="38">
         <f t="shared" si="6"/>
         <v>36745.700000000012</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="38">
         <v>121064</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="38">
         <v>223843</v>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="38">
         <f t="shared" si="5"/>
         <v>381652.7</v>
       </c>
-      <c r="H48" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="32">
+      <c r="H48" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="39">
         <f t="shared" si="1"/>
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="39">
         <f t="shared" si="2"/>
         <v>0.31720986121675543</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="39">
         <f t="shared" si="3"/>
         <v>0.58650967227534356</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="28">
+      <c r="A49" s="36">
         <v>46240</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="37">
         <f>B48+2550-1004</f>
         <v>383198.7</v>
       </c>
-      <c r="C49" s="26">
-        <v>0</v>
-      </c>
-      <c r="D49" s="30">
+      <c r="C49" s="34">
+        <v>0</v>
+      </c>
+      <c r="D49" s="38">
         <f t="shared" si="6"/>
         <v>38291.700000000012</v>
       </c>
-      <c r="E49" s="30">
+      <c r="E49" s="38">
         <v>121064</v>
       </c>
-      <c r="F49" s="30">
+      <c r="F49" s="38">
         <v>223843</v>
       </c>
-      <c r="G49" s="30">
+      <c r="G49" s="38">
         <f t="shared" si="5"/>
         <v>383198.7</v>
       </c>
-      <c r="H49" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="32">
+      <c r="H49" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="39">
         <f t="shared" si="1"/>
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="J49" s="32">
+      <c r="J49" s="39">
         <f t="shared" si="2"/>
         <v>0.31593009057702959</v>
       </c>
-      <c r="K49" s="32">
+      <c r="K49" s="39">
         <f t="shared" si="3"/>
         <v>0.58414342219845738</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="28">
+      <c r="A50" s="36">
         <v>46241</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="37">
         <f>B49+840+738</f>
         <v>384776.7</v>
       </c>
-      <c r="C50" s="26">
-        <v>0</v>
-      </c>
-      <c r="D50" s="30">
+      <c r="C50" s="34">
+        <v>0</v>
+      </c>
+      <c r="D50" s="38">
         <f t="shared" si="6"/>
         <v>39869.700000000012</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="38">
         <v>121064</v>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="38">
         <v>223843</v>
       </c>
-      <c r="G50" s="30">
+      <c r="G50" s="38">
         <f t="shared" si="5"/>
         <v>384776.7</v>
       </c>
-      <c r="H50" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="32">
+      <c r="H50" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="39">
         <f t="shared" si="1"/>
         <v>0.10361776063883289</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="39">
         <f t="shared" si="2"/>
         <v>0.31463443602484248</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="39">
         <f t="shared" si="3"/>
         <v>0.5817478033363247</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="28">
+      <c r="A51" s="36">
         <v>46244</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="37">
         <f>B50+41+540-398-50</f>
         <v>384909.7</v>
       </c>
-      <c r="C51" s="26">
-        <v>0</v>
-      </c>
-      <c r="D51" s="30">
+      <c r="C51" s="34">
+        <v>0</v>
+      </c>
+      <c r="D51" s="38">
         <f t="shared" si="6"/>
         <v>24412.700000000012</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="35">
         <f>185382+121064</f>
         <v>306446</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="35">
         <v>54051</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="38">
         <f t="shared" si="5"/>
         <v>384909.7</v>
       </c>
-      <c r="H51" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="32">
+      <c r="H51" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="39">
         <f t="shared" si="1"/>
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="39">
         <f t="shared" si="2"/>
         <v>0.79615036981401088</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="39">
         <f t="shared" si="3"/>
         <v>0.14042514387140673</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="28">
+      <c r="A52" s="36">
         <v>46245</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="37">
         <f>B51-40-2340-824-1009-1010</f>
         <v>379686.7</v>
       </c>
-      <c r="C52" s="26">
-        <v>0</v>
-      </c>
-      <c r="D52" s="30">
+      <c r="C52" s="34">
+        <v>0</v>
+      </c>
+      <c r="D52" s="38">
         <f t="shared" si="6"/>
         <v>19189.700000000012</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="35">
         <f>185382+121064</f>
         <v>306446</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="35">
         <v>54051</v>
       </c>
-      <c r="G52" s="30">
+      <c r="G52" s="38">
         <f t="shared" si="5"/>
         <v>379686.7</v>
       </c>
-      <c r="H52" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="32">
+      <c r="H52" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="39">
         <f t="shared" si="1"/>
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="J52" s="32">
+      <c r="J52" s="39">
         <f t="shared" si="2"/>
         <v>0.80710227669286283</v>
       </c>
-      <c r="K52" s="32">
+      <c r="K52" s="39">
         <f t="shared" si="3"/>
         <v>0.14235684315515923</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="28">
+      <c r="A53" s="36">
         <v>46246</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="37">
         <f>B52-205-1710-410+2950-212+6683-2764-240</f>
         <v>383778.7</v>
       </c>
-      <c r="C53" s="26">
-        <v>0</v>
-      </c>
-      <c r="D53" s="27">
-        <v>0</v>
-      </c>
-      <c r="E53" s="27">
+      <c r="C53" s="34">
+        <v>0</v>
+      </c>
+      <c r="D53" s="35">
+        <v>0</v>
+      </c>
+      <c r="E53" s="35">
         <f>E52+154290</f>
         <v>460736</v>
       </c>
-      <c r="F53" s="27">
+      <c r="F53" s="35">
         <f>F52+164620</f>
         <v>218671</v>
       </c>
-      <c r="G53" s="30">
+      <c r="G53" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H53" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="32">
+      <c r="H53" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="28">
+      <c r="A54" s="36">
         <v>46247</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="37">
         <f>B53-95-1110+960-1500-1040+875+120</f>
         <v>381988.7</v>
       </c>
-      <c r="C54" s="26">
-        <v>0</v>
-      </c>
-      <c r="D54" s="27">
-        <v>0</v>
-      </c>
-      <c r="E54" s="27">
+      <c r="C54" s="34">
+        <v>0</v>
+      </c>
+      <c r="D54" s="35">
+        <v>0</v>
+      </c>
+      <c r="E54" s="35">
         <v>460736</v>
       </c>
-      <c r="F54" s="27">
+      <c r="F54" s="35">
         <v>218671</v>
       </c>
-      <c r="G54" s="30">
+      <c r="G54" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H54" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="32">
+      <c r="H54" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="28">
+      <c r="A55" s="36">
         <v>46248</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="37">
         <f>B54+25-540-1100-7593+350-1166-690</f>
         <v>371274.7</v>
       </c>
-      <c r="C55" s="26">
-        <v>0</v>
-      </c>
-      <c r="D55" s="27">
-        <v>0</v>
-      </c>
-      <c r="E55" s="27">
+      <c r="C55" s="34">
+        <v>0</v>
+      </c>
+      <c r="D55" s="35">
+        <v>0</v>
+      </c>
+      <c r="E55" s="35">
         <v>460736</v>
       </c>
-      <c r="F55" s="27">
+      <c r="F55" s="35">
         <v>218671</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H55" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="32">
+      <c r="H55" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K55" s="32">
+      <c r="K55" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="28">
+      <c r="A56" s="36">
         <v>46251</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="37">
         <f>B55+95+1620-1380+725+796+220</f>
         <v>373350.7</v>
       </c>
-      <c r="C56" s="26">
-        <v>0</v>
-      </c>
-      <c r="D56" s="27">
-        <v>0</v>
-      </c>
-      <c r="E56" s="27">
+      <c r="C56" s="34">
+        <v>0</v>
+      </c>
+      <c r="D56" s="35">
+        <v>0</v>
+      </c>
+      <c r="E56" s="35">
         <v>460736</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="35">
         <v>218671</v>
       </c>
-      <c r="G56" s="30">
+      <c r="G56" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H56" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="32">
+      <c r="H56" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="28">
+      <c r="A57" s="36">
         <v>46252</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="37">
         <f>B56+590+1620+620+1095+826+2690</f>
         <v>380791.7</v>
       </c>
-      <c r="C57" s="26">
-        <v>0</v>
-      </c>
-      <c r="D57" s="27">
-        <v>0</v>
-      </c>
-      <c r="E57" s="27">
+      <c r="C57" s="34">
+        <v>0</v>
+      </c>
+      <c r="D57" s="35">
+        <v>0</v>
+      </c>
+      <c r="E57" s="35">
         <v>460736</v>
       </c>
-      <c r="F57" s="27">
+      <c r="F57" s="35">
         <v>218671</v>
       </c>
-      <c r="G57" s="30">
+      <c r="G57" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H57" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="32">
+      <c r="H57" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="28">
+      <c r="A58" s="36">
         <v>46253</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="37">
         <f>B57-195+5550+2720-300-3504+1730</f>
         <v>386792.7</v>
       </c>
-      <c r="C58" s="26">
-        <v>0</v>
-      </c>
-      <c r="D58" s="27">
-        <v>0</v>
-      </c>
-      <c r="E58" s="27">
+      <c r="C58" s="34">
+        <v>0</v>
+      </c>
+      <c r="D58" s="35">
+        <v>0</v>
+      </c>
+      <c r="E58" s="35">
         <v>460736</v>
       </c>
-      <c r="F58" s="27">
+      <c r="F58" s="35">
         <v>218671</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G58" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H58" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="32">
+      <c r="H58" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K58" s="32">
+      <c r="K58" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="28">
+      <c r="A59" s="36">
         <v>46254</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="37">
         <f>B58+155+870-1360+1107.05+1330+1165.8+1267.76</f>
         <v>391328.31</v>
       </c>
-      <c r="C59" s="26">
-        <v>0</v>
-      </c>
-      <c r="D59" s="27">
-        <v>0</v>
-      </c>
-      <c r="E59" s="27">
+      <c r="C59" s="34">
+        <v>0</v>
+      </c>
+      <c r="D59" s="35">
+        <v>0</v>
+      </c>
+      <c r="E59" s="35">
         <v>460736</v>
       </c>
-      <c r="F59" s="27">
+      <c r="F59" s="35">
         <v>218671</v>
       </c>
-      <c r="G59" s="30">
+      <c r="G59" s="38">
         <f t="shared" si="5"/>
         <v>679407</v>
       </c>
-      <c r="H59" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="32">
+      <c r="H59" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="39">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="39">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="28">
+      <c r="A60" s="36">
         <v>46255</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="37">
         <f>B59-445-450-580+585-575-2123</f>
         <v>387740.31</v>
       </c>
-      <c r="C60" s="26">
-        <v>0</v>
-      </c>
-      <c r="D60" s="27">
-        <v>0</v>
-      </c>
-      <c r="E60" s="27">
+      <c r="C60" s="34">
+        <v>0</v>
+      </c>
+      <c r="D60" s="35">
+        <v>0</v>
+      </c>
+      <c r="E60" s="35">
         <v>775877</v>
       </c>
-      <c r="F60" s="27">
+      <c r="F60" s="35">
         <v>218671</v>
       </c>
-      <c r="G60" s="30">
+      <c r="G60" s="38">
         <f t="shared" si="5"/>
         <v>994548</v>
       </c>
-      <c r="H60" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="32">
+      <c r="H60" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="39">
         <f t="shared" si="2"/>
         <v>0.78013027023331205</v>
       </c>
-      <c r="K60" s="32">
+      <c r="K60" s="39">
         <f t="shared" si="3"/>
         <v>0.21986972976668798</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="28">
+      <c r="A61" s="36">
         <v>46258</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="37">
         <f>B60+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C61" s="26">
-        <v>0</v>
-      </c>
-      <c r="D61" s="27">
-        <v>0</v>
-      </c>
-      <c r="E61" s="27">
+      <c r="C61" s="34">
+        <v>0</v>
+      </c>
+      <c r="D61" s="35">
+        <v>0</v>
+      </c>
+      <c r="E61" s="35">
         <v>480842</v>
       </c>
-      <c r="F61" s="27">
+      <c r="F61" s="35">
         <v>218671</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="38">
         <f t="shared" si="5"/>
         <v>699513</v>
       </c>
-      <c r="H61" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="32">
+      <c r="H61" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="39">
         <f t="shared" si="2"/>
         <v>0.6873953736385171</v>
       </c>
-      <c r="K61" s="32">
+      <c r="K61" s="39">
         <f t="shared" si="3"/>
         <v>0.3126046263614829</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="28">
+      <c r="A62" s="36">
         <v>46259</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="37">
         <f>B61-390+1290+906-402+1017</f>
         <v>396282.31</v>
       </c>
-      <c r="C62" s="26">
-        <v>0</v>
-      </c>
-      <c r="D62" s="30">
+      <c r="C62" s="34">
+        <v>0</v>
+      </c>
+      <c r="D62" s="38">
         <f t="shared" ref="D62:D65" si="7">B62-E62-F62</f>
         <v>341611.31</v>
       </c>
-      <c r="E62" s="27">
-        <v>0</v>
-      </c>
-      <c r="F62" s="27">
+      <c r="E62" s="35">
+        <v>0</v>
+      </c>
+      <c r="F62" s="35">
         <v>54671</v>
       </c>
-      <c r="G62" s="30">
+      <c r="G62" s="38">
         <f t="shared" si="5"/>
         <v>396282.31</v>
       </c>
-      <c r="H62" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="32">
+      <c r="H62" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="39">
         <f t="shared" si="1"/>
         <v>0.86204027123996529</v>
       </c>
-      <c r="J62" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="32">
+      <c r="J62" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="39">
         <f t="shared" si="3"/>
         <v>0.13795972876003473</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="28">
+      <c r="A63" s="36">
         <v>46260</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="37">
         <f>B62+270-750</f>
         <v>395802.31</v>
       </c>
-      <c r="C63" s="26">
-        <v>0</v>
-      </c>
-      <c r="D63" s="30">
+      <c r="C63" s="34">
+        <v>0</v>
+      </c>
+      <c r="D63" s="38">
         <f t="shared" si="7"/>
         <v>341131.31</v>
       </c>
-      <c r="E63" s="27">
-        <v>0</v>
-      </c>
-      <c r="F63" s="27">
+      <c r="E63" s="35">
+        <v>0</v>
+      </c>
+      <c r="F63" s="35">
         <v>54671</v>
       </c>
-      <c r="G63" s="30">
+      <c r="G63" s="38">
         <f t="shared" si="5"/>
         <v>395802.31</v>
       </c>
-      <c r="H63" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="32">
+      <c r="H63" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="39">
         <f t="shared" si="1"/>
         <v>0.86187296380357159</v>
       </c>
-      <c r="J63" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K63" s="32">
+      <c r="J63" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="39">
         <f t="shared" si="3"/>
         <v>0.13812703619642847</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="28">
+      <c r="A64" s="36">
         <v>46261</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="37">
         <f>B63+125+690</f>
         <v>396617.31</v>
       </c>
-      <c r="C64" s="26">
-        <v>0</v>
-      </c>
-      <c r="D64" s="30">
+      <c r="C64" s="34">
+        <v>0</v>
+      </c>
+      <c r="D64" s="38">
         <f t="shared" si="7"/>
         <v>341946.31</v>
       </c>
-      <c r="E64" s="27">
-        <v>0</v>
-      </c>
-      <c r="F64" s="27">
+      <c r="E64" s="35">
+        <v>0</v>
+      </c>
+      <c r="F64" s="35">
         <v>54671</v>
       </c>
-      <c r="G64" s="30">
+      <c r="G64" s="38">
         <f t="shared" si="5"/>
         <v>396617.31</v>
       </c>
-      <c r="H64" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="32">
+      <c r="H64" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="39">
         <f t="shared" si="1"/>
         <v>0.8621567979471193</v>
       </c>
-      <c r="J64" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K64" s="32">
+      <c r="J64" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="39">
         <f t="shared" si="3"/>
         <v>0.13784320205288064</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="28">
+      <c r="A65" s="36">
         <v>46262</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="37">
         <f>B64+300</f>
         <v>396917.31</v>
       </c>
-      <c r="C65" s="26">
-        <v>0</v>
-      </c>
-      <c r="D65" s="30">
+      <c r="C65" s="34">
+        <v>0</v>
+      </c>
+      <c r="D65" s="38">
         <f t="shared" si="7"/>
         <v>342246.31</v>
       </c>
-      <c r="E65" s="27">
-        <v>0</v>
-      </c>
-      <c r="F65" s="27">
+      <c r="E65" s="35">
+        <v>0</v>
+      </c>
+      <c r="F65" s="35">
         <v>54671</v>
       </c>
-      <c r="G65" s="30">
+      <c r="G65" s="38">
         <f t="shared" si="5"/>
         <v>396917.31</v>
       </c>
-      <c r="H65" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="32">
+      <c r="H65" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="39">
         <f t="shared" si="1"/>
         <v>0.86226098327634038</v>
       </c>
-      <c r="J65" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K65" s="32">
+      <c r="J65" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="39">
         <f t="shared" si="3"/>
         <v>0.13773901672365965</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="28">
+      <c r="A66" s="36">
         <v>46265</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="37">
         <f>B65+135+2220-2.59</f>
         <v>399269.72</v>
       </c>
-      <c r="C66" s="26">
+      <c r="C66" s="34">
         <v>59799</v>
       </c>
-      <c r="D66" s="30">
-        <v>0</v>
-      </c>
-      <c r="E66" s="27">
-        <v>0</v>
-      </c>
-      <c r="F66" s="27">
+      <c r="D66" s="38">
+        <v>0</v>
+      </c>
+      <c r="E66" s="35">
+        <v>0</v>
+      </c>
+      <c r="F66" s="35">
         <v>54671</v>
       </c>
-      <c r="G66" s="30">
+      <c r="G66" s="38">
         <f t="shared" si="5"/>
         <v>114470</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="39">
         <f t="shared" si="0"/>
         <v>0.52239888180309246</v>
       </c>
-      <c r="I66" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="32">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="32">
+      <c r="I66" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K66" s="39">
         <f t="shared" si="3"/>
         <v>0.47760111819690748</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="28">
+      <c r="A67" s="36">
         <v>46266</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="37">
         <f>B66+480-562+1405-1361-623+1800+428</f>
         <v>400836.72</v>
       </c>
-      <c r="C67" s="26">
+      <c r="C67" s="34">
         <v>871422</v>
       </c>
-      <c r="D67" s="27">
-        <v>0</v>
-      </c>
-      <c r="E67" s="27">
-        <v>0</v>
-      </c>
-      <c r="F67" s="27">
+      <c r="D67" s="35">
+        <v>0</v>
+      </c>
+      <c r="E67" s="35">
+        <v>0</v>
+      </c>
+      <c r="F67" s="35">
         <v>54671</v>
       </c>
-      <c r="G67" s="30">
+      <c r="G67" s="38">
         <f t="shared" si="5"/>
         <v>926093</v>
       </c>
-      <c r="H67" s="32">
+      <c r="H67" s="39">
         <f t="shared" ref="H67:H70" si="8">C67/G67</f>
         <v>0.94096597209999433</v>
       </c>
-      <c r="I67" s="32">
+      <c r="I67" s="39">
         <f t="shared" ref="I67:I70" si="9">D67/G67</f>
         <v>0</v>
       </c>
-      <c r="J67" s="32">
+      <c r="J67" s="39">
         <f t="shared" ref="J67:J70" si="10">E67/G67</f>
         <v>0</v>
       </c>
-      <c r="K67" s="32">
+      <c r="K67" s="39">
         <f t="shared" ref="K67:K70" si="11">F67/G67</f>
         <v>5.9034027900005726E-2</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="28">
+      <c r="A68" s="36">
         <v>46267</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="37">
         <f>B67-274+71-569+1738+320</f>
         <v>402122.72</v>
       </c>
-      <c r="C68" s="26">
+      <c r="C68" s="34">
         <f>C67-132000</f>
         <v>739422</v>
       </c>
-      <c r="D68" s="27">
-        <v>0</v>
-      </c>
-      <c r="E68" s="27">
-        <v>0</v>
-      </c>
-      <c r="F68" s="27">
+      <c r="D68" s="35">
+        <v>0</v>
+      </c>
+      <c r="E68" s="35">
+        <v>0</v>
+      </c>
+      <c r="F68" s="35">
         <v>54671</v>
       </c>
-      <c r="G68" s="30">
+      <c r="G68" s="38">
         <f t="shared" si="5"/>
         <v>794093</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="39">
         <f t="shared" si="8"/>
         <v>0.93115290022705144</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="39">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="39">
         <f t="shared" si="11"/>
         <v>6.8847099772948506E-2</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="28">
+      <c r="A69" s="36">
         <v>46268</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="37">
         <f>B68-274+71-569+1738+320</f>
         <v>403408.72</v>
       </c>
-      <c r="C69" s="26">
+      <c r="C69" s="34">
         <v>101060</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="38">
         <f>B69-C69</f>
         <v>302348.71999999997</v>
       </c>
-      <c r="E69" s="27">
-        <v>0</v>
-      </c>
-      <c r="F69" s="27">
-        <v>0</v>
-      </c>
-      <c r="G69" s="30">
+      <c r="E69" s="35">
+        <v>0</v>
+      </c>
+      <c r="F69" s="35">
+        <v>0</v>
+      </c>
+      <c r="G69" s="38">
         <f t="shared" si="5"/>
         <v>403408.72</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="39">
         <f t="shared" si="8"/>
         <v>0.25051515991027662</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="39">
         <f t="shared" si="9"/>
         <v>0.74948484008972338</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="39">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="28">
+      <c r="A70" s="36">
         <v>46269</v>
       </c>
-      <c r="H70" s="32" t="e">
+      <c r="H70" s="39" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="32" t="e">
+      <c r="I70" s="39" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J70" s="32" t="e">
+      <c r="J70" s="39" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K70" s="32" t="e">
+      <c r="K70" s="39" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1048543" s="28"/>
+      <c r="A1048543" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A8418E-C92C-7E42-BDA1-775D05FEF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5002D346-D292-514C-A91D-B68A1DEC6E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6860" yWindow="-38360" windowWidth="45300" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16460" yWindow="-27480" windowWidth="53320" windowHeight="23200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
   <si>
     <t>Trade ID</t>
   </si>
@@ -425,6 +425,9 @@
     <t>Ann. Return</t>
   </si>
   <si>
+    <t>Metals</t>
+  </si>
+  <si>
     <t>Balance</t>
   </si>
   <si>
@@ -447,6 +450,21 @@
   </si>
   <si>
     <t>ETF_Exposure</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Softs</t>
+  </si>
+  <si>
+    <t>Volatility</t>
+  </si>
+  <si>
+    <t>Sectoral</t>
+  </si>
+  <si>
+    <t>Index</t>
   </si>
 </sst>
 </file>
@@ -497,7 +515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,6 +552,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -547,29 +571,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -578,12 +581,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -594,34 +591,9 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,9 +605,6 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -661,6 +630,62 @@
     <xf numFmtId="9" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -975,2188 +1000,2284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="11.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.1640625" style="4"/>
+    <col min="1" max="1" width="8" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="20" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="20" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" style="20" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.1640625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="21">
         <v>46175</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="21">
         <v>46181</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="22">
         <f t="shared" ref="D2:D25" si="0">C2-B2</f>
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="20">
         <v>-100</v>
       </c>
-      <c r="L2" s="4">
+      <c r="M2" s="20">
         <v>1057.1199999999999</v>
       </c>
-      <c r="M2" s="4">
+      <c r="N2" s="20">
         <v>941.37</v>
       </c>
-      <c r="N2" s="4">
-        <f t="shared" ref="N2:N11" si="1">M2</f>
+      <c r="O2" s="20">
+        <f t="shared" ref="O2:O11" si="1">N2</f>
         <v>941.37</v>
       </c>
-      <c r="O2" s="16">
+      <c r="P2" s="26">
         <v>105712</v>
       </c>
-      <c r="P2" s="4">
+      <c r="Q2" s="20">
         <v>2.94</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="R2" s="20">
         <v>1</v>
       </c>
-      <c r="R2" s="5">
-        <f t="shared" ref="R2:R12" si="2">IF(Q2=1, ABS(M2-L2)/L2, 0)</f>
+      <c r="S2" s="27">
+        <f t="shared" ref="S2:S12" si="2">IF(R2=1, ABS(N2-M2)/M2, 0)</f>
         <v>0.10949561071590727</v>
       </c>
-      <c r="S2" s="4">
+      <c r="T2" s="20">
         <v>11575</v>
       </c>
-      <c r="T2" s="13">
+      <c r="U2" s="4">
         <v>11575</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="21">
         <v>46177</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="21">
         <v>46185</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="24">
         <v>-450</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="24">
         <v>308.14999999999998</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="24">
         <v>317.27260000000001</v>
       </c>
-      <c r="N3" s="4">
+      <c r="O3" s="20">
         <f t="shared" si="1"/>
         <v>317.27260000000001</v>
       </c>
-      <c r="O3" s="17">
+      <c r="P3" s="28">
         <v>138667.5</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="24">
         <v>-7.92</v>
       </c>
-      <c r="Q3" s="3">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5">
+      <c r="R3" s="24">
+        <v>0</v>
+      </c>
+      <c r="S3" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="24">
         <v>-4105.18</v>
       </c>
-      <c r="T3" s="14">
+      <c r="U3" s="5">
         <v>-4105.18</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="21">
         <v>46178</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="21">
         <v>46183</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="22">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="20">
         <v>2</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="20">
         <v>66.334999999999994</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="20">
         <v>63</v>
       </c>
-      <c r="N4" s="4">
+      <c r="O4" s="20">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="O4" s="16">
+      <c r="P4" s="26">
         <v>663350</v>
       </c>
-      <c r="P4" s="4">
+      <c r="Q4" s="20">
         <v>10.08</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="20">
         <v>1</v>
       </c>
-      <c r="R4" s="5">
+      <c r="S4" s="27">
         <f t="shared" si="2"/>
         <v>5.0275118715610072E-2</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="20">
         <v>-33350</v>
       </c>
-      <c r="T4" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="21">
         <v>46181</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="21">
         <v>46182</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="20">
         <v>10</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="20">
         <v>1.1535</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="20">
         <v>1.1579600000000001</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="20">
         <f t="shared" si="1"/>
         <v>1.1579600000000001</v>
       </c>
-      <c r="O5" s="16">
+      <c r="P5" s="26">
         <v>2894900</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="20">
         <v>-98.8</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="20">
         <v>1</v>
       </c>
-      <c r="R5" s="5">
+      <c r="S5" s="27">
         <f t="shared" si="2"/>
         <v>3.8664932813178418E-3</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="20">
         <v>11150</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="4">
         <v>11150</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="20">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="21">
         <v>46183</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="21">
         <v>46203</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="22">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="20">
         <v>3</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="20">
         <v>61.529200000000003</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="20">
         <v>66.92</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="20">
         <f t="shared" si="1"/>
         <v>66.92</v>
       </c>
-      <c r="O6" s="16">
+      <c r="P6" s="26">
         <v>461468.75</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="20">
         <v>14.22</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="20">
         <v>1</v>
       </c>
-      <c r="R6" s="5">
+      <c r="S6" s="27">
         <f t="shared" si="2"/>
         <v>8.761368585972186E-2</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="20">
         <v>40406.25</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="4">
         <v>6343</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="21">
         <v>46190</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="21">
         <v>46195</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="20">
         <v>-3</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="20">
         <v>4374.66</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="20">
         <v>4575</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="20">
         <f t="shared" si="1"/>
         <v>4575</v>
       </c>
-      <c r="O7" s="16">
+      <c r="P7" s="26">
         <v>131240</v>
       </c>
-      <c r="P7" s="4">
+      <c r="Q7" s="20">
         <v>17.82</v>
       </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5">
+      <c r="R7" s="20">
+        <v>0</v>
+      </c>
+      <c r="S7" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="20">
         <v>-6010</v>
       </c>
-      <c r="T7" s="14">
+      <c r="U7" s="5">
         <v>-6010</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="21">
         <v>46194</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="21">
         <v>46205</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="22">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="20">
         <v>20</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="20">
         <v>1.2499125</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="20">
         <v>1.2517849999999999</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="20">
         <f t="shared" si="1"/>
         <v>1.2517849999999999</v>
       </c>
-      <c r="O8" s="16">
+      <c r="P8" s="26">
         <v>3124781</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="20">
         <v>98.8</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="20">
         <v>1</v>
       </c>
-      <c r="R8" s="5">
+      <c r="S8" s="27">
         <f t="shared" si="2"/>
         <v>1.4981048673406688E-3</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="20">
         <v>4681.25</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="4">
         <v>4681.25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="24">
         <v>7</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="21">
         <v>46197</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="21">
         <v>46203</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="22">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="24">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="24">
         <v>241.2475</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="24">
         <v>242.61</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="20">
         <f t="shared" si="1"/>
         <v>242.61</v>
       </c>
-      <c r="O9" s="17">
+      <c r="P9" s="28">
         <v>96499</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="24">
         <v>7.43</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="24">
         <v>1</v>
       </c>
-      <c r="R9" s="5">
+      <c r="S9" s="27">
         <f t="shared" si="2"/>
         <v>5.6477269194499897E-3</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="24">
         <v>-545</v>
       </c>
-      <c r="T9" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="U9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="21">
         <v>46197</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="21">
         <v>46203</v>
       </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="22">
+        <v>0</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="24">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="24">
         <v>120.746</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="24">
         <v>124.35</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="20">
         <f t="shared" si="1"/>
         <v>124.35</v>
       </c>
-      <c r="O10" s="17">
+      <c r="P10" s="28">
         <v>96596.800000000003</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="24">
         <v>12.93</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="24">
         <v>1</v>
       </c>
-      <c r="R10" s="5">
+      <c r="S10" s="27">
         <f t="shared" si="2"/>
         <v>2.9847779636592513E-2</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="24">
         <v>2883.2</v>
       </c>
-      <c r="T10" s="15">
+      <c r="U10" s="6">
         <v>2338.1999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="20">
         <v>3</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="21">
         <v>46198</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="21">
         <v>46203</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="22">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K11" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="20">
         <v>-1</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="20">
         <v>4042.5</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="20">
         <v>4028.25</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="20">
         <f t="shared" si="1"/>
         <v>4028.25</v>
       </c>
-      <c r="O11" s="16">
+      <c r="P11" s="26">
         <v>202125</v>
       </c>
-      <c r="P11" s="4">
+      <c r="Q11" s="20">
         <v>4.74</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="20">
         <v>1</v>
       </c>
-      <c r="R11" s="5">
+      <c r="S11" s="27">
         <f t="shared" si="2"/>
         <v>3.5250463821892395E-3</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="20">
         <v>-712.5</v>
       </c>
-      <c r="T11" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="24">
         <v>8</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="21">
         <v>46202</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="21">
         <f ca="1">TODAY()</f>
         <v>46269</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="22">
         <f t="shared" ca="1" si="0"/>
         <v>67</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="24">
         <v>-3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="24">
         <v>74.614400000000003</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="24">
         <v>73.084999999999994</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="24">
         <v>73.084999999999994</v>
       </c>
-      <c r="O12" s="17">
+      <c r="P12" s="28">
         <v>223843.28</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="24">
         <v>44.49</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="24">
         <v>1</v>
       </c>
-      <c r="R12" s="5">
+      <c r="S12" s="27">
         <f t="shared" si="2"/>
         <v>2.0497383883003945E-2</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="24">
         <v>4588</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="4">
         <v>4588</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="24">
         <v>9</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="21">
         <v>46202</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="21">
         <v>46204</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="22">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="24">
         <v>100</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="24">
         <v>550.35</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="24">
         <v>597.52</v>
       </c>
-      <c r="N13" s="4">
-        <f>M13</f>
+      <c r="O13" s="20">
+        <f>N13</f>
         <v>597.52</v>
       </c>
-      <c r="O13" s="17">
+      <c r="P13" s="28">
         <v>55035</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="24">
         <v>2.29</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="24">
         <v>1</v>
       </c>
-      <c r="R13" s="5">
-        <f t="shared" ref="R13:R19" si="3">IF(Q13=1, ABS(M13-L13)/L13, 0)</f>
+      <c r="S13" s="27">
+        <f t="shared" ref="S13:S19" si="3">IF(R13=1, ABS(N13-M13)/M13, 0)</f>
         <v>8.5709094212773618E-2</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="24">
         <v>4717</v>
       </c>
-      <c r="T13" s="15">
+      <c r="U13" s="6">
         <v>4717</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="20">
         <v>10</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="21">
         <v>46203</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="21">
         <v>46255</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="22">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="20">
         <v>60</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="20">
         <v>20.177299999999999</v>
       </c>
-      <c r="M14" s="4">
+      <c r="N14" s="20">
         <v>17.451599999999999</v>
       </c>
-      <c r="N14" s="4">
+      <c r="O14" s="20">
         <v>17.451599999999999</v>
       </c>
-      <c r="O14" s="16">
+      <c r="P14" s="26">
         <v>121064</v>
       </c>
-      <c r="P14" s="4">
+      <c r="Q14" s="20">
         <v>55.5</v>
       </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5">
+      <c r="R14" s="20">
+        <v>0</v>
+      </c>
+      <c r="S14" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="20">
         <v>-16354</v>
       </c>
-      <c r="T14" s="25">
+      <c r="U14" s="7">
         <v>-16354</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="20">
         <v>11</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="21">
         <v>46205</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="21">
         <v>46205</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="D15" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="20">
         <v>-1</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="20">
         <v>3.0939999999999999</v>
       </c>
-      <c r="M15" s="4">
+      <c r="N15" s="20">
         <v>3.0255000000000001</v>
       </c>
-      <c r="N15" s="4">
-        <f>M15</f>
+      <c r="O15" s="20">
+        <f>N15</f>
         <v>3.0255000000000001</v>
       </c>
-      <c r="O15" s="16">
+      <c r="P15" s="26">
         <v>116025</v>
       </c>
-      <c r="P15" s="4">
+      <c r="Q15" s="20">
         <v>5.94</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="20">
         <v>1</v>
       </c>
-      <c r="R15" s="5">
+      <c r="S15" s="27">
         <f t="shared" si="3"/>
         <v>2.2139625080801483E-2</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="20">
         <v>2568.75</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="4">
         <v>2568.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="24">
         <v>12</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="21">
         <v>46211</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="21">
         <v>46217</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="22">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="24">
         <v>-75</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="24">
         <v>1210.816</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="24">
         <v>1155.49</v>
       </c>
-      <c r="N16" s="4">
-        <f>M16</f>
+      <c r="O16" s="20">
+        <f>N16</f>
         <v>1155.49</v>
       </c>
-      <c r="O16" s="17">
+      <c r="P16" s="28">
         <v>90811.199999999997</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="24">
         <v>2.9</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="24">
         <v>1</v>
       </c>
-      <c r="R16" s="5">
+      <c r="S16" s="27">
         <f t="shared" si="3"/>
         <v>4.5693152386489792E-2</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="24">
         <v>4149.45</v>
       </c>
-      <c r="T16" s="15">
+      <c r="U16" s="6">
         <v>4149.45</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" s="20">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="21">
         <v>46231</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="21">
         <v>46233</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="22">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="K17" s="4">
+      <c r="L17" s="20">
         <v>2000</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="20">
         <v>111.46</v>
       </c>
-      <c r="M17" s="4">
+      <c r="N17" s="20">
         <v>117.0329</v>
       </c>
-      <c r="N17" s="4">
-        <f>M17</f>
+      <c r="O17" s="20">
+        <f>N17</f>
         <v>117.0329</v>
       </c>
-      <c r="O17" s="16">
+      <c r="P17" s="26">
         <v>232660</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="20">
         <v>1</v>
       </c>
-      <c r="R17" s="5">
+      <c r="S17" s="27">
         <f t="shared" si="3"/>
         <v>4.9999102817154174E-2</v>
       </c>
-      <c r="S17" s="4">
+      <c r="T17" s="20">
         <v>11150</v>
       </c>
-      <c r="T17" s="13">
+      <c r="U17" s="4">
         <v>11150</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="20">
         <v>14</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="21">
         <v>46231</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="21">
         <v>46233</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="22">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="K18" s="4">
+      <c r="L18" s="20">
         <v>-300</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="20">
         <v>337.98</v>
       </c>
-      <c r="M18" s="4">
+      <c r="N18" s="20">
         <v>331.22</v>
       </c>
-      <c r="N18" s="4">
-        <f>M18</f>
+      <c r="O18" s="20">
+        <f>N18</f>
         <v>331.22</v>
       </c>
-      <c r="O18" s="16">
+      <c r="P18" s="26">
         <v>101964</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="20">
         <v>1</v>
       </c>
-      <c r="R18" s="5">
+      <c r="S18" s="27">
         <f t="shared" si="3"/>
         <v>2.0001183501982336E-2</v>
       </c>
-      <c r="S18" s="4">
+      <c r="T18" s="20">
         <v>2033</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="4">
         <v>2033</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" s="20">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="21">
         <v>46244</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="21">
         <f ca="1">TODAY()</f>
         <v>46269</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="22">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="4">
+      <c r="L19" s="20">
         <v>-500</v>
       </c>
-      <c r="L19" s="4">
+      <c r="M19" s="20">
         <v>108.102</v>
       </c>
-      <c r="M19" s="4">
+      <c r="N19" s="20">
         <v>107.749</v>
       </c>
-      <c r="N19" s="4">
+      <c r="O19" s="20">
         <v>107.749</v>
       </c>
-      <c r="O19" s="16">
+      <c r="P19" s="26">
         <v>54051</v>
       </c>
-      <c r="P19" s="4">
+      <c r="Q19" s="20">
         <v>4.5599999999999996</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="20">
         <v>1</v>
       </c>
-      <c r="R19" s="5">
+      <c r="S19" s="27">
         <f t="shared" si="3"/>
         <v>3.2654344970491629E-3</v>
       </c>
-      <c r="S19" s="4">
+      <c r="T19" s="20">
         <v>177</v>
       </c>
-      <c r="T19" s="13">
+      <c r="U19" s="4">
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" s="20">
         <v>16</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="21">
         <v>46244</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="29">
         <f ca="1">TODAY()</f>
         <v>46269</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="22">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="K20" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="4">
+      <c r="L20" s="20">
         <v>-1</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="20">
         <v>1868.84</v>
       </c>
-      <c r="M20" s="4">
+      <c r="N20" s="20">
         <v>1860.72</v>
       </c>
-      <c r="N20" s="4">
+      <c r="O20" s="20">
         <v>1860.72</v>
       </c>
-      <c r="O20" s="16">
+      <c r="P20" s="26">
         <v>185382</v>
       </c>
-      <c r="P20" s="4">
+      <c r="Q20" s="20">
         <v>11.2</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="20">
         <v>1</v>
       </c>
-      <c r="R20" s="5">
-        <f>IF(Q20=1, ABS(M20-L20)/L20, 0)</f>
+      <c r="S20" s="27">
+        <f>IF(R20=1, ABS(N20-M20)/M20, 0)</f>
         <v>4.3449412469766758E-3</v>
       </c>
-      <c r="S20" s="4">
+      <c r="T20" s="20">
         <v>4060</v>
       </c>
-      <c r="T20" s="13">
+      <c r="U20" s="4">
         <v>4060</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" s="20">
         <v>17</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="21">
         <v>46246</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="21">
         <v>46259</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="22">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="K21" s="4">
+      <c r="L21" s="20">
         <v>2000</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="20">
         <v>82.31</v>
       </c>
-      <c r="M21" s="4">
+      <c r="N21" s="20">
         <v>83.02</v>
       </c>
-      <c r="N21" s="4">
+      <c r="O21" s="20">
         <v>83.02</v>
       </c>
-      <c r="O21" s="16">
+      <c r="P21" s="26">
         <v>164620</v>
       </c>
-      <c r="P21" s="4">
+      <c r="Q21" s="20">
         <v>23.92</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="20">
         <v>1</v>
       </c>
-      <c r="R21" s="5">
-        <f>IF(Q21=1, ABS(M21-L21)/L21, 0)</f>
+      <c r="S21" s="27">
+        <f>IF(R21=1, ABS(N21-M21)/M21, 0)</f>
         <v>8.6259263758959263E-3</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="20">
         <v>1420</v>
       </c>
-      <c r="T21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" s="20">
         <v>17</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="21">
         <v>46246</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="21">
         <v>46259</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="22">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="K22" s="4">
+      <c r="L22" s="20">
         <v>-4</v>
       </c>
-      <c r="L22" s="4">
+      <c r="M22" s="20">
         <v>7763</v>
       </c>
-      <c r="M22" s="4">
+      <c r="N22" s="20">
         <v>7689.75</v>
       </c>
-      <c r="N22" s="4">
+      <c r="O22" s="20">
         <v>7689.75</v>
       </c>
-      <c r="O22" s="16">
+      <c r="P22" s="26">
         <v>154290</v>
       </c>
-      <c r="P22" s="4">
+      <c r="Q22" s="20">
         <v>17.079999999999998</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="R22" s="20">
         <v>1</v>
       </c>
-      <c r="R22" s="5">
-        <f>IF(Q22=1, ABS(M22-L22)/L22, 0)</f>
+      <c r="S22" s="27">
+        <f>IF(R22=1, ABS(N22-M22)/M22, 0)</f>
         <v>9.435785134612908E-3</v>
       </c>
-      <c r="S22" s="4">
+      <c r="T22" s="20">
         <v>1418</v>
       </c>
-      <c r="T22" s="13">
+      <c r="U22" s="4">
         <v>2838</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A23" s="20">
         <v>18</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="21">
         <v>46246</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="21">
         <v>46246</v>
       </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="4">
+      <c r="L23" s="20">
         <v>-10</v>
       </c>
-      <c r="L23" s="4">
+      <c r="M23" s="20">
         <v>0.16914999999999999</v>
       </c>
-      <c r="M23" s="4">
+      <c r="N23" s="20">
         <v>0.16313</v>
       </c>
-      <c r="N23" s="4">
+      <c r="O23" s="20">
         <v>0.16313</v>
       </c>
-      <c r="O23" s="16">
+      <c r="P23" s="26">
         <v>182705</v>
       </c>
-      <c r="P23" s="4">
+      <c r="Q23" s="20">
         <v>29.6</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="R23" s="20">
         <v>1</v>
       </c>
-      <c r="R23" s="5">
-        <f>IF(Q23=1, ABS(M23-L23)/L23, 0)</f>
+      <c r="S23" s="27">
+        <f>IF(R23=1, ABS(N23-M23)/M23, 0)</f>
         <v>3.5589713272243556E-2</v>
       </c>
-      <c r="S23" s="4">
+      <c r="T23" s="20">
         <v>6742</v>
       </c>
-      <c r="T23" s="13">
+      <c r="U23" s="4">
         <v>6742</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A24" s="20">
         <v>19</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="21">
         <v>46254</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="21">
         <v>46254</v>
       </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K24" s="4">
+      <c r="L24" s="20">
         <v>-10</v>
       </c>
-      <c r="L24" s="4">
+      <c r="M24" s="20">
         <v>1.1704300000000001</v>
       </c>
-      <c r="M24" s="4">
+      <c r="N24" s="20">
         <v>1.1695</v>
       </c>
-      <c r="N24" s="4">
+      <c r="O24" s="20">
         <v>1.1695</v>
       </c>
-      <c r="O24" s="16">
+      <c r="P24" s="26">
         <v>1451000</v>
       </c>
-      <c r="P24" s="4">
+      <c r="Q24" s="20">
         <v>6.28</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="R24" s="20">
         <v>1</v>
       </c>
-      <c r="R24" s="5">
+      <c r="S24" s="27">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="S24" s="4">
+      <c r="T24" s="20">
         <v>1245</v>
       </c>
-      <c r="T24" s="13">
+      <c r="U24" s="4">
         <v>1245</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A25" s="20">
         <v>20</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="21">
         <v>46255</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="21">
         <v>46257</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="22">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="4">
+      <c r="L25" s="20">
         <v>-6</v>
       </c>
-      <c r="L25" s="4">
+      <c r="M25" s="20">
         <v>0.72838000000000003</v>
       </c>
-      <c r="M25" s="4">
+      <c r="N25" s="20">
         <v>0.72550000000000003</v>
       </c>
-      <c r="N25" s="4">
+      <c r="O25" s="20">
         <v>0.72550000000000003</v>
       </c>
-      <c r="O25" s="16">
+      <c r="P25" s="26">
         <v>436235</v>
       </c>
-      <c r="P25" s="4">
+      <c r="Q25" s="20">
         <v>4.5599999999999996</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="R25" s="20">
         <v>1</v>
       </c>
-      <c r="R25" s="5">
-        <f t="shared" ref="R25:R31" si="4">IF(Q25=1, ABS(M25-L25)/L25, 0)</f>
+      <c r="S25" s="27">
+        <f t="shared" ref="S25:S31" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
-      <c r="S25" s="4">
+      <c r="T25" s="20">
         <v>1710</v>
       </c>
-      <c r="T25" s="13">
+      <c r="U25" s="4">
         <v>1710</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" s="20">
         <v>21</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="21">
         <v>46258</v>
       </c>
-      <c r="C26" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46269</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" ref="D26:D32" ca="1" si="5">C26-B26</f>
-        <v>11</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="C26" s="21">
+        <v>46259</v>
+      </c>
+      <c r="D26" s="22">
+        <f t="shared" ref="D26:D32" si="5">C26-B26</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K26" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="4">
+      <c r="L26" s="20">
         <v>-3</v>
       </c>
-      <c r="L26" s="4">
+      <c r="M26" s="20">
         <v>4703.32</v>
       </c>
-      <c r="M26" s="4">
+      <c r="N26" s="20">
         <v>4663.8</v>
       </c>
-      <c r="N26" s="4">
+      <c r="O26" s="20">
         <v>4663.8</v>
       </c>
-      <c r="O26" s="16">
+      <c r="P26" s="26">
         <v>141200</v>
       </c>
-      <c r="P26" s="4">
+      <c r="Q26" s="20">
         <v>9.6</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="R26" s="20">
         <v>1</v>
       </c>
-      <c r="R26" s="5">
+      <c r="S26" s="27">
         <f t="shared" si="4"/>
         <v>8.4025752021974973E-3</v>
       </c>
-      <c r="S26" s="4">
+      <c r="T26" s="20">
         <v>715</v>
       </c>
-      <c r="T26" s="13">
+      <c r="U26" s="4">
         <v>715</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A27" s="20">
         <v>22</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="21">
         <v>46258</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="21">
         <v>46258</v>
       </c>
-      <c r="D27" s="7">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D27" s="30">
+        <v>0</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="4">
+      <c r="L27" s="20">
         <v>-1000</v>
       </c>
-      <c r="L27" s="4">
+      <c r="M27" s="20">
         <v>133.33799999999999</v>
       </c>
-      <c r="M27" s="4">
+      <c r="N27" s="20">
         <v>129.84</v>
       </c>
-      <c r="N27" s="4">
+      <c r="O27" s="20">
         <v>129.84</v>
       </c>
-      <c r="O27" s="16">
+      <c r="P27" s="26">
         <v>133338</v>
       </c>
-      <c r="P27" s="4">
+      <c r="Q27" s="20">
         <v>9.65</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="R27" s="20">
         <v>1</v>
       </c>
-      <c r="R27" s="5">
+      <c r="S27" s="27">
         <f t="shared" si="4"/>
         <v>2.623408180713668E-2</v>
       </c>
-      <c r="S27" s="4">
+      <c r="T27" s="20">
         <v>3498</v>
       </c>
-      <c r="T27" s="13">
+      <c r="U27" s="4">
         <v>3498</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28" s="20">
         <v>23</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="21">
         <v>46265</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="21">
         <v>46266</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="22">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="K28" s="4">
+      <c r="L28" s="20">
         <v>-1000</v>
       </c>
-      <c r="L28" s="4">
+      <c r="M28" s="20">
         <v>59.798999999999999</v>
       </c>
-      <c r="M28" s="4">
+      <c r="N28" s="20">
         <v>57.99</v>
       </c>
-      <c r="N28" s="4">
+      <c r="O28" s="20">
         <v>57.99</v>
       </c>
-      <c r="O28" s="16">
+      <c r="P28" s="26">
         <v>59799</v>
       </c>
-      <c r="P28" s="4">
+      <c r="Q28" s="20">
         <v>11.32</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="R28" s="20">
         <v>1</v>
       </c>
-      <c r="R28" s="5">
+      <c r="S28" s="27">
         <f t="shared" si="4"/>
         <v>3.0251341995685504E-2</v>
       </c>
-      <c r="S28" s="4">
+      <c r="T28" s="20">
         <v>1809</v>
       </c>
-      <c r="T28" s="13">
+      <c r="U28" s="4">
         <v>1809</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29" s="20">
         <v>24</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="21">
         <v>46266</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="21">
         <v>46268</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="22">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="4">
+      <c r="L29" s="20">
         <v>900</v>
       </c>
-      <c r="L29" s="4">
+      <c r="M29" s="20">
         <v>269.69299999999998</v>
       </c>
-      <c r="M29" s="4">
+      <c r="N29" s="20">
         <v>270.42500000000001</v>
       </c>
-      <c r="N29" s="4">
+      <c r="O29" s="20">
         <v>270.42500000000001</v>
       </c>
-      <c r="O29" s="16">
+      <c r="P29" s="26">
         <v>242723</v>
       </c>
-      <c r="P29" s="4">
+      <c r="Q29" s="20">
         <v>12.28</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="R29" s="20">
         <v>1</v>
       </c>
-      <c r="R29" s="5">
+      <c r="S29" s="27">
         <f t="shared" si="4"/>
         <v>2.7141972539147393E-3</v>
       </c>
-      <c r="S29" s="4">
+      <c r="T29" s="20">
         <v>2891</v>
       </c>
-      <c r="T29" s="13">
+      <c r="U29" s="4">
         <v>2891</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30" s="20">
         <v>25</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="21">
         <v>46266</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="21">
         <v>46268</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="22">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="J30" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="K30" s="4">
+      <c r="L30" s="20">
         <v>310</v>
       </c>
-      <c r="L30" s="4">
+      <c r="M30" s="20">
         <v>951.66</v>
       </c>
-      <c r="M30" s="4">
+      <c r="N30" s="20">
         <v>949.6</v>
       </c>
-      <c r="N30" s="4">
+      <c r="O30" s="20">
         <v>949.6</v>
       </c>
-      <c r="O30" s="16">
+      <c r="P30" s="26">
         <v>295017</v>
       </c>
-      <c r="P30" s="4">
+      <c r="Q30" s="20">
         <v>9.18</v>
       </c>
-      <c r="Q30" s="4">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5">
+      <c r="R30" s="20">
+        <v>0</v>
+      </c>
+      <c r="S30" s="27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S30" s="4">
+      <c r="T30" s="20">
         <v>-642</v>
       </c>
-      <c r="T30" s="25">
+      <c r="U30" s="7">
         <v>-642</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31" s="20">
         <v>26</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="21">
         <v>46266</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="21">
         <v>46267</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="22">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="K31" s="4">
+      <c r="L31" s="20">
         <v>400</v>
       </c>
-      <c r="L31" s="4">
+      <c r="M31" s="20">
         <v>331.50700000000001</v>
       </c>
-      <c r="M31" s="4">
+      <c r="N31" s="20">
         <v>334.31</v>
       </c>
-      <c r="N31" s="4">
+      <c r="O31" s="20">
         <v>334.31</v>
       </c>
-      <c r="O31" s="16">
+      <c r="P31" s="26">
         <v>132602</v>
       </c>
-      <c r="P31" s="4">
+      <c r="Q31" s="20">
         <v>6.69</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="R31" s="20">
         <v>1</v>
       </c>
-      <c r="R31" s="5">
+      <c r="S31" s="27">
         <f t="shared" si="4"/>
         <v>8.455326735182055E-3</v>
       </c>
-      <c r="S31" s="4">
+      <c r="T31" s="20">
         <v>4108</v>
       </c>
-      <c r="T31" s="13">
+      <c r="U31" s="4">
         <v>4108</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32" s="20">
         <v>27</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="21">
         <v>46266</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="21">
         <v>46268</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="22">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="28" t="s">
+      <c r="J32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K32" s="28">
+      <c r="L32" s="8">
         <v>-2000</v>
       </c>
-      <c r="L32" s="28">
+      <c r="M32" s="8">
         <v>50.406999999999996</v>
       </c>
-      <c r="M32" s="28" t="s">
+      <c r="N32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N32" s="28">
-        <v>50.59</v>
-      </c>
-      <c r="O32" s="30">
+      <c r="O32" s="8">
+        <v>50.14</v>
+      </c>
+      <c r="P32" s="10">
         <v>100080</v>
       </c>
-      <c r="P32" s="28">
+      <c r="Q32" s="8">
         <v>1.21</v>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="R32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="R32" s="31" t="s">
+      <c r="S32" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="S32" s="28" t="s">
+      <c r="T32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T32" s="30" t="s">
+      <c r="U32" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="U32" s="4">
-        <v>-96</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="F33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="O33" s="16"/>
-      <c r="R33" s="5"/>
-      <c r="T33" s="16"/>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="F34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="O34" s="16"/>
-      <c r="R34" s="5"/>
-      <c r="T34" s="16"/>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F35" s="11"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D36" s="24" t="s">
+      <c r="V32" s="20">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="F33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="P33" s="26"/>
+      <c r="S33" s="27"/>
+      <c r="U33" s="26"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="F34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="P34" s="26"/>
+      <c r="S34" s="27"/>
+      <c r="U34" s="26"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F35" s="23"/>
+      <c r="H35" s="23"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="D36" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="7">
-        <f ca="1">AVERAGE(D2:D24)</f>
-        <v>11.478260869565217</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="T36" s="16">
-        <f>SUM(T2:T31)</f>
+      <c r="E36" s="30">
+        <f ca="1">AVERAGE(D2:D32)</f>
+        <v>8.870967741935484</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="U36" s="26">
+        <f>SUM(U2:U31)</f>
         <v>67975.47</v>
       </c>
-      <c r="U36" s="16">
-        <f>SUM(U2:U32)</f>
-        <v>-96</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D37" s="24" t="s">
+      <c r="V36" s="26">
+        <f>SUM(V2:V32)</f>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="D37" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="7">
-        <f ca="1">AVERAGE(D2:D11,D13,D15:D25)</f>
-        <v>6.6818181818181817</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="T37" s="4" t="s">
+      <c r="E37" s="30">
+        <f ca="1">AVERAGE(D2:D11,D13,D15:D32)</f>
+        <v>5.3793103448275863</v>
+      </c>
+      <c r="F37" s="23"/>
+      <c r="U37" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="U37" s="11" t="s">
+      <c r="V37" s="23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F38" s="11"/>
-      <c r="T38" s="4" t="s">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F38" s="23"/>
+      <c r="U38" s="20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F39" s="11"/>
-      <c r="T39" s="16">
-        <f>T36+U36</f>
-        <v>67879.47</v>
-      </c>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F40" s="11"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F41" s="11"/>
-      <c r="T41" s="11" t="s">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F39" s="23"/>
+      <c r="U39" s="26">
+        <f>U36+V36</f>
+        <v>68459.47</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F40" s="23"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F41" s="23"/>
+      <c r="U41" s="23" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F42" s="11"/>
-      <c r="T42" s="16">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F42" s="23"/>
+      <c r="U42" s="26">
         <v>333000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="T44" s="4" t="s">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U44" s="20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="T45" s="23">
-        <f>T39/T42</f>
-        <v>0.20384225225225225</v>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U45" s="32">
+        <f>U39/U42</f>
+        <v>0.20558399399399399</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:T16">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:U16">
     <sortCondition ref="B2:B16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3168,1080 +3289,1082 @@
   <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="34" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.5" style="36"/>
+    <col min="7" max="7" width="15.33203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="32"/>
+      <c r="G1" s="37"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="18">
+      <c r="A2" s="38">
         <v>46184</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="34">
         <v>333455.63</v>
       </c>
-      <c r="C2" s="21">
-        <v>0</v>
-      </c>
-      <c r="D2" s="26">
-        <v>0</v>
-      </c>
-      <c r="G2" s="32" t="s">
+      <c r="C2" s="33">
+        <v>0</v>
+      </c>
+      <c r="D2" s="35">
+        <v>0</v>
+      </c>
+      <c r="G2" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="39">
         <f>AVERAGE(C3:C62)</f>
         <v>1236.5848333333329</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
+      <c r="A3" s="38">
         <v>46185</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="34">
         <v>350216.98</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="34">
         <f>B3-B2</f>
         <v>16761.349999999977</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="35">
         <f>C3/B2</f>
         <v>5.0265608051062075E-2</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="39">
         <f>_xlfn.STDEV.S(C3:C62)</f>
         <v>4530.4268575400629</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+      <c r="A4" s="38">
         <v>46188</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="34">
         <v>356930.64</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="34">
         <f t="shared" ref="C4:C62" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="35">
         <f t="shared" ref="D4:D62" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="40">
         <f>(H2/H3)*SQRT(252)</f>
         <v>4.33296382029316</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+      <c r="A5" s="38">
         <v>46189</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="34">
         <v>351815.49</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="34">
         <f t="shared" si="0"/>
         <v>-5115.1500000000233</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="35">
         <f t="shared" si="1"/>
         <v>-1.4330935556555255E-2</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="41">
         <f>_xlfn.STDEV.S(D2:D62)*SQRT(252)</f>
         <v>0.1970845339269621</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="38">
         <v>46190</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="34">
         <v>358486.01</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="34">
         <f t="shared" si="0"/>
         <v>6670.5200000000186</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="35">
         <f t="shared" si="1"/>
         <v>1.8960279435109632E-2</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="27" cm="1">
+      <c r="H6" s="41" cm="1">
         <f t="array" ref="H6">PRODUCT(1+D2:D62)-1</f>
         <v>0.22250363564112119</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="38">
         <v>46191</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="34">
         <v>360758.08</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="34">
         <f t="shared" si="0"/>
         <v>2272.070000000007</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="35">
         <f t="shared" si="1"/>
         <v>6.3379600224845786E-3</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="27" cm="1">
+      <c r="H7" s="41" cm="1">
         <f t="array" ref="H7">PRODUCT(1+D2:D62)^(252/COUNT(D2:D62))-1</f>
         <v>1.2932071188156953</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="38">
         <v>46192</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="34">
         <v>360243.39</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="34">
         <f t="shared" si="0"/>
         <v>-514.69000000000233</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="35">
         <f t="shared" si="1"/>
         <v>-1.4266901520265389E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+      <c r="A9" s="38">
         <v>46195</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="34">
         <v>351346.76</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="34">
         <f t="shared" si="0"/>
         <v>-8896.6300000000047</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="35">
         <f t="shared" si="1"/>
         <v>-2.4696164445931968E-2</v>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="38">
         <v>46196</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="34">
         <v>352224.24</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="34">
         <f t="shared" si="0"/>
         <v>877.47999999998137</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="35">
         <f t="shared" si="1"/>
         <v>2.4974757131671892E-3</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="18">
+      <c r="A11" s="38">
         <v>46197</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="34">
         <v>347929.11</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="34">
         <f t="shared" si="0"/>
         <v>-4295.1300000000047</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="35">
         <f t="shared" si="1"/>
         <v>-1.219430553672287E-2</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="37"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="38">
         <v>46198</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="34">
         <v>349277.46</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="34">
         <f t="shared" si="0"/>
         <v>1348.3500000000349</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="35">
         <f t="shared" si="1"/>
         <v>3.8753584027505917E-3</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="37"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+      <c r="A13" s="38">
         <v>46199</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="34">
         <v>351579.06</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="34">
         <f t="shared" si="0"/>
         <v>2301.5999999999767</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="35">
         <f t="shared" si="1"/>
         <v>6.5896035776255831E-3</v>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="37"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="38">
         <v>46202</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="34">
         <v>359661.12</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="34">
         <f t="shared" si="0"/>
         <v>8082.0599999999977</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="35">
         <f t="shared" si="1"/>
         <v>2.2987887845197601E-2</v>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="37"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="18">
+      <c r="A15" s="38">
         <v>46203</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="34">
         <v>361447.55</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="34">
         <f t="shared" si="0"/>
         <v>1786.429999999993</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="35">
         <f t="shared" si="1"/>
         <v>4.9669811404690978E-3</v>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="37"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="38">
         <v>46204</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="34">
         <v>363377.97</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="34">
         <f t="shared" si="0"/>
         <v>1930.4199999999837</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="35">
         <f t="shared" si="1"/>
         <v>5.3408025590434456E-3</v>
       </c>
-      <c r="G16" s="32"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="18">
+      <c r="A17" s="38">
         <v>46205</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="34">
         <v>374651</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="34">
         <f t="shared" si="0"/>
         <v>11273.030000000028</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="35">
         <f t="shared" si="1"/>
         <v>3.1022876813363312E-2</v>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="37"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="38">
         <v>46206</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="34">
         <v>374479.39</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="34">
         <f t="shared" si="0"/>
         <v>-171.60999999998603</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="35">
         <f t="shared" si="1"/>
         <v>-4.5805296128926929E-4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="18">
+      <c r="A19" s="38">
         <v>46209</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="34">
         <v>372801.92</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="34">
         <f t="shared" si="0"/>
         <v>-1677.4700000000303</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="35">
         <f t="shared" si="1"/>
         <v>-4.4794721546625839E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+      <c r="A20" s="38">
         <v>46210</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="34">
         <v>375246.11</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="34">
         <f t="shared" si="0"/>
         <v>2444.1900000000023</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="35">
         <f t="shared" si="1"/>
         <v>6.5562698818718594E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="18">
+      <c r="A21" s="38">
         <v>46211</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="34">
         <v>377280.97</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="34">
         <f t="shared" si="0"/>
         <v>2034.859999999986</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="35">
         <f t="shared" si="1"/>
         <v>5.4227344288791859E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="38">
         <v>46212</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="34">
         <v>374471.51</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="34">
         <f t="shared" si="0"/>
         <v>-2809.4599999999627</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="35">
         <f t="shared" si="1"/>
         <v>-7.4465987510580322E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="18">
+      <c r="A23" s="38">
         <v>46213</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="34">
         <v>376468.72</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="34">
         <f t="shared" si="0"/>
         <v>1997.2099999999627</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="35">
         <f t="shared" si="1"/>
         <v>5.3334097432404474E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="38">
         <v>46216</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="34">
         <v>379175.63</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="34">
         <f t="shared" si="0"/>
         <v>2706.9100000000326</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="35">
         <f t="shared" si="1"/>
         <v>7.190265369191982E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="18">
+      <c r="A25" s="38">
         <v>46217</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="34">
         <v>378852.03</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="34">
         <f t="shared" si="0"/>
         <v>-323.59999999997672</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="35">
         <f t="shared" si="1"/>
         <v>-8.5343037473156356E-4</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="18">
+      <c r="A26" s="38">
         <v>46218</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="34">
         <v>374437.1</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="34">
         <f t="shared" si="0"/>
         <v>-4414.9300000000512</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="35">
         <f t="shared" si="1"/>
         <v>-1.1653441582456483E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+      <c r="A27" s="38">
         <v>46219</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="34">
         <v>372248.26</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="34">
         <f t="shared" si="0"/>
         <v>-2188.8399999999674</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="35">
         <f t="shared" si="1"/>
         <v>-5.8456814241963934E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
+      <c r="A28" s="38">
         <v>46220</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="34">
         <v>376025.4</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="34">
         <f t="shared" si="0"/>
         <v>3777.140000000014</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="35">
         <f t="shared" si="1"/>
         <v>1.0146830504996891E-2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="18">
+      <c r="A29" s="38">
         <v>46223</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="34">
         <v>375009.72</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="34">
         <f t="shared" si="0"/>
         <v>-1015.6800000000512</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="35">
         <f t="shared" si="1"/>
         <v>-2.7010941282159429E-3</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+      <c r="A30" s="38">
         <v>46224</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="34">
         <v>375731.28</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="34">
         <f t="shared" si="0"/>
         <v>721.56000000005588</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="35">
         <f t="shared" si="1"/>
         <v>1.9241101270656557E-3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="18">
+      <c r="A31" s="38">
         <v>46225</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="34">
         <v>378174.99</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="34">
         <f t="shared" si="0"/>
         <v>2443.7099999999627</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="35">
         <f t="shared" si="1"/>
         <v>6.5038769196963386E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="18">
+      <c r="A32" s="38">
         <v>46226</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="34">
         <v>380362.45</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="34">
         <f t="shared" si="0"/>
         <v>2187.460000000021</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="35">
         <f t="shared" si="1"/>
         <v>5.7842534748266169E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="18">
+      <c r="A33" s="38">
         <v>46227</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="34">
         <f>B32-1740-1437</f>
         <v>377185.45</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="34">
         <f t="shared" si="0"/>
         <v>-3177</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="35">
         <f t="shared" si="1"/>
         <v>-8.3525595126437945E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="A34" s="38">
         <v>46230</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="34">
         <f>B33+322+630+1019-936</f>
         <v>378220.45</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="34">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="35">
         <f t="shared" si="1"/>
         <v>2.7440082855794143E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="18">
+      <c r="A35" s="38">
         <v>46231</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="34">
         <f>B34-951+8872.25-771</f>
         <v>385370.7</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="34">
         <f t="shared" si="0"/>
         <v>7150.25</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="35">
         <f t="shared" si="1"/>
         <v>1.8904979886730081E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="18">
+      <c r="A36" s="38">
         <v>46232</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="34">
         <f>B35+567+1830-7720+5262</f>
         <v>385309.7</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="34">
         <f t="shared" si="0"/>
         <v>-61</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="35">
         <f t="shared" si="1"/>
         <v>-1.5828914860418811E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="18">
+      <c r="A37" s="38">
         <v>46233</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="34">
         <f>B36+2088+840+8949-5393</f>
         <v>391793.7</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="34">
         <f t="shared" si="0"/>
         <v>6484</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="35">
         <f t="shared" si="1"/>
         <v>1.6828021718633089E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="18">
+      <c r="A38" s="38">
         <v>46234</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="34">
         <f>B37-480-2572</f>
         <v>388741.7</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="34">
         <f t="shared" si="0"/>
         <v>-3052</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="35">
         <f t="shared" si="1"/>
         <v>-7.7898138739852119E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="18">
+      <c r="A39" s="38">
         <v>46237</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="34">
         <f>B38-3000-427</f>
         <v>385314.7</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="34">
         <f t="shared" si="0"/>
         <v>-3427</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="35">
         <f t="shared" si="1"/>
         <v>-8.8156223013893288E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="18">
+      <c r="A40" s="38">
         <v>46238</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="34">
         <f>B39-2340+453</f>
         <v>383427.7</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="34">
         <f t="shared" si="0"/>
         <v>-1887</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="35">
         <f t="shared" si="1"/>
         <v>-4.8972956391230334E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="18">
+      <c r="A41" s="38">
         <v>46239</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="34">
         <f>B40+1500-3275</f>
         <v>381652.7</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="34">
         <f t="shared" si="0"/>
         <v>-1775</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="35">
         <f t="shared" si="1"/>
         <v>-4.6292951709018416E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="18">
+      <c r="A42" s="38">
         <v>46240</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="34">
         <f>B41+2550-1004</f>
         <v>383198.7</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="34">
         <f t="shared" si="0"/>
         <v>1546</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="35">
         <f t="shared" si="1"/>
         <v>4.0508032564685117E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="18">
+      <c r="A43" s="38">
         <v>46241</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="34">
         <f>B42+840+738</f>
         <v>384776.7</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="34">
         <f t="shared" si="0"/>
         <v>1578</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="35">
         <f t="shared" si="1"/>
         <v>4.1179680411233127E-3</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="18">
+      <c r="A44" s="38">
         <v>46244</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="34">
         <f>B43+41+540-398-50</f>
         <v>384909.7</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="34">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="35">
         <f t="shared" si="1"/>
         <v>3.4565502536925964E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="18">
+      <c r="A45" s="38">
         <v>46245</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="34">
         <f>B44-40-2340-824-1009-1010</f>
         <v>379686.7</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="34">
         <f t="shared" si="0"/>
         <v>-5223</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="35">
         <f t="shared" si="1"/>
         <v>-1.3569416411173841E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="18">
+      <c r="A46" s="38">
         <v>46246</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="34">
         <f>B45-205-1710-410+2950-212+6683-2764-240</f>
         <v>383778.7</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="34">
         <f t="shared" si="0"/>
         <v>4092</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="35">
         <f t="shared" si="1"/>
         <v>1.0777306658358061E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="18">
+      <c r="A47" s="38">
         <v>46247</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="34">
         <f>B46-95-1110+960-1500-1040+875+120</f>
         <v>381988.7</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="34">
         <f t="shared" si="0"/>
         <v>-1790</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="35">
         <f t="shared" si="1"/>
         <v>-4.6641462905575529E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="18">
+      <c r="A48" s="38">
         <v>46248</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="34">
         <f>B47+25-540-1100-7593+350-1166-690</f>
         <v>371274.7</v>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="34">
         <f t="shared" si="0"/>
         <v>-10714</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="35">
         <f t="shared" si="1"/>
         <v>-2.8047950109518945E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="18">
+      <c r="A49" s="38">
         <v>46251</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="34">
         <f>B48+95+1620-1380+725+796+220</f>
         <v>373350.7</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="34">
         <f t="shared" si="0"/>
         <v>2076</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="35">
         <f t="shared" si="1"/>
         <v>5.5915471751778398E-3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="18">
+      <c r="A50" s="38">
         <v>46252</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="34">
         <f>B49+590+1620+620+1095+826+2690</f>
         <v>380791.7</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="34">
         <f t="shared" si="0"/>
         <v>7441</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="35">
         <f t="shared" si="1"/>
         <v>1.9930322884087266E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="18">
+      <c r="A51" s="38">
         <v>46253</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="34">
         <f>B50-195+5550+2720-300-3504+1730</f>
         <v>386792.7</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="34">
         <f t="shared" si="0"/>
         <v>6001</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="35">
         <f t="shared" si="1"/>
         <v>1.5759272063965678E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="18">
+      <c r="A52" s="38">
         <v>46254</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="34">
         <f>B51+155+870-1360+1107.05+1330+1165.8+1267.76</f>
         <v>391328.31</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="34">
         <f t="shared" si="0"/>
         <v>4535.609999999986</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="35">
         <f t="shared" si="1"/>
         <v>1.1726203726181973E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="18">
+      <c r="A53" s="38">
         <v>46255</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="34">
         <f>B52-445-450-580+585-575-2123</f>
         <v>387740.31</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="34">
         <f t="shared" si="0"/>
         <v>-3588</v>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="35">
         <f t="shared" si="1"/>
         <v>-9.1687718683066913E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="18">
+      <c r="A54" s="38">
         <v>46258</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="34">
         <f>B53+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="34">
         <f t="shared" si="0"/>
         <v>6121</v>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="35">
         <f t="shared" si="1"/>
         <v>1.5786339057705916E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="18">
+      <c r="A55" s="38">
         <v>46259</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="34">
         <f>B54-390+1290+906-402+1017</f>
         <v>396282.31</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="34">
         <f t="shared" si="0"/>
         <v>2421</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="35">
         <f t="shared" si="1"/>
         <v>6.1468337674497652E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="18">
+      <c r="A56" s="38">
         <v>46260</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="34">
         <f>B55+270-750</f>
         <v>395802.31</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="34">
         <f t="shared" si="0"/>
         <v>-480</v>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="35">
         <f t="shared" si="1"/>
         <v>-1.2112577016117625E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="18">
+      <c r="A57" s="38">
         <v>46261</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="34">
         <f>B56+125+690</f>
         <v>396617.31</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="34">
         <f t="shared" si="0"/>
         <v>815</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="35">
         <f t="shared" si="1"/>
         <v>2.0591087505275043E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="18">
+      <c r="A58" s="38">
         <v>46262</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="34">
         <f>B57+300</f>
         <v>396917.31</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="34">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="D58" s="26">
+      <c r="D58" s="35">
         <f t="shared" si="1"/>
         <v>7.5639663836154808E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="18">
+      <c r="A59" s="38">
         <v>46265</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="34">
         <f>B58+135+2220-2.59</f>
         <v>399269.72</v>
       </c>
-      <c r="C59" s="20">
+      <c r="C59" s="34">
         <f t="shared" si="0"/>
         <v>2352.4099999999744</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="35">
         <f t="shared" si="1"/>
         <v>5.9267004505295434E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="18">
+      <c r="A60" s="38">
         <v>46266</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="34">
         <f>B59+480-562+1405-1361-623+1800+428</f>
         <v>400836.72</v>
       </c>
-      <c r="C60" s="20">
+      <c r="C60" s="34">
         <f t="shared" si="0"/>
         <v>1567</v>
       </c>
-      <c r="D60" s="26">
+      <c r="D60" s="35">
         <f t="shared" si="1"/>
         <v>3.9246652613676792E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="18">
+      <c r="A61" s="38">
         <v>46267</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="34">
         <f>B60-274+71-569+1738+320</f>
         <v>402122.72</v>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="34">
         <f t="shared" si="0"/>
         <v>1286</v>
       </c>
-      <c r="D61" s="26">
+      <c r="D61" s="35">
         <f t="shared" si="1"/>
         <v>3.2082889012763106E-3</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="18">
+      <c r="A62" s="38">
         <v>46268</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="34">
         <f>B61-359+2891+4108-1112</f>
         <v>407650.72</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C62" s="34">
         <f t="shared" si="0"/>
         <v>5528</v>
       </c>
-      <c r="D62" s="26">
+      <c r="D62" s="35">
         <f t="shared" si="1"/>
         <v>1.3747047170077832E-2</v>
       </c>
@@ -4257,2858 +4380,2858 @@
   <dimension ref="A1:L1048543"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" style="40"/>
-    <col min="13" max="16384" width="9.1640625" style="35"/>
+    <col min="1" max="1" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="19"/>
+    <col min="13" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="34" t="s">
+      <c r="B1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="J1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="L1" s="35"/>
+      <c r="K1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="36">
+      <c r="A2" s="15">
         <v>46175</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="16">
         <v>300000</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="16">
         <v>105712</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="17">
         <v>194288</v>
       </c>
-      <c r="E2" s="38">
-        <v>0</v>
-      </c>
-      <c r="F2" s="38">
-        <v>0</v>
-      </c>
-      <c r="G2" s="38">
+      <c r="E2" s="17">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17">
+        <v>0</v>
+      </c>
+      <c r="G2" s="17">
         <v>300000</v>
       </c>
-      <c r="H2" s="39">
+      <c r="H2" s="18">
         <f>C2/G2</f>
         <v>0.35237333333333332</v>
       </c>
-      <c r="I2" s="39">
+      <c r="I2" s="18">
         <f>D2/G2</f>
         <v>0.64762666666666668</v>
       </c>
-      <c r="J2" s="39">
+      <c r="J2" s="18">
         <f>E2/G2</f>
         <v>0</v>
       </c>
-      <c r="K2" s="39">
+      <c r="K2" s="18">
         <f>F2/G2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="36">
+      <c r="A3" s="15">
         <v>46176</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="16">
         <v>300000</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="16">
         <v>105712</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="17">
         <v>194288</v>
       </c>
-      <c r="E3" s="38">
-        <v>0</v>
-      </c>
-      <c r="F3" s="38">
-        <v>0</v>
-      </c>
-      <c r="G3" s="38">
+      <c r="E3" s="17">
+        <v>0</v>
+      </c>
+      <c r="F3" s="17">
+        <v>0</v>
+      </c>
+      <c r="G3" s="17">
         <v>300000</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="18">
         <f t="shared" ref="H3:H66" si="0">C3/G3</f>
         <v>0.35237333333333332</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="18">
         <f t="shared" ref="I3:I66" si="1">D3/G3</f>
         <v>0.64762666666666668</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="18">
         <f t="shared" ref="J3:J66" si="2">E3/G3</f>
         <v>0</v>
       </c>
-      <c r="K3" s="39">
+      <c r="K3" s="18">
         <f t="shared" ref="K3:K66" si="3">F3/G3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="36">
+      <c r="A4" s="15">
         <v>46177</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="16">
         <v>300000</v>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="17">
         <v>244380</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="17">
         <v>55620</v>
       </c>
-      <c r="E4" s="38">
-        <v>0</v>
-      </c>
-      <c r="F4" s="38">
-        <v>0</v>
-      </c>
-      <c r="G4" s="38">
+      <c r="E4" s="17">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17">
         <v>300000</v>
       </c>
-      <c r="H4" s="39">
+      <c r="H4" s="18">
         <f t="shared" si="0"/>
         <v>0.81459999999999999</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="18">
         <f t="shared" si="1"/>
         <v>0.18540000000000001</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="36">
+      <c r="A5" s="15">
         <v>46178</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="16">
         <v>300000</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="17">
         <v>244380</v>
       </c>
-      <c r="D5" s="38">
-        <v>0</v>
-      </c>
-      <c r="E5" s="38">
+      <c r="D5" s="17">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
         <v>663350</v>
       </c>
-      <c r="F5" s="38">
-        <v>0</v>
-      </c>
-      <c r="G5" s="38">
+      <c r="F5" s="17">
+        <v>0</v>
+      </c>
+      <c r="G5" s="17">
         <v>907730</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="18">
         <f t="shared" si="0"/>
         <v>0.2692210238727375</v>
       </c>
-      <c r="I5" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="39">
+      <c r="I5" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="18">
         <f t="shared" si="2"/>
         <v>0.7307789761272625</v>
       </c>
-      <c r="K5" s="39">
+      <c r="K5" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="15">
         <v>46181</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="16">
         <v>300000</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="17">
         <v>138668</v>
       </c>
-      <c r="D6" s="38">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38">
+      <c r="D6" s="17">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17">
         <v>3558250</v>
       </c>
-      <c r="F6" s="38">
-        <v>0</v>
-      </c>
-      <c r="G6" s="38">
+      <c r="F6" s="17">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
         <v>3696918</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="18">
         <f t="shared" si="0"/>
         <v>3.7509081889292646E-2</v>
       </c>
-      <c r="I6" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="39">
+      <c r="I6" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="18">
         <f t="shared" si="2"/>
         <v>0.96249091811070731</v>
       </c>
-      <c r="K6" s="39">
+      <c r="K6" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="36">
+      <c r="A7" s="15">
         <v>46182</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="16">
         <v>300000</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="17">
         <v>138668</v>
       </c>
-      <c r="D7" s="38">
-        <v>0</v>
-      </c>
-      <c r="E7" s="38">
+      <c r="D7" s="17">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17">
         <v>663350</v>
       </c>
-      <c r="F7" s="38">
-        <v>0</v>
-      </c>
-      <c r="G7" s="38">
+      <c r="F7" s="17">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
         <v>802018</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="18">
         <f t="shared" si="0"/>
         <v>0.17289886261904347</v>
       </c>
-      <c r="I7" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="39">
+      <c r="I7" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
         <f t="shared" si="2"/>
         <v>0.82710113738095659</v>
       </c>
-      <c r="K7" s="39">
+      <c r="K7" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="15">
         <v>46183</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="16">
         <v>300000</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="17">
         <v>138668</v>
       </c>
-      <c r="D8" s="38">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38">
+      <c r="D8" s="17">
+        <v>0</v>
+      </c>
+      <c r="E8" s="17">
         <v>461469</v>
       </c>
-      <c r="F8" s="38">
-        <v>0</v>
-      </c>
-      <c r="G8" s="38">
+      <c r="F8" s="17">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17">
         <v>600137</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="18">
         <f t="shared" si="0"/>
         <v>0.23106057450215534</v>
       </c>
-      <c r="I8" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="39">
+      <c r="I8" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
         <f t="shared" si="2"/>
         <v>0.76893942549784466</v>
       </c>
-      <c r="K8" s="39">
+      <c r="K8" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="36">
+      <c r="A9" s="15">
         <v>46184</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="16">
         <v>333455.63</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="17">
         <v>138668</v>
       </c>
-      <c r="D9" s="38">
-        <v>0</v>
-      </c>
-      <c r="E9" s="38">
+      <c r="D9" s="17">
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
         <v>461469</v>
       </c>
-      <c r="F9" s="38">
-        <v>0</v>
-      </c>
-      <c r="G9" s="38">
+      <c r="F9" s="17">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
         <v>600137</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="18">
         <f t="shared" si="0"/>
         <v>0.23106057450215534</v>
       </c>
-      <c r="I9" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="39">
+      <c r="I9" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
         <f t="shared" si="2"/>
         <v>0.76893942549784466</v>
       </c>
-      <c r="K9" s="39">
+      <c r="K9" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="15">
         <v>46185</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="16">
         <v>350216.98</v>
       </c>
-      <c r="C10" s="38">
-        <v>0</v>
-      </c>
-      <c r="D10" s="38">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38">
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
         <v>461469</v>
       </c>
-      <c r="F10" s="38">
-        <v>0</v>
-      </c>
-      <c r="G10" s="38">
+      <c r="F10" s="17">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
         <v>461469</v>
       </c>
-      <c r="H10" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="39">
+      <c r="H10" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K10" s="39">
+      <c r="K10" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="36">
+      <c r="A11" s="15">
         <v>46188</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="16">
         <v>356930.64</v>
       </c>
-      <c r="C11" s="38">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38">
-        <v>0</v>
-      </c>
-      <c r="E11" s="38">
+      <c r="C11" s="17">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17">
         <v>461469</v>
       </c>
-      <c r="F11" s="38">
-        <v>0</v>
-      </c>
-      <c r="G11" s="38">
+      <c r="F11" s="17">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17">
         <v>461469</v>
       </c>
-      <c r="H11" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="39">
+      <c r="H11" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="36">
+      <c r="A12" s="15">
         <v>46189</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="16">
         <v>351815.49</v>
       </c>
-      <c r="C12" s="38">
-        <v>0</v>
-      </c>
-      <c r="D12" s="38">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
+      <c r="C12" s="17">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
         <v>461469</v>
       </c>
-      <c r="F12" s="38">
-        <v>0</v>
-      </c>
-      <c r="G12" s="38">
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
         <v>461469</v>
       </c>
-      <c r="H12" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="39">
+      <c r="H12" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K12" s="39">
+      <c r="K12" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="36">
+      <c r="A13" s="15">
         <v>46190</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="16">
         <v>358486.01</v>
       </c>
-      <c r="C13" s="38">
-        <v>0</v>
-      </c>
-      <c r="D13" s="38">
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
         <f>B13-E13</f>
         <v>227246.01</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="17">
         <v>131240</v>
       </c>
-      <c r="F13" s="38">
-        <v>0</v>
-      </c>
-      <c r="G13" s="38">
-        <f>SUM(C13:F13)</f>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" ref="G13:G32" si="4">SUM(C13:F13)</f>
         <v>358486.01</v>
       </c>
-      <c r="H13" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="39">
+      <c r="H13" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="18">
         <f t="shared" si="1"/>
         <v>0.63390482099984879</v>
       </c>
-      <c r="J13" s="39">
+      <c r="J13" s="18">
         <f t="shared" si="2"/>
         <v>0.36609517900015121</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="15">
         <v>46191</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="16">
         <v>360758.08</v>
       </c>
-      <c r="C14" s="38">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
+      <c r="C14" s="17">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17">
         <f>B14-E14</f>
         <v>229518.08000000002</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="17">
         <v>131240</v>
       </c>
-      <c r="F14" s="38">
-        <v>0</v>
-      </c>
-      <c r="G14" s="38">
-        <f>SUM(C14:F14)</f>
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <f t="shared" si="4"/>
         <v>360758.08</v>
       </c>
-      <c r="H14" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="39">
+      <c r="H14" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="18">
         <f t="shared" si="1"/>
         <v>0.63621050428032</v>
       </c>
-      <c r="J14" s="39">
+      <c r="J14" s="18">
         <f t="shared" si="2"/>
         <v>0.36378949571968006</v>
       </c>
-      <c r="K14" s="39">
+      <c r="K14" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="36">
+      <c r="A15" s="15">
         <v>46192</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="16">
         <v>360243.39</v>
       </c>
-      <c r="C15" s="38">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
+      <c r="C15" s="17">
+        <v>0</v>
+      </c>
+      <c r="D15" s="17">
         <f>B15-E15</f>
         <v>229003.39</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="17">
         <v>131240</v>
       </c>
-      <c r="F15" s="38">
-        <v>0</v>
-      </c>
-      <c r="G15" s="38">
-        <f>SUM(C15:F15)</f>
+      <c r="F15" s="17">
+        <v>0</v>
+      </c>
+      <c r="G15" s="17">
+        <f t="shared" si="4"/>
         <v>360243.39</v>
       </c>
-      <c r="H15" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="39">
+      <c r="H15" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="18">
         <f t="shared" si="1"/>
         <v>0.63569074785799684</v>
       </c>
-      <c r="J15" s="39">
+      <c r="J15" s="18">
         <f t="shared" si="2"/>
         <v>0.36430925214200321</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="36">
+      <c r="A16" s="15">
         <v>46195</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="16">
         <v>351346.76</v>
       </c>
-      <c r="C16" s="38">
-        <v>0</v>
-      </c>
-      <c r="D16" s="38">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
+      <c r="C16" s="17">
+        <v>0</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
         <v>3124781</v>
       </c>
-      <c r="F16" s="38">
-        <v>0</v>
-      </c>
-      <c r="G16" s="38">
-        <f>SUM(C16:F16)</f>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="4"/>
         <v>3124781</v>
       </c>
-      <c r="H16" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="39">
+      <c r="H16" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="36">
+      <c r="A17" s="15">
         <v>46196</v>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="16">
         <v>352224.24</v>
       </c>
-      <c r="C17" s="38">
-        <v>0</v>
-      </c>
-      <c r="D17" s="38">
-        <v>0</v>
-      </c>
-      <c r="E17" s="38">
+      <c r="C17" s="17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17">
         <v>3124781</v>
       </c>
-      <c r="F17" s="38">
-        <v>0</v>
-      </c>
-      <c r="G17" s="38">
-        <f>SUM(C17:F17)</f>
+      <c r="F17" s="17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="4"/>
         <v>3124781</v>
       </c>
-      <c r="H17" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="39">
+      <c r="H17" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="36">
+      <c r="A18" s="15">
         <v>46197</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="16">
         <v>347929.11</v>
       </c>
-      <c r="C18" s="38">
-        <v>0</v>
-      </c>
-      <c r="D18" s="38">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
+      <c r="C18" s="17">
+        <v>0</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
         <v>3124781</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="17">
         <v>193096</v>
       </c>
-      <c r="G18" s="38">
-        <f>SUM(C18:F18)</f>
+      <c r="G18" s="17">
+        <f t="shared" si="4"/>
         <v>3317877</v>
       </c>
-      <c r="H18" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="39">
+      <c r="H18" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="18">
         <f t="shared" si="2"/>
         <v>0.94180133862707993</v>
       </c>
-      <c r="K18" s="39">
+      <c r="K18" s="18">
         <f t="shared" si="3"/>
         <v>5.8198661372920096E-2</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="36">
+      <c r="A19" s="15">
         <v>46198</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="16">
         <v>349277.46</v>
       </c>
-      <c r="C19" s="38">
-        <v>0</v>
-      </c>
-      <c r="D19" s="38">
-        <v>0</v>
-      </c>
-      <c r="E19" s="38">
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17">
         <f>3124781+202125</f>
         <v>3326906</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="17">
         <v>193096</v>
       </c>
-      <c r="G19" s="38">
-        <f>SUM(C19:F19)</f>
+      <c r="G19" s="17">
+        <f t="shared" si="4"/>
         <v>3520002</v>
       </c>
-      <c r="H19" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="39">
+      <c r="H19" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="18">
         <f t="shared" si="2"/>
         <v>0.94514321298681081</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="18">
         <f t="shared" si="3"/>
         <v>5.4856787013189197E-2</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="36">
+      <c r="A20" s="15">
         <v>46199</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="16">
         <v>351579.06</v>
       </c>
-      <c r="C20" s="38">
-        <v>0</v>
-      </c>
-      <c r="D20" s="38">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
+      <c r="C20" s="17">
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
         <v>3326906</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="17">
         <v>193096</v>
       </c>
-      <c r="G20" s="38">
-        <f>SUM(C20:F20)</f>
+      <c r="G20" s="17">
+        <f t="shared" si="4"/>
         <v>3520002</v>
       </c>
-      <c r="H20" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="39">
+      <c r="H20" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="18">
         <f t="shared" si="2"/>
         <v>0.94514321298681081</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="18">
         <f t="shared" si="3"/>
         <v>5.4856787013189197E-2</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="36">
+      <c r="A21" s="15">
         <v>46202</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="16">
         <v>359661.12</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="17">
         <v>55035</v>
       </c>
-      <c r="D21" s="38">
-        <v>0</v>
-      </c>
-      <c r="E21" s="38">
+      <c r="D21" s="17">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17">
         <v>3326906</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="17">
         <f>193096+223843</f>
         <v>416939</v>
       </c>
-      <c r="G21" s="38">
-        <f>SUM(C21:F21)</f>
+      <c r="G21" s="17">
+        <f t="shared" si="4"/>
         <v>3798880</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="18">
         <f t="shared" si="0"/>
         <v>1.4487164637998567E-2</v>
       </c>
-      <c r="I21" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="39">
+      <c r="I21" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="18">
         <f t="shared" si="2"/>
         <v>0.87575969759508066</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="18">
         <f t="shared" si="3"/>
         <v>0.10975313776692078</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="36">
+      <c r="A22" s="15">
         <v>46203</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="16">
         <v>361447.55</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="17">
         <v>55035</v>
       </c>
-      <c r="D22" s="38">
-        <v>0</v>
-      </c>
-      <c r="E22" s="38">
+      <c r="D22" s="17">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17">
         <f>E21-E12-202125+121064</f>
         <v>2784376</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="17">
         <v>223843</v>
       </c>
-      <c r="G22" s="38">
-        <f>SUM(C22:F22)</f>
+      <c r="G22" s="17">
+        <f t="shared" si="4"/>
         <v>3063254</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="18">
         <f t="shared" si="0"/>
         <v>1.7966188895860415E-2</v>
       </c>
-      <c r="I22" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="39">
+      <c r="I22" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="18">
         <f t="shared" si="2"/>
         <v>0.9089602102861859</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="18">
         <f t="shared" si="3"/>
         <v>7.3073600817953721E-2</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="36">
+      <c r="A23" s="15">
         <v>46204</v>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="16">
         <v>363377.97</v>
       </c>
-      <c r="C23" s="38">
-        <v>0</v>
-      </c>
-      <c r="D23" s="38">
-        <v>0</v>
-      </c>
-      <c r="E23" s="38">
+      <c r="C23" s="17">
+        <v>0</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17">
         <v>2784376</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="17">
         <v>223843</v>
       </c>
-      <c r="G23" s="38">
-        <f>SUM(C23:F23)</f>
+      <c r="G23" s="17">
+        <f t="shared" si="4"/>
         <v>3008219</v>
       </c>
-      <c r="H23" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="39">
+      <c r="H23" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="18">
         <f t="shared" si="2"/>
         <v>0.92558952656040006</v>
       </c>
-      <c r="K23" s="39">
+      <c r="K23" s="18">
         <f t="shared" si="3"/>
         <v>7.4410473439599972E-2</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="36">
+      <c r="A24" s="15">
         <v>46205</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="16">
         <v>374651</v>
       </c>
-      <c r="C24" s="38">
-        <v>0</v>
-      </c>
-      <c r="D24" s="38">
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="17">
         <f>B24-E24-F24</f>
         <v>29744</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="17">
         <v>121064</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="17">
         <v>223843</v>
       </c>
-      <c r="G24" s="38">
-        <f>SUM(C24:F24)</f>
+      <c r="G24" s="17">
+        <f t="shared" si="4"/>
         <v>374651</v>
       </c>
-      <c r="H24" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="39">
+      <c r="H24" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="18">
         <f t="shared" si="1"/>
         <v>7.9391220095502216E-2</v>
       </c>
-      <c r="J24" s="39">
+      <c r="J24" s="18">
         <f t="shared" si="2"/>
         <v>0.32313806716117133</v>
       </c>
-      <c r="K24" s="39">
+      <c r="K24" s="18">
         <f t="shared" si="3"/>
         <v>0.59747071274332642</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="36">
+      <c r="A25" s="15">
         <v>46206</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="16">
         <v>374479.39</v>
       </c>
-      <c r="C25" s="38">
-        <v>0</v>
-      </c>
-      <c r="D25" s="38">
+      <c r="C25" s="17">
+        <v>0</v>
+      </c>
+      <c r="D25" s="17">
         <f>B25-E25-F25</f>
         <v>29572.390000000014</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="17">
         <v>121064</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="17">
         <v>223843</v>
       </c>
-      <c r="G25" s="38">
-        <f>SUM(C25:F25)</f>
+      <c r="G25" s="17">
+        <f t="shared" si="4"/>
         <v>374479.39</v>
       </c>
-      <c r="H25" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="39">
+      <c r="H25" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="18">
         <f t="shared" si="1"/>
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="J25" s="39">
+      <c r="J25" s="18">
         <f t="shared" si="2"/>
         <v>0.32328614933921995</v>
       </c>
-      <c r="K25" s="39">
+      <c r="K25" s="18">
         <f t="shared" si="3"/>
         <v>0.59774451138686158</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="36">
+      <c r="A26" s="15">
         <v>46209</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="16">
         <v>372801.92</v>
       </c>
-      <c r="C26" s="38">
-        <v>0</v>
-      </c>
-      <c r="D26" s="38">
+      <c r="C26" s="17">
+        <v>0</v>
+      </c>
+      <c r="D26" s="17">
         <f>B26-E26-F26</f>
         <v>27894.919999999984</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="17">
         <v>121064</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="17">
         <v>223843</v>
       </c>
-      <c r="G26" s="38">
-        <f>SUM(C26:F26)</f>
+      <c r="G26" s="17">
+        <f t="shared" si="4"/>
         <v>372801.92</v>
       </c>
-      <c r="H26" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="39">
+      <c r="H26" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="18">
         <f t="shared" si="1"/>
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="J26" s="39">
+      <c r="J26" s="18">
         <f t="shared" si="2"/>
         <v>0.32474081678549299</v>
       </c>
-      <c r="K26" s="39">
+      <c r="K26" s="18">
         <f t="shared" si="3"/>
         <v>0.60043413939499024</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="36">
+      <c r="A27" s="15">
         <v>46210</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="16">
         <v>375246.11</v>
       </c>
-      <c r="C27" s="38">
-        <v>0</v>
-      </c>
-      <c r="D27" s="38">
+      <c r="C27" s="17">
+        <v>0</v>
+      </c>
+      <c r="D27" s="17">
         <f>B27-E27-F27</f>
         <v>30339.109999999986</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="17">
         <v>121064</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="17">
         <v>223843</v>
       </c>
-      <c r="G27" s="38">
-        <f>SUM(C27:F27)</f>
+      <c r="G27" s="17">
+        <f t="shared" si="4"/>
         <v>375246.11</v>
       </c>
-      <c r="H27" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="39">
+      <c r="H27" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="18">
         <f t="shared" si="1"/>
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="J27" s="39">
+      <c r="J27" s="18">
         <f t="shared" si="2"/>
         <v>0.32262559630531545</v>
       </c>
-      <c r="K27" s="39">
+      <c r="K27" s="18">
         <f t="shared" si="3"/>
         <v>0.59652317248538567</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="36">
+      <c r="A28" s="15">
         <v>46211</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="16">
         <v>377280.97</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="17">
         <v>90811</v>
       </c>
-      <c r="D28" s="38">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38">
+      <c r="D28" s="17">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17">
         <v>121064</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="17">
         <v>223843</v>
       </c>
-      <c r="G28" s="38">
-        <f>SUM(C28:F28)</f>
+      <c r="G28" s="17">
+        <f t="shared" si="4"/>
         <v>435718</v>
       </c>
-      <c r="H28" s="39">
+      <c r="H28" s="18">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I28" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="39">
+      <c r="I28" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="18">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K28" s="39">
+      <c r="K28" s="18">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="36">
+      <c r="A29" s="15">
         <v>46212</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="16">
         <v>374471.51</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="17">
         <v>90811</v>
       </c>
-      <c r="D29" s="38">
-        <v>0</v>
-      </c>
-      <c r="E29" s="38">
+      <c r="D29" s="17">
+        <v>0</v>
+      </c>
+      <c r="E29" s="17">
         <v>121064</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="17">
         <v>223843</v>
       </c>
-      <c r="G29" s="38">
-        <f>SUM(C29:F29)</f>
+      <c r="G29" s="17">
+        <f t="shared" si="4"/>
         <v>435718</v>
       </c>
-      <c r="H29" s="39">
+      <c r="H29" s="18">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I29" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="39">
+      <c r="I29" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="18">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K29" s="39">
+      <c r="K29" s="18">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="36">
+      <c r="A30" s="15">
         <v>46213</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="16">
         <v>376468.72</v>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="17">
         <v>90811</v>
       </c>
-      <c r="D30" s="38">
-        <v>0</v>
-      </c>
-      <c r="E30" s="38">
+      <c r="D30" s="17">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17">
         <v>121064</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="17">
         <v>223843</v>
       </c>
-      <c r="G30" s="38">
-        <f>SUM(C30:F30)</f>
+      <c r="G30" s="17">
+        <f t="shared" si="4"/>
         <v>435718</v>
       </c>
-      <c r="H30" s="39">
+      <c r="H30" s="18">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I30" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="39">
+      <c r="I30" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="18">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K30" s="39">
+      <c r="K30" s="18">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="36">
+      <c r="A31" s="15">
         <v>46216</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="16">
         <v>379175.63</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="17">
         <v>90811</v>
       </c>
-      <c r="D31" s="38">
-        <v>0</v>
-      </c>
-      <c r="E31" s="38">
+      <c r="D31" s="17">
+        <v>0</v>
+      </c>
+      <c r="E31" s="17">
         <v>121064</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="17">
         <v>223843</v>
       </c>
-      <c r="G31" s="38">
-        <f>SUM(C31:F31)</f>
+      <c r="G31" s="17">
+        <f t="shared" si="4"/>
         <v>435718</v>
       </c>
-      <c r="H31" s="39">
+      <c r="H31" s="18">
         <f t="shared" si="0"/>
         <v>0.20841691185583336</v>
       </c>
-      <c r="I31" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="39">
+      <c r="I31" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="18">
         <f t="shared" si="2"/>
         <v>0.27784943472613022</v>
       </c>
-      <c r="K31" s="39">
+      <c r="K31" s="18">
         <f t="shared" si="3"/>
         <v>0.51373365341803645</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="36">
+      <c r="A32" s="15">
         <v>46217</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="16">
         <v>378852.03</v>
       </c>
-      <c r="C32" s="38">
-        <v>0</v>
-      </c>
-      <c r="D32" s="38">
+      <c r="C32" s="17">
+        <v>0</v>
+      </c>
+      <c r="D32" s="17">
         <f>B32-E32-F32</f>
         <v>33945.030000000028</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="17">
         <v>121064</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="17">
         <v>223843</v>
       </c>
-      <c r="G32" s="38">
-        <f>SUM(C32:F32)</f>
+      <c r="G32" s="17">
+        <f t="shared" si="4"/>
         <v>378852.03</v>
       </c>
-      <c r="H32" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="39">
+      <c r="H32" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="18">
         <f t="shared" si="1"/>
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="J32" s="39">
+      <c r="J32" s="18">
         <f t="shared" si="2"/>
         <v>0.31955484044786558</v>
       </c>
-      <c r="K32" s="39">
+      <c r="K32" s="18">
         <f t="shared" si="3"/>
         <v>0.5908454548864368</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="36">
+      <c r="A33" s="15">
         <v>46218</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="16">
         <v>374437.1</v>
       </c>
-      <c r="C33" s="38">
-        <v>0</v>
-      </c>
-      <c r="D33" s="38">
-        <f t="shared" ref="D33:D41" si="4">B33-E33-F33</f>
+      <c r="C33" s="17">
+        <v>0</v>
+      </c>
+      <c r="D33" s="17">
+        <f t="shared" ref="D33:D41" si="5">B33-E33-F33</f>
         <v>29530.099999999977</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="17">
         <v>121064</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="17">
         <v>223843</v>
       </c>
-      <c r="G33" s="38">
-        <f t="shared" ref="G33:G69" si="5">SUM(C33:F33)</f>
+      <c r="G33" s="17">
+        <f t="shared" ref="G33:G69" si="6">SUM(C33:F33)</f>
         <v>374437.1</v>
       </c>
-      <c r="H33" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="39">
+      <c r="H33" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="18">
         <f t="shared" si="1"/>
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="J33" s="39">
+      <c r="J33" s="18">
         <f t="shared" si="2"/>
         <v>0.32332266220414591</v>
       </c>
-      <c r="K33" s="39">
+      <c r="K33" s="18">
         <f t="shared" si="3"/>
         <v>0.59781202236637343</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="36">
+      <c r="A34" s="15">
         <v>46219</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="16">
         <v>372248.26</v>
       </c>
-      <c r="C34" s="38">
-        <v>0</v>
-      </c>
-      <c r="D34" s="38">
-        <f t="shared" si="4"/>
+      <c r="C34" s="17">
+        <v>0</v>
+      </c>
+      <c r="D34" s="17">
+        <f t="shared" si="5"/>
         <v>27341.260000000009</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="17">
         <v>121064</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="17">
         <v>223843</v>
       </c>
-      <c r="G34" s="38">
-        <f t="shared" si="5"/>
+      <c r="G34" s="17">
+        <f t="shared" si="6"/>
         <v>372248.26</v>
       </c>
-      <c r="H34" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="39">
+      <c r="H34" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="18">
         <f t="shared" si="1"/>
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="J34" s="39">
+      <c r="J34" s="18">
         <f t="shared" si="2"/>
         <v>0.32522381703006481</v>
       </c>
-      <c r="K34" s="39">
+      <c r="K34" s="18">
         <f t="shared" si="3"/>
         <v>0.60132718954817943</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="36">
+      <c r="A35" s="15">
         <v>46220</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="16">
         <v>376025.4</v>
       </c>
-      <c r="C35" s="38">
-        <v>0</v>
-      </c>
-      <c r="D35" s="38">
-        <f t="shared" si="4"/>
+      <c r="C35" s="17">
+        <v>0</v>
+      </c>
+      <c r="D35" s="17">
+        <f t="shared" si="5"/>
         <v>31118.400000000023</v>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="17">
         <v>121064</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="17">
         <v>223843</v>
       </c>
-      <c r="G35" s="38">
-        <f t="shared" si="5"/>
+      <c r="G35" s="17">
+        <f t="shared" si="6"/>
         <v>376025.4</v>
       </c>
-      <c r="H35" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="39">
+      <c r="H35" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="18">
         <f t="shared" si="1"/>
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="J35" s="39">
+      <c r="J35" s="18">
         <f t="shared" si="2"/>
         <v>0.32195697418312696</v>
       </c>
-      <c r="K35" s="39">
+      <c r="K35" s="18">
         <f t="shared" si="3"/>
         <v>0.59528691412867318</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="36">
+      <c r="A36" s="15">
         <v>46223</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="16">
         <v>375009.72</v>
       </c>
-      <c r="C36" s="38">
-        <v>0</v>
-      </c>
-      <c r="D36" s="38">
-        <f t="shared" si="4"/>
+      <c r="C36" s="17">
+        <v>0</v>
+      </c>
+      <c r="D36" s="17">
+        <f t="shared" si="5"/>
         <v>30102.719999999972</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="17">
         <v>121064</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="17">
         <v>223843</v>
       </c>
-      <c r="G36" s="38">
-        <f t="shared" si="5"/>
+      <c r="G36" s="17">
+        <f t="shared" si="6"/>
         <v>375009.72</v>
       </c>
-      <c r="H36" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="39">
+      <c r="H36" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="18">
         <f t="shared" si="1"/>
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="J36" s="39">
+      <c r="J36" s="18">
         <f t="shared" si="2"/>
         <v>0.32282896560654484</v>
       </c>
-      <c r="K36" s="39">
+      <c r="K36" s="18">
         <f t="shared" si="3"/>
         <v>0.59689919503953126</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="36">
+      <c r="A37" s="15">
         <v>46224</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="16">
         <v>375731.28</v>
       </c>
-      <c r="C37" s="38">
-        <v>0</v>
-      </c>
-      <c r="D37" s="38">
-        <f t="shared" si="4"/>
+      <c r="C37" s="17">
+        <v>0</v>
+      </c>
+      <c r="D37" s="17">
+        <f t="shared" si="5"/>
         <v>30824.280000000028</v>
       </c>
-      <c r="E37" s="38">
+      <c r="E37" s="17">
         <v>121064</v>
       </c>
-      <c r="F37" s="38">
+      <c r="F37" s="17">
         <v>223843</v>
       </c>
-      <c r="G37" s="38">
-        <f t="shared" si="5"/>
+      <c r="G37" s="17">
+        <f t="shared" si="6"/>
         <v>375731.28</v>
       </c>
-      <c r="H37" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="39">
+      <c r="H37" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="18">
         <f t="shared" si="1"/>
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="J37" s="39">
+      <c r="J37" s="18">
         <f t="shared" si="2"/>
         <v>0.32220900000660047</v>
       </c>
-      <c r="K37" s="39">
+      <c r="K37" s="18">
         <f t="shared" si="3"/>
         <v>0.5957529008497775</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="36">
+      <c r="A38" s="15">
         <v>46225</v>
       </c>
-      <c r="B38" s="37">
+      <c r="B38" s="16">
         <v>378174.99</v>
       </c>
-      <c r="C38" s="38">
-        <v>0</v>
-      </c>
-      <c r="D38" s="38">
-        <f t="shared" si="4"/>
+      <c r="C38" s="17">
+        <v>0</v>
+      </c>
+      <c r="D38" s="17">
+        <f t="shared" si="5"/>
         <v>33267.989999999991</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="17">
         <v>121064</v>
       </c>
-      <c r="F38" s="38">
+      <c r="F38" s="17">
         <v>223843</v>
       </c>
-      <c r="G38" s="38">
-        <f t="shared" si="5"/>
+      <c r="G38" s="17">
+        <f t="shared" si="6"/>
         <v>378174.99</v>
       </c>
-      <c r="H38" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="39">
+      <c r="H38" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
         <f t="shared" si="1"/>
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="J38" s="39">
+      <c r="J38" s="18">
         <f t="shared" si="2"/>
         <v>0.32012693383028845</v>
       </c>
-      <c r="K38" s="39">
+      <c r="K38" s="18">
         <f t="shared" si="3"/>
         <v>0.59190323506057341</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="36">
+      <c r="A39" s="15">
         <v>46226</v>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="16">
         <v>380362.45</v>
       </c>
-      <c r="C39" s="38">
-        <v>0</v>
-      </c>
-      <c r="D39" s="38">
-        <f t="shared" si="4"/>
+      <c r="C39" s="17">
+        <v>0</v>
+      </c>
+      <c r="D39" s="17">
+        <f t="shared" si="5"/>
         <v>35455.450000000012</v>
       </c>
-      <c r="E39" s="38">
+      <c r="E39" s="17">
         <v>121064</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F39" s="17">
         <v>223843</v>
       </c>
-      <c r="G39" s="38">
-        <f t="shared" si="5"/>
+      <c r="G39" s="17">
+        <f t="shared" si="6"/>
         <v>380362.45</v>
       </c>
-      <c r="H39" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="39">
+      <c r="H39" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="18">
         <f t="shared" si="1"/>
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="J39" s="39">
+      <c r="J39" s="18">
         <f t="shared" si="2"/>
         <v>0.31828588757907095</v>
       </c>
-      <c r="K39" s="39">
+      <c r="K39" s="18">
         <f t="shared" si="3"/>
         <v>0.58849920648055554</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="36">
+      <c r="A40" s="15">
         <v>46227</v>
       </c>
-      <c r="B40" s="37">
+      <c r="B40" s="16">
         <f>B39-1740-1437</f>
         <v>377185.45</v>
       </c>
-      <c r="C40" s="38">
-        <v>0</v>
-      </c>
-      <c r="D40" s="38">
-        <f t="shared" si="4"/>
+      <c r="C40" s="17">
+        <v>0</v>
+      </c>
+      <c r="D40" s="17">
+        <f t="shared" si="5"/>
         <v>32278.450000000012</v>
       </c>
-      <c r="E40" s="38">
+      <c r="E40" s="17">
         <v>121064</v>
       </c>
-      <c r="F40" s="38">
+      <c r="F40" s="17">
         <v>223843</v>
       </c>
-      <c r="G40" s="38">
-        <f t="shared" si="5"/>
+      <c r="G40" s="17">
+        <f t="shared" si="6"/>
         <v>377185.45</v>
       </c>
-      <c r="H40" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="39">
+      <c r="H40" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="18">
         <f t="shared" si="1"/>
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="J40" s="39">
+      <c r="J40" s="18">
         <f t="shared" si="2"/>
         <v>0.32096678172501086</v>
       </c>
-      <c r="K40" s="39">
+      <c r="K40" s="18">
         <f t="shared" si="3"/>
         <v>0.59345608373811876</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="36">
+      <c r="A41" s="15">
         <v>46230</v>
       </c>
-      <c r="B41" s="37">
+      <c r="B41" s="16">
         <f>B40+322+630+1019-936</f>
         <v>378220.45</v>
       </c>
-      <c r="C41" s="38">
-        <v>0</v>
-      </c>
-      <c r="D41" s="38">
-        <f t="shared" si="4"/>
+      <c r="C41" s="17">
+        <v>0</v>
+      </c>
+      <c r="D41" s="17">
+        <f t="shared" si="5"/>
         <v>33313.450000000012</v>
       </c>
-      <c r="E41" s="38">
+      <c r="E41" s="17">
         <v>121064</v>
       </c>
-      <c r="F41" s="38">
+      <c r="F41" s="17">
         <v>223843</v>
       </c>
-      <c r="G41" s="38">
-        <f t="shared" si="5"/>
+      <c r="G41" s="17">
+        <f t="shared" si="6"/>
         <v>378220.45</v>
       </c>
-      <c r="H41" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="39">
+      <c r="H41" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="18">
         <f t="shared" si="1"/>
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="J41" s="39">
+      <c r="J41" s="18">
         <f t="shared" si="2"/>
         <v>0.32008845634867178</v>
       </c>
-      <c r="K41" s="39">
+      <c r="K41" s="18">
         <f t="shared" si="3"/>
         <v>0.5918320915751647</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="36">
+      <c r="A42" s="15">
         <v>46231</v>
       </c>
-      <c r="B42" s="37">
+      <c r="B42" s="16">
         <f>B41-951+8872.25-771</f>
         <v>385370.7</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="13">
         <v>334624</v>
       </c>
-      <c r="D42" s="35">
-        <v>0</v>
-      </c>
-      <c r="E42" s="38">
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17">
         <v>121064</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F42" s="17">
         <v>223843</v>
       </c>
-      <c r="G42" s="38">
-        <f t="shared" si="5"/>
+      <c r="G42" s="17">
+        <f t="shared" si="6"/>
         <v>679531</v>
       </c>
-      <c r="H42" s="39">
+      <c r="H42" s="18">
         <f t="shared" si="0"/>
         <v>0.49243375210255308</v>
       </c>
-      <c r="I42" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="39">
+      <c r="I42" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="18">
         <f t="shared" si="2"/>
         <v>0.17815817085607574</v>
       </c>
-      <c r="K42" s="39">
+      <c r="K42" s="18">
         <f t="shared" si="3"/>
         <v>0.32940807704137121</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="36">
+      <c r="A43" s="15">
         <v>46232</v>
       </c>
-      <c r="B43" s="37">
+      <c r="B43" s="16">
         <f>B42+567+1830-7720+5262</f>
         <v>385309.7</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="13">
         <v>334624</v>
       </c>
-      <c r="D43" s="35">
-        <v>0</v>
-      </c>
-      <c r="E43" s="38">
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17">
         <v>121064</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="17">
         <v>223843</v>
       </c>
-      <c r="G43" s="38">
-        <f t="shared" si="5"/>
+      <c r="G43" s="17">
+        <f t="shared" si="6"/>
         <v>679531</v>
       </c>
-      <c r="H43" s="39">
+      <c r="H43" s="18">
         <f t="shared" si="0"/>
         <v>0.49243375210255308</v>
       </c>
-      <c r="I43" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="39">
+      <c r="I43" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="18">
         <f t="shared" si="2"/>
         <v>0.17815817085607574</v>
       </c>
-      <c r="K43" s="39">
+      <c r="K43" s="18">
         <f t="shared" si="3"/>
         <v>0.32940807704137121</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="36">
+      <c r="A44" s="15">
         <v>46233</v>
       </c>
-      <c r="B44" s="37">
+      <c r="B44" s="16">
         <f>B43+2088+840+8949-5393</f>
         <v>391793.7</v>
       </c>
-      <c r="C44" s="34">
-        <v>0</v>
-      </c>
-      <c r="D44" s="38">
-        <f t="shared" ref="D44:D52" si="6">B44-E44-F44</f>
+      <c r="C44" s="13">
+        <v>0</v>
+      </c>
+      <c r="D44" s="17">
+        <f t="shared" ref="D44:D52" si="7">B44-E44-F44</f>
         <v>46886.700000000012</v>
       </c>
-      <c r="E44" s="38">
+      <c r="E44" s="17">
         <v>121064</v>
       </c>
-      <c r="F44" s="38">
+      <c r="F44" s="17">
         <v>223843</v>
       </c>
-      <c r="G44" s="38">
-        <f t="shared" si="5"/>
+      <c r="G44" s="17">
+        <f t="shared" si="6"/>
         <v>391793.7</v>
       </c>
-      <c r="H44" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="39">
+      <c r="H44" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="18">
         <f t="shared" si="1"/>
         <v>0.11967190896637697</v>
       </c>
-      <c r="J44" s="39">
+      <c r="J44" s="18">
         <f t="shared" si="2"/>
         <v>0.30899935348628627</v>
       </c>
-      <c r="K44" s="39">
+      <c r="K44" s="18">
         <f t="shared" si="3"/>
         <v>0.57132873754733671</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="36">
+      <c r="A45" s="15">
         <v>46234</v>
       </c>
-      <c r="B45" s="37">
+      <c r="B45" s="16">
         <f>B44-480-2572</f>
         <v>388741.7</v>
       </c>
-      <c r="C45" s="34">
-        <v>0</v>
-      </c>
-      <c r="D45" s="38">
+      <c r="C45" s="13">
+        <v>0</v>
+      </c>
+      <c r="D45" s="17">
+        <f t="shared" si="7"/>
+        <v>43834.700000000012</v>
+      </c>
+      <c r="E45" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F45" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G45" s="17">
         <f t="shared" si="6"/>
-        <v>43834.700000000012</v>
-      </c>
-      <c r="E45" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F45" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G45" s="38">
-        <f t="shared" si="5"/>
         <v>388741.7</v>
       </c>
-      <c r="H45" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="39">
+      <c r="H45" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="18">
         <f t="shared" si="1"/>
         <v>0.11276047823014616</v>
       </c>
-      <c r="J45" s="39">
+      <c r="J45" s="18">
         <f t="shared" si="2"/>
         <v>0.3114252985980151</v>
       </c>
-      <c r="K45" s="39">
+      <c r="K45" s="18">
         <f t="shared" si="3"/>
         <v>0.57581422317183872</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="36">
+      <c r="A46" s="15">
         <v>46237</v>
       </c>
-      <c r="B46" s="37">
+      <c r="B46" s="16">
         <f>B45-3000-427</f>
         <v>385314.7</v>
       </c>
-      <c r="C46" s="34">
-        <v>0</v>
-      </c>
-      <c r="D46" s="38">
+      <c r="C46" s="13">
+        <v>0</v>
+      </c>
+      <c r="D46" s="17">
+        <f t="shared" si="7"/>
+        <v>40407.700000000012</v>
+      </c>
+      <c r="E46" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F46" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G46" s="17">
         <f t="shared" si="6"/>
-        <v>40407.700000000012</v>
-      </c>
-      <c r="E46" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F46" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G46" s="38">
-        <f t="shared" si="5"/>
         <v>385314.7</v>
       </c>
-      <c r="H46" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="39">
+      <c r="H46" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="18">
         <f t="shared" si="1"/>
         <v>0.10486934446051503</v>
       </c>
-      <c r="J46" s="39">
+      <c r="J46" s="18">
         <f t="shared" si="2"/>
         <v>0.31419512414138362</v>
       </c>
-      <c r="K46" s="39">
+      <c r="K46" s="18">
         <f t="shared" si="3"/>
         <v>0.58093553139810128</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="36">
+      <c r="A47" s="15">
         <v>46238</v>
       </c>
-      <c r="B47" s="37">
+      <c r="B47" s="16">
         <f>B46-2340+453</f>
         <v>383427.7</v>
       </c>
-      <c r="C47" s="34">
-        <v>0</v>
-      </c>
-      <c r="D47" s="38">
+      <c r="C47" s="13">
+        <v>0</v>
+      </c>
+      <c r="D47" s="17">
+        <f t="shared" si="7"/>
+        <v>38520.700000000012</v>
+      </c>
+      <c r="E47" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F47" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G47" s="17">
         <f t="shared" si="6"/>
-        <v>38520.700000000012</v>
-      </c>
-      <c r="E47" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F47" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G47" s="38">
-        <f t="shared" si="5"/>
         <v>383427.7</v>
       </c>
-      <c r="H47" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="39">
+      <c r="H47" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="18">
         <f t="shared" si="1"/>
         <v>0.1004640509801457</v>
       </c>
-      <c r="J47" s="39">
+      <c r="J47" s="18">
         <f t="shared" si="2"/>
         <v>0.31574140313806226</v>
       </c>
-      <c r="K47" s="39">
+      <c r="K47" s="18">
         <f t="shared" si="3"/>
         <v>0.58379454588179203</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="36">
+      <c r="A48" s="15">
         <v>46239</v>
       </c>
-      <c r="B48" s="37">
+      <c r="B48" s="16">
         <f>B47+1500-3275</f>
         <v>381652.7</v>
       </c>
-      <c r="C48" s="34">
-        <v>0</v>
-      </c>
-      <c r="D48" s="38">
+      <c r="C48" s="13">
+        <v>0</v>
+      </c>
+      <c r="D48" s="17">
+        <f t="shared" si="7"/>
+        <v>36745.700000000012</v>
+      </c>
+      <c r="E48" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F48" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G48" s="17">
         <f t="shared" si="6"/>
-        <v>36745.700000000012</v>
-      </c>
-      <c r="E48" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F48" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G48" s="38">
-        <f t="shared" si="5"/>
         <v>381652.7</v>
       </c>
-      <c r="H48" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="39">
+      <c r="H48" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="18">
         <f t="shared" si="1"/>
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="J48" s="39">
+      <c r="J48" s="18">
         <f t="shared" si="2"/>
         <v>0.31720986121675543</v>
       </c>
-      <c r="K48" s="39">
+      <c r="K48" s="18">
         <f t="shared" si="3"/>
         <v>0.58650967227534356</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="36">
+      <c r="A49" s="15">
         <v>46240</v>
       </c>
-      <c r="B49" s="37">
+      <c r="B49" s="16">
         <f>B48+2550-1004</f>
         <v>383198.7</v>
       </c>
-      <c r="C49" s="34">
-        <v>0</v>
-      </c>
-      <c r="D49" s="38">
+      <c r="C49" s="13">
+        <v>0</v>
+      </c>
+      <c r="D49" s="17">
+        <f t="shared" si="7"/>
+        <v>38291.700000000012</v>
+      </c>
+      <c r="E49" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F49" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G49" s="17">
         <f t="shared" si="6"/>
-        <v>38291.700000000012</v>
-      </c>
-      <c r="E49" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F49" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G49" s="38">
-        <f t="shared" si="5"/>
         <v>383198.7</v>
       </c>
-      <c r="H49" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="39">
+      <c r="H49" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="18">
         <f t="shared" si="1"/>
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="J49" s="39">
+      <c r="J49" s="18">
         <f t="shared" si="2"/>
         <v>0.31593009057702959</v>
       </c>
-      <c r="K49" s="39">
+      <c r="K49" s="18">
         <f t="shared" si="3"/>
         <v>0.58414342219845738</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="36">
+      <c r="A50" s="15">
         <v>46241</v>
       </c>
-      <c r="B50" s="37">
+      <c r="B50" s="16">
         <f>B49+840+738</f>
         <v>384776.7</v>
       </c>
-      <c r="C50" s="34">
-        <v>0</v>
-      </c>
-      <c r="D50" s="38">
+      <c r="C50" s="13">
+        <v>0</v>
+      </c>
+      <c r="D50" s="17">
+        <f t="shared" si="7"/>
+        <v>39869.700000000012</v>
+      </c>
+      <c r="E50" s="17">
+        <v>121064</v>
+      </c>
+      <c r="F50" s="17">
+        <v>223843</v>
+      </c>
+      <c r="G50" s="17">
         <f t="shared" si="6"/>
-        <v>39869.700000000012</v>
-      </c>
-      <c r="E50" s="38">
-        <v>121064</v>
-      </c>
-      <c r="F50" s="38">
-        <v>223843</v>
-      </c>
-      <c r="G50" s="38">
-        <f t="shared" si="5"/>
         <v>384776.7</v>
       </c>
-      <c r="H50" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="39">
+      <c r="H50" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="18">
         <f t="shared" si="1"/>
         <v>0.10361776063883289</v>
       </c>
-      <c r="J50" s="39">
+      <c r="J50" s="18">
         <f t="shared" si="2"/>
         <v>0.31463443602484248</v>
       </c>
-      <c r="K50" s="39">
+      <c r="K50" s="18">
         <f t="shared" si="3"/>
         <v>0.5817478033363247</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="36">
+      <c r="A51" s="15">
         <v>46244</v>
       </c>
-      <c r="B51" s="37">
+      <c r="B51" s="16">
         <f>B50+41+540-398-50</f>
         <v>384909.7</v>
       </c>
-      <c r="C51" s="34">
-        <v>0</v>
-      </c>
-      <c r="D51" s="38">
-        <f t="shared" si="6"/>
+      <c r="C51" s="13">
+        <v>0</v>
+      </c>
+      <c r="D51" s="17">
+        <f t="shared" si="7"/>
         <v>24412.700000000012</v>
       </c>
-      <c r="E51" s="35">
+      <c r="E51" s="14">
         <f>185382+121064</f>
         <v>306446</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="14">
         <v>54051</v>
       </c>
-      <c r="G51" s="38">
-        <f t="shared" si="5"/>
+      <c r="G51" s="17">
+        <f t="shared" si="6"/>
         <v>384909.7</v>
       </c>
-      <c r="H51" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="39">
+      <c r="H51" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="18">
         <f t="shared" si="1"/>
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="J51" s="39">
+      <c r="J51" s="18">
         <f t="shared" si="2"/>
         <v>0.79615036981401088</v>
       </c>
-      <c r="K51" s="39">
+      <c r="K51" s="18">
         <f t="shared" si="3"/>
         <v>0.14042514387140673</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="36">
+      <c r="A52" s="15">
         <v>46245</v>
       </c>
-      <c r="B52" s="37">
+      <c r="B52" s="16">
         <f>B51-40-2340-824-1009-1010</f>
         <v>379686.7</v>
       </c>
-      <c r="C52" s="34">
-        <v>0</v>
-      </c>
-      <c r="D52" s="38">
-        <f t="shared" si="6"/>
+      <c r="C52" s="13">
+        <v>0</v>
+      </c>
+      <c r="D52" s="17">
+        <f t="shared" si="7"/>
         <v>19189.700000000012</v>
       </c>
-      <c r="E52" s="35">
+      <c r="E52" s="14">
         <f>185382+121064</f>
         <v>306446</v>
       </c>
-      <c r="F52" s="35">
+      <c r="F52" s="14">
         <v>54051</v>
       </c>
-      <c r="G52" s="38">
-        <f t="shared" si="5"/>
+      <c r="G52" s="17">
+        <f t="shared" si="6"/>
         <v>379686.7</v>
       </c>
-      <c r="H52" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="39">
+      <c r="H52" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="18">
         <f t="shared" si="1"/>
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="J52" s="39">
+      <c r="J52" s="18">
         <f t="shared" si="2"/>
         <v>0.80710227669286283</v>
       </c>
-      <c r="K52" s="39">
+      <c r="K52" s="18">
         <f t="shared" si="3"/>
         <v>0.14235684315515923</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="36">
+      <c r="A53" s="15">
         <v>46246</v>
       </c>
-      <c r="B53" s="37">
+      <c r="B53" s="16">
         <f>B52-205-1710-410+2950-212+6683-2764-240</f>
         <v>383778.7</v>
       </c>
-      <c r="C53" s="34">
-        <v>0</v>
-      </c>
-      <c r="D53" s="35">
-        <v>0</v>
-      </c>
-      <c r="E53" s="35">
+      <c r="C53" s="13">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
         <f>E52+154290</f>
         <v>460736</v>
       </c>
-      <c r="F53" s="35">
+      <c r="F53" s="14">
         <f>F52+164620</f>
         <v>218671</v>
       </c>
-      <c r="G53" s="38">
-        <f t="shared" si="5"/>
+      <c r="G53" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H53" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="39">
+      <c r="H53" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K53" s="39">
+      <c r="K53" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="36">
+      <c r="A54" s="15">
         <v>46247</v>
       </c>
-      <c r="B54" s="37">
+      <c r="B54" s="16">
         <f>B53-95-1110+960-1500-1040+875+120</f>
         <v>381988.7</v>
       </c>
-      <c r="C54" s="34">
-        <v>0</v>
-      </c>
-      <c r="D54" s="35">
-        <v>0</v>
-      </c>
-      <c r="E54" s="35">
+      <c r="C54" s="13">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
         <v>460736</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="14">
         <v>218671</v>
       </c>
-      <c r="G54" s="38">
-        <f t="shared" si="5"/>
+      <c r="G54" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H54" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="39">
+      <c r="H54" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K54" s="39">
+      <c r="K54" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="36">
+      <c r="A55" s="15">
         <v>46248</v>
       </c>
-      <c r="B55" s="37">
+      <c r="B55" s="16">
         <f>B54+25-540-1100-7593+350-1166-690</f>
         <v>371274.7</v>
       </c>
-      <c r="C55" s="34">
-        <v>0</v>
-      </c>
-      <c r="D55" s="35">
-        <v>0</v>
-      </c>
-      <c r="E55" s="35">
+      <c r="C55" s="13">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
         <v>460736</v>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="14">
         <v>218671</v>
       </c>
-      <c r="G55" s="38">
-        <f t="shared" si="5"/>
+      <c r="G55" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H55" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="39">
+      <c r="H55" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K55" s="39">
+      <c r="K55" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="36">
+      <c r="A56" s="15">
         <v>46251</v>
       </c>
-      <c r="B56" s="37">
+      <c r="B56" s="16">
         <f>B55+95+1620-1380+725+796+220</f>
         <v>373350.7</v>
       </c>
-      <c r="C56" s="34">
-        <v>0</v>
-      </c>
-      <c r="D56" s="35">
-        <v>0</v>
-      </c>
-      <c r="E56" s="35">
+      <c r="C56" s="13">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
         <v>460736</v>
       </c>
-      <c r="F56" s="35">
+      <c r="F56" s="14">
         <v>218671</v>
       </c>
-      <c r="G56" s="38">
-        <f t="shared" si="5"/>
+      <c r="G56" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H56" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="39">
+      <c r="H56" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K56" s="39">
+      <c r="K56" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="36">
+      <c r="A57" s="15">
         <v>46252</v>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="16">
         <f>B56+590+1620+620+1095+826+2690</f>
         <v>380791.7</v>
       </c>
-      <c r="C57" s="34">
-        <v>0</v>
-      </c>
-      <c r="D57" s="35">
-        <v>0</v>
-      </c>
-      <c r="E57" s="35">
+      <c r="C57" s="13">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
         <v>460736</v>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="14">
         <v>218671</v>
       </c>
-      <c r="G57" s="38">
-        <f t="shared" si="5"/>
+      <c r="G57" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H57" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="39">
+      <c r="H57" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K57" s="39">
+      <c r="K57" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="36">
+      <c r="A58" s="15">
         <v>46253</v>
       </c>
-      <c r="B58" s="37">
+      <c r="B58" s="16">
         <f>B57-195+5550+2720-300-3504+1730</f>
         <v>386792.7</v>
       </c>
-      <c r="C58" s="34">
-        <v>0</v>
-      </c>
-      <c r="D58" s="35">
-        <v>0</v>
-      </c>
-      <c r="E58" s="35">
+      <c r="C58" s="13">
+        <v>0</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
         <v>460736</v>
       </c>
-      <c r="F58" s="35">
+      <c r="F58" s="14">
         <v>218671</v>
       </c>
-      <c r="G58" s="38">
-        <f t="shared" si="5"/>
+      <c r="G58" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H58" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="39">
+      <c r="H58" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K58" s="39">
+      <c r="K58" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="36">
+      <c r="A59" s="15">
         <v>46254</v>
       </c>
-      <c r="B59" s="37">
+      <c r="B59" s="16">
         <f>B58+155+870-1360+1107.05+1330+1165.8+1267.76</f>
         <v>391328.31</v>
       </c>
-      <c r="C59" s="34">
-        <v>0</v>
-      </c>
-      <c r="D59" s="35">
-        <v>0</v>
-      </c>
-      <c r="E59" s="35">
+      <c r="C59" s="13">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
         <v>460736</v>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="14">
         <v>218671</v>
       </c>
-      <c r="G59" s="38">
-        <f t="shared" si="5"/>
+      <c r="G59" s="17">
+        <f t="shared" si="6"/>
         <v>679407</v>
       </c>
-      <c r="H59" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="39">
+      <c r="H59" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="18">
         <f t="shared" si="2"/>
         <v>0.67814432291689664</v>
       </c>
-      <c r="K59" s="39">
+      <c r="K59" s="18">
         <f t="shared" si="3"/>
         <v>0.32185567708310336</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="36">
+      <c r="A60" s="15">
         <v>46255</v>
       </c>
-      <c r="B60" s="37">
+      <c r="B60" s="16">
         <f>B59-445-450-580+585-575-2123</f>
         <v>387740.31</v>
       </c>
-      <c r="C60" s="34">
-        <v>0</v>
-      </c>
-      <c r="D60" s="35">
-        <v>0</v>
-      </c>
-      <c r="E60" s="35">
+      <c r="C60" s="13">
+        <v>0</v>
+      </c>
+      <c r="D60" s="14">
+        <v>0</v>
+      </c>
+      <c r="E60" s="14">
         <v>775877</v>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="14">
         <v>218671</v>
       </c>
-      <c r="G60" s="38">
-        <f t="shared" si="5"/>
+      <c r="G60" s="17">
+        <f t="shared" si="6"/>
         <v>994548</v>
       </c>
-      <c r="H60" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="39">
+      <c r="H60" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="18">
         <f t="shared" si="2"/>
         <v>0.78013027023331205</v>
       </c>
-      <c r="K60" s="39">
+      <c r="K60" s="18">
         <f t="shared" si="3"/>
         <v>0.21986972976668798</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="36">
+      <c r="A61" s="15">
         <v>46258</v>
       </c>
-      <c r="B61" s="37">
+      <c r="B61" s="16">
         <f>B60+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C61" s="34">
-        <v>0</v>
-      </c>
-      <c r="D61" s="35">
-        <v>0</v>
-      </c>
-      <c r="E61" s="35">
+      <c r="C61" s="13">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>0</v>
+      </c>
+      <c r="E61" s="14">
         <v>480842</v>
       </c>
-      <c r="F61" s="35">
+      <c r="F61" s="14">
         <v>218671</v>
       </c>
-      <c r="G61" s="38">
-        <f t="shared" si="5"/>
+      <c r="G61" s="17">
+        <f t="shared" si="6"/>
         <v>699513</v>
       </c>
-      <c r="H61" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="39">
+      <c r="H61" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="18">
         <f t="shared" si="2"/>
         <v>0.6873953736385171</v>
       </c>
-      <c r="K61" s="39">
+      <c r="K61" s="18">
         <f t="shared" si="3"/>
         <v>0.3126046263614829</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="36">
+      <c r="A62" s="15">
         <v>46259</v>
       </c>
-      <c r="B62" s="37">
+      <c r="B62" s="16">
         <f>B61-390+1290+906-402+1017</f>
         <v>396282.31</v>
       </c>
-      <c r="C62" s="34">
-        <v>0</v>
-      </c>
-      <c r="D62" s="38">
-        <f t="shared" ref="D62:D65" si="7">B62-E62-F62</f>
+      <c r="C62" s="13">
+        <v>0</v>
+      </c>
+      <c r="D62" s="17">
+        <f t="shared" ref="D62:D65" si="8">B62-E62-F62</f>
         <v>341611.31</v>
       </c>
-      <c r="E62" s="35">
-        <v>0</v>
-      </c>
-      <c r="F62" s="35">
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
         <v>54671</v>
       </c>
-      <c r="G62" s="38">
-        <f t="shared" si="5"/>
+      <c r="G62" s="17">
+        <f t="shared" si="6"/>
         <v>396282.31</v>
       </c>
-      <c r="H62" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="39">
+      <c r="H62" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="18">
         <f t="shared" si="1"/>
         <v>0.86204027123996529</v>
       </c>
-      <c r="J62" s="39">
+      <c r="J62" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K62" s="39">
+      <c r="K62" s="18">
         <f t="shared" si="3"/>
         <v>0.13795972876003473</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="36">
+      <c r="A63" s="15">
         <v>46260</v>
       </c>
-      <c r="B63" s="37">
+      <c r="B63" s="16">
         <f>B62+270-750</f>
         <v>395802.31</v>
       </c>
-      <c r="C63" s="34">
-        <v>0</v>
-      </c>
-      <c r="D63" s="38">
-        <f t="shared" si="7"/>
+      <c r="C63" s="13">
+        <v>0</v>
+      </c>
+      <c r="D63" s="17">
+        <f t="shared" si="8"/>
         <v>341131.31</v>
       </c>
-      <c r="E63" s="35">
-        <v>0</v>
-      </c>
-      <c r="F63" s="35">
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
         <v>54671</v>
       </c>
-      <c r="G63" s="38">
-        <f t="shared" si="5"/>
+      <c r="G63" s="17">
+        <f t="shared" si="6"/>
         <v>395802.31</v>
       </c>
-      <c r="H63" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="39">
+      <c r="H63" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="18">
         <f t="shared" si="1"/>
         <v>0.86187296380357159</v>
       </c>
-      <c r="J63" s="39">
+      <c r="J63" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K63" s="39">
+      <c r="K63" s="18">
         <f t="shared" si="3"/>
         <v>0.13812703619642847</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="36">
+      <c r="A64" s="15">
         <v>46261</v>
       </c>
-      <c r="B64" s="37">
+      <c r="B64" s="16">
         <f>B63+125+690</f>
         <v>396617.31</v>
       </c>
-      <c r="C64" s="34">
-        <v>0</v>
-      </c>
-      <c r="D64" s="38">
-        <f t="shared" si="7"/>
+      <c r="C64" s="13">
+        <v>0</v>
+      </c>
+      <c r="D64" s="17">
+        <f t="shared" si="8"/>
         <v>341946.31</v>
       </c>
-      <c r="E64" s="35">
-        <v>0</v>
-      </c>
-      <c r="F64" s="35">
+      <c r="E64" s="14">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
         <v>54671</v>
       </c>
-      <c r="G64" s="38">
-        <f t="shared" si="5"/>
+      <c r="G64" s="17">
+        <f t="shared" si="6"/>
         <v>396617.31</v>
       </c>
-      <c r="H64" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="39">
+      <c r="H64" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="18">
         <f t="shared" si="1"/>
         <v>0.8621567979471193</v>
       </c>
-      <c r="J64" s="39">
+      <c r="J64" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K64" s="39">
+      <c r="K64" s="18">
         <f t="shared" si="3"/>
         <v>0.13784320205288064</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="36">
+      <c r="A65" s="15">
         <v>46262</v>
       </c>
-      <c r="B65" s="37">
+      <c r="B65" s="16">
         <f>B64+300</f>
         <v>396917.31</v>
       </c>
-      <c r="C65" s="34">
-        <v>0</v>
-      </c>
-      <c r="D65" s="38">
-        <f t="shared" si="7"/>
+      <c r="C65" s="13">
+        <v>0</v>
+      </c>
+      <c r="D65" s="17">
+        <f t="shared" si="8"/>
         <v>342246.31</v>
       </c>
-      <c r="E65" s="35">
-        <v>0</v>
-      </c>
-      <c r="F65" s="35">
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
         <v>54671</v>
       </c>
-      <c r="G65" s="38">
-        <f t="shared" si="5"/>
+      <c r="G65" s="17">
+        <f t="shared" si="6"/>
         <v>396917.31</v>
       </c>
-      <c r="H65" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="39">
+      <c r="H65" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="18">
         <f t="shared" si="1"/>
         <v>0.86226098327634038</v>
       </c>
-      <c r="J65" s="39">
+      <c r="J65" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K65" s="39">
+      <c r="K65" s="18">
         <f t="shared" si="3"/>
         <v>0.13773901672365965</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="36">
+      <c r="A66" s="15">
         <v>46265</v>
       </c>
-      <c r="B66" s="37">
+      <c r="B66" s="16">
         <f>B65+135+2220-2.59</f>
         <v>399269.72</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="13">
         <v>59799</v>
       </c>
-      <c r="D66" s="38">
-        <v>0</v>
-      </c>
-      <c r="E66" s="35">
-        <v>0</v>
-      </c>
-      <c r="F66" s="35">
+      <c r="D66" s="17">
+        <v>0</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
         <v>54671</v>
       </c>
-      <c r="G66" s="38">
-        <f t="shared" si="5"/>
+      <c r="G66" s="17">
+        <f t="shared" si="6"/>
         <v>114470</v>
       </c>
-      <c r="H66" s="39">
+      <c r="H66" s="18">
         <f t="shared" si="0"/>
         <v>0.52239888180309246</v>
       </c>
-      <c r="I66" s="39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="39">
+      <c r="I66" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K66" s="39">
+      <c r="K66" s="18">
         <f t="shared" si="3"/>
         <v>0.47760111819690748</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="36">
+      <c r="A67" s="15">
         <v>46266</v>
       </c>
-      <c r="B67" s="37">
+      <c r="B67" s="16">
         <f>B66+480-562+1405-1361-623+1800+428</f>
         <v>400836.72</v>
       </c>
-      <c r="C67" s="34">
+      <c r="C67" s="13">
         <v>871422</v>
       </c>
-      <c r="D67" s="35">
-        <v>0</v>
-      </c>
-      <c r="E67" s="35">
-        <v>0</v>
-      </c>
-      <c r="F67" s="35">
+      <c r="D67" s="14">
+        <v>0</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
         <v>54671</v>
       </c>
-      <c r="G67" s="38">
-        <f t="shared" si="5"/>
+      <c r="G67" s="17">
+        <f t="shared" si="6"/>
         <v>926093</v>
       </c>
-      <c r="H67" s="39">
-        <f t="shared" ref="H67:H70" si="8">C67/G67</f>
+      <c r="H67" s="18">
+        <f t="shared" ref="H67:H70" si="9">C67/G67</f>
         <v>0.94096597209999433</v>
       </c>
-      <c r="I67" s="39">
-        <f t="shared" ref="I67:I70" si="9">D67/G67</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="39">
-        <f t="shared" ref="J67:J70" si="10">E67/G67</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="39">
-        <f t="shared" ref="K67:K70" si="11">F67/G67</f>
+      <c r="I67" s="18">
+        <f t="shared" ref="I67:I70" si="10">D67/G67</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="18">
+        <f t="shared" ref="J67:J70" si="11">E67/G67</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="18">
+        <f t="shared" ref="K67:K70" si="12">F67/G67</f>
         <v>5.9034027900005726E-2</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="36">
+      <c r="A68" s="15">
         <v>46267</v>
       </c>
-      <c r="B68" s="37">
+      <c r="B68" s="16">
         <f>B67-274+71-569+1738+320</f>
         <v>402122.72</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="13">
         <f>C67-132000</f>
         <v>739422</v>
       </c>
-      <c r="D68" s="35">
-        <v>0</v>
-      </c>
-      <c r="E68" s="35">
-        <v>0</v>
-      </c>
-      <c r="F68" s="35">
+      <c r="D68" s="14">
+        <v>0</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
         <v>54671</v>
       </c>
-      <c r="G68" s="38">
-        <f t="shared" si="5"/>
+      <c r="G68" s="17">
+        <f t="shared" si="6"/>
         <v>794093</v>
       </c>
-      <c r="H68" s="39">
-        <f t="shared" si="8"/>
+      <c r="H68" s="18">
+        <f t="shared" si="9"/>
         <v>0.93115290022705144</v>
       </c>
-      <c r="I68" s="39">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="39">
+      <c r="I68" s="18">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K68" s="39">
+      <c r="J68" s="18">
         <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="18">
+        <f t="shared" si="12"/>
         <v>6.8847099772948506E-2</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="36">
+      <c r="A69" s="15">
         <v>46268</v>
       </c>
-      <c r="B69" s="37">
+      <c r="B69" s="16">
         <f>B68-274+71-569+1738+320</f>
         <v>403408.72</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="13">
         <v>101060</v>
       </c>
-      <c r="D69" s="38">
+      <c r="D69" s="17">
         <f>B69-C69</f>
         <v>302348.71999999997</v>
       </c>
-      <c r="E69" s="35">
-        <v>0</v>
-      </c>
-      <c r="F69" s="35">
-        <v>0</v>
-      </c>
-      <c r="G69" s="38">
-        <f t="shared" si="5"/>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="17">
+        <f t="shared" si="6"/>
         <v>403408.72</v>
       </c>
-      <c r="H69" s="39">
-        <f t="shared" si="8"/>
+      <c r="H69" s="18">
+        <f t="shared" si="9"/>
         <v>0.25051515991027662</v>
       </c>
-      <c r="I69" s="39">
-        <f t="shared" si="9"/>
+      <c r="I69" s="18">
+        <f t="shared" si="10"/>
         <v>0.74948484008972338</v>
       </c>
-      <c r="J69" s="39">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="39">
+      <c r="J69" s="18">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="K69" s="18">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="36">
+      <c r="A70" s="15">
         <v>46269</v>
       </c>
-      <c r="H70" s="39" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I70" s="39" t="e">
+      <c r="H70" s="18" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J70" s="39" t="e">
+      <c r="I70" s="18" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K70" s="39" t="e">
+      <c r="J70" s="18" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="K70" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1048543" s="36"/>
+      <c r="A1048543" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2916B97A-C99E-F542-86A5-0EE99A282E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A73BF9-2075-5A4A-BFC0-9C3A02F8AB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="660" windowWidth="35840" windowHeight="20740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
     <sheet name="Daily PnL" sheetId="3" r:id="rId2"/>
-    <sheet name="exposure" sheetId="6" r:id="rId3"/>
+    <sheet name="exposure" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -698,10 +698,10 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -710,10 +710,10 @@
     <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3316,7 +3316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="34" bestFit="1" customWidth="1"/>
@@ -3361,8 +3361,8 @@
         <v>114</v>
       </c>
       <c r="H2" s="37">
-        <f>AVERAGE(C3:C62)</f>
-        <v>1236.5848333333329</v>
+        <f>AVERAGE(C3:C63)</f>
+        <v>1231.0670491803273</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -3384,8 +3384,8 @@
         <v>115</v>
       </c>
       <c r="H3" s="37">
-        <f>_xlfn.STDEV.S(C3:C62)</f>
-        <v>4530.4268575400629</v>
+        <f>_xlfn.STDEV.S(C3:C63)</f>
+        <v>4492.7213641015505</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -3396,11 +3396,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="32">
-        <f t="shared" ref="C4:C62" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C63" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="33">
-        <f t="shared" ref="D4:D62" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D63" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
       <c r="G4" s="35" t="s">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H4" s="38">
         <f>(H2/H3)*SQRT(252)</f>
-        <v>4.33296382029316</v>
+        <v>4.3498320889463207</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -3430,8 +3430,8 @@
         <v>117</v>
       </c>
       <c r="H5" s="39">
-        <f>_xlfn.STDEV.S(D2:D62)*SQRT(252)</f>
-        <v>0.1970845339269621</v>
+        <f>_xlfn.STDEV.S(D2:D63)*SQRT(252)</f>
+        <v>0.19547655346884943</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -3453,8 +3453,8 @@
         <v>118</v>
       </c>
       <c r="H6" s="39" cm="1">
-        <f t="array" ref="H6">PRODUCT(1+D2:D62)-1</f>
-        <v>0.22250363564112119</v>
+        <f t="array" ref="H6">PRODUCT(1+D2:D63)-1</f>
+        <v>0.2252026454014302</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -3476,8 +3476,8 @@
         <v>119</v>
       </c>
       <c r="H7" s="39" cm="1">
-        <f t="array" ref="H7">PRODUCT(1+D2:D62)^(252/COUNT(D2:D62))-1</f>
-        <v>1.2932071188156953</v>
+        <f t="array" ref="H7">PRODUCT(1+D2:D63)^(252/COUNT(D2:D63))-1</f>
+        <v>1.2830874002729455</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4397,6 +4397,23 @@
       <c r="D62" s="33">
         <f t="shared" si="1"/>
         <v>1.3747047170077832E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="36">
+        <v>46269</v>
+      </c>
+      <c r="B63" s="32">
+        <f>B62+900</f>
+        <v>408550.72</v>
+      </c>
+      <c r="C63" s="32">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="D63" s="33">
+        <f t="shared" si="1"/>
+        <v>2.2077723792564381E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4406,33 +4423,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCEC7B0-BA8A-0742-BC28-9DF7B1D541EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEDD2B-54BB-1449-BCF8-F93ADB145E3A}">
   <dimension ref="A1:T1048543"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="40" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="9.1640625" style="15" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="44" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="41" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.1640625" style="17" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="17.5" style="40" customWidth="1"/>
-    <col min="18" max="18" width="19.1640625" style="40" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5" style="45" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="17.5" style="45" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" style="45" customWidth="1"/>
     <col min="19" max="19" width="12.83203125" style="17" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9.1640625" style="17"/>
     <col min="21" max="16384" width="9.1640625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>121</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -4459,7 +4476,7 @@
       <c r="J1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="41" t="s">
         <v>124</v>
       </c>
       <c r="L1" s="13" t="s">
@@ -4519,7 +4536,7 @@
       <c r="J2" s="15">
         <v>0</v>
       </c>
-      <c r="K2" s="45">
+      <c r="K2" s="44">
         <v>300000</v>
       </c>
       <c r="L2" s="16">
@@ -4528,19 +4545,19 @@
       <c r="M2" s="16">
         <v>0.64762666666666668</v>
       </c>
-      <c r="N2" s="40">
-        <v>0</v>
-      </c>
-      <c r="O2" s="40">
-        <v>0</v>
-      </c>
-      <c r="P2" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="40">
-        <v>0</v>
-      </c>
-      <c r="R2" s="40">
+      <c r="N2" s="45">
+        <v>0</v>
+      </c>
+      <c r="O2" s="45">
+        <v>0</v>
+      </c>
+      <c r="P2" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="45">
+        <v>0</v>
+      </c>
+      <c r="R2" s="45">
         <v>0</v>
       </c>
       <c r="S2" s="16">
@@ -4578,7 +4595,7 @@
       <c r="J3" s="15">
         <v>0</v>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="44">
         <v>300000</v>
       </c>
       <c r="L3" s="16">
@@ -4587,19 +4604,19 @@
       <c r="M3" s="16">
         <v>0.64762666666666668</v>
       </c>
-      <c r="N3" s="40">
-        <v>0</v>
-      </c>
-      <c r="O3" s="40">
-        <v>0</v>
-      </c>
-      <c r="P3" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="40">
-        <v>0</v>
-      </c>
-      <c r="R3" s="40">
+      <c r="N3" s="45">
+        <v>0</v>
+      </c>
+      <c r="O3" s="45">
+        <v>0</v>
+      </c>
+      <c r="P3" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="45">
+        <v>0</v>
+      </c>
+      <c r="R3" s="45">
         <v>0</v>
       </c>
       <c r="S3" s="16">
@@ -4637,7 +4654,7 @@
       <c r="J4" s="15">
         <v>0</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="44">
         <v>300000</v>
       </c>
       <c r="L4" s="16">
@@ -4646,19 +4663,19 @@
       <c r="M4" s="16">
         <v>0.18540000000000001</v>
       </c>
-      <c r="N4" s="40">
-        <v>0</v>
-      </c>
-      <c r="O4" s="40">
-        <v>0</v>
-      </c>
-      <c r="P4" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="40">
-        <v>0</v>
-      </c>
-      <c r="R4" s="40">
+      <c r="N4" s="45">
+        <v>0</v>
+      </c>
+      <c r="O4" s="45">
+        <v>0</v>
+      </c>
+      <c r="P4" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="45">
+        <v>0</v>
+      </c>
+      <c r="R4" s="45">
         <v>0</v>
       </c>
       <c r="S4" s="16">
@@ -4696,7 +4713,7 @@
       <c r="J5" s="15">
         <v>0</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="44">
         <v>907730</v>
       </c>
       <c r="L5" s="16">
@@ -4705,19 +4722,19 @@
       <c r="M5" s="16">
         <v>0</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="45">
         <v>0.7307789761272625</v>
       </c>
-      <c r="O5" s="40">
-        <v>0</v>
-      </c>
-      <c r="P5" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="40">
-        <v>0</v>
-      </c>
-      <c r="R5" s="40">
+      <c r="O5" s="45">
+        <v>0</v>
+      </c>
+      <c r="P5" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="45">
+        <v>0</v>
+      </c>
+      <c r="R5" s="45">
         <v>0</v>
       </c>
       <c r="S5" s="16">
@@ -4755,7 +4772,7 @@
       <c r="J6" s="15">
         <v>0</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="44">
         <v>3696918</v>
       </c>
       <c r="L6" s="16">
@@ -4764,19 +4781,19 @@
       <c r="M6" s="16">
         <v>0</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="45">
         <v>0.17943324682884501</v>
       </c>
-      <c r="O6" s="40">
+      <c r="O6" s="45">
         <v>0.78305767128186232</v>
       </c>
-      <c r="P6" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="40">
-        <v>0</v>
-      </c>
-      <c r="R6" s="40">
+      <c r="P6" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="45">
+        <v>0</v>
+      </c>
+      <c r="R6" s="45">
         <v>0</v>
       </c>
       <c r="S6" s="16">
@@ -4814,7 +4831,7 @@
       <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="45">
+      <c r="K7" s="44">
         <v>802018</v>
       </c>
       <c r="L7" s="16">
@@ -4823,19 +4840,19 @@
       <c r="M7" s="16">
         <v>0</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="45">
         <v>0.82710113738095659</v>
       </c>
-      <c r="O7" s="40">
-        <v>0</v>
-      </c>
-      <c r="P7" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="40">
-        <v>0</v>
-      </c>
-      <c r="R7" s="40">
+      <c r="O7" s="45">
+        <v>0</v>
+      </c>
+      <c r="P7" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="45">
+        <v>0</v>
+      </c>
+      <c r="R7" s="45">
         <v>0</v>
       </c>
       <c r="S7" s="16">
@@ -4873,7 +4890,7 @@
       <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="45">
+      <c r="K8" s="44">
         <v>600137</v>
       </c>
       <c r="L8" s="16">
@@ -4882,19 +4899,19 @@
       <c r="M8" s="16">
         <v>0</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="45">
         <v>0.76893942549784466</v>
       </c>
-      <c r="O8" s="40">
-        <v>0</v>
-      </c>
-      <c r="P8" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="40">
-        <v>0</v>
-      </c>
-      <c r="R8" s="40">
+      <c r="O8" s="45">
+        <v>0</v>
+      </c>
+      <c r="P8" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="45">
+        <v>0</v>
+      </c>
+      <c r="R8" s="45">
         <v>0</v>
       </c>
       <c r="S8" s="16">
@@ -4932,7 +4949,7 @@
       <c r="J9" s="15">
         <v>0</v>
       </c>
-      <c r="K9" s="45">
+      <c r="K9" s="44">
         <v>600137</v>
       </c>
       <c r="L9" s="16">
@@ -4941,19 +4958,19 @@
       <c r="M9" s="16">
         <v>0</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="45">
         <v>0.76893942549784466</v>
       </c>
-      <c r="O9" s="40">
-        <v>0</v>
-      </c>
-      <c r="P9" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="40">
-        <v>0</v>
-      </c>
-      <c r="R9" s="40">
+      <c r="O9" s="45">
+        <v>0</v>
+      </c>
+      <c r="P9" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="45">
+        <v>0</v>
+      </c>
+      <c r="R9" s="45">
         <v>0</v>
       </c>
       <c r="S9" s="16">
@@ -4991,7 +5008,7 @@
       <c r="J10" s="15">
         <v>0</v>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="44">
         <v>461469</v>
       </c>
       <c r="L10" s="16">
@@ -5000,19 +5017,19 @@
       <c r="M10" s="16">
         <v>0</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="45">
         <v>1</v>
       </c>
-      <c r="O10" s="40">
-        <v>0</v>
-      </c>
-      <c r="P10" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="40">
-        <v>0</v>
-      </c>
-      <c r="R10" s="40">
+      <c r="O10" s="45">
+        <v>0</v>
+      </c>
+      <c r="P10" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="45">
+        <v>0</v>
+      </c>
+      <c r="R10" s="45">
         <v>0</v>
       </c>
       <c r="S10" s="16">
@@ -5050,7 +5067,7 @@
       <c r="J11" s="15">
         <v>0</v>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="44">
         <v>461469</v>
       </c>
       <c r="L11" s="16">
@@ -5059,19 +5076,19 @@
       <c r="M11" s="16">
         <v>0</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="45">
         <v>1</v>
       </c>
-      <c r="O11" s="40">
-        <v>0</v>
-      </c>
-      <c r="P11" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="40">
-        <v>0</v>
-      </c>
-      <c r="R11" s="40">
+      <c r="O11" s="45">
+        <v>0</v>
+      </c>
+      <c r="P11" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="45">
+        <v>0</v>
+      </c>
+      <c r="R11" s="45">
         <v>0</v>
       </c>
       <c r="S11" s="16">
@@ -5109,7 +5126,7 @@
       <c r="J12" s="15">
         <v>0</v>
       </c>
-      <c r="K12" s="45">
+      <c r="K12" s="44">
         <v>461469</v>
       </c>
       <c r="L12" s="16">
@@ -5118,19 +5135,19 @@
       <c r="M12" s="16">
         <v>0</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="45">
         <v>1</v>
       </c>
-      <c r="O12" s="40">
-        <v>0</v>
-      </c>
-      <c r="P12" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="40">
-        <v>0</v>
-      </c>
-      <c r="R12" s="40">
+      <c r="O12" s="45">
+        <v>0</v>
+      </c>
+      <c r="P12" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>0</v>
+      </c>
+      <c r="R12" s="45">
         <v>0</v>
       </c>
       <c r="S12" s="16">
@@ -5168,7 +5185,7 @@
       <c r="J13" s="15">
         <v>0</v>
       </c>
-      <c r="K13" s="45">
+      <c r="K13" s="44">
         <v>592709</v>
       </c>
       <c r="L13" s="16">
@@ -5177,19 +5194,19 @@
       <c r="M13" s="16">
         <v>0</v>
       </c>
-      <c r="N13" s="40">
+      <c r="N13" s="45">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O13" s="40">
-        <v>0</v>
-      </c>
-      <c r="P13" s="40">
+      <c r="O13" s="45">
+        <v>0</v>
+      </c>
+      <c r="P13" s="45">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q13" s="40">
-        <v>0</v>
-      </c>
-      <c r="R13" s="40">
+      <c r="Q13" s="45">
+        <v>0</v>
+      </c>
+      <c r="R13" s="45">
         <v>0</v>
       </c>
       <c r="S13" s="16">
@@ -5227,7 +5244,7 @@
       <c r="J14" s="15">
         <v>0</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="44">
         <v>592709</v>
       </c>
       <c r="L14" s="16">
@@ -5236,19 +5253,19 @@
       <c r="M14" s="16">
         <v>0</v>
       </c>
-      <c r="N14" s="40">
+      <c r="N14" s="45">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O14" s="40">
-        <v>0</v>
-      </c>
-      <c r="P14" s="40">
+      <c r="O14" s="45">
+        <v>0</v>
+      </c>
+      <c r="P14" s="45">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q14" s="40">
-        <v>0</v>
-      </c>
-      <c r="R14" s="40">
+      <c r="Q14" s="45">
+        <v>0</v>
+      </c>
+      <c r="R14" s="45">
         <v>0</v>
       </c>
       <c r="S14" s="16">
@@ -5286,7 +5303,7 @@
       <c r="J15" s="15">
         <v>0</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="44">
         <v>592709</v>
       </c>
       <c r="L15" s="16">
@@ -5295,19 +5312,19 @@
       <c r="M15" s="16">
         <v>0</v>
       </c>
-      <c r="N15" s="40">
+      <c r="N15" s="45">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O15" s="40">
-        <v>0</v>
-      </c>
-      <c r="P15" s="40">
+      <c r="O15" s="45">
+        <v>0</v>
+      </c>
+      <c r="P15" s="45">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q15" s="40">
-        <v>0</v>
-      </c>
-      <c r="R15" s="40">
+      <c r="Q15" s="45">
+        <v>0</v>
+      </c>
+      <c r="R15" s="45">
         <v>0</v>
       </c>
       <c r="S15" s="16">
@@ -5345,7 +5362,7 @@
       <c r="J16" s="15">
         <v>0</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="44">
         <v>3586250</v>
       </c>
       <c r="L16" s="16">
@@ -5354,19 +5371,19 @@
       <c r="M16" s="16">
         <v>0</v>
       </c>
-      <c r="N16" s="40">
+      <c r="N16" s="45">
         <v>0.12867730916695713</v>
       </c>
-      <c r="O16" s="40">
+      <c r="O16" s="45">
         <v>0.87132269083304292</v>
       </c>
-      <c r="P16" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="40">
-        <v>0</v>
-      </c>
-      <c r="R16" s="40">
+      <c r="P16" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="45">
+        <v>0</v>
+      </c>
+      <c r="R16" s="45">
         <v>0</v>
       </c>
       <c r="S16" s="16">
@@ -5404,7 +5421,7 @@
       <c r="J17" s="15">
         <v>0</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="44">
         <v>3586250</v>
       </c>
       <c r="L17" s="16">
@@ -5413,19 +5430,19 @@
       <c r="M17" s="16">
         <v>0</v>
       </c>
-      <c r="N17" s="40">
+      <c r="N17" s="45">
         <v>0.12867730916695713</v>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="45">
         <v>0.87132269083304292</v>
       </c>
-      <c r="P17" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="40">
-        <v>0</v>
-      </c>
-      <c r="R17" s="40">
+      <c r="P17" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="45">
+        <v>0</v>
+      </c>
+      <c r="R17" s="45">
         <v>0</v>
       </c>
       <c r="S17" s="16">
@@ -5463,7 +5480,7 @@
       <c r="J18" s="15">
         <v>193096</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="44">
         <v>3779346</v>
       </c>
       <c r="L18" s="16">
@@ -5472,19 +5489,19 @@
       <c r="M18" s="16">
         <v>0</v>
       </c>
-      <c r="N18" s="40">
+      <c r="N18" s="45">
         <v>0.12210287176670249</v>
       </c>
-      <c r="O18" s="40">
+      <c r="O18" s="45">
         <v>0.8268046905469888</v>
       </c>
-      <c r="P18" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="40">
-        <v>0</v>
-      </c>
-      <c r="R18" s="40">
+      <c r="P18" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="45">
+        <v>0</v>
+      </c>
+      <c r="R18" s="45">
         <v>0</v>
       </c>
       <c r="S18" s="16">
@@ -5522,7 +5539,7 @@
       <c r="J19" s="15">
         <v>193096</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="44">
         <v>3981471</v>
       </c>
       <c r="L19" s="16">
@@ -5531,19 +5548,19 @@
       <c r="M19" s="16">
         <v>0</v>
       </c>
-      <c r="N19" s="40">
+      <c r="N19" s="45">
         <v>0.16667055970017111</v>
       </c>
-      <c r="O19" s="40">
+      <c r="O19" s="45">
         <v>0.78483078239173409</v>
       </c>
-      <c r="P19" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="40">
-        <v>0</v>
-      </c>
-      <c r="R19" s="40">
+      <c r="P19" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="45">
+        <v>0</v>
+      </c>
+      <c r="R19" s="45">
         <v>0</v>
       </c>
       <c r="S19" s="16">
@@ -5581,7 +5598,7 @@
       <c r="J20" s="15">
         <v>193096</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="44">
         <v>3981471</v>
       </c>
       <c r="L20" s="16">
@@ -5590,19 +5607,19 @@
       <c r="M20" s="16">
         <v>0</v>
       </c>
-      <c r="N20" s="40">
+      <c r="N20" s="45">
         <v>0.16667055970017111</v>
       </c>
-      <c r="O20" s="40">
+      <c r="O20" s="45">
         <v>0.78483078239173409</v>
       </c>
-      <c r="P20" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="40">
-        <v>0</v>
-      </c>
-      <c r="R20" s="40">
+      <c r="P20" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="45">
+        <v>0</v>
+      </c>
+      <c r="R20" s="45">
         <v>0</v>
       </c>
       <c r="S20" s="16">
@@ -5640,7 +5657,7 @@
       <c r="J21" s="15">
         <v>416939</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="44">
         <v>4260349</v>
       </c>
       <c r="L21" s="16">
@@ -5649,19 +5666,19 @@
       <c r="M21" s="16">
         <v>0</v>
       </c>
-      <c r="N21" s="40">
+      <c r="N21" s="45">
         <v>0.1557604787776776</v>
       </c>
-      <c r="O21" s="40">
+      <c r="O21" s="45">
         <v>0.73345657832257405</v>
       </c>
-      <c r="P21" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="40">
-        <v>0</v>
-      </c>
-      <c r="R21" s="40">
+      <c r="P21" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="45">
+        <v>0</v>
+      </c>
+      <c r="R21" s="45">
         <v>0</v>
       </c>
       <c r="S21" s="16">
@@ -5699,7 +5716,7 @@
       <c r="J22" s="15">
         <v>223843</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="44">
         <v>3524723</v>
       </c>
       <c r="L22" s="16">
@@ -5708,19 +5725,19 @@
       <c r="M22" s="16">
         <v>0</v>
       </c>
-      <c r="N22" s="40">
-        <v>0</v>
-      </c>
-      <c r="O22" s="40">
+      <c r="N22" s="45">
+        <v>0</v>
+      </c>
+      <c r="O22" s="45">
         <v>0.88653236013156211</v>
       </c>
-      <c r="P22" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="40">
+      <c r="P22" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="45">
         <v>3.4347096211532084E-2</v>
       </c>
-      <c r="R22" s="40">
+      <c r="R22" s="45">
         <v>0</v>
       </c>
       <c r="S22" s="16">
@@ -5758,7 +5775,7 @@
       <c r="J23" s="15">
         <v>223843</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="44">
         <v>3469688</v>
       </c>
       <c r="L23" s="16">
@@ -5767,19 +5784,19 @@
       <c r="M23" s="16">
         <v>0</v>
       </c>
-      <c r="N23" s="40">
-        <v>0</v>
-      </c>
-      <c r="O23" s="40">
+      <c r="N23" s="45">
+        <v>0</v>
+      </c>
+      <c r="O23" s="45">
         <v>0.90059423210386635</v>
       </c>
-      <c r="P23" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="40">
+      <c r="P23" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="45">
         <v>3.4891898061151318E-2</v>
       </c>
-      <c r="R23" s="40">
+      <c r="R23" s="45">
         <v>0</v>
       </c>
       <c r="S23" s="16">
@@ -5817,7 +5834,7 @@
       <c r="J24" s="15">
         <v>223843</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="44">
         <v>374651</v>
       </c>
       <c r="L24" s="16">
@@ -5826,19 +5843,19 @@
       <c r="M24" s="16">
         <v>7.9391220095502216E-2</v>
       </c>
-      <c r="N24" s="40">
-        <v>0</v>
-      </c>
-      <c r="O24" s="40">
-        <v>0</v>
-      </c>
-      <c r="P24" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="40">
+      <c r="N24" s="45">
+        <v>0</v>
+      </c>
+      <c r="O24" s="45">
+        <v>0</v>
+      </c>
+      <c r="P24" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="45">
         <v>0.32313806716117133</v>
       </c>
-      <c r="R24" s="40">
+      <c r="R24" s="45">
         <v>0</v>
       </c>
       <c r="S24" s="16">
@@ -5876,7 +5893,7 @@
       <c r="J25" s="15">
         <v>223843</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="44">
         <v>374479.39</v>
       </c>
       <c r="L25" s="16">
@@ -5885,19 +5902,19 @@
       <c r="M25" s="16">
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="N25" s="40">
-        <v>0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>0</v>
-      </c>
-      <c r="P25" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="40">
+      <c r="N25" s="45">
+        <v>0</v>
+      </c>
+      <c r="O25" s="45">
+        <v>0</v>
+      </c>
+      <c r="P25" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="45">
         <v>0.32328614933921995</v>
       </c>
-      <c r="R25" s="40">
+      <c r="R25" s="45">
         <v>0</v>
       </c>
       <c r="S25" s="16">
@@ -5935,7 +5952,7 @@
       <c r="J26" s="15">
         <v>223843</v>
       </c>
-      <c r="K26" s="45">
+      <c r="K26" s="44">
         <v>372801.92</v>
       </c>
       <c r="L26" s="16">
@@ -5944,19 +5961,19 @@
       <c r="M26" s="16">
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="N26" s="40">
-        <v>0</v>
-      </c>
-      <c r="O26" s="40">
-        <v>0</v>
-      </c>
-      <c r="P26" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="40">
+      <c r="N26" s="45">
+        <v>0</v>
+      </c>
+      <c r="O26" s="45">
+        <v>0</v>
+      </c>
+      <c r="P26" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="45">
         <v>0.32474081678549299</v>
       </c>
-      <c r="R26" s="40">
+      <c r="R26" s="45">
         <v>0</v>
       </c>
       <c r="S26" s="16">
@@ -5994,7 +6011,7 @@
       <c r="J27" s="15">
         <v>223843</v>
       </c>
-      <c r="K27" s="45">
+      <c r="K27" s="44">
         <v>375246.11</v>
       </c>
       <c r="L27" s="16">
@@ -6003,19 +6020,19 @@
       <c r="M27" s="16">
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="N27" s="40">
-        <v>0</v>
-      </c>
-      <c r="O27" s="40">
-        <v>0</v>
-      </c>
-      <c r="P27" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="40">
+      <c r="N27" s="45">
+        <v>0</v>
+      </c>
+      <c r="O27" s="45">
+        <v>0</v>
+      </c>
+      <c r="P27" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="45">
         <v>0.32262559630531545</v>
       </c>
-      <c r="R27" s="40">
+      <c r="R27" s="45">
         <v>0</v>
       </c>
       <c r="S27" s="16">
@@ -6053,7 +6070,7 @@
       <c r="J28" s="15">
         <v>223843</v>
       </c>
-      <c r="K28" s="45">
+      <c r="K28" s="44">
         <v>435718</v>
       </c>
       <c r="L28" s="16">
@@ -6062,19 +6079,19 @@
       <c r="M28" s="16">
         <v>0</v>
       </c>
-      <c r="N28" s="40">
-        <v>0</v>
-      </c>
-      <c r="O28" s="40">
-        <v>0</v>
-      </c>
-      <c r="P28" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="40">
+      <c r="N28" s="45">
+        <v>0</v>
+      </c>
+      <c r="O28" s="45">
+        <v>0</v>
+      </c>
+      <c r="P28" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="45">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R28" s="40">
+      <c r="R28" s="45">
         <v>0</v>
       </c>
       <c r="S28" s="16">
@@ -6112,7 +6129,7 @@
       <c r="J29" s="15">
         <v>223843</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="44">
         <v>435718</v>
       </c>
       <c r="L29" s="16">
@@ -6121,19 +6138,19 @@
       <c r="M29" s="16">
         <v>0</v>
       </c>
-      <c r="N29" s="40">
-        <v>0</v>
-      </c>
-      <c r="O29" s="40">
-        <v>0</v>
-      </c>
-      <c r="P29" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="40">
+      <c r="N29" s="45">
+        <v>0</v>
+      </c>
+      <c r="O29" s="45">
+        <v>0</v>
+      </c>
+      <c r="P29" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="45">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R29" s="40">
+      <c r="R29" s="45">
         <v>0</v>
       </c>
       <c r="S29" s="16">
@@ -6171,7 +6188,7 @@
       <c r="J30" s="15">
         <v>223843</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="44">
         <v>435718</v>
       </c>
       <c r="L30" s="16">
@@ -6180,19 +6197,19 @@
       <c r="M30" s="16">
         <v>0</v>
       </c>
-      <c r="N30" s="40">
-        <v>0</v>
-      </c>
-      <c r="O30" s="40">
-        <v>0</v>
-      </c>
-      <c r="P30" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="40">
+      <c r="N30" s="45">
+        <v>0</v>
+      </c>
+      <c r="O30" s="45">
+        <v>0</v>
+      </c>
+      <c r="P30" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="45">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R30" s="40">
+      <c r="R30" s="45">
         <v>0</v>
       </c>
       <c r="S30" s="16">
@@ -6230,7 +6247,7 @@
       <c r="J31" s="15">
         <v>223843</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="44">
         <v>435718</v>
       </c>
       <c r="L31" s="16">
@@ -6239,19 +6256,19 @@
       <c r="M31" s="16">
         <v>0</v>
       </c>
-      <c r="N31" s="40">
-        <v>0</v>
-      </c>
-      <c r="O31" s="40">
-        <v>0</v>
-      </c>
-      <c r="P31" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="40">
+      <c r="N31" s="45">
+        <v>0</v>
+      </c>
+      <c r="O31" s="45">
+        <v>0</v>
+      </c>
+      <c r="P31" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="45">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R31" s="40">
+      <c r="R31" s="45">
         <v>0</v>
       </c>
       <c r="S31" s="16">
@@ -6289,7 +6306,7 @@
       <c r="J32" s="15">
         <v>223843</v>
       </c>
-      <c r="K32" s="45">
+      <c r="K32" s="44">
         <v>378852.03</v>
       </c>
       <c r="L32" s="16">
@@ -6298,19 +6315,19 @@
       <c r="M32" s="16">
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="N32" s="40">
-        <v>0</v>
-      </c>
-      <c r="O32" s="40">
-        <v>0</v>
-      </c>
-      <c r="P32" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="40">
+      <c r="N32" s="45">
+        <v>0</v>
+      </c>
+      <c r="O32" s="45">
+        <v>0</v>
+      </c>
+      <c r="P32" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="45">
         <v>0.31955484044786558</v>
       </c>
-      <c r="R32" s="40">
+      <c r="R32" s="45">
         <v>0</v>
       </c>
       <c r="S32" s="16">
@@ -6348,7 +6365,7 @@
       <c r="J33" s="15">
         <v>223843</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="44">
         <v>374437.1</v>
       </c>
       <c r="L33" s="16">
@@ -6357,19 +6374,19 @@
       <c r="M33" s="16">
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="N33" s="40">
-        <v>0</v>
-      </c>
-      <c r="O33" s="40">
-        <v>0</v>
-      </c>
-      <c r="P33" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="40">
+      <c r="N33" s="45">
+        <v>0</v>
+      </c>
+      <c r="O33" s="45">
+        <v>0</v>
+      </c>
+      <c r="P33" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="45">
         <v>0.32332266220414591</v>
       </c>
-      <c r="R33" s="40">
+      <c r="R33" s="45">
         <v>0</v>
       </c>
       <c r="S33" s="16">
@@ -6407,7 +6424,7 @@
       <c r="J34" s="15">
         <v>223843</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="44">
         <v>372248.26</v>
       </c>
       <c r="L34" s="16">
@@ -6416,19 +6433,19 @@
       <c r="M34" s="16">
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="N34" s="40">
-        <v>0</v>
-      </c>
-      <c r="O34" s="40">
-        <v>0</v>
-      </c>
-      <c r="P34" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="40">
+      <c r="N34" s="45">
+        <v>0</v>
+      </c>
+      <c r="O34" s="45">
+        <v>0</v>
+      </c>
+      <c r="P34" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="45">
         <v>0.32522381703006481</v>
       </c>
-      <c r="R34" s="40">
+      <c r="R34" s="45">
         <v>0</v>
       </c>
       <c r="S34" s="16">
@@ -6466,7 +6483,7 @@
       <c r="J35" s="15">
         <v>223843</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="44">
         <v>376025.4</v>
       </c>
       <c r="L35" s="16">
@@ -6475,19 +6492,19 @@
       <c r="M35" s="16">
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="N35" s="40">
-        <v>0</v>
-      </c>
-      <c r="O35" s="40">
-        <v>0</v>
-      </c>
-      <c r="P35" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="40">
+      <c r="N35" s="45">
+        <v>0</v>
+      </c>
+      <c r="O35" s="45">
+        <v>0</v>
+      </c>
+      <c r="P35" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="45">
         <v>0.32195697418312696</v>
       </c>
-      <c r="R35" s="40">
+      <c r="R35" s="45">
         <v>0</v>
       </c>
       <c r="S35" s="16">
@@ -6525,7 +6542,7 @@
       <c r="J36" s="15">
         <v>223843</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="44">
         <v>375009.72</v>
       </c>
       <c r="L36" s="16">
@@ -6534,19 +6551,19 @@
       <c r="M36" s="16">
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="N36" s="40">
-        <v>0</v>
-      </c>
-      <c r="O36" s="40">
-        <v>0</v>
-      </c>
-      <c r="P36" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="40">
+      <c r="N36" s="45">
+        <v>0</v>
+      </c>
+      <c r="O36" s="45">
+        <v>0</v>
+      </c>
+      <c r="P36" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="45">
         <v>0.32282896560654484</v>
       </c>
-      <c r="R36" s="40">
+      <c r="R36" s="45">
         <v>0</v>
       </c>
       <c r="S36" s="16">
@@ -6584,7 +6601,7 @@
       <c r="J37" s="15">
         <v>223843</v>
       </c>
-      <c r="K37" s="45">
+      <c r="K37" s="44">
         <v>375731.28</v>
       </c>
       <c r="L37" s="16">
@@ -6593,19 +6610,19 @@
       <c r="M37" s="16">
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="N37" s="40">
-        <v>0</v>
-      </c>
-      <c r="O37" s="40">
-        <v>0</v>
-      </c>
-      <c r="P37" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="40">
+      <c r="N37" s="45">
+        <v>0</v>
+      </c>
+      <c r="O37" s="45">
+        <v>0</v>
+      </c>
+      <c r="P37" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="45">
         <v>0.32220900000660047</v>
       </c>
-      <c r="R37" s="40">
+      <c r="R37" s="45">
         <v>0</v>
       </c>
       <c r="S37" s="16">
@@ -6643,7 +6660,7 @@
       <c r="J38" s="15">
         <v>223843</v>
       </c>
-      <c r="K38" s="45">
+      <c r="K38" s="44">
         <v>378174.99</v>
       </c>
       <c r="L38" s="16">
@@ -6652,19 +6669,19 @@
       <c r="M38" s="16">
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="N38" s="40">
-        <v>0</v>
-      </c>
-      <c r="O38" s="40">
-        <v>0</v>
-      </c>
-      <c r="P38" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="40">
+      <c r="N38" s="45">
+        <v>0</v>
+      </c>
+      <c r="O38" s="45">
+        <v>0</v>
+      </c>
+      <c r="P38" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="45">
         <v>0.32012693383028845</v>
       </c>
-      <c r="R38" s="40">
+      <c r="R38" s="45">
         <v>0</v>
       </c>
       <c r="S38" s="16">
@@ -6702,7 +6719,7 @@
       <c r="J39" s="15">
         <v>223843</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="44">
         <v>380362.45</v>
       </c>
       <c r="L39" s="16">
@@ -6711,19 +6728,19 @@
       <c r="M39" s="16">
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="N39" s="40">
-        <v>0</v>
-      </c>
-      <c r="O39" s="40">
-        <v>0</v>
-      </c>
-      <c r="P39" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="40">
+      <c r="N39" s="45">
+        <v>0</v>
+      </c>
+      <c r="O39" s="45">
+        <v>0</v>
+      </c>
+      <c r="P39" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="45">
         <v>0.31828588757907095</v>
       </c>
-      <c r="R39" s="40">
+      <c r="R39" s="45">
         <v>0</v>
       </c>
       <c r="S39" s="16">
@@ -6762,7 +6779,7 @@
       <c r="J40" s="15">
         <v>223843</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="44">
         <v>377185.45</v>
       </c>
       <c r="L40" s="16">
@@ -6771,19 +6788,19 @@
       <c r="M40" s="16">
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="N40" s="40">
-        <v>0</v>
-      </c>
-      <c r="O40" s="40">
-        <v>0</v>
-      </c>
-      <c r="P40" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="40">
+      <c r="N40" s="45">
+        <v>0</v>
+      </c>
+      <c r="O40" s="45">
+        <v>0</v>
+      </c>
+      <c r="P40" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="45">
         <v>0.32096678172501086</v>
       </c>
-      <c r="R40" s="40">
+      <c r="R40" s="45">
         <v>0</v>
       </c>
       <c r="S40" s="16">
@@ -6822,7 +6839,7 @@
       <c r="J41" s="15">
         <v>223843</v>
       </c>
-      <c r="K41" s="45">
+      <c r="K41" s="44">
         <v>378220.45</v>
       </c>
       <c r="L41" s="16">
@@ -6831,19 +6848,19 @@
       <c r="M41" s="16">
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="N41" s="40">
-        <v>0</v>
-      </c>
-      <c r="O41" s="40">
-        <v>0</v>
-      </c>
-      <c r="P41" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="40">
+      <c r="N41" s="45">
+        <v>0</v>
+      </c>
+      <c r="O41" s="45">
+        <v>0</v>
+      </c>
+      <c r="P41" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="45">
         <v>0.32008845634867178</v>
       </c>
-      <c r="R41" s="40">
+      <c r="R41" s="45">
         <v>0</v>
       </c>
       <c r="S41" s="16">
@@ -6882,7 +6899,7 @@
       <c r="J42" s="15">
         <v>223843</v>
       </c>
-      <c r="K42" s="45">
+      <c r="K42" s="44">
         <v>679531</v>
       </c>
       <c r="L42" s="16">
@@ -6891,19 +6908,19 @@
       <c r="M42" s="16">
         <v>0</v>
       </c>
-      <c r="N42" s="40">
-        <v>0</v>
-      </c>
-      <c r="O42" s="40">
-        <v>0</v>
-      </c>
-      <c r="P42" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="40">
+      <c r="N42" s="45">
+        <v>0</v>
+      </c>
+      <c r="O42" s="45">
+        <v>0</v>
+      </c>
+      <c r="P42" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="45">
         <v>0.17815817085607574</v>
       </c>
-      <c r="R42" s="40">
+      <c r="R42" s="45">
         <v>0</v>
       </c>
       <c r="S42" s="16">
@@ -6942,7 +6959,7 @@
       <c r="J43" s="15">
         <v>223843</v>
       </c>
-      <c r="K43" s="45">
+      <c r="K43" s="44">
         <v>679531</v>
       </c>
       <c r="L43" s="16">
@@ -6951,19 +6968,19 @@
       <c r="M43" s="16">
         <v>0</v>
       </c>
-      <c r="N43" s="40">
-        <v>0</v>
-      </c>
-      <c r="O43" s="40">
-        <v>0</v>
-      </c>
-      <c r="P43" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="40">
+      <c r="N43" s="45">
+        <v>0</v>
+      </c>
+      <c r="O43" s="45">
+        <v>0</v>
+      </c>
+      <c r="P43" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="45">
         <v>0.17815817085607574</v>
       </c>
-      <c r="R43" s="40">
+      <c r="R43" s="45">
         <v>0</v>
       </c>
       <c r="S43" s="16">
@@ -7002,7 +7019,7 @@
       <c r="J44" s="15">
         <v>223843</v>
       </c>
-      <c r="K44" s="45">
+      <c r="K44" s="44">
         <v>391793.7</v>
       </c>
       <c r="L44" s="16">
@@ -7011,19 +7028,19 @@
       <c r="M44" s="16">
         <v>0.11967190896637697</v>
       </c>
-      <c r="N44" s="40">
-        <v>0</v>
-      </c>
-      <c r="O44" s="40">
-        <v>0</v>
-      </c>
-      <c r="P44" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="40">
+      <c r="N44" s="45">
+        <v>0</v>
+      </c>
+      <c r="O44" s="45">
+        <v>0</v>
+      </c>
+      <c r="P44" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="45">
         <v>0.30899935348628627</v>
       </c>
-      <c r="R44" s="40">
+      <c r="R44" s="45">
         <v>0</v>
       </c>
       <c r="S44" s="16">
@@ -7062,7 +7079,7 @@
       <c r="J45" s="15">
         <v>223843</v>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="44">
         <v>388741.7</v>
       </c>
       <c r="L45" s="16">
@@ -7071,19 +7088,19 @@
       <c r="M45" s="16">
         <v>0.11276047823014616</v>
       </c>
-      <c r="N45" s="40">
-        <v>0</v>
-      </c>
-      <c r="O45" s="40">
-        <v>0</v>
-      </c>
-      <c r="P45" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="40">
+      <c r="N45" s="45">
+        <v>0</v>
+      </c>
+      <c r="O45" s="45">
+        <v>0</v>
+      </c>
+      <c r="P45" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="45">
         <v>0.3114252985980151</v>
       </c>
-      <c r="R45" s="40">
+      <c r="R45" s="45">
         <v>0</v>
       </c>
       <c r="S45" s="16">
@@ -7122,7 +7139,7 @@
       <c r="J46" s="15">
         <v>223843</v>
       </c>
-      <c r="K46" s="45">
+      <c r="K46" s="44">
         <v>385314.7</v>
       </c>
       <c r="L46" s="16">
@@ -7131,19 +7148,19 @@
       <c r="M46" s="16">
         <v>0.10486934446051503</v>
       </c>
-      <c r="N46" s="40">
-        <v>0</v>
-      </c>
-      <c r="O46" s="40">
-        <v>0</v>
-      </c>
-      <c r="P46" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="40">
+      <c r="N46" s="45">
+        <v>0</v>
+      </c>
+      <c r="O46" s="45">
+        <v>0</v>
+      </c>
+      <c r="P46" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="45">
         <v>0.31419512414138362</v>
       </c>
-      <c r="R46" s="40">
+      <c r="R46" s="45">
         <v>0</v>
       </c>
       <c r="S46" s="16">
@@ -7182,7 +7199,7 @@
       <c r="J47" s="15">
         <v>223843</v>
       </c>
-      <c r="K47" s="45">
+      <c r="K47" s="44">
         <v>383427.7</v>
       </c>
       <c r="L47" s="16">
@@ -7191,19 +7208,19 @@
       <c r="M47" s="16">
         <v>0.1004640509801457</v>
       </c>
-      <c r="N47" s="40">
-        <v>0</v>
-      </c>
-      <c r="O47" s="40">
-        <v>0</v>
-      </c>
-      <c r="P47" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="40">
+      <c r="N47" s="45">
+        <v>0</v>
+      </c>
+      <c r="O47" s="45">
+        <v>0</v>
+      </c>
+      <c r="P47" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="45">
         <v>0.31574140313806226</v>
       </c>
-      <c r="R47" s="40">
+      <c r="R47" s="45">
         <v>0</v>
       </c>
       <c r="S47" s="16">
@@ -7242,7 +7259,7 @@
       <c r="J48" s="15">
         <v>223843</v>
       </c>
-      <c r="K48" s="45">
+      <c r="K48" s="44">
         <v>381652.7</v>
       </c>
       <c r="L48" s="16">
@@ -7251,19 +7268,19 @@
       <c r="M48" s="16">
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="N48" s="40">
-        <v>0</v>
-      </c>
-      <c r="O48" s="40">
-        <v>0</v>
-      </c>
-      <c r="P48" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="40">
+      <c r="N48" s="45">
+        <v>0</v>
+      </c>
+      <c r="O48" s="45">
+        <v>0</v>
+      </c>
+      <c r="P48" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="45">
         <v>0.31720986121675543</v>
       </c>
-      <c r="R48" s="40">
+      <c r="R48" s="45">
         <v>0</v>
       </c>
       <c r="S48" s="16">
@@ -7302,7 +7319,7 @@
       <c r="J49" s="15">
         <v>223843</v>
       </c>
-      <c r="K49" s="45">
+      <c r="K49" s="44">
         <v>383198.7</v>
       </c>
       <c r="L49" s="16">
@@ -7311,19 +7328,19 @@
       <c r="M49" s="16">
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="N49" s="40">
-        <v>0</v>
-      </c>
-      <c r="O49" s="40">
-        <v>0</v>
-      </c>
-      <c r="P49" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="40">
+      <c r="N49" s="45">
+        <v>0</v>
+      </c>
+      <c r="O49" s="45">
+        <v>0</v>
+      </c>
+      <c r="P49" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="45">
         <v>0.31593009057702959</v>
       </c>
-      <c r="R49" s="40">
+      <c r="R49" s="45">
         <v>0</v>
       </c>
       <c r="S49" s="16">
@@ -7362,7 +7379,7 @@
       <c r="J50" s="15">
         <v>223843</v>
       </c>
-      <c r="K50" s="45">
+      <c r="K50" s="44">
         <v>384776.7</v>
       </c>
       <c r="L50" s="16">
@@ -7371,19 +7388,19 @@
       <c r="M50" s="16">
         <v>0.10361776063883289</v>
       </c>
-      <c r="N50" s="40">
-        <v>0</v>
-      </c>
-      <c r="O50" s="40">
-        <v>0</v>
-      </c>
-      <c r="P50" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="40">
+      <c r="N50" s="45">
+        <v>0</v>
+      </c>
+      <c r="O50" s="45">
+        <v>0</v>
+      </c>
+      <c r="P50" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="45">
         <v>0.31463443602484248</v>
       </c>
-      <c r="R50" s="40">
+      <c r="R50" s="45">
         <v>0</v>
       </c>
       <c r="S50" s="16">
@@ -7422,7 +7439,7 @@
       <c r="J51" s="13">
         <v>54051</v>
       </c>
-      <c r="K51" s="45">
+      <c r="K51" s="44">
         <v>384909.7</v>
       </c>
       <c r="L51" s="16">
@@ -7431,19 +7448,19 @@
       <c r="M51" s="16">
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="N51" s="40">
-        <v>0</v>
-      </c>
-      <c r="O51" s="40">
-        <v>0</v>
-      </c>
-      <c r="P51" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="40">
+      <c r="N51" s="45">
+        <v>0</v>
+      </c>
+      <c r="O51" s="45">
+        <v>0</v>
+      </c>
+      <c r="P51" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="45">
         <v>0.31452571862959028</v>
       </c>
-      <c r="R51" s="40">
+      <c r="R51" s="45">
         <v>0.48162465118442066</v>
       </c>
       <c r="S51" s="16">
@@ -7482,7 +7499,7 @@
       <c r="J52" s="13">
         <v>54051</v>
       </c>
-      <c r="K52" s="45">
+      <c r="K52" s="44">
         <v>379686.7</v>
       </c>
       <c r="L52" s="16">
@@ -7491,19 +7508,19 @@
       <c r="M52" s="16">
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="N52" s="40">
-        <v>0</v>
-      </c>
-      <c r="O52" s="40">
-        <v>0</v>
-      </c>
-      <c r="P52" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="40">
+      <c r="N52" s="45">
+        <v>0</v>
+      </c>
+      <c r="O52" s="45">
+        <v>0</v>
+      </c>
+      <c r="P52" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="45">
         <v>0.31885235906340675</v>
       </c>
-      <c r="R52" s="40">
+      <c r="R52" s="45">
         <v>0.48824991762945608</v>
       </c>
       <c r="S52" s="16">
@@ -7542,7 +7559,7 @@
       <c r="J53" s="13">
         <v>218671</v>
       </c>
-      <c r="K53" s="45">
+      <c r="K53" s="44">
         <v>494025</v>
       </c>
       <c r="L53" s="16">
@@ -7551,19 +7568,19 @@
       <c r="M53" s="16">
         <v>0</v>
       </c>
-      <c r="N53" s="40">
-        <v>0</v>
-      </c>
-      <c r="O53" s="40">
-        <v>0</v>
-      </c>
-      <c r="P53" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="40">
+      <c r="N53" s="45">
+        <v>0</v>
+      </c>
+      <c r="O53" s="45">
+        <v>0</v>
+      </c>
+      <c r="P53" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R53" s="40">
+      <c r="R53" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S53" s="16">
@@ -7602,7 +7619,7 @@
       <c r="J54" s="13">
         <v>218671</v>
       </c>
-      <c r="K54" s="45">
+      <c r="K54" s="44">
         <v>494025</v>
       </c>
       <c r="L54" s="16">
@@ -7611,19 +7628,19 @@
       <c r="M54" s="16">
         <v>0</v>
       </c>
-      <c r="N54" s="40">
-        <v>0</v>
-      </c>
-      <c r="O54" s="40">
-        <v>0</v>
-      </c>
-      <c r="P54" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="40">
+      <c r="N54" s="45">
+        <v>0</v>
+      </c>
+      <c r="O54" s="45">
+        <v>0</v>
+      </c>
+      <c r="P54" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R54" s="40">
+      <c r="R54" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S54" s="16">
@@ -7662,7 +7679,7 @@
       <c r="J55" s="13">
         <v>218671</v>
       </c>
-      <c r="K55" s="45">
+      <c r="K55" s="44">
         <v>494025</v>
       </c>
       <c r="L55" s="16">
@@ -7671,19 +7688,19 @@
       <c r="M55" s="16">
         <v>0</v>
       </c>
-      <c r="N55" s="40">
-        <v>0</v>
-      </c>
-      <c r="O55" s="40">
-        <v>0</v>
-      </c>
-      <c r="P55" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="40">
+      <c r="N55" s="45">
+        <v>0</v>
+      </c>
+      <c r="O55" s="45">
+        <v>0</v>
+      </c>
+      <c r="P55" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R55" s="40">
+      <c r="R55" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S55" s="16">
@@ -7722,7 +7739,7 @@
       <c r="J56" s="13">
         <v>218671</v>
       </c>
-      <c r="K56" s="45">
+      <c r="K56" s="44">
         <v>494025</v>
       </c>
       <c r="L56" s="16">
@@ -7731,19 +7748,19 @@
       <c r="M56" s="16">
         <v>0</v>
       </c>
-      <c r="N56" s="40">
-        <v>0</v>
-      </c>
-      <c r="O56" s="40">
-        <v>0</v>
-      </c>
-      <c r="P56" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="40">
+      <c r="N56" s="45">
+        <v>0</v>
+      </c>
+      <c r="O56" s="45">
+        <v>0</v>
+      </c>
+      <c r="P56" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R56" s="40">
+      <c r="R56" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S56" s="16">
@@ -7782,7 +7799,7 @@
       <c r="J57" s="13">
         <v>218671</v>
       </c>
-      <c r="K57" s="45">
+      <c r="K57" s="44">
         <v>494025</v>
       </c>
       <c r="L57" s="16">
@@ -7791,19 +7808,19 @@
       <c r="M57" s="16">
         <v>0</v>
       </c>
-      <c r="N57" s="40">
-        <v>0</v>
-      </c>
-      <c r="O57" s="40">
-        <v>0</v>
-      </c>
-      <c r="P57" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="40">
+      <c r="N57" s="45">
+        <v>0</v>
+      </c>
+      <c r="O57" s="45">
+        <v>0</v>
+      </c>
+      <c r="P57" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R57" s="40">
+      <c r="R57" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S57" s="16">
@@ -7842,7 +7859,7 @@
       <c r="J58" s="13">
         <v>218671</v>
       </c>
-      <c r="K58" s="45">
+      <c r="K58" s="44">
         <v>494025</v>
       </c>
       <c r="L58" s="16">
@@ -7851,19 +7868,19 @@
       <c r="M58" s="16">
         <v>0</v>
       </c>
-      <c r="N58" s="40">
-        <v>0</v>
-      </c>
-      <c r="O58" s="40">
-        <v>0</v>
-      </c>
-      <c r="P58" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="40">
+      <c r="N58" s="45">
+        <v>0</v>
+      </c>
+      <c r="O58" s="45">
+        <v>0</v>
+      </c>
+      <c r="P58" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R58" s="40">
+      <c r="R58" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S58" s="16">
@@ -7902,7 +7919,7 @@
       <c r="J59" s="13">
         <v>218671</v>
       </c>
-      <c r="K59" s="45">
+      <c r="K59" s="44">
         <v>494025</v>
       </c>
       <c r="L59" s="16">
@@ -7911,19 +7928,19 @@
       <c r="M59" s="16">
         <v>0</v>
       </c>
-      <c r="N59" s="40">
-        <v>0</v>
-      </c>
-      <c r="O59" s="40">
-        <v>0</v>
-      </c>
-      <c r="P59" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="40">
+      <c r="N59" s="45">
+        <v>0</v>
+      </c>
+      <c r="O59" s="45">
+        <v>0</v>
+      </c>
+      <c r="P59" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="45">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R59" s="40">
+      <c r="R59" s="45">
         <v>0.31231212995293761</v>
       </c>
       <c r="S59" s="16">
@@ -7962,7 +7979,7 @@
       <c r="J60" s="13">
         <v>218671</v>
       </c>
-      <c r="K60" s="45">
+      <c r="K60" s="44">
         <v>930260</v>
       </c>
       <c r="L60" s="16">
@@ -7971,19 +7988,19 @@
       <c r="M60" s="16">
         <v>0</v>
       </c>
-      <c r="N60" s="40">
-        <v>0</v>
-      </c>
-      <c r="O60" s="40">
+      <c r="N60" s="45">
+        <v>0</v>
+      </c>
+      <c r="O60" s="45">
         <v>0.46893879130565647</v>
       </c>
-      <c r="P60" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="40">
+      <c r="P60" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="45">
         <v>0.13013996087115431</v>
       </c>
-      <c r="R60" s="40">
+      <c r="R60" s="45">
         <v>0.16585685722271193</v>
       </c>
       <c r="S60" s="16">
@@ -8022,7 +8039,7 @@
       <c r="J61" s="13">
         <v>218671</v>
       </c>
-      <c r="K61" s="45">
+      <c r="K61" s="44">
         <v>1071460</v>
       </c>
       <c r="L61" s="16">
@@ -8031,19 +8048,19 @@
       <c r="M61" s="16">
         <v>0</v>
       </c>
-      <c r="N61" s="40">
+      <c r="N61" s="45">
         <v>0.13178280103783621</v>
       </c>
-      <c r="O61" s="40">
+      <c r="O61" s="45">
         <v>0.40714072387209976</v>
       </c>
-      <c r="P61" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="40">
+      <c r="P61" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="45">
         <v>0.11298975230059918</v>
       </c>
-      <c r="R61" s="40">
+      <c r="R61" s="45">
         <v>0.14399977600657046</v>
       </c>
       <c r="S61" s="16">
@@ -8082,7 +8099,7 @@
       <c r="J62" s="13">
         <v>54671</v>
       </c>
-      <c r="K62" s="45">
+      <c r="K62" s="44">
         <v>396282.31</v>
       </c>
       <c r="L62" s="16">
@@ -8091,19 +8108,19 @@
       <c r="M62" s="16">
         <v>0.86204027123996529</v>
       </c>
-      <c r="N62" s="40">
-        <v>0</v>
-      </c>
-      <c r="O62" s="40">
-        <v>0</v>
-      </c>
-      <c r="P62" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="40">
-        <v>0</v>
-      </c>
-      <c r="R62" s="40">
+      <c r="N62" s="45">
+        <v>0</v>
+      </c>
+      <c r="O62" s="45">
+        <v>0</v>
+      </c>
+      <c r="P62" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="45">
+        <v>0</v>
+      </c>
+      <c r="R62" s="45">
         <v>0</v>
       </c>
       <c r="S62" s="16">
@@ -8142,7 +8159,7 @@
       <c r="J63" s="13">
         <v>54671</v>
       </c>
-      <c r="K63" s="45">
+      <c r="K63" s="44">
         <v>395802.31</v>
       </c>
       <c r="L63" s="16">
@@ -8151,19 +8168,19 @@
       <c r="M63" s="16">
         <v>0.86187296380357159</v>
       </c>
-      <c r="N63" s="40">
-        <v>0</v>
-      </c>
-      <c r="O63" s="40">
-        <v>0</v>
-      </c>
-      <c r="P63" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="40">
-        <v>0</v>
-      </c>
-      <c r="R63" s="40">
+      <c r="N63" s="45">
+        <v>0</v>
+      </c>
+      <c r="O63" s="45">
+        <v>0</v>
+      </c>
+      <c r="P63" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="45">
+        <v>0</v>
+      </c>
+      <c r="R63" s="45">
         <v>0</v>
       </c>
       <c r="S63" s="16">
@@ -8202,7 +8219,7 @@
       <c r="J64" s="13">
         <v>54671</v>
       </c>
-      <c r="K64" s="45">
+      <c r="K64" s="44">
         <v>396617.31</v>
       </c>
       <c r="L64" s="16">
@@ -8211,19 +8228,19 @@
       <c r="M64" s="16">
         <v>0.8621567979471193</v>
       </c>
-      <c r="N64" s="40">
-        <v>0</v>
-      </c>
-      <c r="O64" s="40">
-        <v>0</v>
-      </c>
-      <c r="P64" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="40">
-        <v>0</v>
-      </c>
-      <c r="R64" s="40">
+      <c r="N64" s="45">
+        <v>0</v>
+      </c>
+      <c r="O64" s="45">
+        <v>0</v>
+      </c>
+      <c r="P64" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="45">
+        <v>0</v>
+      </c>
+      <c r="R64" s="45">
         <v>0</v>
       </c>
       <c r="S64" s="16">
@@ -8262,7 +8279,7 @@
       <c r="J65" s="13">
         <v>54671</v>
       </c>
-      <c r="K65" s="45">
+      <c r="K65" s="44">
         <v>396917.31</v>
       </c>
       <c r="L65" s="16">
@@ -8271,19 +8288,19 @@
       <c r="M65" s="16">
         <v>0.86226098327634038</v>
       </c>
-      <c r="N65" s="40">
-        <v>0</v>
-      </c>
-      <c r="O65" s="40">
-        <v>0</v>
-      </c>
-      <c r="P65" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="40">
-        <v>0</v>
-      </c>
-      <c r="R65" s="40">
+      <c r="N65" s="45">
+        <v>0</v>
+      </c>
+      <c r="O65" s="45">
+        <v>0</v>
+      </c>
+      <c r="P65" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="45">
+        <v>0</v>
+      </c>
+      <c r="R65" s="45">
         <v>0</v>
       </c>
       <c r="S65" s="16">
@@ -8322,7 +8339,7 @@
       <c r="J66" s="13">
         <v>54671</v>
       </c>
-      <c r="K66" s="45">
+      <c r="K66" s="44">
         <v>399269.72</v>
       </c>
       <c r="L66" s="16">
@@ -8331,19 +8348,19 @@
       <c r="M66" s="16">
         <v>0.71330157468490218</v>
       </c>
-      <c r="N66" s="40">
-        <v>0</v>
-      </c>
-      <c r="O66" s="40">
-        <v>0</v>
-      </c>
-      <c r="P66" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="40">
-        <v>0</v>
-      </c>
-      <c r="R66" s="40">
+      <c r="N66" s="45">
+        <v>0</v>
+      </c>
+      <c r="O66" s="45">
+        <v>0</v>
+      </c>
+      <c r="P66" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="45">
+        <v>0</v>
+      </c>
+      <c r="R66" s="45">
         <v>0</v>
       </c>
       <c r="S66" s="16">
@@ -8382,7 +8399,7 @@
       <c r="J67" s="13">
         <v>54671</v>
       </c>
-      <c r="K67" s="45">
+      <c r="K67" s="44">
         <v>926093</v>
       </c>
       <c r="L67" s="16">
@@ -8391,19 +8408,19 @@
       <c r="M67" s="16">
         <v>0</v>
       </c>
-      <c r="N67" s="40">
-        <v>0</v>
-      </c>
-      <c r="O67" s="40">
-        <v>0</v>
-      </c>
-      <c r="P67" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="40">
-        <v>0</v>
-      </c>
-      <c r="R67" s="40">
+      <c r="N67" s="45">
+        <v>0</v>
+      </c>
+      <c r="O67" s="45">
+        <v>0</v>
+      </c>
+      <c r="P67" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="45">
+        <v>0</v>
+      </c>
+      <c r="R67" s="45">
         <v>0</v>
       </c>
       <c r="S67" s="16">
@@ -8442,7 +8459,7 @@
       <c r="J68" s="13">
         <v>54671</v>
       </c>
-      <c r="K68" s="45">
+      <c r="K68" s="44">
         <v>794093</v>
       </c>
       <c r="L68" s="16">
@@ -8451,19 +8468,19 @@
       <c r="M68" s="16">
         <v>0</v>
       </c>
-      <c r="N68" s="40">
-        <v>0</v>
-      </c>
-      <c r="O68" s="40">
-        <v>0</v>
-      </c>
-      <c r="P68" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="40">
-        <v>0</v>
-      </c>
-      <c r="R68" s="40">
+      <c r="N68" s="45">
+        <v>0</v>
+      </c>
+      <c r="O68" s="45">
+        <v>0</v>
+      </c>
+      <c r="P68" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="45">
+        <v>0</v>
+      </c>
+      <c r="R68" s="45">
         <v>0</v>
       </c>
       <c r="S68" s="16">
@@ -8475,14 +8492,14 @@
         <v>46268</v>
       </c>
       <c r="B69" s="43">
-        <f>B68-274+71-569+1738+320</f>
-        <v>403408.72</v>
+        <v>407651</v>
       </c>
       <c r="C69" s="12">
         <v>101060</v>
       </c>
       <c r="D69" s="15">
-        <v>302348.71999999997</v>
+        <f>B69-C69</f>
+        <v>306591</v>
       </c>
       <c r="E69" s="15">
         <v>0</v>
@@ -8502,8 +8519,9 @@
       <c r="J69" s="13">
         <v>0</v>
       </c>
-      <c r="K69" s="45">
-        <v>403408.72</v>
+      <c r="K69" s="44">
+        <f>SUM(C69:J69)</f>
+        <v>407651</v>
       </c>
       <c r="L69" s="16">
         <v>0.25051515991027662</v>
@@ -8511,19 +8529,19 @@
       <c r="M69" s="16">
         <v>0.74948484008972338</v>
       </c>
-      <c r="N69" s="40">
-        <v>0</v>
-      </c>
-      <c r="O69" s="40">
-        <v>0</v>
-      </c>
-      <c r="P69" s="40">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="40">
-        <v>0</v>
-      </c>
-      <c r="R69" s="40">
+      <c r="N69" s="45">
+        <v>0</v>
+      </c>
+      <c r="O69" s="45">
+        <v>0</v>
+      </c>
+      <c r="P69" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="45">
+        <v>0</v>
+      </c>
+      <c r="R69" s="45">
         <v>0</v>
       </c>
       <c r="S69" s="16">
@@ -8534,9 +8552,64 @@
       <c r="A70" s="42">
         <v>46269</v>
       </c>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="S70" s="16"/>
+      <c r="B70" s="43">
+        <v>408551</v>
+      </c>
+      <c r="C70" s="12">
+        <v>101060</v>
+      </c>
+      <c r="D70" s="15">
+        <f>B70-C70</f>
+        <v>307491</v>
+      </c>
+      <c r="E70" s="15">
+        <v>0</v>
+      </c>
+      <c r="F70" s="15">
+        <v>0</v>
+      </c>
+      <c r="G70" s="15">
+        <v>0</v>
+      </c>
+      <c r="H70" s="15">
+        <v>0</v>
+      </c>
+      <c r="I70" s="15">
+        <v>0</v>
+      </c>
+      <c r="J70" s="13">
+        <v>0</v>
+      </c>
+      <c r="K70" s="44">
+        <f>SUM(C70:J70)</f>
+        <v>408551</v>
+      </c>
+      <c r="L70" s="16">
+        <f>C70/K70</f>
+        <v>0.24736201845057287</v>
+      </c>
+      <c r="M70" s="16">
+        <f>D70/K70</f>
+        <v>0.75263798154942707</v>
+      </c>
+      <c r="N70" s="45">
+        <v>0</v>
+      </c>
+      <c r="O70" s="45">
+        <v>0</v>
+      </c>
+      <c r="P70" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="45">
+        <v>0</v>
+      </c>
+      <c r="R70" s="45">
+        <v>0</v>
+      </c>
+      <c r="S70" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1048543" s="42"/>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A73BF9-2075-5A4A-BFC0-9C3A02F8AB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C960501-C645-C74A-A582-7AC72D58DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="660" windowWidth="35840" windowHeight="20740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -5814,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="15">
-        <v>29744</v>
+        <v>0</v>
       </c>
       <c r="E24" s="15">
         <v>0</v>
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="15">
-        <v>0</v>
+        <v>116025</v>
       </c>
       <c r="H24" s="15">
         <v>121064</v>
@@ -5835,13 +5835,14 @@
         <v>223843</v>
       </c>
       <c r="K24" s="44">
-        <v>374651</v>
+        <f>SUM(C24:J24)</f>
+        <v>460932</v>
       </c>
       <c r="L24" s="16">
         <v>0</v>
       </c>
       <c r="M24" s="16">
-        <v>7.9391220095502216E-2</v>
+        <v>0</v>
       </c>
       <c r="N24" s="45">
         <v>0</v>
@@ -5850,16 +5851,19 @@
         <v>0</v>
       </c>
       <c r="P24" s="45">
-        <v>0</v>
+        <f>G24/K24</f>
+        <v>0.25171825779073703</v>
       </c>
       <c r="Q24" s="45">
-        <v>0.32313806716117133</v>
+        <f>H24/K24</f>
+        <v>0.2626504560325601</v>
       </c>
       <c r="R24" s="45">
         <v>0</v>
       </c>
       <c r="S24" s="16">
-        <v>0.59747071274332642</v>
+        <f>J24/K24</f>
+        <v>0.48563128617670287</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -7548,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="15">
-        <v>0</v>
+        <v>182705</v>
       </c>
       <c r="H53" s="15">
         <v>121064</v>
@@ -7560,7 +7564,8 @@
         <v>218671</v>
       </c>
       <c r="K53" s="44">
-        <v>494025</v>
+        <f>SUM(C53:J53)</f>
+        <v>676730</v>
       </c>
       <c r="L53" s="16">
         <v>0</v>
@@ -7575,16 +7580,20 @@
         <v>0</v>
       </c>
       <c r="P53" s="45">
-        <v>0</v>
+        <f>G53/K53</f>
+        <v>0.2699821199001079</v>
       </c>
       <c r="Q53" s="45">
-        <v>0.24505642427002683</v>
+        <f>H53/K53</f>
+        <v>0.17889557135046474</v>
       </c>
       <c r="R53" s="45">
-        <v>0.31231212995293761</v>
+        <f>I53/K53</f>
+        <v>0.22799343903772554</v>
       </c>
       <c r="S53" s="16">
-        <v>0.44263144577703556</v>
+        <f>J53/K53</f>
+        <v>0.32312886971170185</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -7902,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="15">
-        <v>0</v>
+        <v>1451000</v>
       </c>
       <c r="F59" s="15">
         <v>0</v>
@@ -7920,7 +7929,8 @@
         <v>218671</v>
       </c>
       <c r="K59" s="44">
-        <v>494025</v>
+        <f>SUM(C59:J59)</f>
+        <v>1945025</v>
       </c>
       <c r="L59" s="16">
         <v>0</v>
@@ -7932,19 +7942,23 @@
         <v>0</v>
       </c>
       <c r="O59" s="45">
-        <v>0</v>
+        <f>E59/K59</f>
+        <v>0.7460058354005733</v>
       </c>
       <c r="P59" s="45">
         <v>0</v>
       </c>
       <c r="Q59" s="45">
-        <v>0.24505642427002683</v>
+        <f>H59/K59</f>
+        <v>6.2242901762188149E-2</v>
       </c>
       <c r="R59" s="45">
-        <v>0.31231212995293761</v>
+        <f>I59/K59</f>
+        <v>7.9325458541663993E-2</v>
       </c>
       <c r="S59" s="16">
-        <v>0.44263144577703556</v>
+        <f>J59/K59</f>
+        <v>0.11242580429557461</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
@@ -8015,8 +8029,8 @@
         <f>B60+105+300+3482+1020+1095+430-311</f>
         <v>393861.31</v>
       </c>
-      <c r="C61" s="12">
-        <v>0</v>
+      <c r="C61" s="15">
+        <v>133338</v>
       </c>
       <c r="D61" s="13">
         <v>0</v>
@@ -8040,31 +8054,38 @@
         <v>218671</v>
       </c>
       <c r="K61" s="44">
-        <v>1071460</v>
+        <f>SUM(C61:J61)</f>
+        <v>1204798</v>
       </c>
       <c r="L61" s="16">
-        <v>0</v>
+        <f>C61/K61</f>
+        <v>0.11067249447625245</v>
       </c>
       <c r="M61" s="16">
         <v>0</v>
       </c>
       <c r="N61" s="45">
-        <v>0.13178280103783621</v>
+        <f>F61/K61</f>
+        <v>0.11719806971791122</v>
       </c>
       <c r="O61" s="45">
-        <v>0.40714072387209976</v>
+        <f>E61/K61</f>
+        <v>0.36208144435830736</v>
       </c>
       <c r="P61" s="45">
         <v>0</v>
       </c>
       <c r="Q61" s="45">
-        <v>0.11298975230059918</v>
+        <f>H61/K61</f>
+        <v>0.10048489456323799</v>
       </c>
       <c r="R61" s="45">
-        <v>0.14399977600657046</v>
+        <f>I61/K61</f>
+        <v>0.12806296159190173</v>
       </c>
       <c r="S61" s="16">
-        <v>0.20408694678289438</v>
+        <f>J61/K61</f>
+        <v>0.18150013529238926</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C960501-C645-C74A-A582-7AC72D58DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C811AB-1DD3-B844-B765-C8F6A3004B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="540" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -1809,12 +1809,11 @@
         <v>46202</v>
       </c>
       <c r="C12" s="19">
-        <f ca="1">TODAY()</f>
-        <v>46270</v>
+        <v>46266</v>
       </c>
       <c r="D12" s="20">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>54</v>
@@ -2145,14 +2144,14 @@
         <v>13</v>
       </c>
       <c r="B17" s="19">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C17" s="19">
         <v>46233</v>
       </c>
       <c r="D17" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>66</v>
@@ -2210,14 +2209,14 @@
         <v>14</v>
       </c>
       <c r="B18" s="19">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C18" s="19">
         <v>46233</v>
       </c>
       <c r="D18" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>68</v>
@@ -2278,12 +2277,11 @@
         <v>46244</v>
       </c>
       <c r="C19" s="19">
-        <f ca="1">TODAY()</f>
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="D19" s="20">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>70</v>
@@ -2345,13 +2343,12 @@
       <c r="B20" s="19">
         <v>46244</v>
       </c>
-      <c r="C20" s="27">
-        <f ca="1">TODAY()</f>
-        <v>46270</v>
+      <c r="C20" s="19">
+        <v>46254</v>
       </c>
       <c r="D20" s="20">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>73</v>
@@ -3237,8 +3234,8 @@
         <v>103</v>
       </c>
       <c r="E36" s="28">
-        <f ca="1">AVERAGE(D2:D32)</f>
-        <v>8.9677419354838701</v>
+        <f>AVERAGE(D2:D32)</f>
+        <v>8.32258064516129</v>
       </c>
       <c r="F36" s="21"/>
       <c r="H36" s="21"/>
@@ -3256,8 +3253,8 @@
         <v>104</v>
       </c>
       <c r="E37" s="28">
-        <f ca="1">AVERAGE(D2:D11,D13,D15:D32)</f>
-        <v>5.4482758620689653</v>
+        <f>AVERAGE(D2:D11,D13,D15:D32)</f>
+        <v>4.8965517241379306</v>
       </c>
       <c r="F37" s="21"/>
       <c r="U37" s="18" t="s">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15311AE-9663-034B-814D-8F0F27F0B5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6794DE4F-A7E7-8B40-9D61-BBB584ACE56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18460" yWindow="-30960" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -3350,7 +3350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
@@ -3363,7 +3363,7 @@
     <col min="9" max="16384" width="11.5" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>110</v>
       </c>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="G1" s="21"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="22">
         <v>46184</v>
       </c>
@@ -3391,15 +3391,8 @@
       <c r="D2" s="19">
         <v>0</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="23">
-        <f>AVERAGE(C3:C64)</f>
-        <v>1211.2111290322575</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="22">
         <v>46185</v>
       </c>
@@ -3414,15 +3407,8 @@
         <f>C3/B2</f>
         <v>5.0265608051062075E-2</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="23">
-        <f>_xlfn.STDEV.S(C3:C64)</f>
-        <v>4458.4857339644241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="22">
         <v>46188</v>
       </c>
@@ -3430,22 +3416,15 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C63" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C65" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D64" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D65" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="24">
-        <f>(H2/H3)*SQRT(252)</f>
-        <v>4.3125360812990623</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="22">
         <v>46189</v>
       </c>
@@ -3460,15 +3439,8 @@
         <f t="shared" si="1"/>
         <v>-1.4330935556555255E-2</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="25">
-        <f>_xlfn.STDEV.S(D2:D64)*SQRT(252)</f>
-        <v>0.19400980901652598</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="22">
         <v>46190</v>
       </c>
@@ -3483,15 +3455,8 @@
         <f t="shared" si="1"/>
         <v>1.8960279435109632E-2</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="H6" s="25" cm="1">
-        <f t="array" ref="H6">PRODUCT(1+D2:D64)-1</f>
-        <v>0.2252026454014302</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="22">
         <v>46191</v>
       </c>
@@ -3506,15 +3471,8 @@
         <f t="shared" si="1"/>
         <v>6.3379600224845786E-3</v>
       </c>
-      <c r="G7" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="25" cm="1">
-        <f t="array" ref="H7">PRODUCT(1+D2:D64)^(252/COUNT(D2:D64))-1</f>
-        <v>1.2533658247082546</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="22">
         <v>46192</v>
       </c>
@@ -3530,7 +3488,7 @@
         <v>-1.4266901520265389E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46195</v>
       </c>
@@ -3547,7 +3505,7 @@
       </c>
       <c r="G9" s="21"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46196</v>
       </c>
@@ -3564,7 +3522,7 @@
       </c>
       <c r="G10" s="21"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46197</v>
       </c>
@@ -3581,7 +3539,7 @@
       </c>
       <c r="G11" s="21"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46198</v>
       </c>
@@ -3598,7 +3556,7 @@
       </c>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46199</v>
       </c>
@@ -3615,7 +3573,7 @@
       </c>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46202</v>
       </c>
@@ -3632,7 +3590,7 @@
       </c>
       <c r="G14" s="21"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46203</v>
       </c>
@@ -3649,7 +3607,7 @@
       </c>
       <c r="G15" s="21"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46204</v>
       </c>
@@ -4463,6 +4421,75 @@
       <c r="D64" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="22">
+        <v>46273</v>
+      </c>
+      <c r="B65" s="1">
+        <f>B64-540</f>
+        <v>408011</v>
+      </c>
+      <c r="C65" s="1">
+        <f t="shared" si="0"/>
+        <v>-540</v>
+      </c>
+      <c r="D65" s="19">
+        <f t="shared" si="1"/>
+        <v>-1.3217444088987665E-3</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G65" s="23">
+        <f>AVERAGE(C3:C65)</f>
+        <v>1183.4141269841264</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F66" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G66" s="23">
+        <f>_xlfn.STDEV.S(C3:C65)</f>
+        <v>4427.8842603636631</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F67" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G67" s="24">
+        <f>(G65/G66)*SQRT(252)</f>
+        <v>4.2426847142704576</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F68" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G68" s="25">
+        <f>_xlfn.STDEV.S(D2:D65)*SQRT(252)</f>
+        <v>0.19268245470913598</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F69" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G69" s="25" cm="1">
+        <f t="array" ref="G69">PRODUCT(1+D2:D65)-1</f>
+        <v>0.22358324065510282</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F70" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G70" s="25" cm="1">
+        <f t="array" ref="G70">PRODUCT(1+D2:D65)^(252/COUNT(D2:D64))-1</f>
+        <v>1.2414759290746655</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6794DE4F-A7E7-8B40-9D61-BBB584ACE56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACC9A86-B3EE-184A-8FFB-57FD03BC6A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18460" yWindow="-30960" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="140">
   <si>
     <t>Trade ID</t>
   </si>
@@ -477,6 +477,12 @@
   </si>
   <si>
     <t>Index_Exposure</t>
+  </si>
+  <si>
+    <t>TRIP</t>
+  </si>
+  <si>
+    <t>Tripadvisor</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.1640625" style="47" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="42" customWidth="1"/>
     <col min="5" max="5" width="7.33203125" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="43.33203125" style="29" bestFit="1" customWidth="1"/>
@@ -2785,7 +2791,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="31">
-        <f t="shared" ref="D26:D32" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D34" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="29" t="s">
@@ -3241,32 +3247,154 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>-56</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="F33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="P33" s="35"/>
-      <c r="S33" s="36"/>
-      <c r="U33" s="35"/>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="F34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="P34" s="35"/>
-      <c r="S34" s="36"/>
-      <c r="U34" s="35"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="29">
+        <v>28</v>
+      </c>
+      <c r="B33" s="30">
+        <v>46274</v>
+      </c>
+      <c r="C33" s="30">
+        <f ca="1">TODAY()</f>
+        <v>46274</v>
+      </c>
+      <c r="D33" s="31">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33" s="43">
+        <v>6100</v>
+      </c>
+      <c r="M33" s="43">
+        <v>8.8520000000000003</v>
+      </c>
+      <c r="N33" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" s="43">
+        <v>9.07</v>
+      </c>
+      <c r="P33" s="45">
+        <v>52826</v>
+      </c>
+      <c r="Q33" s="43">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R33" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S33" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T33" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U33" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V33" s="29">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" s="29">
+        <v>29</v>
+      </c>
+      <c r="B34" s="30">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="30">
+        <f ca="1">TODAY()</f>
+        <v>46274</v>
+      </c>
+      <c r="D34" s="31">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G34" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L34" s="43">
+        <v>100</v>
+      </c>
+      <c r="M34" s="43">
+        <v>321.976</v>
+      </c>
+      <c r="N34" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" s="43">
+        <v>320.8</v>
+      </c>
+      <c r="P34" s="45">
+        <v>32080</v>
+      </c>
+      <c r="Q34" s="43">
+        <v>2.87</v>
+      </c>
+      <c r="R34" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S34" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T34" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U34" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V34" s="29">
+        <v>-118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F35" s="32"/>
       <c r="H35" s="32"/>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D36" s="48" t="s">
         <v>103</v>
       </c>
@@ -3281,11 +3409,11 @@
         <v>67975.47</v>
       </c>
       <c r="V36" s="35">
-        <f>SUM(V2:V32)</f>
-        <v>-56</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+        <f>SUM(V2:V34)</f>
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D37" s="48" t="s">
         <v>104</v>
       </c>
@@ -3301,43 +3429,43 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F38" s="32"/>
       <c r="U38" s="29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F39" s="32"/>
       <c r="U39" s="35">
         <f>U36+V36</f>
-        <v>67919.47</v>
-      </c>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+        <v>69542.47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F40" s="32"/>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F41" s="32"/>
       <c r="U41" s="32" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F42" s="32"/>
       <c r="U42" s="35">
         <v>333000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="U44" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="U45" s="50">
         <f>U39/U42</f>
-        <v>0.20396237237237239</v>
+        <v>0.20883624624624625</v>
       </c>
     </row>
   </sheetData>
@@ -8775,7 +8903,130 @@
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
+      <c r="A72" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B72" s="7">
+        <v>408551</v>
+      </c>
+      <c r="C72" s="15">
+        <v>101060</v>
+      </c>
+      <c r="D72" s="9">
+        <f>B72-C72</f>
+        <v>307491</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0</v>
+      </c>
+      <c r="F72" s="9">
+        <v>0</v>
+      </c>
+      <c r="G72" s="9">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0</v>
+      </c>
+      <c r="I72" s="9">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14">
+        <v>0</v>
+      </c>
+      <c r="K72" s="10">
+        <f>SUM(C72:J72)</f>
+        <v>408551</v>
+      </c>
+      <c r="L72" s="11">
+        <f>C72/K72</f>
+        <v>0.24736201845057287</v>
+      </c>
+      <c r="M72" s="11">
+        <f>D72/K72</f>
+        <v>0.75263798154942707</v>
+      </c>
+      <c r="N72" s="12">
+        <v>0</v>
+      </c>
+      <c r="O72" s="12">
+        <v>0</v>
+      </c>
+      <c r="P72" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="12">
+        <v>0</v>
+      </c>
+      <c r="R72" s="12">
+        <v>0</v>
+      </c>
+      <c r="S72" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B73" s="7">
+        <v>408551</v>
+      </c>
+      <c r="C73" s="15">
+        <v>184986</v>
+      </c>
+      <c r="D73" s="9">
+        <f>B73-C73</f>
+        <v>223565</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0</v>
+      </c>
+      <c r="F73" s="9">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0</v>
+      </c>
+      <c r="I73" s="9">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14">
+        <v>0</v>
+      </c>
+      <c r="K73" s="10">
+        <f>SUM(C73:J73)</f>
+        <v>408551</v>
+      </c>
+      <c r="L73" s="11">
+        <f>C73/K73</f>
+        <v>0.45278557634175415</v>
+      </c>
+      <c r="M73" s="11">
+        <f>D73/K73</f>
+        <v>0.5472144236582458</v>
+      </c>
+      <c r="N73" s="12">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
+      <c r="R73" s="12">
+        <v>0</v>
+      </c>
+      <c r="S73" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048543" s="6"/>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACC9A86-B3EE-184A-8FFB-57FD03BC6A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCBF48D-A144-ED4F-A840-BFD9CD1452F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3258,11 +3258,10 @@
         <v>46274</v>
       </c>
       <c r="C33" s="30">
-        <f ca="1">TODAY()</f>
         <v>46274</v>
       </c>
       <c r="D33" s="31">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E33" s="43" t="s">
@@ -3328,11 +3327,10 @@
         <v>46274</v>
       </c>
       <c r="C34" s="30">
-        <f ca="1">TODAY()</f>
         <v>46274</v>
       </c>
       <c r="D34" s="31">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E34" s="43" t="s">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCBF48D-A144-ED4F-A840-BFD9CD1452F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899A9833-C9E6-1C48-85D3-664BEC9AE5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B73" s="7">
         <v>408551</v>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899A9833-C9E6-1C48-85D3-664BEC9AE5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54069DB-7AC8-AF48-82C6-4A75072FC95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3546,7 +3546,7 @@
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D65" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D66" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4569,17 +4569,31 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C65)</f>
-        <v>1183.4141269841264</v>
+        <f>AVERAGE(C3:C66)</f>
+        <v>1164.9232812499995</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="22">
+        <v>46274</v>
+      </c>
+      <c r="B66" s="1">
+        <f>B65</f>
+        <v>408011</v>
+      </c>
+      <c r="C66" s="18">
+        <v>0</v>
+      </c>
+      <c r="D66" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F66" s="21" t="s">
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C65)</f>
-        <v>4427.8842603636631</v>
+        <f>_xlfn.STDEV.S(C3:C66)</f>
+        <v>4395.0918622770741</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4588,7 +4602,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.2426847142704576</v>
+        <v>4.2075534189995736</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4596,8 +4610,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D65)*SQRT(252)</f>
-        <v>0.19268245470913598</v>
+        <f>_xlfn.STDEV.S(D2:D66)*SQRT(252)</f>
+        <v>0.19127693942966356</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4605,7 +4619,7 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D65)-1</f>
+        <f t="array" ref="G69">PRODUCT(1+D2:D66)-1</f>
         <v>0.22358324065510282</v>
       </c>
     </row>
@@ -4614,8 +4628,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D65)^(252/COUNT(D2:D64))-1</f>
-        <v>1.2414759290746655</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D66)^(252/COUNT(D2:D66))-1</f>
+        <v>1.1864946317679896</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54069DB-7AC8-AF48-82C6-4A75072FC95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A9EAA7-1EEB-B84D-B2AC-35FA3349779D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -3226,7 +3226,7 @@
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>50.41</v>
+        <v>49.74</v>
       </c>
       <c r="P32" s="45">
         <v>100080</v>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A9EAA7-1EEB-B84D-B2AC-35FA3349779D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A718BE2B-696A-ED43-A192-A54CA848CCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3226,7 +3226,7 @@
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>49.74</v>
+        <v>50.41</v>
       </c>
       <c r="P32" s="45">
         <v>100080</v>
@@ -3258,10 +3258,11 @@
         <v>46274</v>
       </c>
       <c r="C33" s="30">
+        <f ca="1">TODAY()</f>
         <v>46274</v>
       </c>
       <c r="D33" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E33" s="43" t="s">
@@ -3295,7 +3296,7 @@
         <v>72</v>
       </c>
       <c r="O33" s="43">
-        <v>9.07</v>
+        <v>9.11</v>
       </c>
       <c r="P33" s="45">
         <v>52826</v>
@@ -3316,7 +3317,8 @@
         <v>72</v>
       </c>
       <c r="V33" s="29">
-        <v>753</v>
+        <f>(O33-M33)*L33</f>
+        <v>1573.7999999999947</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -3327,10 +3329,11 @@
         <v>46274</v>
       </c>
       <c r="C34" s="30">
+        <f ca="1">TODAY()</f>
         <v>46274</v>
       </c>
       <c r="D34" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E34" s="43" t="s">
@@ -3408,7 +3411,7 @@
       </c>
       <c r="V36" s="35">
         <f>SUM(V2:V34)</f>
-        <v>1567</v>
+        <v>2387.7999999999947</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3437,7 +3440,7 @@
       <c r="F39" s="32"/>
       <c r="U39" s="35">
         <f>U36+V36</f>
-        <v>69542.47</v>
+        <v>70363.26999999999</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -3463,7 +3466,7 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="U45" s="50">
         <f>U39/U42</f>
-        <v>0.20883624624624625</v>
+        <v>0.21130111111111108</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3549,7 @@
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D66" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D65" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4569,31 +4572,17 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C66)</f>
-        <v>1164.9232812499995</v>
+        <f>AVERAGE(C3:C65)</f>
+        <v>1183.4141269841264</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="22">
-        <v>46274</v>
-      </c>
-      <c r="B66" s="1">
-        <f>B65</f>
-        <v>408011</v>
-      </c>
-      <c r="C66" s="18">
-        <v>0</v>
-      </c>
-      <c r="D66" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="F66" s="21" t="s">
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C66)</f>
-        <v>4395.0918622770741</v>
+        <f>_xlfn.STDEV.S(C3:C65)</f>
+        <v>4427.8842603636631</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4602,7 +4591,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.2075534189995736</v>
+        <v>4.2426847142704576</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4610,8 +4599,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D66)*SQRT(252)</f>
-        <v>0.19127693942966356</v>
+        <f>_xlfn.STDEV.S(D2:D65)*SQRT(252)</f>
+        <v>0.19268245470913598</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4619,7 +4608,7 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D66)-1</f>
+        <f t="array" ref="G69">PRODUCT(1+D2:D65)-1</f>
         <v>0.22358324065510282</v>
       </c>
     </row>
@@ -4628,8 +4617,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D66)^(252/COUNT(D2:D66))-1</f>
-        <v>1.1864946317679896</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D65)^(252/COUNT(D2:D64))-1</f>
+        <v>1.2414759290746655</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A718BE2B-696A-ED43-A192-A54CA848CCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2006CC21-42D9-304E-B625-B28CF9B5270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3545,11 +3545,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C65" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C66" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D65" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D66" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4572,17 +4572,32 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C65)</f>
-        <v>1183.4141269841264</v>
+        <f>AVERAGE(C3:C66)</f>
+        <v>1202.2357812499995</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="22">
+        <v>46274</v>
+      </c>
+      <c r="B66" s="1">
+        <f>B65+2388</f>
+        <v>410399</v>
+      </c>
+      <c r="C66" s="1">
+        <f t="shared" si="0"/>
+        <v>2388</v>
+      </c>
+      <c r="D66" s="19">
+        <f t="shared" si="1"/>
+        <v>5.8527833808402225E-3</v>
+      </c>
       <c r="F66" s="21" t="s">
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C65)</f>
-        <v>4427.8842603636631</v>
+        <f>_xlfn.STDEV.S(C3:C66)</f>
+        <v>4395.1817310127199</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4591,7 +4606,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.2426847142704576</v>
+        <v>4.3422325934878296</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4599,8 +4614,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D65)*SQRT(252)</f>
-        <v>0.19268245470913598</v>
+        <f>_xlfn.STDEV.S(D2:D66)*SQRT(252)</f>
+        <v>0.19124094964609878</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4608,8 +4623,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D65)-1</f>
-        <v>0.22358324065510282</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D66)-1</f>
+        <v>0.23074460831108357</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4617,8 +4632,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D65)^(252/COUNT(D2:D64))-1</f>
-        <v>1.2414759290746655</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D66)^(252/COUNT(D2:D66))-1</f>
+        <v>1.2365271503279844</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2006CC21-42D9-304E-B625-B28CF9B5270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE38D52-186F-9349-AE10-B3C46176B2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3296,7 +3296,7 @@
         <v>72</v>
       </c>
       <c r="O33" s="43">
-        <v>9.11</v>
+        <v>8.82</v>
       </c>
       <c r="P33" s="45">
         <v>52826</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="V33" s="29">
         <f>(O33-M33)*L33</f>
-        <v>1573.7999999999947</v>
+        <v>-195.20000000000016</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="V36" s="35">
         <f>SUM(V2:V34)</f>
-        <v>2387.7999999999947</v>
+        <v>618.79999999999984</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3440,7 +3440,7 @@
       <c r="F39" s="32"/>
       <c r="U39" s="35">
         <f>U36+V36</f>
-        <v>70363.26999999999</v>
+        <v>68594.27</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -3466,7 +3466,7 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="U45" s="50">
         <f>U39/U42</f>
-        <v>0.21130111111111108</v>
+        <v>0.20598879879879881</v>
       </c>
     </row>
   </sheetData>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="G65" s="23">
         <f>AVERAGE(C3:C66)</f>
-        <v>1202.2357812499995</v>
+        <v>1185.9701562499995</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4581,23 +4581,23 @@
         <v>46274</v>
       </c>
       <c r="B66" s="1">
-        <f>B65+2388</f>
-        <v>410399</v>
+        <f>B65+1639-159-133</f>
+        <v>409358</v>
       </c>
       <c r="C66" s="1">
         <f t="shared" si="0"/>
-        <v>2388</v>
+        <v>1347</v>
       </c>
       <c r="D66" s="19">
         <f t="shared" si="1"/>
-        <v>5.8527833808402225E-3</v>
+        <v>3.3013815803985677E-3</v>
       </c>
       <c r="F66" s="21" t="s">
         <v>115</v>
       </c>
       <c r="G66" s="23">
         <f>_xlfn.STDEV.S(C3:C66)</f>
-        <v>4395.1817310127199</v>
+        <v>4392.6493463593724</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3422325934878296</v>
+        <v>4.2859538948391229</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="G68" s="25">
         <f>_xlfn.STDEV.S(D2:D66)*SQRT(252)</f>
-        <v>0.19124094964609878</v>
+        <v>0.19117124847058889</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G69" s="25" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D66)-1</f>
-        <v>0.23074460831108357</v>
+        <v>0.22762275582788605</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G70" s="25" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D66)^(252/COUNT(D2:D66))-1</f>
-        <v>1.2365271503279844</v>
+        <v>1.214613193981763</v>
       </c>
     </row>
   </sheetData>
@@ -8986,14 +8986,14 @@
         <v>46274</v>
       </c>
       <c r="B73" s="7">
-        <v>408551</v>
+        <v>409358</v>
       </c>
       <c r="C73" s="15">
         <v>184986</v>
       </c>
       <c r="D73" s="9">
         <f>B73-C73</f>
-        <v>223565</v>
+        <v>224372</v>
       </c>
       <c r="E73" s="9">
         <v>0</v>
@@ -9015,15 +9015,15 @@
       </c>
       <c r="K73" s="10">
         <f>SUM(C73:J73)</f>
-        <v>408551</v>
+        <v>409358</v>
       </c>
       <c r="L73" s="11">
         <f>C73/K73</f>
-        <v>0.45278557634175415</v>
+        <v>0.45189296410476892</v>
       </c>
       <c r="M73" s="11">
         <f>D73/K73</f>
-        <v>0.5472144236582458</v>
+        <v>0.54810703589523102</v>
       </c>
       <c r="N73" s="12">
         <v>0</v>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE38D52-186F-9349-AE10-B3C46176B2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC07741-326E-CE46-8544-A3275DB70914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="149">
   <si>
     <t>Trade ID</t>
   </si>
@@ -425,6 +425,9 @@
     <t>Ann. Return</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>Metals</t>
   </si>
   <si>
@@ -483,6 +486,30 @@
   </si>
   <si>
     <t>Tripadvisor</t>
+  </si>
+  <si>
+    <t>MYM</t>
+  </si>
+  <si>
+    <t>Dow Jones Futures Mini</t>
+  </si>
+  <si>
+    <t>Meta Platforms</t>
+  </si>
+  <si>
+    <t>AFL</t>
+  </si>
+  <si>
+    <t>Aflac Incorporated</t>
+  </si>
+  <si>
+    <t>GBL</t>
+  </si>
+  <si>
+    <t>Euro-Bund Futures</t>
+  </si>
+  <si>
+    <t>Rates_Exposure</t>
   </si>
 </sst>
 </file>
@@ -612,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,6 +779,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1076,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="29" bestFit="1" customWidth="1"/>
@@ -1084,7 +1114,7 @@
     <col min="4" max="4" width="16.5" style="42" customWidth="1"/>
     <col min="5" max="5" width="7.33203125" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="43.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="13" style="29" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" style="29" bestFit="1" customWidth="1"/>
@@ -1333,7 +1363,7 @@
         <v>32</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K4" s="29" t="s">
         <v>33</v>
@@ -1401,7 +1431,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K5" s="29" t="s">
         <v>34</v>
@@ -1468,7 +1498,7 @@
         <v>32</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K6" s="29" t="s">
         <v>38</v>
@@ -1536,7 +1566,7 @@
         <v>32</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K7" s="29" t="s">
         <v>41</v>
@@ -1604,7 +1634,7 @@
         <v>32</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K8" s="29" t="s">
         <v>44</v>
@@ -1806,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="J11" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K11" s="29" t="s">
         <v>53</v>
@@ -2009,7 +2039,7 @@
         <v>32</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K14" s="29" t="s">
         <v>60</v>
@@ -2076,7 +2106,7 @@
         <v>32</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K15" s="29" t="s">
         <v>63</v>
@@ -2409,7 +2439,7 @@
         <v>32</v>
       </c>
       <c r="J20" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K20" s="29" t="s">
         <v>75</v>
@@ -2543,7 +2573,7 @@
         <v>32</v>
       </c>
       <c r="J22" s="29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K22" s="29" t="s">
         <v>79</v>
@@ -2610,7 +2640,7 @@
         <v>32</v>
       </c>
       <c r="J23" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K23" s="29" t="s">
         <v>83</v>
@@ -2677,7 +2707,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K24" s="29" t="s">
         <v>84</v>
@@ -2743,7 +2773,7 @@
         <v>32</v>
       </c>
       <c r="J25" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K25" s="29" t="s">
         <v>87</v>
@@ -2791,7 +2821,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="31">
-        <f t="shared" ref="D26:D34" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D38" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="29" t="s">
@@ -2810,7 +2840,7 @@
         <v>32</v>
       </c>
       <c r="J26" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K26" s="29" t="s">
         <v>90</v>
@@ -3188,12 +3218,12 @@
       <c r="B32" s="30">
         <v>46266</v>
       </c>
-      <c r="C32" s="30">
-        <v>46268</v>
+      <c r="C32" s="51">
+        <v>46275</v>
       </c>
       <c r="D32" s="31">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E32" s="43" t="s">
         <v>101</v>
@@ -3217,19 +3247,19 @@
         <v>101</v>
       </c>
       <c r="L32" s="43">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="M32" s="43">
-        <v>50.406999999999996</v>
+        <v>50.25</v>
       </c>
       <c r="N32" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>50.41</v>
+        <v>49.97</v>
       </c>
       <c r="P32" s="45">
-        <v>100080</v>
+        <v>149745</v>
       </c>
       <c r="Q32" s="43">
         <v>1.21</v>
@@ -3247,7 +3277,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>932</v>
+        <v>865</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3257,19 +3287,18 @@
       <c r="B33" s="30">
         <v>46274</v>
       </c>
-      <c r="C33" s="30">
-        <f ca="1">TODAY()</f>
-        <v>46274</v>
+      <c r="C33" s="51">
+        <v>46275</v>
       </c>
       <c r="D33" s="31">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G33" s="43" t="s">
         <v>23</v>
@@ -3284,13 +3313,13 @@
         <v>25</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L33" s="43">
-        <v>6100</v>
+        <v>9000</v>
       </c>
       <c r="M33" s="43">
-        <v>8.8520000000000003</v>
+        <v>8.6980000000000004</v>
       </c>
       <c r="N33" s="43" t="s">
         <v>72</v>
@@ -3299,7 +3328,7 @@
         <v>8.82</v>
       </c>
       <c r="P33" s="45">
-        <v>52826</v>
+        <v>79470</v>
       </c>
       <c r="Q33" s="43">
         <v>2.4500000000000002</v>
@@ -3317,8 +3346,7 @@
         <v>72</v>
       </c>
       <c r="V33" s="29">
-        <f>(O33-M33)*L33</f>
-        <v>-195.20000000000016</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -3328,13 +3356,12 @@
       <c r="B34" s="30">
         <v>46274</v>
       </c>
-      <c r="C34" s="30">
-        <f ca="1">TODAY()</f>
-        <v>46274</v>
+      <c r="C34" s="51">
+        <v>46275</v>
       </c>
       <c r="D34" s="31">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E34" s="43" t="s">
         <v>99</v>
@@ -3358,19 +3385,19 @@
         <v>99</v>
       </c>
       <c r="L34" s="43">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M34" s="43">
-        <v>321.976</v>
+        <v>318.87</v>
       </c>
       <c r="N34" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O34" s="43">
-        <v>320.8</v>
+        <v>317.44</v>
       </c>
       <c r="P34" s="45">
-        <v>32080</v>
+        <v>126488</v>
       </c>
       <c r="Q34" s="43">
         <v>2.87</v>
@@ -3388,85 +3415,361 @@
         <v>72</v>
       </c>
       <c r="V34" s="29">
-        <v>-118</v>
+        <v>-572</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F35" s="32"/>
-      <c r="H35" s="32"/>
+      <c r="A35" s="29">
+        <v>30</v>
+      </c>
+      <c r="B35" s="30">
+        <v>46275</v>
+      </c>
+      <c r="C35" s="51">
+        <v>46275</v>
+      </c>
+      <c r="D35" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="L35" s="43">
+        <v>1</v>
+      </c>
+      <c r="M35" s="43">
+        <v>52061.3</v>
+      </c>
+      <c r="N35" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O35" s="43">
+        <v>52095</v>
+      </c>
+      <c r="P35" s="45">
+        <v>26031</v>
+      </c>
+      <c r="Q35" s="43">
+        <v>3.11</v>
+      </c>
+      <c r="R35" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S35" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T35" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U35" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V35" s="29">
+        <v>15</v>
+      </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D36" s="48" t="s">
+      <c r="A36" s="29">
+        <v>31</v>
+      </c>
+      <c r="B36" s="30">
+        <v>46275</v>
+      </c>
+      <c r="C36" s="51">
+        <v>46275</v>
+      </c>
+      <c r="D36" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="43">
+        <v>-50</v>
+      </c>
+      <c r="M36" s="43">
+        <v>656.66</v>
+      </c>
+      <c r="N36" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O36" s="43">
+        <v>643.87</v>
+      </c>
+      <c r="P36" s="45">
+        <v>32575</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>2.1</v>
+      </c>
+      <c r="R36" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S36" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T36" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U36" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" s="29">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="29">
+        <v>32</v>
+      </c>
+      <c r="B37" s="30">
+        <v>46275</v>
+      </c>
+      <c r="C37" s="51">
+        <v>46275</v>
+      </c>
+      <c r="D37" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="L37" s="43">
+        <v>250</v>
+      </c>
+      <c r="M37" s="43">
+        <v>113.7</v>
+      </c>
+      <c r="N37" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O37" s="43">
+        <v>114.47</v>
+      </c>
+      <c r="P37" s="45">
+        <v>28435</v>
+      </c>
+      <c r="Q37" s="43">
+        <v>1.6</v>
+      </c>
+      <c r="R37" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S37" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T37" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U37" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V37" s="29">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="29">
+        <v>33</v>
+      </c>
+      <c r="B38" s="30">
+        <v>46275</v>
+      </c>
+      <c r="C38" s="51">
+        <v>46275</v>
+      </c>
+      <c r="D38" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="K38" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L38" s="43">
+        <v>1</v>
+      </c>
+      <c r="M38" s="43">
+        <v>120.35</v>
+      </c>
+      <c r="N38" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O38" s="43">
+        <v>120.36</v>
+      </c>
+      <c r="P38" s="45">
+        <v>120370</v>
+      </c>
+      <c r="Q38" s="43">
+        <v>3.6</v>
+      </c>
+      <c r="R38" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S38" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T38" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U38" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V38" s="29">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F39" s="32"/>
+      <c r="H39" s="32"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D40" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="42">
-        <f>AVERAGE(D2:D32)</f>
-        <v>8.32258064516129</v>
-      </c>
-      <c r="F36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="U36" s="35">
+      <c r="E40" s="42">
+        <f>AVERAGE(D2:D31)</f>
+        <v>8.5333333333333332</v>
+      </c>
+      <c r="F40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="U40" s="35">
         <f>SUM(U2:U31)</f>
         <v>67975.47</v>
       </c>
-      <c r="V36" s="35">
-        <f>SUM(V2:V34)</f>
-        <v>618.79999999999984</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D37" s="48" t="s">
+      <c r="V40" s="35">
+        <f>SUM(V2:V38)</f>
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D41" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="42">
-        <f>AVERAGE(D2:D11,D13,D15:D32)</f>
-        <v>4.8965517241379306</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="U37" s="49" t="s">
+      <c r="E41" s="42">
+        <f>AVERAGE(D2:D11,D13,D15:D31)</f>
+        <v>5</v>
+      </c>
+      <c r="F41" s="32"/>
+      <c r="U41" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="V37" s="32" t="s">
+      <c r="V41" s="32" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F38" s="32"/>
-      <c r="U38" s="29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F39" s="32"/>
-      <c r="U39" s="35">
-        <f>U36+V36</f>
-        <v>68594.27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F40" s="32"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F41" s="32"/>
-      <c r="U41" s="32" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F42" s="32"/>
-      <c r="U42" s="35">
+      <c r="U42" s="29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F43" s="32"/>
+      <c r="U43" s="35">
+        <f>U40+V40</f>
+        <v>70319.47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F44" s="32"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F45" s="32"/>
+      <c r="U45" s="32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F46" s="32"/>
+      <c r="U46" s="35">
         <v>333000</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U44" s="29" t="s">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U48" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U45" s="50">
-        <f>U39/U42</f>
-        <v>0.20598879879879881</v>
+    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
+      <c r="U49" s="50">
+        <f>U43/U46</f>
+        <v>0.21116957957957957</v>
       </c>
     </row>
   </sheetData>
@@ -3545,11 +3848,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C66" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C67" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D66" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D67" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4572,8 +4875,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C66)</f>
-        <v>1185.9701562499995</v>
+        <f>AVERAGE(C3:C67)</f>
+        <v>1203.5706153846149</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4596,17 +4899,32 @@
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C66)</f>
-        <v>4392.6493463593724</v>
+        <f>_xlfn.STDEV.S(C3:C67)</f>
+        <v>4360.5061175520677</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="22">
+        <v>46275</v>
+      </c>
+      <c r="B67" s="1">
+        <f>B66+2330</f>
+        <v>411688</v>
+      </c>
+      <c r="C67" s="1">
+        <f t="shared" si="0"/>
+        <v>2330</v>
+      </c>
+      <c r="D67" s="19">
+        <f t="shared" si="1"/>
+        <v>5.6918394168429592E-3</v>
+      </c>
       <c r="F67" s="21" t="s">
         <v>116</v>
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.2859538948391229</v>
+        <v>4.3816223820371301</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4614,8 +4932,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D66)*SQRT(252)</f>
-        <v>0.19117124847058889</v>
+        <f>_xlfn.STDEV.S(D2:D67)*SQRT(252)</f>
+        <v>0.18975594310276095</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4623,8 +4941,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D66)-1</f>
-        <v>0.22762275582788605</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D67)-1</f>
+        <v>0.23461018741852069</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4632,8 +4950,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D66)^(252/COUNT(D2:D66))-1</f>
-        <v>1.214613193981763</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D67)^(252/COUNT(D2:D66))-1</f>
+        <v>1.2638842177316159</v>
       </c>
     </row>
   </sheetData>
@@ -4644,7 +4962,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEDD2B-54BB-1449-BCF8-F93ADB145E3A}">
-  <dimension ref="A1:T1048543"/>
+  <dimension ref="A1:U1048543"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="16" bestFit="1" customWidth="1"/>
@@ -4655,62 +4973,63 @@
     <col min="6" max="7" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.1640625" style="13"/>
-    <col min="21" max="16384" width="9.1640625" style="14"/>
+    <col min="10" max="10" width="9.33203125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.1640625" style="12" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.1640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>125</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>126</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>134</v>
@@ -4725,10 +5044,16 @@
         <v>137</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>46175</v>
       </c>
@@ -4759,18 +5084,18 @@
       <c r="J2" s="9">
         <v>0</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
         <v>300000</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="11">
         <v>0.35237333333333332</v>
       </c>
-      <c r="M2" s="11">
+      <c r="N2" s="11">
         <v>0.64762666666666668</v>
       </c>
-      <c r="N2" s="12">
-        <v>0</v>
-      </c>
       <c r="O2" s="12">
         <v>0</v>
       </c>
@@ -4783,11 +5108,17 @@
       <c r="R2" s="12">
         <v>0</v>
       </c>
-      <c r="S2" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S2" s="12">
+        <v>0</v>
+      </c>
+      <c r="T2" s="12">
+        <v>0</v>
+      </c>
+      <c r="U2" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>46176</v>
       </c>
@@ -4818,18 +5149,18 @@
       <c r="J3" s="9">
         <v>0</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
         <v>300000</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="11">
         <v>0.35237333333333332</v>
       </c>
-      <c r="M3" s="11">
+      <c r="N3" s="11">
         <v>0.64762666666666668</v>
       </c>
-      <c r="N3" s="12">
-        <v>0</v>
-      </c>
       <c r="O3" s="12">
         <v>0</v>
       </c>
@@ -4842,11 +5173,17 @@
       <c r="R3" s="12">
         <v>0</v>
       </c>
-      <c r="S3" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S3" s="12">
+        <v>0</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0</v>
+      </c>
+      <c r="U3" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>46177</v>
       </c>
@@ -4877,18 +5214,18 @@
       <c r="J4" s="9">
         <v>0</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
         <v>300000</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <v>0.81459999999999999</v>
       </c>
-      <c r="M4" s="11">
+      <c r="N4" s="11">
         <v>0.18540000000000001</v>
       </c>
-      <c r="N4" s="12">
-        <v>0</v>
-      </c>
       <c r="O4" s="12">
         <v>0</v>
       </c>
@@ -4901,11 +5238,17 @@
       <c r="R4" s="12">
         <v>0</v>
       </c>
-      <c r="S4" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S4" s="12">
+        <v>0</v>
+      </c>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>46178</v>
       </c>
@@ -4936,21 +5279,21 @@
       <c r="J5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
         <v>907730</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="11">
         <v>0.2692210238727375</v>
       </c>
-      <c r="M5" s="11">
-        <v>0</v>
-      </c>
-      <c r="N5" s="12">
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12">
         <v>0.7307789761272625</v>
       </c>
-      <c r="O5" s="12">
-        <v>0</v>
-      </c>
       <c r="P5" s="12">
         <v>0</v>
       </c>
@@ -4960,11 +5303,17 @@
       <c r="R5" s="12">
         <v>0</v>
       </c>
-      <c r="S5" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+      <c r="T5" s="12">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>46181</v>
       </c>
@@ -4995,35 +5344,41 @@
       <c r="J6" s="9">
         <v>0</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
         <v>3696918</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>3.7509081889292646E-2</v>
       </c>
-      <c r="M6" s="11">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
         <v>0.17943324682884501</v>
       </c>
-      <c r="O6" s="12">
+      <c r="P6" s="12">
         <v>0.78305767128186232</v>
       </c>
-      <c r="P6" s="12">
-        <v>0</v>
-      </c>
       <c r="Q6" s="12">
         <v>0</v>
       </c>
       <c r="R6" s="12">
         <v>0</v>
       </c>
-      <c r="S6" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+      <c r="T6" s="12">
+        <v>0</v>
+      </c>
+      <c r="U6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>46182</v>
       </c>
@@ -5054,21 +5409,21 @@
       <c r="J7" s="9">
         <v>0</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
         <v>802018</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>0.17289886261904347</v>
       </c>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
         <v>0.82710113738095659</v>
       </c>
-      <c r="O7" s="12">
-        <v>0</v>
-      </c>
       <c r="P7" s="12">
         <v>0</v>
       </c>
@@ -5078,11 +5433,17 @@
       <c r="R7" s="12">
         <v>0</v>
       </c>
-      <c r="S7" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>46183</v>
       </c>
@@ -5113,21 +5474,21 @@
       <c r="J8" s="9">
         <v>0</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
         <v>600137</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="11">
         <v>0.23106057450215534</v>
       </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12">
         <v>0.76893942549784466</v>
       </c>
-      <c r="O8" s="12">
-        <v>0</v>
-      </c>
       <c r="P8" s="12">
         <v>0</v>
       </c>
@@ -5137,11 +5498,17 @@
       <c r="R8" s="12">
         <v>0</v>
       </c>
-      <c r="S8" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>46184</v>
       </c>
@@ -5172,21 +5539,21 @@
       <c r="J9" s="9">
         <v>0</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
         <v>600137</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>0.23106057450215534</v>
       </c>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12">
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12">
         <v>0.76893942549784466</v>
       </c>
-      <c r="O9" s="12">
-        <v>0</v>
-      </c>
       <c r="P9" s="12">
         <v>0</v>
       </c>
@@ -5196,11 +5563,17 @@
       <c r="R9" s="12">
         <v>0</v>
       </c>
-      <c r="S9" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>46185</v>
       </c>
@@ -5231,21 +5604,21 @@
       <c r="J10" s="9">
         <v>0</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
         <v>461469</v>
       </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
       <c r="M10" s="11">
         <v>0</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12">
         <v>1</v>
       </c>
-      <c r="O10" s="12">
-        <v>0</v>
-      </c>
       <c r="P10" s="12">
         <v>0</v>
       </c>
@@ -5255,11 +5628,17 @@
       <c r="R10" s="12">
         <v>0</v>
       </c>
-      <c r="S10" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>46188</v>
       </c>
@@ -5290,21 +5669,21 @@
       <c r="J11" s="9">
         <v>0</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
         <v>461469</v>
       </c>
-      <c r="L11" s="11">
-        <v>0</v>
-      </c>
       <c r="M11" s="11">
         <v>0</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12">
         <v>1</v>
       </c>
-      <c r="O11" s="12">
-        <v>0</v>
-      </c>
       <c r="P11" s="12">
         <v>0</v>
       </c>
@@ -5314,11 +5693,17 @@
       <c r="R11" s="12">
         <v>0</v>
       </c>
-      <c r="S11" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>46189</v>
       </c>
@@ -5349,21 +5734,21 @@
       <c r="J12" s="9">
         <v>0</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
         <v>461469</v>
       </c>
-      <c r="L12" s="11">
-        <v>0</v>
-      </c>
       <c r="M12" s="11">
         <v>0</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
+        <v>0</v>
+      </c>
+      <c r="O12" s="12">
         <v>1</v>
       </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
       <c r="P12" s="12">
         <v>0</v>
       </c>
@@ -5373,11 +5758,17 @@
       <c r="R12" s="12">
         <v>0</v>
       </c>
-      <c r="S12" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>46190</v>
       </c>
@@ -5408,35 +5799,41 @@
       <c r="J13" s="9">
         <v>0</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
         <v>592709</v>
       </c>
-      <c r="L13" s="11">
-        <v>0</v>
-      </c>
       <c r="M13" s="11">
         <v>0</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
       <c r="P13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
       <c r="R13" s="12">
         <v>0</v>
       </c>
-      <c r="S13" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S13" s="12">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>46191</v>
       </c>
@@ -5467,35 +5864,41 @@
       <c r="J14" s="9">
         <v>0</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
         <v>592709</v>
       </c>
-      <c r="L14" s="11">
-        <v>0</v>
-      </c>
       <c r="M14" s="11">
         <v>0</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="11">
+        <v>0</v>
+      </c>
+      <c r="O14" s="12">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O14" s="12">
-        <v>0</v>
-      </c>
       <c r="P14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="12">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q14" s="12">
-        <v>0</v>
-      </c>
       <c r="R14" s="12">
         <v>0</v>
       </c>
-      <c r="S14" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S14" s="12">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>46192</v>
       </c>
@@ -5526,35 +5929,41 @@
       <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
         <v>592709</v>
       </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
       <c r="M15" s="11">
         <v>0</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12">
         <v>0.77857599597779015</v>
       </c>
-      <c r="O15" s="12">
-        <v>0</v>
-      </c>
       <c r="P15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12">
         <v>0.22142400402220988</v>
       </c>
-      <c r="Q15" s="12">
-        <v>0</v>
-      </c>
       <c r="R15" s="12">
         <v>0</v>
       </c>
-      <c r="S15" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S15" s="12">
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>46195</v>
       </c>
@@ -5585,35 +5994,41 @@
       <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
         <v>3586250</v>
       </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
       <c r="M16" s="11">
         <v>0</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12">
         <v>0.12867730916695713</v>
       </c>
-      <c r="O16" s="12">
+      <c r="P16" s="12">
         <v>0.87132269083304292</v>
       </c>
-      <c r="P16" s="12">
-        <v>0</v>
-      </c>
       <c r="Q16" s="12">
         <v>0</v>
       </c>
       <c r="R16" s="12">
         <v>0</v>
       </c>
-      <c r="S16" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S16" s="12">
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <v>0</v>
+      </c>
+      <c r="U16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>46196</v>
       </c>
@@ -5644,35 +6059,41 @@
       <c r="J17" s="9">
         <v>0</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
         <v>3586250</v>
       </c>
-      <c r="L17" s="11">
-        <v>0</v>
-      </c>
       <c r="M17" s="11">
         <v>0</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12">
         <v>0.12867730916695713</v>
       </c>
-      <c r="O17" s="12">
+      <c r="P17" s="12">
         <v>0.87132269083304292</v>
       </c>
-      <c r="P17" s="12">
-        <v>0</v>
-      </c>
       <c r="Q17" s="12">
         <v>0</v>
       </c>
       <c r="R17" s="12">
         <v>0</v>
       </c>
-      <c r="S17" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>0</v>
+      </c>
+      <c r="U17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>46197</v>
       </c>
@@ -5701,37 +6122,43 @@
         <v>0</v>
       </c>
       <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
         <v>193096</v>
       </c>
-      <c r="K18" s="10">
+      <c r="L18" s="10">
         <v>3779346</v>
       </c>
-      <c r="L18" s="11">
-        <v>0</v>
-      </c>
       <c r="M18" s="11">
         <v>0</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="12">
         <v>0.12210287176670249</v>
       </c>
-      <c r="O18" s="12">
+      <c r="P18" s="12">
         <v>0.8268046905469888</v>
       </c>
-      <c r="P18" s="12">
-        <v>0</v>
-      </c>
       <c r="Q18" s="12">
         <v>0</v>
       </c>
       <c r="R18" s="12">
         <v>0</v>
       </c>
-      <c r="S18" s="11">
+      <c r="S18" s="12">
+        <v>0</v>
+      </c>
+      <c r="T18" s="12">
+        <v>0</v>
+      </c>
+      <c r="U18" s="11">
         <v>5.1092437686308688E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>46198</v>
       </c>
@@ -5760,37 +6187,43 @@
         <v>0</v>
       </c>
       <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
         <v>193096</v>
       </c>
-      <c r="K19" s="10">
+      <c r="L19" s="10">
         <v>3981471</v>
       </c>
-      <c r="L19" s="11">
-        <v>0</v>
-      </c>
       <c r="M19" s="11">
         <v>0</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="11">
+        <v>0</v>
+      </c>
+      <c r="O19" s="12">
         <v>0.16667055970017111</v>
       </c>
-      <c r="O19" s="12">
+      <c r="P19" s="12">
         <v>0.78483078239173409</v>
       </c>
-      <c r="P19" s="12">
-        <v>0</v>
-      </c>
       <c r="Q19" s="12">
         <v>0</v>
       </c>
       <c r="R19" s="12">
         <v>0</v>
       </c>
-      <c r="S19" s="11">
+      <c r="S19" s="12">
+        <v>0</v>
+      </c>
+      <c r="T19" s="12">
+        <v>0</v>
+      </c>
+      <c r="U19" s="11">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>46199</v>
       </c>
@@ -5819,37 +6252,43 @@
         <v>0</v>
       </c>
       <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
         <v>193096</v>
       </c>
-      <c r="K20" s="10">
+      <c r="L20" s="10">
         <v>3981471</v>
       </c>
-      <c r="L20" s="11">
-        <v>0</v>
-      </c>
       <c r="M20" s="11">
         <v>0</v>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="12">
         <v>0.16667055970017111</v>
       </c>
-      <c r="O20" s="12">
+      <c r="P20" s="12">
         <v>0.78483078239173409</v>
       </c>
-      <c r="P20" s="12">
-        <v>0</v>
-      </c>
       <c r="Q20" s="12">
         <v>0</v>
       </c>
       <c r="R20" s="12">
         <v>0</v>
       </c>
-      <c r="S20" s="11">
+      <c r="S20" s="12">
+        <v>0</v>
+      </c>
+      <c r="T20" s="12">
+        <v>0</v>
+      </c>
+      <c r="U20" s="11">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>46202</v>
       </c>
@@ -5878,37 +6317,43 @@
         <v>0</v>
       </c>
       <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
         <v>416939</v>
       </c>
-      <c r="K21" s="10">
+      <c r="L21" s="10">
         <v>4260349</v>
       </c>
-      <c r="L21" s="11">
+      <c r="M21" s="11">
         <v>1.2917955782495754E-2</v>
       </c>
-      <c r="M21" s="11">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12">
+      <c r="N21" s="11">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12">
         <v>0.1557604787776776</v>
       </c>
-      <c r="O21" s="12">
+      <c r="P21" s="12">
         <v>0.73345657832257405</v>
       </c>
-      <c r="P21" s="12">
-        <v>0</v>
-      </c>
       <c r="Q21" s="12">
         <v>0</v>
       </c>
       <c r="R21" s="12">
         <v>0</v>
       </c>
-      <c r="S21" s="11">
+      <c r="S21" s="12">
+        <v>0</v>
+      </c>
+      <c r="T21" s="12">
+        <v>0</v>
+      </c>
+      <c r="U21" s="11">
         <v>9.7864987117252597E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>46203</v>
       </c>
@@ -5937,37 +6382,43 @@
         <v>0</v>
       </c>
       <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
         <v>223843</v>
       </c>
-      <c r="K22" s="10">
+      <c r="L22" s="10">
         <v>3524723</v>
       </c>
-      <c r="L22" s="11">
+      <c r="M22" s="11">
         <v>1.5613992929373457E-2</v>
       </c>
-      <c r="M22" s="11">
-        <v>0</v>
-      </c>
-      <c r="N22" s="12">
+      <c r="N22" s="11">
         <v>0</v>
       </c>
       <c r="O22" s="12">
+        <v>0</v>
+      </c>
+      <c r="P22" s="12">
         <v>0.88653236013156211</v>
       </c>
-      <c r="P22" s="12">
-        <v>0</v>
-      </c>
       <c r="Q22" s="12">
+        <v>0</v>
+      </c>
+      <c r="R22" s="12">
         <v>3.4347096211532084E-2</v>
       </c>
-      <c r="R22" s="12">
-        <v>0</v>
-      </c>
-      <c r="S22" s="11">
+      <c r="S22" s="12">
+        <v>0</v>
+      </c>
+      <c r="T22" s="12">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11">
         <v>6.3506550727532349E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>46204</v>
       </c>
@@ -5996,37 +6447,43 @@
         <v>0</v>
       </c>
       <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
         <v>223843</v>
       </c>
-      <c r="K23" s="10">
+      <c r="L23" s="10">
         <v>3469688</v>
       </c>
-      <c r="L23" s="11">
-        <v>0</v>
-      </c>
       <c r="M23" s="11">
         <v>0</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="11">
         <v>0</v>
       </c>
       <c r="O23" s="12">
+        <v>0</v>
+      </c>
+      <c r="P23" s="12">
         <v>0.90059423210386635</v>
       </c>
-      <c r="P23" s="12">
-        <v>0</v>
-      </c>
       <c r="Q23" s="12">
+        <v>0</v>
+      </c>
+      <c r="R23" s="12">
         <v>3.4891898061151318E-2</v>
       </c>
-      <c r="R23" s="12">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11">
+      <c r="S23" s="12">
+        <v>0</v>
+      </c>
+      <c r="T23" s="12">
+        <v>0</v>
+      </c>
+      <c r="U23" s="11">
         <v>6.4513869834982279E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>46205</v>
       </c>
@@ -6055,41 +6512,47 @@
         <v>0</v>
       </c>
       <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
         <v>223843</v>
       </c>
-      <c r="K24" s="10">
-        <f>SUM(C24:J24)</f>
+      <c r="L24" s="10">
+        <f>SUM(C24:K24)</f>
         <v>460932</v>
       </c>
-      <c r="L24" s="11">
-        <v>0</v>
-      </c>
       <c r="M24" s="11">
         <v>0</v>
       </c>
-      <c r="N24" s="12">
+      <c r="N24" s="11">
         <v>0</v>
       </c>
       <c r="O24" s="12">
         <v>0</v>
       </c>
       <c r="P24" s="12">
-        <f>G24/K24</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="12">
+        <f>G24/L24</f>
         <v>0.25171825779073703</v>
       </c>
-      <c r="Q24" s="12">
-        <f>H24/K24</f>
+      <c r="R24" s="12">
+        <f>H24/L24</f>
         <v>0.2626504560325601</v>
       </c>
-      <c r="R24" s="12">
-        <v>0</v>
-      </c>
-      <c r="S24" s="11">
-        <f>J24/K24</f>
+      <c r="S24" s="12">
+        <v>0</v>
+      </c>
+      <c r="T24" s="12">
+        <v>0</v>
+      </c>
+      <c r="U24" s="11">
+        <f>K24/L24</f>
         <v>0.48563128617670287</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>46206</v>
       </c>
@@ -6118,20 +6581,20 @@
         <v>0</v>
       </c>
       <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
         <v>223843</v>
       </c>
-      <c r="K25" s="10">
+      <c r="L25" s="10">
         <v>374479.39</v>
       </c>
-      <c r="L25" s="11">
-        <v>0</v>
-      </c>
       <c r="M25" s="11">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11">
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="N25" s="12">
-        <v>0</v>
-      </c>
       <c r="O25" s="12">
         <v>0</v>
       </c>
@@ -6139,16 +6602,22 @@
         <v>0</v>
       </c>
       <c r="Q25" s="12">
+        <v>0</v>
+      </c>
+      <c r="R25" s="12">
         <v>0.32328614933921995</v>
       </c>
-      <c r="R25" s="12">
-        <v>0</v>
-      </c>
-      <c r="S25" s="11">
+      <c r="S25" s="12">
+        <v>0</v>
+      </c>
+      <c r="T25" s="12">
+        <v>0</v>
+      </c>
+      <c r="U25" s="11">
         <v>0.59774451138686158</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>46209</v>
       </c>
@@ -6177,20 +6646,20 @@
         <v>0</v>
       </c>
       <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
         <v>223843</v>
       </c>
-      <c r="K26" s="10">
+      <c r="L26" s="10">
         <v>372801.92</v>
       </c>
-      <c r="L26" s="11">
-        <v>0</v>
-      </c>
       <c r="M26" s="11">
+        <v>0</v>
+      </c>
+      <c r="N26" s="11">
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="N26" s="12">
-        <v>0</v>
-      </c>
       <c r="O26" s="12">
         <v>0</v>
       </c>
@@ -6198,16 +6667,22 @@
         <v>0</v>
       </c>
       <c r="Q26" s="12">
+        <v>0</v>
+      </c>
+      <c r="R26" s="12">
         <v>0.32474081678549299</v>
       </c>
-      <c r="R26" s="12">
-        <v>0</v>
-      </c>
-      <c r="S26" s="11">
+      <c r="S26" s="12">
+        <v>0</v>
+      </c>
+      <c r="T26" s="12">
+        <v>0</v>
+      </c>
+      <c r="U26" s="11">
         <v>0.60043413939499024</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>46210</v>
       </c>
@@ -6236,20 +6711,20 @@
         <v>0</v>
       </c>
       <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
         <v>223843</v>
       </c>
-      <c r="K27" s="10">
+      <c r="L27" s="10">
         <v>375246.11</v>
       </c>
-      <c r="L27" s="11">
-        <v>0</v>
-      </c>
       <c r="M27" s="11">
+        <v>0</v>
+      </c>
+      <c r="N27" s="11">
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="N27" s="12">
-        <v>0</v>
-      </c>
       <c r="O27" s="12">
         <v>0</v>
       </c>
@@ -6257,16 +6732,22 @@
         <v>0</v>
       </c>
       <c r="Q27" s="12">
+        <v>0</v>
+      </c>
+      <c r="R27" s="12">
         <v>0.32262559630531545</v>
       </c>
-      <c r="R27" s="12">
-        <v>0</v>
-      </c>
-      <c r="S27" s="11">
+      <c r="S27" s="12">
+        <v>0</v>
+      </c>
+      <c r="T27" s="12">
+        <v>0</v>
+      </c>
+      <c r="U27" s="11">
         <v>0.59652317248538567</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>46211</v>
       </c>
@@ -6295,18 +6776,18 @@
         <v>0</v>
       </c>
       <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
         <v>223843</v>
       </c>
-      <c r="K28" s="10">
+      <c r="L28" s="10">
         <v>435718</v>
       </c>
-      <c r="L28" s="11">
+      <c r="M28" s="11">
         <v>0.20841691185583336</v>
       </c>
-      <c r="M28" s="11">
-        <v>0</v>
-      </c>
-      <c r="N28" s="12">
+      <c r="N28" s="11">
         <v>0</v>
       </c>
       <c r="O28" s="12">
@@ -6316,16 +6797,22 @@
         <v>0</v>
       </c>
       <c r="Q28" s="12">
+        <v>0</v>
+      </c>
+      <c r="R28" s="12">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R28" s="12">
-        <v>0</v>
-      </c>
-      <c r="S28" s="11">
+      <c r="S28" s="12">
+        <v>0</v>
+      </c>
+      <c r="T28" s="12">
+        <v>0</v>
+      </c>
+      <c r="U28" s="11">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>46212</v>
       </c>
@@ -6354,18 +6841,18 @@
         <v>0</v>
       </c>
       <c r="J29" s="9">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
         <v>223843</v>
       </c>
-      <c r="K29" s="10">
+      <c r="L29" s="10">
         <v>435718</v>
       </c>
-      <c r="L29" s="11">
+      <c r="M29" s="11">
         <v>0.20841691185583336</v>
       </c>
-      <c r="M29" s="11">
-        <v>0</v>
-      </c>
-      <c r="N29" s="12">
+      <c r="N29" s="11">
         <v>0</v>
       </c>
       <c r="O29" s="12">
@@ -6375,16 +6862,22 @@
         <v>0</v>
       </c>
       <c r="Q29" s="12">
+        <v>0</v>
+      </c>
+      <c r="R29" s="12">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R29" s="12">
-        <v>0</v>
-      </c>
-      <c r="S29" s="11">
+      <c r="S29" s="12">
+        <v>0</v>
+      </c>
+      <c r="T29" s="12">
+        <v>0</v>
+      </c>
+      <c r="U29" s="11">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>46213</v>
       </c>
@@ -6413,18 +6906,18 @@
         <v>0</v>
       </c>
       <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
         <v>223843</v>
       </c>
-      <c r="K30" s="10">
+      <c r="L30" s="10">
         <v>435718</v>
       </c>
-      <c r="L30" s="11">
+      <c r="M30" s="11">
         <v>0.20841691185583336</v>
       </c>
-      <c r="M30" s="11">
-        <v>0</v>
-      </c>
-      <c r="N30" s="12">
+      <c r="N30" s="11">
         <v>0</v>
       </c>
       <c r="O30" s="12">
@@ -6434,16 +6927,22 @@
         <v>0</v>
       </c>
       <c r="Q30" s="12">
+        <v>0</v>
+      </c>
+      <c r="R30" s="12">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R30" s="12">
-        <v>0</v>
-      </c>
-      <c r="S30" s="11">
+      <c r="S30" s="12">
+        <v>0</v>
+      </c>
+      <c r="T30" s="12">
+        <v>0</v>
+      </c>
+      <c r="U30" s="11">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>46216</v>
       </c>
@@ -6472,18 +6971,18 @@
         <v>0</v>
       </c>
       <c r="J31" s="9">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
         <v>223843</v>
       </c>
-      <c r="K31" s="10">
+      <c r="L31" s="10">
         <v>435718</v>
       </c>
-      <c r="L31" s="11">
+      <c r="M31" s="11">
         <v>0.20841691185583336</v>
       </c>
-      <c r="M31" s="11">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12">
+      <c r="N31" s="11">
         <v>0</v>
       </c>
       <c r="O31" s="12">
@@ -6493,16 +6992,22 @@
         <v>0</v>
       </c>
       <c r="Q31" s="12">
+        <v>0</v>
+      </c>
+      <c r="R31" s="12">
         <v>0.27784943472613022</v>
       </c>
-      <c r="R31" s="12">
-        <v>0</v>
-      </c>
-      <c r="S31" s="11">
+      <c r="S31" s="12">
+        <v>0</v>
+      </c>
+      <c r="T31" s="12">
+        <v>0</v>
+      </c>
+      <c r="U31" s="11">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>46217</v>
       </c>
@@ -6531,20 +7036,20 @@
         <v>0</v>
       </c>
       <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
         <v>223843</v>
       </c>
-      <c r="K32" s="10">
+      <c r="L32" s="10">
         <v>378852.03</v>
       </c>
-      <c r="L32" s="11">
-        <v>0</v>
-      </c>
       <c r="M32" s="11">
+        <v>0</v>
+      </c>
+      <c r="N32" s="11">
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="N32" s="12">
-        <v>0</v>
-      </c>
       <c r="O32" s="12">
         <v>0</v>
       </c>
@@ -6552,16 +7057,22 @@
         <v>0</v>
       </c>
       <c r="Q32" s="12">
+        <v>0</v>
+      </c>
+      <c r="R32" s="12">
         <v>0.31955484044786558</v>
       </c>
-      <c r="R32" s="12">
-        <v>0</v>
-      </c>
-      <c r="S32" s="11">
+      <c r="S32" s="12">
+        <v>0</v>
+      </c>
+      <c r="T32" s="12">
+        <v>0</v>
+      </c>
+      <c r="U32" s="11">
         <v>0.5908454548864368</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>46218</v>
       </c>
@@ -6590,20 +7101,20 @@
         <v>0</v>
       </c>
       <c r="J33" s="9">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9">
         <v>223843</v>
       </c>
-      <c r="K33" s="10">
+      <c r="L33" s="10">
         <v>374437.1</v>
       </c>
-      <c r="L33" s="11">
-        <v>0</v>
-      </c>
       <c r="M33" s="11">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="N33" s="12">
-        <v>0</v>
-      </c>
       <c r="O33" s="12">
         <v>0</v>
       </c>
@@ -6611,16 +7122,22 @@
         <v>0</v>
       </c>
       <c r="Q33" s="12">
+        <v>0</v>
+      </c>
+      <c r="R33" s="12">
         <v>0.32332266220414591</v>
       </c>
-      <c r="R33" s="12">
-        <v>0</v>
-      </c>
-      <c r="S33" s="11">
+      <c r="S33" s="12">
+        <v>0</v>
+      </c>
+      <c r="T33" s="12">
+        <v>0</v>
+      </c>
+      <c r="U33" s="11">
         <v>0.59781202236637343</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>46219</v>
       </c>
@@ -6649,20 +7166,20 @@
         <v>0</v>
       </c>
       <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
         <v>223843</v>
       </c>
-      <c r="K34" s="10">
+      <c r="L34" s="10">
         <v>372248.26</v>
       </c>
-      <c r="L34" s="11">
-        <v>0</v>
-      </c>
       <c r="M34" s="11">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11">
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="N34" s="12">
-        <v>0</v>
-      </c>
       <c r="O34" s="12">
         <v>0</v>
       </c>
@@ -6670,16 +7187,22 @@
         <v>0</v>
       </c>
       <c r="Q34" s="12">
+        <v>0</v>
+      </c>
+      <c r="R34" s="12">
         <v>0.32522381703006481</v>
       </c>
-      <c r="R34" s="12">
-        <v>0</v>
-      </c>
-      <c r="S34" s="11">
+      <c r="S34" s="12">
+        <v>0</v>
+      </c>
+      <c r="T34" s="12">
+        <v>0</v>
+      </c>
+      <c r="U34" s="11">
         <v>0.60132718954817943</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>46220</v>
       </c>
@@ -6708,20 +7231,20 @@
         <v>0</v>
       </c>
       <c r="J35" s="9">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9">
         <v>223843</v>
       </c>
-      <c r="K35" s="10">
+      <c r="L35" s="10">
         <v>376025.4</v>
       </c>
-      <c r="L35" s="11">
-        <v>0</v>
-      </c>
       <c r="M35" s="11">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11">
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="N35" s="12">
-        <v>0</v>
-      </c>
       <c r="O35" s="12">
         <v>0</v>
       </c>
@@ -6729,16 +7252,22 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12">
+        <v>0</v>
+      </c>
+      <c r="R35" s="12">
         <v>0.32195697418312696</v>
       </c>
-      <c r="R35" s="12">
-        <v>0</v>
-      </c>
-      <c r="S35" s="11">
+      <c r="S35" s="12">
+        <v>0</v>
+      </c>
+      <c r="T35" s="12">
+        <v>0</v>
+      </c>
+      <c r="U35" s="11">
         <v>0.59528691412867318</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>46223</v>
       </c>
@@ -6767,20 +7296,20 @@
         <v>0</v>
       </c>
       <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
         <v>223843</v>
       </c>
-      <c r="K36" s="10">
+      <c r="L36" s="10">
         <v>375009.72</v>
       </c>
-      <c r="L36" s="11">
-        <v>0</v>
-      </c>
       <c r="M36" s="11">
+        <v>0</v>
+      </c>
+      <c r="N36" s="11">
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="N36" s="12">
-        <v>0</v>
-      </c>
       <c r="O36" s="12">
         <v>0</v>
       </c>
@@ -6788,16 +7317,22 @@
         <v>0</v>
       </c>
       <c r="Q36" s="12">
+        <v>0</v>
+      </c>
+      <c r="R36" s="12">
         <v>0.32282896560654484</v>
       </c>
-      <c r="R36" s="12">
-        <v>0</v>
-      </c>
-      <c r="S36" s="11">
+      <c r="S36" s="12">
+        <v>0</v>
+      </c>
+      <c r="T36" s="12">
+        <v>0</v>
+      </c>
+      <c r="U36" s="11">
         <v>0.59689919503953126</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>46224</v>
       </c>
@@ -6826,20 +7361,20 @@
         <v>0</v>
       </c>
       <c r="J37" s="9">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9">
         <v>223843</v>
       </c>
-      <c r="K37" s="10">
+      <c r="L37" s="10">
         <v>375731.28</v>
       </c>
-      <c r="L37" s="11">
-        <v>0</v>
-      </c>
       <c r="M37" s="11">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11">
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="N37" s="12">
-        <v>0</v>
-      </c>
       <c r="O37" s="12">
         <v>0</v>
       </c>
@@ -6847,16 +7382,22 @@
         <v>0</v>
       </c>
       <c r="Q37" s="12">
+        <v>0</v>
+      </c>
+      <c r="R37" s="12">
         <v>0.32220900000660047</v>
       </c>
-      <c r="R37" s="12">
-        <v>0</v>
-      </c>
-      <c r="S37" s="11">
+      <c r="S37" s="12">
+        <v>0</v>
+      </c>
+      <c r="T37" s="12">
+        <v>0</v>
+      </c>
+      <c r="U37" s="11">
         <v>0.5957529008497775</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>46225</v>
       </c>
@@ -6885,20 +7426,20 @@
         <v>0</v>
       </c>
       <c r="J38" s="9">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
         <v>223843</v>
       </c>
-      <c r="K38" s="10">
+      <c r="L38" s="10">
         <v>378174.99</v>
       </c>
-      <c r="L38" s="11">
-        <v>0</v>
-      </c>
       <c r="M38" s="11">
+        <v>0</v>
+      </c>
+      <c r="N38" s="11">
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="N38" s="12">
-        <v>0</v>
-      </c>
       <c r="O38" s="12">
         <v>0</v>
       </c>
@@ -6906,16 +7447,22 @@
         <v>0</v>
       </c>
       <c r="Q38" s="12">
+        <v>0</v>
+      </c>
+      <c r="R38" s="12">
         <v>0.32012693383028845</v>
       </c>
-      <c r="R38" s="12">
-        <v>0</v>
-      </c>
-      <c r="S38" s="11">
+      <c r="S38" s="12">
+        <v>0</v>
+      </c>
+      <c r="T38" s="12">
+        <v>0</v>
+      </c>
+      <c r="U38" s="11">
         <v>0.59190323506057341</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>46226</v>
       </c>
@@ -6944,20 +7491,20 @@
         <v>0</v>
       </c>
       <c r="J39" s="9">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9">
         <v>223843</v>
       </c>
-      <c r="K39" s="10">
+      <c r="L39" s="10">
         <v>380362.45</v>
       </c>
-      <c r="L39" s="11">
-        <v>0</v>
-      </c>
       <c r="M39" s="11">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="N39" s="12">
-        <v>0</v>
-      </c>
       <c r="O39" s="12">
         <v>0</v>
       </c>
@@ -6965,16 +7512,22 @@
         <v>0</v>
       </c>
       <c r="Q39" s="12">
+        <v>0</v>
+      </c>
+      <c r="R39" s="12">
         <v>0.31828588757907095</v>
       </c>
-      <c r="R39" s="12">
-        <v>0</v>
-      </c>
-      <c r="S39" s="11">
+      <c r="S39" s="12">
+        <v>0</v>
+      </c>
+      <c r="T39" s="12">
+        <v>0</v>
+      </c>
+      <c r="U39" s="11">
         <v>0.58849920648055554</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>46227</v>
       </c>
@@ -7004,20 +7557,20 @@
         <v>0</v>
       </c>
       <c r="J40" s="9">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9">
         <v>223843</v>
       </c>
-      <c r="K40" s="10">
+      <c r="L40" s="10">
         <v>377185.45</v>
       </c>
-      <c r="L40" s="11">
-        <v>0</v>
-      </c>
       <c r="M40" s="11">
+        <v>0</v>
+      </c>
+      <c r="N40" s="11">
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="N40" s="12">
-        <v>0</v>
-      </c>
       <c r="O40" s="12">
         <v>0</v>
       </c>
@@ -7025,16 +7578,22 @@
         <v>0</v>
       </c>
       <c r="Q40" s="12">
+        <v>0</v>
+      </c>
+      <c r="R40" s="12">
         <v>0.32096678172501086</v>
       </c>
-      <c r="R40" s="12">
-        <v>0</v>
-      </c>
-      <c r="S40" s="11">
+      <c r="S40" s="12">
+        <v>0</v>
+      </c>
+      <c r="T40" s="12">
+        <v>0</v>
+      </c>
+      <c r="U40" s="11">
         <v>0.59345608373811876</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>46230</v>
       </c>
@@ -7064,20 +7623,20 @@
         <v>0</v>
       </c>
       <c r="J41" s="9">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9">
         <v>223843</v>
       </c>
-      <c r="K41" s="10">
+      <c r="L41" s="10">
         <v>378220.45</v>
       </c>
-      <c r="L41" s="11">
-        <v>0</v>
-      </c>
       <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11">
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="N41" s="12">
-        <v>0</v>
-      </c>
       <c r="O41" s="12">
         <v>0</v>
       </c>
@@ -7085,16 +7644,22 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12">
+        <v>0</v>
+      </c>
+      <c r="R41" s="12">
         <v>0.32008845634867178</v>
       </c>
-      <c r="R41" s="12">
-        <v>0</v>
-      </c>
-      <c r="S41" s="11">
+      <c r="S41" s="12">
+        <v>0</v>
+      </c>
+      <c r="T41" s="12">
+        <v>0</v>
+      </c>
+      <c r="U41" s="11">
         <v>0.5918320915751647</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>46231</v>
       </c>
@@ -7124,18 +7689,18 @@
         <v>0</v>
       </c>
       <c r="J42" s="9">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9">
         <v>223843</v>
       </c>
-      <c r="K42" s="10">
+      <c r="L42" s="10">
         <v>679531</v>
       </c>
-      <c r="L42" s="11">
+      <c r="M42" s="11">
         <v>0.49243375210255308</v>
       </c>
-      <c r="M42" s="11">
-        <v>0</v>
-      </c>
-      <c r="N42" s="12">
+      <c r="N42" s="11">
         <v>0</v>
       </c>
       <c r="O42" s="12">
@@ -7145,16 +7710,22 @@
         <v>0</v>
       </c>
       <c r="Q42" s="12">
+        <v>0</v>
+      </c>
+      <c r="R42" s="12">
         <v>0.17815817085607574</v>
       </c>
-      <c r="R42" s="12">
-        <v>0</v>
-      </c>
-      <c r="S42" s="11">
+      <c r="S42" s="12">
+        <v>0</v>
+      </c>
+      <c r="T42" s="12">
+        <v>0</v>
+      </c>
+      <c r="U42" s="11">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>46232</v>
       </c>
@@ -7184,18 +7755,18 @@
         <v>0</v>
       </c>
       <c r="J43" s="9">
+        <v>0</v>
+      </c>
+      <c r="K43" s="9">
         <v>223843</v>
       </c>
-      <c r="K43" s="10">
+      <c r="L43" s="10">
         <v>679531</v>
       </c>
-      <c r="L43" s="11">
+      <c r="M43" s="11">
         <v>0.49243375210255308</v>
       </c>
-      <c r="M43" s="11">
-        <v>0</v>
-      </c>
-      <c r="N43" s="12">
+      <c r="N43" s="11">
         <v>0</v>
       </c>
       <c r="O43" s="12">
@@ -7205,16 +7776,22 @@
         <v>0</v>
       </c>
       <c r="Q43" s="12">
+        <v>0</v>
+      </c>
+      <c r="R43" s="12">
         <v>0.17815817085607574</v>
       </c>
-      <c r="R43" s="12">
-        <v>0</v>
-      </c>
-      <c r="S43" s="11">
+      <c r="S43" s="12">
+        <v>0</v>
+      </c>
+      <c r="T43" s="12">
+        <v>0</v>
+      </c>
+      <c r="U43" s="11">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>46233</v>
       </c>
@@ -7244,20 +7821,20 @@
         <v>0</v>
       </c>
       <c r="J44" s="9">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9">
         <v>223843</v>
       </c>
-      <c r="K44" s="10">
+      <c r="L44" s="10">
         <v>391793.7</v>
       </c>
-      <c r="L44" s="11">
-        <v>0</v>
-      </c>
       <c r="M44" s="11">
+        <v>0</v>
+      </c>
+      <c r="N44" s="11">
         <v>0.11967190896637697</v>
       </c>
-      <c r="N44" s="12">
-        <v>0</v>
-      </c>
       <c r="O44" s="12">
         <v>0</v>
       </c>
@@ -7265,16 +7842,22 @@
         <v>0</v>
       </c>
       <c r="Q44" s="12">
+        <v>0</v>
+      </c>
+      <c r="R44" s="12">
         <v>0.30899935348628627</v>
       </c>
-      <c r="R44" s="12">
-        <v>0</v>
-      </c>
-      <c r="S44" s="11">
+      <c r="S44" s="12">
+        <v>0</v>
+      </c>
+      <c r="T44" s="12">
+        <v>0</v>
+      </c>
+      <c r="U44" s="11">
         <v>0.57132873754733671</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>46234</v>
       </c>
@@ -7304,20 +7887,20 @@
         <v>0</v>
       </c>
       <c r="J45" s="9">
+        <v>0</v>
+      </c>
+      <c r="K45" s="9">
         <v>223843</v>
       </c>
-      <c r="K45" s="10">
+      <c r="L45" s="10">
         <v>388741.7</v>
       </c>
-      <c r="L45" s="11">
-        <v>0</v>
-      </c>
       <c r="M45" s="11">
+        <v>0</v>
+      </c>
+      <c r="N45" s="11">
         <v>0.11276047823014616</v>
       </c>
-      <c r="N45" s="12">
-        <v>0</v>
-      </c>
       <c r="O45" s="12">
         <v>0</v>
       </c>
@@ -7325,16 +7908,22 @@
         <v>0</v>
       </c>
       <c r="Q45" s="12">
+        <v>0</v>
+      </c>
+      <c r="R45" s="12">
         <v>0.3114252985980151</v>
       </c>
-      <c r="R45" s="12">
-        <v>0</v>
-      </c>
-      <c r="S45" s="11">
+      <c r="S45" s="12">
+        <v>0</v>
+      </c>
+      <c r="T45" s="12">
+        <v>0</v>
+      </c>
+      <c r="U45" s="11">
         <v>0.57581422317183872</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46237</v>
       </c>
@@ -7364,20 +7953,20 @@
         <v>0</v>
       </c>
       <c r="J46" s="9">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9">
         <v>223843</v>
       </c>
-      <c r="K46" s="10">
+      <c r="L46" s="10">
         <v>385314.7</v>
       </c>
-      <c r="L46" s="11">
-        <v>0</v>
-      </c>
       <c r="M46" s="11">
+        <v>0</v>
+      </c>
+      <c r="N46" s="11">
         <v>0.10486934446051503</v>
       </c>
-      <c r="N46" s="12">
-        <v>0</v>
-      </c>
       <c r="O46" s="12">
         <v>0</v>
       </c>
@@ -7385,16 +7974,22 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12">
+        <v>0</v>
+      </c>
+      <c r="R46" s="12">
         <v>0.31419512414138362</v>
       </c>
-      <c r="R46" s="12">
-        <v>0</v>
-      </c>
-      <c r="S46" s="11">
+      <c r="S46" s="12">
+        <v>0</v>
+      </c>
+      <c r="T46" s="12">
+        <v>0</v>
+      </c>
+      <c r="U46" s="11">
         <v>0.58093553139810128</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46238</v>
       </c>
@@ -7424,20 +8019,20 @@
         <v>0</v>
       </c>
       <c r="J47" s="9">
+        <v>0</v>
+      </c>
+      <c r="K47" s="9">
         <v>223843</v>
       </c>
-      <c r="K47" s="10">
+      <c r="L47" s="10">
         <v>383427.7</v>
       </c>
-      <c r="L47" s="11">
-        <v>0</v>
-      </c>
       <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11">
         <v>0.1004640509801457</v>
       </c>
-      <c r="N47" s="12">
-        <v>0</v>
-      </c>
       <c r="O47" s="12">
         <v>0</v>
       </c>
@@ -7445,16 +8040,22 @@
         <v>0</v>
       </c>
       <c r="Q47" s="12">
+        <v>0</v>
+      </c>
+      <c r="R47" s="12">
         <v>0.31574140313806226</v>
       </c>
-      <c r="R47" s="12">
-        <v>0</v>
-      </c>
-      <c r="S47" s="11">
+      <c r="S47" s="12">
+        <v>0</v>
+      </c>
+      <c r="T47" s="12">
+        <v>0</v>
+      </c>
+      <c r="U47" s="11">
         <v>0.58379454588179203</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>46239</v>
       </c>
@@ -7484,20 +8085,20 @@
         <v>0</v>
       </c>
       <c r="J48" s="9">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9">
         <v>223843</v>
       </c>
-      <c r="K48" s="10">
+      <c r="L48" s="10">
         <v>381652.7</v>
       </c>
-      <c r="L48" s="11">
-        <v>0</v>
-      </c>
       <c r="M48" s="11">
+        <v>0</v>
+      </c>
+      <c r="N48" s="11">
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="N48" s="12">
-        <v>0</v>
-      </c>
       <c r="O48" s="12">
         <v>0</v>
       </c>
@@ -7505,16 +8106,22 @@
         <v>0</v>
       </c>
       <c r="Q48" s="12">
+        <v>0</v>
+      </c>
+      <c r="R48" s="12">
         <v>0.31720986121675543</v>
       </c>
-      <c r="R48" s="12">
-        <v>0</v>
-      </c>
-      <c r="S48" s="11">
+      <c r="S48" s="12">
+        <v>0</v>
+      </c>
+      <c r="T48" s="12">
+        <v>0</v>
+      </c>
+      <c r="U48" s="11">
         <v>0.58650967227534356</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>46240</v>
       </c>
@@ -7544,20 +8151,20 @@
         <v>0</v>
       </c>
       <c r="J49" s="9">
+        <v>0</v>
+      </c>
+      <c r="K49" s="9">
         <v>223843</v>
       </c>
-      <c r="K49" s="10">
+      <c r="L49" s="10">
         <v>383198.7</v>
       </c>
-      <c r="L49" s="11">
-        <v>0</v>
-      </c>
       <c r="M49" s="11">
+        <v>0</v>
+      </c>
+      <c r="N49" s="11">
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="N49" s="12">
-        <v>0</v>
-      </c>
       <c r="O49" s="12">
         <v>0</v>
       </c>
@@ -7565,16 +8172,22 @@
         <v>0</v>
       </c>
       <c r="Q49" s="12">
+        <v>0</v>
+      </c>
+      <c r="R49" s="12">
         <v>0.31593009057702959</v>
       </c>
-      <c r="R49" s="12">
-        <v>0</v>
-      </c>
-      <c r="S49" s="11">
+      <c r="S49" s="12">
+        <v>0</v>
+      </c>
+      <c r="T49" s="12">
+        <v>0</v>
+      </c>
+      <c r="U49" s="11">
         <v>0.58414342219845738</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>46241</v>
       </c>
@@ -7604,20 +8217,20 @@
         <v>0</v>
       </c>
       <c r="J50" s="9">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9">
         <v>223843</v>
       </c>
-      <c r="K50" s="10">
+      <c r="L50" s="10">
         <v>384776.7</v>
       </c>
-      <c r="L50" s="11">
-        <v>0</v>
-      </c>
       <c r="M50" s="11">
+        <v>0</v>
+      </c>
+      <c r="N50" s="11">
         <v>0.10361776063883289</v>
       </c>
-      <c r="N50" s="12">
-        <v>0</v>
-      </c>
       <c r="O50" s="12">
         <v>0</v>
       </c>
@@ -7625,16 +8238,22 @@
         <v>0</v>
       </c>
       <c r="Q50" s="12">
+        <v>0</v>
+      </c>
+      <c r="R50" s="12">
         <v>0.31463443602484248</v>
       </c>
-      <c r="R50" s="12">
-        <v>0</v>
-      </c>
-      <c r="S50" s="11">
+      <c r="S50" s="12">
+        <v>0</v>
+      </c>
+      <c r="T50" s="12">
+        <v>0</v>
+      </c>
+      <c r="U50" s="11">
         <v>0.5817478033363247</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>46244</v>
       </c>
@@ -7663,21 +8282,21 @@
       <c r="I51" s="9">
         <v>185382</v>
       </c>
-      <c r="J51" s="14">
+      <c r="J51" s="9">
+        <v>0</v>
+      </c>
+      <c r="K51" s="14">
         <v>54051</v>
       </c>
-      <c r="K51" s="10">
+      <c r="L51" s="10">
         <v>384909.7</v>
       </c>
-      <c r="L51" s="11">
-        <v>0</v>
-      </c>
       <c r="M51" s="11">
+        <v>0</v>
+      </c>
+      <c r="N51" s="11">
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="N51" s="12">
-        <v>0</v>
-      </c>
       <c r="O51" s="12">
         <v>0</v>
       </c>
@@ -7685,16 +8304,22 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
+        <v>0</v>
+      </c>
+      <c r="R51" s="12">
         <v>0.31452571862959028</v>
       </c>
-      <c r="R51" s="12">
+      <c r="S51" s="12">
         <v>0.48162465118442066</v>
       </c>
-      <c r="S51" s="11">
+      <c r="T51" s="12">
+        <v>0</v>
+      </c>
+      <c r="U51" s="11">
         <v>0.14042514387140673</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>46245</v>
       </c>
@@ -7723,21 +8348,21 @@
       <c r="I52" s="9">
         <v>185382</v>
       </c>
-      <c r="J52" s="14">
+      <c r="J52" s="9">
+        <v>0</v>
+      </c>
+      <c r="K52" s="14">
         <v>54051</v>
       </c>
-      <c r="K52" s="10">
+      <c r="L52" s="10">
         <v>379686.7</v>
       </c>
-      <c r="L52" s="11">
-        <v>0</v>
-      </c>
       <c r="M52" s="11">
+        <v>0</v>
+      </c>
+      <c r="N52" s="11">
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="N52" s="12">
-        <v>0</v>
-      </c>
       <c r="O52" s="12">
         <v>0</v>
       </c>
@@ -7745,16 +8370,22 @@
         <v>0</v>
       </c>
       <c r="Q52" s="12">
+        <v>0</v>
+      </c>
+      <c r="R52" s="12">
         <v>0.31885235906340675</v>
       </c>
-      <c r="R52" s="12">
+      <c r="S52" s="12">
         <v>0.48824991762945608</v>
       </c>
-      <c r="S52" s="11">
+      <c r="T52" s="12">
+        <v>0</v>
+      </c>
+      <c r="U52" s="11">
         <v>0.14235684315515923</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>46246</v>
       </c>
@@ -7783,43 +8414,49 @@
       <c r="I53" s="9">
         <v>154290</v>
       </c>
-      <c r="J53" s="14">
+      <c r="J53" s="9">
+        <v>0</v>
+      </c>
+      <c r="K53" s="14">
         <v>218671</v>
       </c>
-      <c r="K53" s="10">
-        <f>SUM(C53:J53)</f>
+      <c r="L53" s="10">
+        <f>SUM(C53:K53)</f>
         <v>676730</v>
       </c>
-      <c r="L53" s="11">
-        <v>0</v>
-      </c>
       <c r="M53" s="11">
         <v>0</v>
       </c>
-      <c r="N53" s="12">
+      <c r="N53" s="11">
         <v>0</v>
       </c>
       <c r="O53" s="12">
         <v>0</v>
       </c>
       <c r="P53" s="12">
-        <f>G53/K53</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="12">
+        <f>G53/L53</f>
         <v>0.2699821199001079</v>
       </c>
-      <c r="Q53" s="12">
-        <f>H53/K53</f>
+      <c r="R53" s="12">
+        <f>H53/L53</f>
         <v>0.17889557135046474</v>
       </c>
-      <c r="R53" s="12">
-        <f>I53/K53</f>
+      <c r="S53" s="12">
+        <f>I53/L53</f>
         <v>0.22799343903772554</v>
       </c>
-      <c r="S53" s="11">
-        <f>J53/K53</f>
+      <c r="T53" s="12">
+        <v>0</v>
+      </c>
+      <c r="U53" s="11">
+        <f>K53/L53</f>
         <v>0.32312886971170185</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>46247</v>
       </c>
@@ -7848,19 +8485,19 @@
       <c r="I54" s="9">
         <v>154290</v>
       </c>
-      <c r="J54" s="14">
+      <c r="J54" s="9">
+        <v>0</v>
+      </c>
+      <c r="K54" s="14">
         <v>218671</v>
       </c>
-      <c r="K54" s="10">
+      <c r="L54" s="10">
         <v>494025</v>
       </c>
-      <c r="L54" s="11">
-        <v>0</v>
-      </c>
       <c r="M54" s="11">
         <v>0</v>
       </c>
-      <c r="N54" s="12">
+      <c r="N54" s="11">
         <v>0</v>
       </c>
       <c r="O54" s="12">
@@ -7870,16 +8507,22 @@
         <v>0</v>
       </c>
       <c r="Q54" s="12">
+        <v>0</v>
+      </c>
+      <c r="R54" s="12">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R54" s="12">
+      <c r="S54" s="12">
         <v>0.31231212995293761</v>
       </c>
-      <c r="S54" s="11">
+      <c r="T54" s="12">
+        <v>0</v>
+      </c>
+      <c r="U54" s="11">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>46248</v>
       </c>
@@ -7908,19 +8551,19 @@
       <c r="I55" s="9">
         <v>154290</v>
       </c>
-      <c r="J55" s="14">
+      <c r="J55" s="9">
+        <v>0</v>
+      </c>
+      <c r="K55" s="14">
         <v>218671</v>
       </c>
-      <c r="K55" s="10">
+      <c r="L55" s="10">
         <v>494025</v>
       </c>
-      <c r="L55" s="11">
-        <v>0</v>
-      </c>
       <c r="M55" s="11">
         <v>0</v>
       </c>
-      <c r="N55" s="12">
+      <c r="N55" s="11">
         <v>0</v>
       </c>
       <c r="O55" s="12">
@@ -7930,16 +8573,22 @@
         <v>0</v>
       </c>
       <c r="Q55" s="12">
+        <v>0</v>
+      </c>
+      <c r="R55" s="12">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R55" s="12">
+      <c r="S55" s="12">
         <v>0.31231212995293761</v>
       </c>
-      <c r="S55" s="11">
+      <c r="T55" s="12">
+        <v>0</v>
+      </c>
+      <c r="U55" s="11">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>46251</v>
       </c>
@@ -7968,19 +8617,19 @@
       <c r="I56" s="9">
         <v>154290</v>
       </c>
-      <c r="J56" s="14">
+      <c r="J56" s="9">
+        <v>0</v>
+      </c>
+      <c r="K56" s="14">
         <v>218671</v>
       </c>
-      <c r="K56" s="10">
+      <c r="L56" s="10">
         <v>494025</v>
       </c>
-      <c r="L56" s="11">
-        <v>0</v>
-      </c>
       <c r="M56" s="11">
         <v>0</v>
       </c>
-      <c r="N56" s="12">
+      <c r="N56" s="11">
         <v>0</v>
       </c>
       <c r="O56" s="12">
@@ -7990,16 +8639,22 @@
         <v>0</v>
       </c>
       <c r="Q56" s="12">
+        <v>0</v>
+      </c>
+      <c r="R56" s="12">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R56" s="12">
+      <c r="S56" s="12">
         <v>0.31231212995293761</v>
       </c>
-      <c r="S56" s="11">
+      <c r="T56" s="12">
+        <v>0</v>
+      </c>
+      <c r="U56" s="11">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>46252</v>
       </c>
@@ -8028,19 +8683,19 @@
       <c r="I57" s="9">
         <v>154290</v>
       </c>
-      <c r="J57" s="14">
+      <c r="J57" s="9">
+        <v>0</v>
+      </c>
+      <c r="K57" s="14">
         <v>218671</v>
       </c>
-      <c r="K57" s="10">
+      <c r="L57" s="10">
         <v>494025</v>
       </c>
-      <c r="L57" s="11">
-        <v>0</v>
-      </c>
       <c r="M57" s="11">
         <v>0</v>
       </c>
-      <c r="N57" s="12">
+      <c r="N57" s="11">
         <v>0</v>
       </c>
       <c r="O57" s="12">
@@ -8050,16 +8705,22 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R57" s="12">
+      <c r="S57" s="12">
         <v>0.31231212995293761</v>
       </c>
-      <c r="S57" s="11">
+      <c r="T57" s="12">
+        <v>0</v>
+      </c>
+      <c r="U57" s="11">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>46253</v>
       </c>
@@ -8088,19 +8749,19 @@
       <c r="I58" s="9">
         <v>154290</v>
       </c>
-      <c r="J58" s="14">
+      <c r="J58" s="9">
+        <v>0</v>
+      </c>
+      <c r="K58" s="14">
         <v>218671</v>
       </c>
-      <c r="K58" s="10">
+      <c r="L58" s="10">
         <v>494025</v>
       </c>
-      <c r="L58" s="11">
-        <v>0</v>
-      </c>
       <c r="M58" s="11">
         <v>0</v>
       </c>
-      <c r="N58" s="12">
+      <c r="N58" s="11">
         <v>0</v>
       </c>
       <c r="O58" s="12">
@@ -8110,16 +8771,22 @@
         <v>0</v>
       </c>
       <c r="Q58" s="12">
+        <v>0</v>
+      </c>
+      <c r="R58" s="12">
         <v>0.24505642427002683</v>
       </c>
-      <c r="R58" s="12">
+      <c r="S58" s="12">
         <v>0.31231212995293761</v>
       </c>
-      <c r="S58" s="11">
+      <c r="T58" s="12">
+        <v>0</v>
+      </c>
+      <c r="U58" s="11">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>46254</v>
       </c>
@@ -8148,43 +8815,49 @@
       <c r="I59" s="9">
         <v>154290</v>
       </c>
-      <c r="J59" s="14">
+      <c r="J59" s="9">
+        <v>0</v>
+      </c>
+      <c r="K59" s="14">
         <v>218671</v>
       </c>
-      <c r="K59" s="10">
-        <f>SUM(C59:J59)</f>
+      <c r="L59" s="10">
+        <f>SUM(C59:K59)</f>
         <v>1945025</v>
       </c>
-      <c r="L59" s="11">
-        <v>0</v>
-      </c>
       <c r="M59" s="11">
         <v>0</v>
       </c>
-      <c r="N59" s="12">
+      <c r="N59" s="11">
         <v>0</v>
       </c>
       <c r="O59" s="12">
-        <f>E59/K59</f>
+        <v>0</v>
+      </c>
+      <c r="P59" s="12">
+        <f>E59/L59</f>
         <v>0.7460058354005733</v>
       </c>
-      <c r="P59" s="12">
-        <v>0</v>
-      </c>
       <c r="Q59" s="12">
-        <f>H59/K59</f>
+        <v>0</v>
+      </c>
+      <c r="R59" s="12">
+        <f>H59/L59</f>
         <v>6.2242901762188149E-2</v>
       </c>
-      <c r="R59" s="12">
-        <f>I59/K59</f>
+      <c r="S59" s="12">
+        <f>I59/L59</f>
         <v>7.9325458541663993E-2</v>
       </c>
-      <c r="S59" s="11">
-        <f>J59/K59</f>
+      <c r="T59" s="12">
+        <v>0</v>
+      </c>
+      <c r="U59" s="11">
+        <f>K59/L59</f>
         <v>0.11242580429557461</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>46255</v>
       </c>
@@ -8213,38 +8886,44 @@
       <c r="I60" s="9">
         <v>154290</v>
       </c>
-      <c r="J60" s="14">
+      <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="14">
         <v>218671</v>
       </c>
-      <c r="K60" s="10">
+      <c r="L60" s="10">
         <v>930260</v>
       </c>
-      <c r="L60" s="11">
-        <v>0</v>
-      </c>
       <c r="M60" s="11">
         <v>0</v>
       </c>
-      <c r="N60" s="12">
+      <c r="N60" s="11">
         <v>0</v>
       </c>
       <c r="O60" s="12">
+        <v>0</v>
+      </c>
+      <c r="P60" s="12">
         <v>0.46893879130565647</v>
       </c>
-      <c r="P60" s="12">
-        <v>0</v>
-      </c>
       <c r="Q60" s="12">
+        <v>0</v>
+      </c>
+      <c r="R60" s="12">
         <v>0.13013996087115431</v>
       </c>
-      <c r="R60" s="12">
+      <c r="S60" s="12">
         <v>0.16585685722271193</v>
       </c>
-      <c r="S60" s="11">
+      <c r="T60" s="12">
+        <v>0</v>
+      </c>
+      <c r="U60" s="11">
         <v>0.23506439060047729</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>46258</v>
       </c>
@@ -8273,45 +8952,51 @@
       <c r="I61" s="9">
         <v>154290</v>
       </c>
-      <c r="J61" s="14">
+      <c r="J61" s="9">
+        <v>0</v>
+      </c>
+      <c r="K61" s="14">
         <v>218671</v>
       </c>
-      <c r="K61" s="10">
-        <f>SUM(C61:J61)</f>
+      <c r="L61" s="10">
+        <f>SUM(C61:K61)</f>
         <v>1204798</v>
       </c>
-      <c r="L61" s="11">
-        <f>C61/K61</f>
+      <c r="M61" s="11">
+        <f>C61/L61</f>
         <v>0.11067249447625245</v>
       </c>
-      <c r="M61" s="11">
-        <v>0</v>
-      </c>
-      <c r="N61" s="12">
-        <f>F61/K61</f>
+      <c r="N61" s="11">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12">
+        <f>F61/L61</f>
         <v>0.11719806971791122</v>
       </c>
-      <c r="O61" s="12">
-        <f>E61/K61</f>
+      <c r="P61" s="12">
+        <f>E61/L61</f>
         <v>0.36208144435830736</v>
       </c>
-      <c r="P61" s="12">
-        <v>0</v>
-      </c>
       <c r="Q61" s="12">
-        <f>H61/K61</f>
+        <v>0</v>
+      </c>
+      <c r="R61" s="12">
+        <f>H61/L61</f>
         <v>0.10048489456323799</v>
       </c>
-      <c r="R61" s="12">
-        <f>I61/K61</f>
+      <c r="S61" s="12">
+        <f>I61/L61</f>
         <v>0.12806296159190173</v>
       </c>
-      <c r="S61" s="11">
-        <f>J61/K61</f>
+      <c r="T61" s="12">
+        <v>0</v>
+      </c>
+      <c r="U61" s="11">
+        <f>K61/L61</f>
         <v>0.18150013529238926</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>46259</v>
       </c>
@@ -8340,21 +9025,21 @@
       <c r="I62" s="9">
         <v>0</v>
       </c>
-      <c r="J62" s="14">
+      <c r="J62" s="9">
+        <v>0</v>
+      </c>
+      <c r="K62" s="14">
         <v>54671</v>
       </c>
-      <c r="K62" s="10">
+      <c r="L62" s="10">
         <v>396282.31</v>
       </c>
-      <c r="L62" s="11">
-        <v>0</v>
-      </c>
       <c r="M62" s="11">
+        <v>0</v>
+      </c>
+      <c r="N62" s="11">
         <v>0.86204027123996529</v>
       </c>
-      <c r="N62" s="12">
-        <v>0</v>
-      </c>
       <c r="O62" s="12">
         <v>0</v>
       </c>
@@ -8367,11 +9052,17 @@
       <c r="R62" s="12">
         <v>0</v>
       </c>
-      <c r="S62" s="11">
+      <c r="S62" s="12">
+        <v>0</v>
+      </c>
+      <c r="T62" s="12">
+        <v>0</v>
+      </c>
+      <c r="U62" s="11">
         <v>0.13795972876003473</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>46260</v>
       </c>
@@ -8400,21 +9091,21 @@
       <c r="I63" s="9">
         <v>0</v>
       </c>
-      <c r="J63" s="14">
+      <c r="J63" s="9">
+        <v>0</v>
+      </c>
+      <c r="K63" s="14">
         <v>54671</v>
       </c>
-      <c r="K63" s="10">
+      <c r="L63" s="10">
         <v>395802.31</v>
       </c>
-      <c r="L63" s="11">
-        <v>0</v>
-      </c>
       <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="N63" s="11">
         <v>0.86187296380357159</v>
       </c>
-      <c r="N63" s="12">
-        <v>0</v>
-      </c>
       <c r="O63" s="12">
         <v>0</v>
       </c>
@@ -8427,11 +9118,17 @@
       <c r="R63" s="12">
         <v>0</v>
       </c>
-      <c r="S63" s="11">
+      <c r="S63" s="12">
+        <v>0</v>
+      </c>
+      <c r="T63" s="12">
+        <v>0</v>
+      </c>
+      <c r="U63" s="11">
         <v>0.13812703619642847</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>46261</v>
       </c>
@@ -8460,21 +9157,21 @@
       <c r="I64" s="9">
         <v>0</v>
       </c>
-      <c r="J64" s="14">
+      <c r="J64" s="9">
+        <v>0</v>
+      </c>
+      <c r="K64" s="14">
         <v>54671</v>
       </c>
-      <c r="K64" s="10">
+      <c r="L64" s="10">
         <v>396617.31</v>
       </c>
-      <c r="L64" s="11">
-        <v>0</v>
-      </c>
       <c r="M64" s="11">
+        <v>0</v>
+      </c>
+      <c r="N64" s="11">
         <v>0.8621567979471193</v>
       </c>
-      <c r="N64" s="12">
-        <v>0</v>
-      </c>
       <c r="O64" s="12">
         <v>0</v>
       </c>
@@ -8487,11 +9184,17 @@
       <c r="R64" s="12">
         <v>0</v>
       </c>
-      <c r="S64" s="11">
+      <c r="S64" s="12">
+        <v>0</v>
+      </c>
+      <c r="T64" s="12">
+        <v>0</v>
+      </c>
+      <c r="U64" s="11">
         <v>0.13784320205288064</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>46262</v>
       </c>
@@ -8520,21 +9223,21 @@
       <c r="I65" s="9">
         <v>0</v>
       </c>
-      <c r="J65" s="14">
+      <c r="J65" s="9">
+        <v>0</v>
+      </c>
+      <c r="K65" s="14">
         <v>54671</v>
       </c>
-      <c r="K65" s="10">
+      <c r="L65" s="10">
         <v>396917.31</v>
       </c>
-      <c r="L65" s="11">
-        <v>0</v>
-      </c>
       <c r="M65" s="11">
+        <v>0</v>
+      </c>
+      <c r="N65" s="11">
         <v>0.86226098327634038</v>
       </c>
-      <c r="N65" s="12">
-        <v>0</v>
-      </c>
       <c r="O65" s="12">
         <v>0</v>
       </c>
@@ -8547,11 +9250,17 @@
       <c r="R65" s="12">
         <v>0</v>
       </c>
-      <c r="S65" s="11">
+      <c r="S65" s="12">
+        <v>0</v>
+      </c>
+      <c r="T65" s="12">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11">
         <v>0.13773901672365965</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>46265</v>
       </c>
@@ -8580,21 +9289,21 @@
       <c r="I66" s="9">
         <v>0</v>
       </c>
-      <c r="J66" s="14">
+      <c r="J66" s="9">
+        <v>0</v>
+      </c>
+      <c r="K66" s="14">
         <v>54671</v>
       </c>
-      <c r="K66" s="10">
+      <c r="L66" s="10">
         <v>399269.72</v>
       </c>
-      <c r="L66" s="11">
+      <c r="M66" s="11">
         <v>0.14977093679931452</v>
       </c>
-      <c r="M66" s="11">
+      <c r="N66" s="11">
         <v>0.71330157468490218</v>
       </c>
-      <c r="N66" s="12">
-        <v>0</v>
-      </c>
       <c r="O66" s="12">
         <v>0</v>
       </c>
@@ -8607,11 +9316,17 @@
       <c r="R66" s="12">
         <v>0</v>
       </c>
-      <c r="S66" s="11">
+      <c r="S66" s="12">
+        <v>0</v>
+      </c>
+      <c r="T66" s="12">
+        <v>0</v>
+      </c>
+      <c r="U66" s="11">
         <v>0.13692748851578326</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>46266</v>
       </c>
@@ -8640,19 +9355,19 @@
       <c r="I67" s="9">
         <v>0</v>
       </c>
-      <c r="J67" s="14">
+      <c r="J67" s="9">
+        <v>0</v>
+      </c>
+      <c r="K67" s="14">
         <v>54671</v>
       </c>
-      <c r="K67" s="10">
+      <c r="L67" s="10">
         <v>926093</v>
       </c>
-      <c r="L67" s="11">
+      <c r="M67" s="11">
         <v>0.94096597209999433</v>
       </c>
-      <c r="M67" s="11">
-        <v>0</v>
-      </c>
-      <c r="N67" s="12">
+      <c r="N67" s="11">
         <v>0</v>
       </c>
       <c r="O67" s="12">
@@ -8667,11 +9382,17 @@
       <c r="R67" s="12">
         <v>0</v>
       </c>
-      <c r="S67" s="11">
+      <c r="S67" s="12">
+        <v>0</v>
+      </c>
+      <c r="T67" s="12">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11">
         <v>5.9034027900005726E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>46267</v>
       </c>
@@ -8700,19 +9421,19 @@
       <c r="I68" s="9">
         <v>0</v>
       </c>
-      <c r="J68" s="14">
+      <c r="J68" s="9">
+        <v>0</v>
+      </c>
+      <c r="K68" s="14">
         <v>54671</v>
       </c>
-      <c r="K68" s="10">
+      <c r="L68" s="10">
         <v>794093</v>
       </c>
-      <c r="L68" s="11">
+      <c r="M68" s="11">
         <v>0.93115290022705144</v>
       </c>
-      <c r="M68" s="11">
-        <v>0</v>
-      </c>
-      <c r="N68" s="12">
+      <c r="N68" s="11">
         <v>0</v>
       </c>
       <c r="O68" s="12">
@@ -8727,11 +9448,17 @@
       <c r="R68" s="12">
         <v>0</v>
       </c>
-      <c r="S68" s="11">
+      <c r="S68" s="12">
+        <v>0</v>
+      </c>
+      <c r="T68" s="12">
+        <v>0</v>
+      </c>
+      <c r="U68" s="11">
         <v>6.8847099772948506E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>46268</v>
       </c>
@@ -8760,22 +9487,22 @@
       <c r="I69" s="9">
         <v>0</v>
       </c>
-      <c r="J69" s="14">
-        <v>0</v>
-      </c>
-      <c r="K69" s="10">
-        <f>SUM(C69:J69)</f>
+      <c r="J69" s="9">
+        <v>0</v>
+      </c>
+      <c r="K69" s="14">
+        <v>0</v>
+      </c>
+      <c r="L69" s="10">
+        <f>SUM(C69:K69)</f>
         <v>407651</v>
       </c>
-      <c r="L69" s="11">
+      <c r="M69" s="11">
         <v>0.25051515991027662</v>
       </c>
-      <c r="M69" s="11">
+      <c r="N69" s="11">
         <v>0.74948484008972338</v>
       </c>
-      <c r="N69" s="12">
-        <v>0</v>
-      </c>
       <c r="O69" s="12">
         <v>0</v>
       </c>
@@ -8788,11 +9515,17 @@
       <c r="R69" s="12">
         <v>0</v>
       </c>
-      <c r="S69" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S69" s="12">
+        <v>0</v>
+      </c>
+      <c r="T69" s="12">
+        <v>0</v>
+      </c>
+      <c r="U69" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>46269</v>
       </c>
@@ -8821,24 +9554,24 @@
       <c r="I70" s="9">
         <v>0</v>
       </c>
-      <c r="J70" s="14">
-        <v>0</v>
-      </c>
-      <c r="K70" s="10">
-        <f>SUM(C70:J70)</f>
+      <c r="J70" s="9">
+        <v>0</v>
+      </c>
+      <c r="K70" s="14">
+        <v>0</v>
+      </c>
+      <c r="L70" s="10">
+        <f>SUM(C70:K70)</f>
         <v>408551</v>
       </c>
-      <c r="L70" s="11">
-        <f>C70/K70</f>
+      <c r="M70" s="11">
+        <f>C70/L70</f>
         <v>0.24736201845057287</v>
       </c>
-      <c r="M70" s="11">
-        <f>D70/K70</f>
+      <c r="N70" s="11">
+        <f>D70/L70</f>
         <v>0.75263798154942707</v>
       </c>
-      <c r="N70" s="12">
-        <v>0</v>
-      </c>
       <c r="O70" s="12">
         <v>0</v>
       </c>
@@ -8851,11 +9584,17 @@
       <c r="R70" s="12">
         <v>0</v>
       </c>
-      <c r="S70" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S70" s="12">
+        <v>0</v>
+      </c>
+      <c r="T70" s="12">
+        <v>0</v>
+      </c>
+      <c r="U70" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>46272</v>
       </c>
@@ -8884,24 +9623,24 @@
       <c r="I71" s="9">
         <v>0</v>
       </c>
-      <c r="J71" s="14">
-        <v>0</v>
-      </c>
-      <c r="K71" s="10">
-        <f>SUM(C71:J71)</f>
+      <c r="J71" s="9">
+        <v>0</v>
+      </c>
+      <c r="K71" s="14">
+        <v>0</v>
+      </c>
+      <c r="L71" s="10">
+        <f>SUM(C71:K71)</f>
         <v>408551</v>
       </c>
-      <c r="L71" s="11">
-        <f>C71/K71</f>
+      <c r="M71" s="11">
+        <f>C71/L71</f>
         <v>0.24736201845057287</v>
       </c>
-      <c r="M71" s="11">
-        <f>D71/K71</f>
+      <c r="N71" s="11">
+        <f>D71/L71</f>
         <v>0.75263798154942707</v>
       </c>
-      <c r="N71" s="12">
-        <v>0</v>
-      </c>
       <c r="O71" s="12">
         <v>0</v>
       </c>
@@ -8914,11 +9653,17 @@
       <c r="R71" s="12">
         <v>0</v>
       </c>
-      <c r="S71" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S71" s="12">
+        <v>0</v>
+      </c>
+      <c r="T71" s="12">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>46273</v>
       </c>
@@ -8947,24 +9692,24 @@
       <c r="I72" s="9">
         <v>0</v>
       </c>
-      <c r="J72" s="14">
-        <v>0</v>
-      </c>
-      <c r="K72" s="10">
-        <f>SUM(C72:J72)</f>
+      <c r="J72" s="9">
+        <v>0</v>
+      </c>
+      <c r="K72" s="14">
+        <v>0</v>
+      </c>
+      <c r="L72" s="10">
+        <f>SUM(C72:K72)</f>
         <v>408551</v>
       </c>
-      <c r="L72" s="11">
-        <f>C72/K72</f>
+      <c r="M72" s="11">
+        <f>C72/L72</f>
         <v>0.24736201845057287</v>
       </c>
-      <c r="M72" s="11">
-        <f>D72/K72</f>
+      <c r="N72" s="11">
+        <f>D72/L72</f>
         <v>0.75263798154942707</v>
       </c>
-      <c r="N72" s="12">
-        <v>0</v>
-      </c>
       <c r="O72" s="12">
         <v>0</v>
       </c>
@@ -8977,11 +9722,17 @@
       <c r="R72" s="12">
         <v>0</v>
       </c>
-      <c r="S72" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S72" s="12">
+        <v>0</v>
+      </c>
+      <c r="T72" s="12">
+        <v>0</v>
+      </c>
+      <c r="U72" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>46274</v>
       </c>
@@ -9010,24 +9761,24 @@
       <c r="I73" s="9">
         <v>0</v>
       </c>
-      <c r="J73" s="14">
-        <v>0</v>
-      </c>
-      <c r="K73" s="10">
-        <f>SUM(C73:J73)</f>
+      <c r="J73" s="9">
+        <v>0</v>
+      </c>
+      <c r="K73" s="14">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10">
+        <f>SUM(C73:K73)</f>
         <v>409358</v>
       </c>
-      <c r="L73" s="11">
-        <f>C73/K73</f>
+      <c r="M73" s="11">
+        <f>C73/L73</f>
         <v>0.45189296410476892</v>
       </c>
-      <c r="M73" s="11">
-        <f>D73/K73</f>
+      <c r="N73" s="11">
+        <f>D73/L73</f>
         <v>0.54810703589523102</v>
       </c>
-      <c r="N73" s="12">
-        <v>0</v>
-      </c>
       <c r="O73" s="12">
         <v>0</v>
       </c>
@@ -9040,7 +9791,83 @@
       <c r="R73" s="12">
         <v>0</v>
       </c>
-      <c r="S73" s="11">
+      <c r="S73" s="12">
+        <v>0</v>
+      </c>
+      <c r="T73" s="12">
+        <v>0</v>
+      </c>
+      <c r="U73" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>46275</v>
+      </c>
+      <c r="B74" s="7">
+        <v>411688</v>
+      </c>
+      <c r="C74" s="15">
+        <v>416713</v>
+      </c>
+      <c r="D74" s="14">
+        <v>0</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0</v>
+      </c>
+      <c r="I74" s="9">
+        <v>26031</v>
+      </c>
+      <c r="J74" s="9">
+        <v>0</v>
+      </c>
+      <c r="K74" s="14">
+        <v>120370</v>
+      </c>
+      <c r="L74" s="10">
+        <f>SUM(C74:K74)</f>
+        <v>563114</v>
+      </c>
+      <c r="M74" s="11">
+        <f>C74/L74</f>
+        <v>0.74001534325198803</v>
+      </c>
+      <c r="N74" s="11">
+        <f>D74/L74</f>
+        <v>0</v>
+      </c>
+      <c r="O74" s="12">
+        <v>0</v>
+      </c>
+      <c r="P74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
+      <c r="R74" s="12">
+        <v>0</v>
+      </c>
+      <c r="S74" s="12">
+        <f>I74/L74</f>
+        <v>4.6226874132058518E-2</v>
+      </c>
+      <c r="T74" s="12">
+        <f>K74/L74</f>
+        <v>0.21375778261595343</v>
+      </c>
+      <c r="U74" s="11">
         <v>0</v>
       </c>
     </row>
@@ -9048,7 +9875,7 @@
       <c r="A1048543" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:S1048576">
+  <conditionalFormatting sqref="M2:U1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC07741-326E-CE46-8544-A3275DB70914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D65203-4467-DE40-A847-4E2ECDB6D95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3219,11 +3219,11 @@
         <v>46266</v>
       </c>
       <c r="C32" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D32" s="31">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32" s="43" t="s">
         <v>101</v>
@@ -3277,7 +3277,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>865</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3288,11 +3288,11 @@
         <v>46274</v>
       </c>
       <c r="C33" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D33" s="31">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="43" t="s">
         <v>139</v>
@@ -3346,7 +3346,7 @@
         <v>72</v>
       </c>
       <c r="V33" s="29">
-        <v>1192</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -3357,11 +3357,11 @@
         <v>46274</v>
       </c>
       <c r="C34" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D34" s="31">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="43" t="s">
         <v>99</v>
@@ -3426,11 +3426,11 @@
         <v>46275</v>
       </c>
       <c r="C35" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D35" s="31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="43" t="s">
         <v>141</v>
@@ -3484,7 +3484,7 @@
         <v>72</v>
       </c>
       <c r="V35" s="29">
-        <v>15</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -3495,11 +3495,11 @@
         <v>46275</v>
       </c>
       <c r="C36" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D36" s="31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="43" t="s">
         <v>56</v>
@@ -3553,7 +3553,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>633</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3564,11 +3564,11 @@
         <v>46275</v>
       </c>
       <c r="C37" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D37" s="31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="43" t="s">
         <v>144</v>
@@ -3633,11 +3633,11 @@
         <v>46275</v>
       </c>
       <c r="C38" s="51">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D38" s="31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="43" t="s">
         <v>146</v>
@@ -3691,7 +3691,7 @@
         <v>72</v>
       </c>
       <c r="V38" s="29">
-        <v>19</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="V40" s="35">
         <f>SUM(V2:V38)</f>
-        <v>2344</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3743,7 +3743,7 @@
       <c r="F43" s="32"/>
       <c r="U43" s="35">
         <f>U40+V40</f>
-        <v>70319.47</v>
+        <v>71733.47</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3769,7 +3769,7 @@
     <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="50">
         <f>U43/U46</f>
-        <v>0.21116957957957957</v>
+        <v>0.21541582582582583</v>
       </c>
     </row>
   </sheetData>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G65" s="23">
         <f>AVERAGE(C3:C67)</f>
-        <v>1203.5706153846149</v>
+        <v>1205.4783076923072</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="G66" s="23">
         <f>_xlfn.STDEV.S(C3:C67)</f>
-        <v>4360.5061175520677</v>
+        <v>4361.0337156367577</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4908,23 +4908,23 @@
         <v>46275</v>
       </c>
       <c r="B67" s="1">
-        <f>B66+2330</f>
-        <v>411688</v>
+        <f>B66+192+614-438+1783+67+219+17</f>
+        <v>411812</v>
       </c>
       <c r="C67" s="1">
         <f t="shared" si="0"/>
-        <v>2330</v>
+        <v>2454</v>
       </c>
       <c r="D67" s="19">
         <f t="shared" si="1"/>
-        <v>5.6918394168429592E-3</v>
+        <v>5.9947527591985503E-3</v>
       </c>
       <c r="F67" s="21" t="s">
         <v>116</v>
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3816223820371301</v>
+        <v>4.3880364441133333</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G68" s="25">
         <f>_xlfn.STDEV.S(D2:D67)*SQRT(252)</f>
-        <v>0.18975594310276095</v>
+        <v>0.18977186551707964</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G69" s="25" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D67)-1</f>
-        <v>0.23461018741852069</v>
+        <v>0.23498205073064016</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="G70" s="25" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D67)^(252/COUNT(D2:D66))-1</f>
-        <v>1.2638842177316159</v>
+        <v>1.2665289580221999</v>
       </c>
     </row>
   </sheetData>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="10">
-        <f>SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L74" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="11">
@@ -9561,7 +9561,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="10">
-        <f>SUM(C70:K70)</f>
+        <f t="shared" si="0"/>
         <v>408551</v>
       </c>
       <c r="M70" s="11">
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="10">
-        <f>SUM(C71:K71)</f>
+        <f t="shared" si="0"/>
         <v>408551</v>
       </c>
       <c r="M71" s="11">
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="10">
-        <f>SUM(C72:K72)</f>
+        <f t="shared" si="0"/>
         <v>408551</v>
       </c>
       <c r="M72" s="11">
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="10">
-        <f>SUM(C73:K73)</f>
+        <f t="shared" si="0"/>
         <v>409358</v>
       </c>
       <c r="M73" s="11">
@@ -9836,7 +9836,7 @@
         <v>120370</v>
       </c>
       <c r="L74" s="10">
-        <f>SUM(C74:K74)</f>
+        <f t="shared" si="0"/>
         <v>563114</v>
       </c>
       <c r="M74" s="11">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D65203-4467-DE40-A847-4E2ECDB6D95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4110711-6F61-0845-82EC-0816FC2ACD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="-32700" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="149">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="36">
-        <f t="shared" ref="S25:S31" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
+        <f t="shared" ref="S25:S34" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="T25" s="29">
@@ -3277,7 +3277,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>505</v>
+        <v>-1055</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3287,66 +3287,64 @@
       <c r="B33" s="30">
         <v>46274</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="30">
         <v>46276</v>
       </c>
       <c r="D33" s="31">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E33" s="43" t="s">
+      <c r="E33" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F33" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="43" t="s">
+      <c r="G33" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="43" t="s">
+      <c r="I33" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="43" t="s">
+      <c r="J33" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="43" t="s">
+      <c r="K33" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L33" s="43">
-        <v>9000</v>
-      </c>
-      <c r="M33" s="43">
-        <v>8.6980000000000004</v>
-      </c>
-      <c r="N33" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O33" s="43">
-        <v>8.82</v>
-      </c>
-      <c r="P33" s="45">
-        <v>79470</v>
-      </c>
-      <c r="Q33" s="43">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="R33" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="S33" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="T33" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="U33" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V33" s="29">
-        <v>2807</v>
+      <c r="L33" s="29">
+        <v>13000</v>
+      </c>
+      <c r="M33" s="29">
+        <v>8.6943999999999999</v>
+      </c>
+      <c r="N33" s="29">
+        <v>8.8673000000000002</v>
+      </c>
+      <c r="O33" s="29">
+        <v>8.8673000000000002</v>
+      </c>
+      <c r="P33" s="35">
+        <v>113028</v>
+      </c>
+      <c r="Q33" s="29">
+        <v>105.64</v>
+      </c>
+      <c r="R33" s="29">
+        <v>1</v>
+      </c>
+      <c r="S33" s="36">
+        <f t="shared" si="4"/>
+        <v>1.9886363636363667E-2</v>
+      </c>
+      <c r="T33" s="29">
+        <v>2247</v>
+      </c>
+      <c r="U33" s="37">
+        <v>2247</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
@@ -3356,66 +3354,64 @@
       <c r="B34" s="30">
         <v>46274</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="30">
         <v>46276</v>
       </c>
       <c r="D34" s="31">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="E34" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="43" t="s">
+      <c r="G34" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="43" t="s">
+      <c r="I34" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="J34" s="43" t="s">
+      <c r="J34" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="K34" s="43" t="s">
+      <c r="K34" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="L34" s="43">
+      <c r="L34" s="29">
         <v>400</v>
       </c>
-      <c r="M34" s="43">
+      <c r="M34" s="29">
         <v>318.87</v>
       </c>
-      <c r="N34" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O34" s="43">
-        <v>317.44</v>
-      </c>
-      <c r="P34" s="45">
-        <v>126488</v>
-      </c>
-      <c r="Q34" s="43">
-        <v>2.87</v>
-      </c>
-      <c r="R34" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="S34" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="T34" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="U34" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V34" s="29">
-        <v>-572</v>
+      <c r="N34" s="29">
+        <v>322</v>
+      </c>
+      <c r="O34" s="29">
+        <v>322</v>
+      </c>
+      <c r="P34" s="35">
+        <v>127547</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>4.71</v>
+      </c>
+      <c r="R34" s="29">
+        <v>1</v>
+      </c>
+      <c r="S34" s="36">
+        <f t="shared" si="4"/>
+        <v>9.8159124408065835E-3</v>
+      </c>
+      <c r="T34" s="29">
+        <v>1253</v>
+      </c>
+      <c r="U34" s="37">
+        <v>1253</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
@@ -3484,7 +3480,7 @@
         <v>72</v>
       </c>
       <c r="V35" s="29">
-        <v>159</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -3553,7 +3549,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>408</v>
+        <v>677</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3563,66 +3559,64 @@
       <c r="B37" s="30">
         <v>46275</v>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="30">
         <v>46276</v>
       </c>
       <c r="D37" s="31">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E37" s="43" t="s">
+      <c r="E37" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="43" t="s">
+      <c r="G37" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="43" t="s">
+      <c r="I37" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="43" t="s">
+      <c r="J37" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="K37" s="43" t="s">
+      <c r="K37" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="L37" s="43">
+      <c r="L37" s="29">
         <v>250</v>
       </c>
-      <c r="M37" s="43">
+      <c r="M37" s="29">
         <v>113.7</v>
       </c>
-      <c r="N37" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O37" s="43">
-        <v>114.47</v>
-      </c>
-      <c r="P37" s="45">
-        <v>28435</v>
-      </c>
-      <c r="Q37" s="43">
-        <v>1.6</v>
-      </c>
-      <c r="R37" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="S37" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="T37" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="U37" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V37" s="29">
-        <v>192</v>
+      <c r="N37" s="29">
+        <v>115.08</v>
+      </c>
+      <c r="O37" s="29">
+        <v>115.08</v>
+      </c>
+      <c r="P37" s="35">
+        <v>28770</v>
+      </c>
+      <c r="Q37" s="29">
+        <v>2.94</v>
+      </c>
+      <c r="R37" s="29">
+        <v>1</v>
+      </c>
+      <c r="S37" s="36">
+        <f t="shared" ref="S37:S38" si="6">IF(R37=1, ABS(N37-M37)/M37, 0)</f>
+        <v>1.2137203166226873E-2</v>
+      </c>
+      <c r="T37" s="29">
+        <v>345</v>
+      </c>
+      <c r="U37" s="37">
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
@@ -3632,66 +3626,64 @@
       <c r="B38" s="30">
         <v>46275</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="30">
         <v>46276</v>
       </c>
       <c r="D38" s="31">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="44" t="s">
+      <c r="F38" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="G38" s="43" t="s">
+      <c r="G38" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="43" t="s">
+      <c r="I38" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="J38" s="43" t="s">
+      <c r="J38" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="K38" s="43" t="s">
+      <c r="K38" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="L38" s="43">
+      <c r="L38" s="29">
         <v>1</v>
       </c>
-      <c r="M38" s="43">
+      <c r="M38" s="29">
         <v>120.35</v>
       </c>
-      <c r="N38" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O38" s="43">
-        <v>120.36</v>
-      </c>
-      <c r="P38" s="45">
+      <c r="N38" s="29">
+        <v>120.57</v>
+      </c>
+      <c r="O38" s="29">
+        <v>120.57</v>
+      </c>
+      <c r="P38" s="35">
         <v>120370</v>
       </c>
-      <c r="Q38" s="43">
-        <v>3.6</v>
-      </c>
-      <c r="R38" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="S38" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="T38" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="U38" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V38" s="29">
-        <v>259</v>
+      <c r="Q38" s="29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R38" s="29">
+        <v>1</v>
+      </c>
+      <c r="S38" s="36">
+        <f t="shared" si="6"/>
+        <v>1.8280016618196831E-3</v>
+      </c>
+      <c r="T38" s="29">
+        <v>220</v>
+      </c>
+      <c r="U38" s="37">
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
@@ -3709,12 +3701,12 @@
       <c r="F40" s="32"/>
       <c r="H40" s="32"/>
       <c r="U40" s="35">
-        <f>SUM(U2:U31)</f>
-        <v>67975.47</v>
+        <f>SUM(U2:U38)</f>
+        <v>72040.47</v>
       </c>
       <c r="V40" s="35">
         <f>SUM(V2:V38)</f>
-        <v>3758</v>
+        <v>-112</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3743,7 +3735,7 @@
       <c r="F43" s="32"/>
       <c r="U43" s="35">
         <f>U40+V40</f>
-        <v>71733.47</v>
+        <v>71928.47</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3769,7 +3761,7 @@
     <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="50">
         <f>U43/U46</f>
-        <v>0.21541582582582583</v>
+        <v>0.21600141141141141</v>
       </c>
     </row>
   </sheetData>
@@ -3848,11 +3840,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C67" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C68" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D67" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D68" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4875,8 +4867,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C67)</f>
-        <v>1205.4783076923072</v>
+        <f>AVERAGE(C3:C68)</f>
+        <v>1200.7437878787873</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4899,8 +4891,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C67)</f>
-        <v>4361.0337156367577</v>
+        <f>_xlfn.STDEV.S(C3:C68)</f>
+        <v>4327.5282120023458</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4924,16 +4916,31 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3880364441133333</v>
+        <v>4.4046429676256613</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="22">
+        <v>46276</v>
+      </c>
+      <c r="B68" s="1">
+        <f>B67+893</f>
+        <v>412705</v>
+      </c>
+      <c r="C68" s="1">
+        <f t="shared" si="0"/>
+        <v>893</v>
+      </c>
+      <c r="D68" s="19">
+        <f t="shared" si="1"/>
+        <v>2.1684652219945023E-3</v>
+      </c>
       <c r="F68" s="21" t="s">
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D67)*SQRT(252)</f>
-        <v>0.18977186551707964</v>
+        <f>_xlfn.STDEV.S(D2:D68)*SQRT(252)</f>
+        <v>0.18834088862804979</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4941,8 +4948,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D67)-1</f>
-        <v>0.23498205073064016</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D68)-1</f>
+        <v>0.23766006635743686</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4950,8 +4957,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D67)^(252/COUNT(D2:D66))-1</f>
-        <v>1.2665289580221999</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D68)^(252/COUNT(D2:D68))-1</f>
+        <v>1.2299326780676472</v>
       </c>
     </row>
   </sheetData>
@@ -9494,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="10">
-        <f t="shared" ref="L69:L74" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L75" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="11">
@@ -9868,6 +9875,78 @@
         <v>0.21375778261595343</v>
       </c>
       <c r="U74" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>46276</v>
+      </c>
+      <c r="B75" s="7">
+        <v>412705</v>
+      </c>
+      <c r="C75" s="15">
+        <f>64754+151830</f>
+        <v>216584</v>
+      </c>
+      <c r="D75" s="9">
+        <f>B75-C75-I75</f>
+        <v>170090</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9">
+        <v>26031</v>
+      </c>
+      <c r="J75" s="9">
+        <v>0</v>
+      </c>
+      <c r="K75" s="9">
+        <v>0</v>
+      </c>
+      <c r="L75" s="10">
+        <f t="shared" si="0"/>
+        <v>412705</v>
+      </c>
+      <c r="M75" s="11">
+        <f>C75/L75</f>
+        <v>0.52479131583092042</v>
+      </c>
+      <c r="N75" s="11">
+        <f>D75/L75</f>
+        <v>0.41213457554427496</v>
+      </c>
+      <c r="O75" s="12">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
+      <c r="R75" s="12">
+        <v>0</v>
+      </c>
+      <c r="S75" s="12">
+        <f>I75/L75</f>
+        <v>6.3074108624804642E-2</v>
+      </c>
+      <c r="T75" s="12">
+        <f>K75/L75</f>
+        <v>0</v>
+      </c>
+      <c r="U75" s="11">
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4110711-6F61-0845-82EC-0816FC2ACD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72532952-AB7C-EC42-8765-472FC711BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3519,7 +3519,7 @@
         <v>56</v>
       </c>
       <c r="L36" s="43">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="M36" s="43">
         <v>656.66</v>
@@ -3531,7 +3531,7 @@
         <v>643.87</v>
       </c>
       <c r="P36" s="45">
-        <v>32575</v>
+        <v>64709</v>
       </c>
       <c r="Q36" s="43">
         <v>2.1</v>
@@ -9572,11 +9572,11 @@
         <v>408551</v>
       </c>
       <c r="M70" s="11">
-        <f>C70/L70</f>
+        <f t="shared" ref="M70:M75" si="1">C70/L70</f>
         <v>0.24736201845057287</v>
       </c>
       <c r="N70" s="11">
-        <f>D70/L70</f>
+        <f t="shared" ref="N70:N75" si="2">D70/L70</f>
         <v>0.75263798154942707</v>
       </c>
       <c r="O70" s="12">
@@ -9641,11 +9641,11 @@
         <v>408551</v>
       </c>
       <c r="M71" s="11">
-        <f>C71/L71</f>
+        <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
       <c r="N71" s="11">
-        <f>D71/L71</f>
+        <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
       <c r="O71" s="12">
@@ -9710,11 +9710,11 @@
         <v>408551</v>
       </c>
       <c r="M72" s="11">
-        <f>C72/L72</f>
+        <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
       <c r="N72" s="11">
-        <f>D72/L72</f>
+        <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
       <c r="O72" s="12">
@@ -9779,11 +9779,11 @@
         <v>409358</v>
       </c>
       <c r="M73" s="11">
-        <f>C73/L73</f>
+        <f t="shared" si="1"/>
         <v>0.45189296410476892</v>
       </c>
       <c r="N73" s="11">
-        <f>D73/L73</f>
+        <f t="shared" si="2"/>
         <v>0.54810703589523102</v>
       </c>
       <c r="O73" s="12">
@@ -9847,11 +9847,11 @@
         <v>563114</v>
       </c>
       <c r="M74" s="11">
-        <f>C74/L74</f>
+        <f t="shared" si="1"/>
         <v>0.74001534325198803</v>
       </c>
       <c r="N74" s="11">
-        <f>D74/L74</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O74" s="12">
@@ -9919,11 +9919,11 @@
         <v>412705</v>
       </c>
       <c r="M75" s="11">
-        <f>C75/L75</f>
+        <f t="shared" si="1"/>
         <v>0.52479131583092042</v>
       </c>
       <c r="N75" s="11">
-        <f>D75/L75</f>
+        <f t="shared" si="2"/>
         <v>0.41213457554427496</v>
       </c>
       <c r="O75" s="12">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72532952-AB7C-EC42-8765-472FC711BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE21736-EF1F-9241-8730-0154EB555737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -3256,7 +3256,7 @@
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>49.97</v>
+        <v>50.59</v>
       </c>
       <c r="P32" s="45">
         <v>149745</v>
@@ -3277,7 +3277,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>-1055</v>
+        <v>-994</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>72</v>
       </c>
       <c r="O35" s="43">
-        <v>52095</v>
+        <v>52575</v>
       </c>
       <c r="P35" s="45">
         <v>26031</v>
@@ -3480,7 +3480,7 @@
         <v>72</v>
       </c>
       <c r="V35" s="29">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -3522,13 +3522,13 @@
         <v>-100</v>
       </c>
       <c r="M36" s="43">
-        <v>656.66</v>
+        <v>653.82000000000005</v>
       </c>
       <c r="N36" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O36" s="43">
-        <v>643.87</v>
+        <v>647.32000000000005</v>
       </c>
       <c r="P36" s="45">
         <v>64709</v>
@@ -3549,7 +3549,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>677</v>
+        <v>646</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="V40" s="35">
         <f>SUM(V2:V38)</f>
-        <v>-112</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3735,7 +3735,7 @@
       <c r="F43" s="32"/>
       <c r="U43" s="35">
         <f>U40+V40</f>
-        <v>71928.47</v>
+        <v>71948.47</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3761,7 +3761,7 @@
     <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="50">
         <f>U43/U46</f>
-        <v>0.21600141141141141</v>
+        <v>0.21606147147147148</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE21736-EF1F-9241-8730-0154EB555737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A88FAA-C236-C240-8D51-3405750F5112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="G65" s="23">
         <f>AVERAGE(C3:C68)</f>
-        <v>1200.7437878787873</v>
+        <v>1196.1983333333328</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G66" s="23">
         <f>_xlfn.STDEV.S(C3:C68)</f>
-        <v>4327.5282120023458</v>
+        <v>4328.013952603199</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.4046429676256613</v>
+        <v>4.3874765793761332</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4924,23 +4924,23 @@
         <v>46276</v>
       </c>
       <c r="B68" s="1">
-        <f>B67+893</f>
-        <v>412705</v>
+        <f>B67+150+25+1820+518-1920</f>
+        <v>412405</v>
       </c>
       <c r="C68" s="1">
         <f t="shared" si="0"/>
-        <v>893</v>
+        <v>593</v>
       </c>
       <c r="D68" s="19">
         <f t="shared" si="1"/>
-        <v>2.1684652219945023E-3</v>
+        <v>1.4399774654453973E-3</v>
       </c>
       <c r="F68" s="21" t="s">
         <v>117</v>
       </c>
       <c r="G68" s="25">
         <f>_xlfn.STDEV.S(D2:D68)*SQRT(252)</f>
-        <v>0.18834088862804979</v>
+        <v>0.18836225122995642</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="G69" s="25" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D68)-1</f>
-        <v>0.23766006635743686</v>
+        <v>0.23676039705392182</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G70" s="25" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D68)^(252/COUNT(D2:D68))-1</f>
-        <v>1.2299326780676472</v>
+        <v>1.223842035187003</v>
       </c>
     </row>
   </sheetData>
@@ -9883,7 +9883,7 @@
         <v>46276</v>
       </c>
       <c r="B75" s="7">
-        <v>412705</v>
+        <v>412405</v>
       </c>
       <c r="C75" s="15">
         <f>64754+151830</f>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="D75" s="9">
         <f>B75-C75-I75</f>
-        <v>170090</v>
+        <v>169790</v>
       </c>
       <c r="E75" s="9">
         <v>0</v>
@@ -9916,15 +9916,15 @@
       </c>
       <c r="L75" s="10">
         <f t="shared" si="0"/>
-        <v>412705</v>
+        <v>412405</v>
       </c>
       <c r="M75" s="11">
         <f t="shared" si="1"/>
-        <v>0.52479131583092042</v>
+        <v>0.52517307016161296</v>
       </c>
       <c r="N75" s="11">
         <f t="shared" si="2"/>
-        <v>0.41213457554427496</v>
+        <v>0.41170693856767016</v>
       </c>
       <c r="O75" s="12">
         <v>0</v>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="S75" s="12">
         <f>I75/L75</f>
-        <v>6.3074108624804642E-2</v>
+        <v>6.3119991270716894E-2</v>
       </c>
       <c r="T75" s="12">
         <f>K75/L75</f>
